--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -203,7 +203,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
@@ -228,7 +228,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
@@ -253,7 +253,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="762000"/>
@@ -278,7 +278,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>13</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
@@ -328,8 +328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -353,8 +353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -378,8 +378,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -403,8 +403,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -428,8 +428,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -453,8 +453,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>2171700</rowOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -478,8 +478,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>13</row>
-      <rowOff>2171700</rowOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="952500" cy="1047750"/>
     <pic>
@@ -503,8 +503,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>13</row>
-      <rowOff>2171700</rowOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -528,8 +528,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>13</row>
-      <rowOff>2171700</rowOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -553,8 +553,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>13</row>
-      <rowOff>2171700</rowOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -578,8 +578,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>3257550</rowOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -603,8 +603,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>13</row>
-      <rowOff>3257550</rowOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
     <pic>
@@ -628,8 +628,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>13</row>
-      <rowOff>3257550</rowOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="571500"/>
     <pic>
@@ -653,7 +653,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -678,7 +678,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>25</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="876300"/>
@@ -703,7 +703,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>25</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
@@ -728,7 +728,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>25</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
@@ -753,7 +753,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>25</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
@@ -778,8 +778,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -803,8 +803,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>25</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -828,8 +828,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>25</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -853,8 +853,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>25</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -878,8 +878,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>25</row>
-      <rowOff>1085850</rowOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -903,8 +903,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>2171700</rowOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -928,8 +928,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>25</row>
-      <rowOff>2171700</rowOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -953,8 +953,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>25</row>
-      <rowOff>2171700</rowOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -978,8 +978,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>25</row>
-      <rowOff>2171700</rowOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1003,8 +1003,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>25</row>
-      <rowOff>2171700</rowOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1028,8 +1028,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>3257550</rowOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1053,8 +1053,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>25</row>
-      <rowOff>3257550</rowOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1000125" cy="1047750"/>
     <pic>
@@ -1078,7 +1078,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1103,7 +1103,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>42</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1128,7 +1128,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>42</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1153,7 +1153,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>42</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1178,7 +1178,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>42</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1203,8 +1203,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>1085850</rowOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1228,8 +1228,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>42</row>
-      <rowOff>1085850</rowOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1253,8 +1253,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>42</row>
-      <rowOff>1085850</rowOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1278,8 +1278,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>42</row>
-      <rowOff>1085850</rowOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1303,8 +1303,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>42</row>
-      <rowOff>1085850</rowOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1328,8 +1328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>42</row>
-      <rowOff>2171700</rowOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1353,8 +1353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>42</row>
-      <rowOff>2171700</rowOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1378,8 +1378,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>42</row>
-      <rowOff>2171700</rowOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1403,8 +1403,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>42</row>
-      <rowOff>2171700</rowOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1428,7 +1428,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1453,7 +1453,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>52</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="923925" cy="1047750"/>
@@ -1478,7 +1478,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>52</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1503,7 +1503,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>52</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1528,7 +1528,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>52</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1553,7 +1553,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1578,7 +1578,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>66</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1603,7 +1603,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>66</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1628,7 +1628,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>66</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1653,7 +1653,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>66</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1664,131 +1664,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>66</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>66</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>66</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>66</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1806,14 +1681,14 @@
       <row>76</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1831,14 +1706,14 @@
       <row>76</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="923925" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1859,11 +1734,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1884,11 +1759,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1909,6 +1784,131 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="923925" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>87</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="69" name="Image 69" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1928,7 +1928,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="695325"/>
@@ -1953,7 +1953,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>89</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1978,7 +1978,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>89</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2003,7 +2003,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>89</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2028,7 +2028,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>89</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2053,8 +2053,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2078,8 +2078,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>89</row>
-      <rowOff>1085850</rowOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2089,256 +2089,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="876300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>102</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>102</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="923925"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>102</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>102</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="952500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2356,14 +2106,14 @@
       <row>114</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
+    <ext cx="1047750" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2381,14 +2131,14 @@
       <row>114</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2406,14 +2156,14 @@
       <row>114</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2431,264 +2181,264 @@
       <row>114</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="923925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="90" name="Image 90" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>129</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>129</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>129</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>129</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>129</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>129</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2706,14 +2456,14 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2731,14 +2481,14 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="885825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2756,14 +2506,14 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="333375"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2781,14 +2531,14 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2806,9 +2556,259 @@
       <row>143</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="885825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="333375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="105" name="Image 105" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -2828,8 +2828,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>143</row>
-      <rowOff>1085850</rowOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2853,8 +2853,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>143</row>
-      <rowOff>1085850</rowOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2878,8 +2878,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>143</row>
-      <rowOff>1085850</rowOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2903,8 +2903,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>143</row>
-      <rowOff>1085850</rowOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2928,8 +2928,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>143</row>
-      <rowOff>1085850</rowOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2953,8 +2953,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>143</row>
-      <rowOff>2171700</rowOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2978,8 +2978,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>143</row>
-      <rowOff>2171700</rowOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3003,7 +3003,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>154</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3028,7 +3028,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>154</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="885825"/>
@@ -3053,7 +3053,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>154</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="895350"/>
@@ -3078,7 +3078,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>154</row>
+      <row>172</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="333375"/>
@@ -3103,7 +3103,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>165</row>
+      <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -3128,7 +3128,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>176</row>
+      <row>194</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -3153,7 +3153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>189</row>
+      <row>207</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="714375" cy="1047750"/>
@@ -3178,7 +3178,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>201</row>
+      <row>219</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -3203,7 +3203,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>213</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3228,7 +3228,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>213</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3253,7 +3253,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>213</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3278,7 +3278,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>213</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3303,7 +3303,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>213</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3328,8 +3328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>1085850</rowOff>
+      <row>233</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3353,8 +3353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>213</row>
-      <rowOff>1085850</rowOff>
+      <row>233</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3666,7 +3666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D214"/>
+  <dimension ref="A1:D234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3707,7 +3707,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="45" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>베이킹소다</t>
@@ -3725,7 +3725,7 @@
       </c>
       <c r="D3" s="4" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>구연산</t>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="80" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>옥수수전분</t>
@@ -3769,7 +3769,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>카카오분말</t>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>초코향</t>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>애플계면활성제</t>
@@ -3845,7 +3845,7 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
     </row>
-    <row r="10" ht="75" customHeight="1">
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>초콜렛음료 속에 잠기는 기분~음?! 재미있겠죠.
@@ -3866,7 +3866,7 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
     </row>
-    <row r="12" ht="420" customHeight="1">
+    <row r="12" ht="384" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 먼저 계량한다. 덩어리지는 경우가 많아 특별히 베이킹소다만 체에 친다. 덩어리는 문질러주세요.
@@ -3880,174 +3880,183 @@
 [쿠키 톡톡] 연인에게 초콜릿을 선물하며 서로의 마음을 확인하는 밸런타인데이. 이때가 되면 모든 상점은 초콜릿과 관련된 상품을 기획, 판매하는데 공을 들인다.
 일본에서 밸런타인데이를 맞아 목욕물안에 진짜 초콜릿이 들어간 ‘초콜릿탕’이 이달 말까지 개장해 화제를 모으고 있다고 일본 문화생활정보지 도쿄 워커가 2일 보도했다.
 유명 관광지인 가나가와현 하코네에 위치한 온천 테마파크에 최근 선보인 초콜릿 목욕탕은 다갈색의 끈적이는 초콜릿 원액을 부어 만들었다. 카카오 향기가 감돌아 마치 따뜻한 초콜릿 음료 속에 잠기는 기분을 만끽할 수 있다고 도쿄 워커는 설명했다.
-이 업체는 하루 세 번 이용객들 앞에서 부드럽게 녹은 초콜릿을 탕 안에 붓는 이벤트도 실시하고 있다. 향과 색을 흉내 낸 가짜 초콜릿 탕과 차별을 주기 위해서다.
-도쿄워커는 “진짜 초콜릿이 들어간 목욕탕”이라며 “초콜릿 속에 있는 폴리페놀은 혈액 촉진과 노폐물 배출 효과가 있고 또 셀룰라이트(울퉁붕툴해 보이는 피하 지방) 분해 효과도 기대할 수 있다”고 설명했다.
+이 업체는 하루 세 번 이용객들 앞에서 부드럽게 녹은 초콜릿을 탕 안에 붓는 이벤트도 실시하고 있다. 향과 색을 흉내 낸 가짜 초콜릿 탕과 차별을 주기 위해서다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>도쿄워커는 “진짜 초콜릿이 들어간 목욕탕”이라며 “초콜릿 속에 있는 폴리페놀은 혈액 촉진과 노폐물 배출 효과가 있고 또 셀룰라이트(울퉁붕툴해 보이는 피하 지방) 분해 효과도 기대할 수 있다”고 설명했다.
 [국민일보 쿠키뉴스 신은정 기자]</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="342" customHeight="1"/>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="85.5" customHeight="1"/>
+    <row r="16" ht="85.5" customHeight="1"/>
+    <row r="17" ht="85.5" customHeight="1"/>
+    <row r="18" ht="85.5" customHeight="1"/>
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="45" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="D22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="24" ht="80" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="270" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28" ht="288" customHeight="1">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -4066,235 +4075,253 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="342" customHeight="1">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="6" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="85.5" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="85.5" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+    </row>
+    <row r="32" ht="85.5" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="85.5" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>코치닐+물</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>1g+3g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>반드시 양조절해서 / 색내기에 사용하세요.</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>원하는 색</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="D38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>주석산</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="D39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>코코넛유래, / 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="D41" s="4" t="n"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>애플 / 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="43" ht="80" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-    </row>
-    <row r="39" ht="90" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -4305,18 +4332,18 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-    </row>
-    <row r="41" ht="180" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+    </row>
+    <row r="48" ht="192" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -4333,80 +4360,82 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-    </row>
-    <row r="43" ht="256.5" customHeight="1"/>
-    <row r="44" ht="6" customHeight="1"/>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="85.5" customHeight="1"/>
+    <row r="51" ht="85.5" customHeight="1"/>
+    <row r="52" ht="85.5" customHeight="1"/>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B45" s="2" t="n"/>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="B54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>풍부한 미네랄, / 노폐물제거</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="D56" s="8" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-    </row>
-    <row r="49" ht="165" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="176" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -4421,22 +4450,22 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+    </row>
+    <row r="60" ht="64" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -4444,173 +4473,173 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="14" customHeight="1">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-    </row>
-    <row r="53" ht="85.5" customHeight="1">
-      <c r="A53" s="10" t="n"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n"/>
+      <c r="D61" s="6" t="n"/>
+    </row>
+    <row r="62" ht="85.5" customHeight="1">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+    </row>
+    <row r="63" ht="6" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>탄산수소나트륨 / , 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="D57" s="4" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="D66" s="4" t="n"/>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="68" ht="80" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="69" ht="32" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴, / 철함유로 자체 / 핑크색, / 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="D61" s="4" t="n"/>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="D70" s="4" t="n"/>
+    </row>
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-    </row>
-    <row r="63" ht="225" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="240" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -4630,18 +4659,18 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-    </row>
-    <row r="65" ht="195" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="208" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -4656,80 +4685,81 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="5" t="inlineStr">
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-    </row>
-    <row r="67" ht="171" customHeight="1"/>
-    <row r="68" ht="6" customHeight="1"/>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="1" t="inlineStr">
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="85.5" customHeight="1"/>
+    <row r="77" ht="85.5" customHeight="1"/>
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B71" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="D71" s="8" t="n"/>
-    </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="D81" s="8" t="n"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-    </row>
-    <row r="73" ht="390" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n"/>
+    </row>
+    <row r="83" ht="384" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -4754,27 +4784,36 @@
 핑크 소금에 들어있는 것으로 알려져있어요.
 붉은빛을 띠는 이유는
 소량의 산화철이 녹아있기 때문입니다.
-다양한
-아로마오일을 히말라야 핑크소금에 배합해
+다양한</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="10" t="n"/>
+      <c r="D83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>아로마오일을 히말라야 핑크소금에 배합해
 아로마테리피 효과도 함께 누리세요.</t>
         </is>
       </c>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="10" t="n"/>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="10" t="n"/>
+      <c r="D84" s="10" t="n"/>
+    </row>
+    <row r="85" ht="14" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-    </row>
-    <row r="75" ht="75" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+    </row>
+    <row r="86" ht="80" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -4783,151 +4822,151 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="10" t="n"/>
+      <c r="D86" s="10" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="85.5" customHeight="1">
-      <c r="A77" s="10" t="n"/>
-      <c r="B77" s="10" t="n"/>
-      <c r="C77" s="10" t="n"/>
-      <c r="D77" s="10" t="n"/>
-    </row>
-    <row r="78" ht="6" customHeight="1"/>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="1" t="inlineStr">
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="6" t="n"/>
+      <c r="D87" s="6" t="n"/>
+    </row>
+    <row r="88" ht="85.5" customHeight="1">
+      <c r="A88" s="10" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="10" t="n"/>
+      <c r="D88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="6" customHeight="1"/>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B79" s="2" t="n"/>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="B90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="45" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="92" ht="64" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨, / 산소금=암염, 수분함량 적고 / 미네럴 풍부, / 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="D81" s="4" t="n"/>
-    </row>
-    <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="D92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C82" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B83" s="4" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C83" s="4" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>입,족욕용 또는 / 바디 마사지/ 스크럽 겸용</t>
         </is>
       </c>
-      <c r="D83" s="4" t="n"/>
-    </row>
-    <row r="84" ht="45" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="D94" s="4" t="n"/>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B84" s="4" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C84" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-    </row>
-    <row r="86" ht="240" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="B96" s="6" t="n"/>
+      <c r="C96" s="6" t="n"/>
+      <c r="D96" s="6" t="n"/>
+    </row>
+    <row r="97" ht="256" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4948,18 +4987,18 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="105" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="B98" s="6" t="n"/>
+      <c r="C98" s="6" t="n"/>
+      <c r="D98" s="6" t="n"/>
+    </row>
+    <row r="99" ht="112" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -4971,146 +5010,147 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="171" customHeight="1"/>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="B100" s="6" t="n"/>
+      <c r="C100" s="6" t="n"/>
+      <c r="D100" s="6" t="n"/>
+    </row>
+    <row r="101" ht="85.5" customHeight="1"/>
+    <row r="102" ht="85.5" customHeight="1"/>
+    <row r="103" ht="6" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="45" customHeight="1">
-      <c r="A94" s="8" t="inlineStr">
+    <row r="106" ht="48" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B94" s="8" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="D94" s="8" t="n"/>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="8" t="inlineStr">
+      <c r="D106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B95" s="8" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr">
+      <c r="C107" s="8" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D107" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="75" customHeight="1">
-      <c r="A96" s="8" t="inlineStr">
+    <row r="108" ht="96" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B96" s="8" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr">
+      <c r="C108" s="8" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D108" s="8" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" s="8" t="inlineStr">
+    <row r="109" ht="64" customHeight="1">
+      <c r="A109" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B97" s="8" t="inlineStr">
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr">
+      <c r="C109" s="8" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D97" s="8" t="inlineStr">
+      <c r="D109" s="8" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-    </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="9" t="inlineStr">
+      <c r="B110" s="6" t="n"/>
+      <c r="C110" s="6" t="n"/>
+      <c r="D110" s="6" t="n"/>
+    </row>
+    <row r="111" ht="64" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -5118,22 +5158,22 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="10" t="n"/>
-      <c r="D99" s="10" t="n"/>
-    </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="10" t="n"/>
+      <c r="D111" s="10" t="n"/>
+    </row>
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-    </row>
-    <row r="101" ht="180" customHeight="1">
-      <c r="A101" s="9" t="inlineStr">
+      <c r="B112" s="6" t="n"/>
+      <c r="C112" s="6" t="n"/>
+      <c r="D112" s="6" t="n"/>
+    </row>
+    <row r="113" ht="192" customHeight="1">
+      <c r="A113" s="9" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -5148,129 +5188,135 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B101" s="10" t="n"/>
-      <c r="C101" s="10" t="n"/>
-      <c r="D101" s="10" t="n"/>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="10" t="n"/>
+      <c r="D113" s="10" t="n"/>
+    </row>
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-    </row>
-    <row r="103" ht="171" customHeight="1">
-      <c r="A103" s="10" t="n"/>
-      <c r="B103" s="10" t="n"/>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="10" t="n"/>
-    </row>
-    <row r="104" ht="6" customHeight="1"/>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="1" t="inlineStr">
+      <c r="B114" s="6" t="n"/>
+      <c r="C114" s="6" t="n"/>
+      <c r="D114" s="6" t="n"/>
+    </row>
+    <row r="115" ht="85.5" customHeight="1">
+      <c r="A115" s="10" t="n"/>
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="10" t="n"/>
+      <c r="D115" s="10" t="n"/>
+    </row>
+    <row r="116" ht="85.5" customHeight="1">
+      <c r="A116" s="10" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="10" t="n"/>
+      <c r="D116" s="10" t="n"/>
+    </row>
+    <row r="117" ht="6" customHeight="1"/>
+    <row r="118" ht="22" customHeight="1">
+      <c r="A118" s="1" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B105" s="2" t="n"/>
-      <c r="C105" s="2" t="n"/>
-      <c r="D105" s="2" t="n"/>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="B118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="4" t="inlineStr">
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C107" s="4" t="inlineStr">
+      <c r="C120" s="4" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="D107" s="4" t="n"/>
-    </row>
-    <row r="108" ht="45" customHeight="1">
-      <c r="A108" s="4" t="inlineStr">
+      <c r="D120" s="4" t="n"/>
+    </row>
+    <row r="121" ht="48" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B121" s="4" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C108" s="4" t="inlineStr">
+      <c r="C121" s="4" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 / 시어버터, 아보카도, 꿀추출물 등 / 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="D108" s="4" t="n"/>
-    </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="4" t="inlineStr">
+      <c r="D121" s="4" t="n"/>
+    </row>
+    <row r="122" ht="64" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B122" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C109" s="4" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>아로마테라피 / 여드름-티트리, / 바디 용도별 추천오일 / -쿨링 :페파민트, / -다이어트 : 레몬+자몽오일 / -이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="D109" s="4" t="inlineStr">
+      <c r="D122" s="4" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-    </row>
-    <row r="111" ht="480" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+    </row>
+    <row r="124" ht="384" customHeight="1">
+      <c r="A124" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5294,8 +5340,14 @@
 (확실히 사해소금에 비해 수분함량은 낮아요)
 최근 소금에 미세플라스틱이 많다는
 이야기가 있습니다. ㅜㅜ
-히말라야 핑크소금은
-미세플라스틱이 없다, 있을 수 없다고
+히말라야 핑크소금은</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="128" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>미세플라스틱이 없다, 있을 수 없다고
 알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
 잠겨있을 시기에 생성된 소금이고
@@ -5306,18 +5358,18 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-    </row>
-    <row r="113" ht="75" customHeight="1">
-      <c r="A113" s="7" t="inlineStr">
+      <c r="B126" s="6" t="n"/>
+      <c r="C126" s="6" t="n"/>
+      <c r="D126" s="6" t="n"/>
+    </row>
+    <row r="127" ht="80" customHeight="1">
+      <c r="A127" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -5327,186 +5379,186 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-    </row>
-    <row r="115" ht="85.5" customHeight="1"/>
-    <row r="116" ht="6" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="B128" s="6" t="n"/>
+      <c r="C128" s="6" t="n"/>
+      <c r="D128" s="6" t="n"/>
+    </row>
+    <row r="129" ht="85.5" customHeight="1"/>
+    <row r="130" ht="6" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="1" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="B131" s="2" t="n"/>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="8" t="inlineStr">
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B119" s="8" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr">
+      <c r="C133" s="8" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="D119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="8" t="inlineStr">
+      <c r="D133" s="8" t="n"/>
+    </row>
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B120" s="8" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr">
+      <c r="C134" s="8" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="D120" s="8" t="inlineStr">
+      <c r="D134" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="8" t="inlineStr">
+    <row r="135" ht="80" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B121" s="8" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C121" s="8" t="inlineStr">
+      <c r="C135" s="8" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D135" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="8" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B122" s="8" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr">
+      <c r="C136" s="8" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="D122" s="8" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="8" t="inlineStr">
+      <c r="D136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B123" s="8" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C123" s="8" t="inlineStr">
+      <c r="C137" s="8" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D137" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="45" customHeight="1">
-      <c r="A124" s="8" t="inlineStr">
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B124" s="8" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr">
+      <c r="C138" s="8" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D138" s="8" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-    </row>
-    <row r="126" ht="210" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+    </row>
+    <row r="140" ht="224" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -5524,22 +5576,22 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B126" s="10" t="n"/>
-      <c r="C126" s="10" t="n"/>
-      <c r="D126" s="10" t="n"/>
-    </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="10" t="n"/>
+      <c r="D140" s="10" t="n"/>
+    </row>
+    <row r="141" ht="14" customHeight="1">
+      <c r="A141" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B127" s="6" t="n"/>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6" t="n"/>
-    </row>
-    <row r="128" ht="150" customHeight="1">
-      <c r="A128" s="9" t="inlineStr">
+      <c r="B141" s="6" t="n"/>
+      <c r="C141" s="6" t="n"/>
+      <c r="D141" s="6" t="n"/>
+    </row>
+    <row r="142" ht="160" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -5553,217 +5605,223 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B128" s="10" t="n"/>
-      <c r="C128" s="10" t="n"/>
-      <c r="D128" s="10" t="n"/>
-    </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="10" t="n"/>
+      <c r="D142" s="10" t="n"/>
+    </row>
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="171" customHeight="1">
-      <c r="A130" s="10" t="n"/>
-      <c r="B130" s="10" t="n"/>
-      <c r="C130" s="10" t="n"/>
-      <c r="D130" s="10" t="n"/>
-    </row>
-    <row r="131" ht="6" customHeight="1"/>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="1" t="inlineStr">
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+    </row>
+    <row r="144" ht="85.5" customHeight="1">
+      <c r="A144" s="10" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="10" t="n"/>
+      <c r="D144" s="10" t="n"/>
+    </row>
+    <row r="145" ht="85.5" customHeight="1">
+      <c r="A145" s="10" t="n"/>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="10" t="n"/>
+      <c r="D145" s="10" t="n"/>
+    </row>
+    <row r="146" ht="6" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="1" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B132" s="2" t="n"/>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n"/>
-    </row>
-    <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="B147" s="2" t="n"/>
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+    </row>
+    <row r="148" ht="15" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B148" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C148" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
+      <c r="D148" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="4" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C134" s="4" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="D134" s="4" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="4" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B150" s="4" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C135" s="4" t="inlineStr">
+      <c r="C150" s="4" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="D135" s="4" t="inlineStr">
+      <c r="D150" s="4" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="45" customHeight="1">
-      <c r="A136" s="4" t="inlineStr">
+    <row r="151" ht="48" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B151" s="4" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C136" s="4" t="inlineStr">
+      <c r="C151" s="4" t="inlineStr">
         <is>
           <t>에코인증, 물과 오일의 분리를 저지</t>
         </is>
       </c>
-      <c r="D136" s="4" t="inlineStr">
+      <c r="D151" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="45" customHeight="1">
-      <c r="A137" s="4" t="inlineStr">
+    <row r="152" ht="48" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>순한 (샴푸) / 베이스</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
         <is>
           <t>38g</t>
         </is>
       </c>
-      <c r="C137" s="4" t="inlineStr">
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="D137" s="4" t="n"/>
-    </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="4" t="inlineStr">
+      <c r="D152" s="4" t="n"/>
+    </row>
+    <row r="153" ht="16" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
         <is>
           <t>13g</t>
         </is>
       </c>
-      <c r="C138" s="4" t="inlineStr">
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="D138" s="4" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>꿀 등</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="30" customHeight="1">
-      <c r="A139" s="4" t="inlineStr">
+    <row r="154" ht="32" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C139" s="4" t="inlineStr">
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>각질제거, 보습. / 필요에 따라 양을 더 넣어서 / 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="D139" s="4" t="n"/>
-    </row>
-    <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+      <c r="D154" s="4" t="n"/>
+    </row>
+    <row r="155" ht="32" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B155" s="4" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C155" s="4" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D155" s="4" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="14" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B141" s="6" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-    </row>
-    <row r="142" ht="315" customHeight="1">
-      <c r="A142" s="7" t="inlineStr">
+      <c r="B156" s="6" t="n"/>
+      <c r="C156" s="6" t="n"/>
+      <c r="D156" s="6" t="n"/>
+    </row>
+    <row r="157" ht="336" customHeight="1">
+      <c r="A157" s="7" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -5789,106 +5847,108 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="158" ht="14" customHeight="1">
+      <c r="A158" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6" t="n"/>
-    </row>
-    <row r="144" ht="256.5" customHeight="1"/>
-    <row r="145" ht="6" customHeight="1"/>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="1" t="inlineStr">
+      <c r="B158" s="6" t="n"/>
+      <c r="C158" s="6" t="n"/>
+      <c r="D158" s="6" t="n"/>
+    </row>
+    <row r="159" ht="85.5" customHeight="1"/>
+    <row r="160" ht="85.5" customHeight="1"/>
+    <row r="161" ht="85.5" customHeight="1"/>
+    <row r="162" ht="6" customHeight="1"/>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="1" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B146" s="2" t="n"/>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="B163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+    </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B147" s="3" t="inlineStr">
+      <c r="B164" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C147" s="3" t="inlineStr">
+      <c r="C164" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D147" s="3" t="inlineStr">
+      <c r="D164" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="60" customHeight="1">
-      <c r="A148" s="8" t="inlineStr">
+    <row r="165" ht="64" customHeight="1">
+      <c r="A165" s="8" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B148" s="8" t="inlineStr">
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr">
+      <c r="C165" s="8" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
         </is>
       </c>
-      <c r="D148" s="8" t="inlineStr">
+      <c r="D165" s="8" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="8" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B166" s="8" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C166" s="8" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 / 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="D149" s="8" t="inlineStr">
+      <c r="D166" s="8" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="5" t="inlineStr">
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-    </row>
-    <row r="151" ht="405" customHeight="1">
-      <c r="A151" s="9" t="inlineStr">
+      <c r="B167" s="6" t="n"/>
+      <c r="C167" s="6" t="n"/>
+      <c r="D167" s="6" t="n"/>
+    </row>
+    <row r="168" ht="384" customHeight="1">
+      <c r="A168" s="9" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -5913,28 +5973,37 @@
 넣고 섞기만 하면 됩니다.
 유기농 설탕과 카카오분말로 구성된
 카카오스크럽파우더를 스크럽베이스에 섞어주세요.
-항산화작용이 우수한 폴리페놀 함량이 높은 카카오와
-각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
+항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
+        </is>
+      </c>
+      <c r="B168" s="10" t="n"/>
+      <c r="C168" s="10" t="n"/>
+      <c r="D168" s="10" t="n"/>
+    </row>
+    <row r="169" ht="48" customHeight="1">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B151" s="10" t="n"/>
-      <c r="C151" s="10" t="n"/>
-      <c r="D151" s="10" t="n"/>
-    </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="5" t="inlineStr">
+      <c r="B169" s="10" t="n"/>
+      <c r="C169" s="10" t="n"/>
+      <c r="D169" s="10" t="n"/>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="n"/>
-    </row>
-    <row r="153" ht="300" customHeight="1">
-      <c r="A153" s="9" t="inlineStr">
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+    </row>
+    <row r="171" ht="320" customHeight="1">
+      <c r="A171" s="9" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -5958,151 +6027,151 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B153" s="10" t="n"/>
-      <c r="C153" s="10" t="n"/>
-      <c r="D153" s="10" t="n"/>
-    </row>
-    <row r="154" ht="14" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
+      <c r="B171" s="10" t="n"/>
+      <c r="C171" s="10" t="n"/>
+      <c r="D171" s="10" t="n"/>
+    </row>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-    </row>
-    <row r="155" ht="85.5" customHeight="1">
-      <c r="A155" s="10" t="n"/>
-      <c r="B155" s="10" t="n"/>
-      <c r="C155" s="10" t="n"/>
-      <c r="D155" s="10" t="n"/>
-    </row>
-    <row r="156" ht="6" customHeight="1"/>
-    <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="1" t="inlineStr">
+      <c r="B172" s="6" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+    </row>
+    <row r="173" ht="85.5" customHeight="1">
+      <c r="A173" s="10" t="n"/>
+      <c r="B173" s="10" t="n"/>
+      <c r="C173" s="10" t="n"/>
+      <c r="D173" s="10" t="n"/>
+    </row>
+    <row r="174" ht="6" customHeight="1"/>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="1" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B157" s="2" t="n"/>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n"/>
-    </row>
-    <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="3" t="inlineStr">
+      <c r="B175" s="2" t="n"/>
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+    </row>
+    <row r="176" ht="15" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr">
+      <c r="B176" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="C176" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D158" s="3" t="inlineStr">
+      <c r="D176" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="45" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
+    <row r="177" ht="64" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D159" s="4" t="n"/>
-    </row>
-    <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+      <c r="D177" s="4" t="n"/>
+    </row>
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C178" s="4" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="D178" s="4" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B179" s="4" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C179" s="4" t="inlineStr">
         <is>
           <t>스크럽, 노폐물, / 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="D161" s="4" t="n"/>
-    </row>
-    <row r="162" ht="75" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
+      <c r="D179" s="4" t="n"/>
+    </row>
+    <row r="180" ht="96" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B163" s="6" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-    </row>
-    <row r="164" ht="165" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
+      <c r="B181" s="6" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+    </row>
+    <row r="182" ht="176" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -6116,106 +6185,106 @@
         </is>
       </c>
     </row>
-    <row r="165" ht="14" customHeight="1">
-      <c r="A165" s="5" t="inlineStr">
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B165" s="6" t="n"/>
-      <c r="C165" s="6" t="n"/>
-      <c r="D165" s="6" t="n"/>
-    </row>
-    <row r="166" ht="85.5" customHeight="1"/>
-    <row r="167" ht="6" customHeight="1"/>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="1" t="inlineStr">
+      <c r="B183" s="6" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+    </row>
+    <row r="184" ht="85.5" customHeight="1"/>
+    <row r="185" ht="6" customHeight="1"/>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="1" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B168" s="2" t="n"/>
-      <c r="C168" s="2" t="n"/>
-      <c r="D168" s="2" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+      <c r="B186" s="2" t="n"/>
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+    </row>
+    <row r="187" ht="15" customHeight="1">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B169" s="3" t="inlineStr">
+      <c r="B187" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C169" s="3" t="inlineStr">
+      <c r="C187" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D169" s="3" t="inlineStr">
+      <c r="D187" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="8" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B188" s="8" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C170" s="8" t="inlineStr">
+      <c r="C188" s="8" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="D170" s="8" t="inlineStr">
+      <c r="D188" s="8" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="45" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="189" ht="48" customHeight="1">
+      <c r="A189" s="8" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="C189" s="8" t="inlineStr">
         <is>
           <t>감초의 수/지용성성분추출물.</t>
         </is>
       </c>
-      <c r="D171" s="8" t="inlineStr">
+      <c r="D189" s="8" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="5" t="inlineStr">
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="105" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
+      <c r="B190" s="6" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+    </row>
+    <row r="191" ht="112" customHeight="1">
+      <c r="A191" s="9" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -6223,22 +6292,22 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="10" t="n"/>
-      <c r="D173" s="10" t="n"/>
-    </row>
-    <row r="174" ht="14" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
+      <c r="B191" s="10" t="n"/>
+      <c r="C191" s="10" t="n"/>
+      <c r="D191" s="10" t="n"/>
+    </row>
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-    </row>
-    <row r="175" ht="105" customHeight="1">
-      <c r="A175" s="9" t="inlineStr">
+      <c r="B192" s="6" t="n"/>
+      <c r="C192" s="6" t="n"/>
+      <c r="D192" s="6" t="n"/>
+    </row>
+    <row r="193" ht="112" customHeight="1">
+      <c r="A193" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -6248,199 +6317,199 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B175" s="10" t="n"/>
-      <c r="C175" s="10" t="n"/>
-      <c r="D175" s="10" t="n"/>
-    </row>
-    <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="5" t="inlineStr">
+      <c r="B193" s="10" t="n"/>
+      <c r="C193" s="10" t="n"/>
+      <c r="D193" s="10" t="n"/>
+    </row>
+    <row r="194" ht="14" customHeight="1">
+      <c r="A194" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B176" s="6" t="n"/>
-      <c r="C176" s="6" t="n"/>
-      <c r="D176" s="6" t="n"/>
-    </row>
-    <row r="177" ht="85.5" customHeight="1">
-      <c r="A177" s="10" t="n"/>
-      <c r="B177" s="10" t="n"/>
-      <c r="C177" s="10" t="n"/>
-      <c r="D177" s="10" t="n"/>
-    </row>
-    <row r="178" ht="6" customHeight="1"/>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="1" t="inlineStr">
+      <c r="B194" s="6" t="n"/>
+      <c r="C194" s="6" t="n"/>
+      <c r="D194" s="6" t="n"/>
+    </row>
+    <row r="195" ht="85.5" customHeight="1">
+      <c r="A195" s="10" t="n"/>
+      <c r="B195" s="10" t="n"/>
+      <c r="C195" s="10" t="n"/>
+      <c r="D195" s="10" t="n"/>
+    </row>
+    <row r="196" ht="6" customHeight="1"/>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="1" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B179" s="2" t="n"/>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n"/>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="B197" s="2" t="n"/>
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+    </row>
+    <row r="198" ht="15" customHeight="1">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C198" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D180" s="3" t="inlineStr">
+      <c r="D198" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="45" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="199" ht="64" customHeight="1">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D181" s="4" t="n"/>
-    </row>
-    <row r="182" ht="30" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+      <c r="D199" s="4" t="n"/>
+    </row>
+    <row r="200" ht="32" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B200" s="4" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D200" s="4" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="75" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
+    <row r="201" ht="96" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B183" s="4" t="inlineStr">
+      <c r="B201" s="4" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C183" s="4" t="inlineStr">
+      <c r="C201" s="4" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D183" s="4" t="inlineStr">
+      <c r="D201" s="4" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="45" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
+    <row r="202" ht="48" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B202" s="4" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C184" s="4" t="inlineStr">
+      <c r="C202" s="4" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="D184" s="4" t="inlineStr">
+      <c r="D202" s="4" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="60" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
+    <row r="203" ht="64" customHeight="1">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B185" s="4" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C185" s="4" t="inlineStr">
+      <c r="C203" s="4" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D185" s="4" t="inlineStr">
+      <c r="D203" s="4" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="30" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
+    <row r="204" ht="32" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C186" s="4" t="inlineStr">
+      <c r="C204" s="4" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="D186" s="4" t="inlineStr">
+      <c r="D204" s="4" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6" t="n"/>
-    </row>
-    <row r="188" ht="105" customHeight="1">
-      <c r="A188" s="7" t="inlineStr">
+      <c r="B205" s="6" t="n"/>
+      <c r="C205" s="6" t="n"/>
+      <c r="D205" s="6" t="n"/>
+    </row>
+    <row r="206" ht="112" customHeight="1">
+      <c r="A206" s="7" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -6450,145 +6519,145 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="5" t="inlineStr">
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="85.5" customHeight="1"/>
-    <row r="191" ht="6" customHeight="1"/>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="B207" s="6" t="n"/>
+      <c r="C207" s="6" t="n"/>
+      <c r="D207" s="6" t="n"/>
+    </row>
+    <row r="208" ht="85.5" customHeight="1"/>
+    <row r="209" ht="6" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="1" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B192" s="2" t="n"/>
-      <c r="C192" s="2" t="n"/>
-      <c r="D192" s="2" t="n"/>
-    </row>
-    <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="3" t="inlineStr">
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="2" t="n"/>
+      <c r="D210" s="2" t="n"/>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B193" s="3" t="inlineStr">
+      <c r="B211" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D193" s="3" t="inlineStr">
+      <c r="D211" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="8" t="inlineStr">
+    <row r="212" ht="32" customHeight="1">
+      <c r="A212" s="8" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C212" s="8" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="D194" s="8" t="n"/>
-    </row>
-    <row r="195" ht="75" customHeight="1">
-      <c r="A195" s="8" t="inlineStr">
+      <c r="D212" s="8" t="n"/>
+    </row>
+    <row r="213" ht="80" customHeight="1">
+      <c r="A213" s="8" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
+      <c r="C213" s="8" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D213" s="8" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="8" t="inlineStr">
+    <row r="214" ht="32" customHeight="1">
+      <c r="A214" s="8" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B214" s="8" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C196" s="8" t="inlineStr">
+      <c r="C214" s="8" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="D196" s="8" t="inlineStr">
+      <c r="D214" s="8" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="197" ht="14" customHeight="1">
-      <c r="A197" s="5" t="inlineStr">
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B197" s="6" t="n"/>
-      <c r="C197" s="6" t="n"/>
-      <c r="D197" s="6" t="n"/>
-    </row>
-    <row r="198" ht="75" customHeight="1">
-      <c r="A198" s="9" t="inlineStr">
+      <c r="B215" s="6" t="n"/>
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+    </row>
+    <row r="216" ht="80" customHeight="1">
+      <c r="A216" s="9" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B198" s="10" t="n"/>
-      <c r="C198" s="10" t="n"/>
-      <c r="D198" s="10" t="n"/>
-    </row>
-    <row r="199" ht="14" customHeight="1">
-      <c r="A199" s="5" t="inlineStr">
+      <c r="B216" s="10" t="n"/>
+      <c r="C216" s="10" t="n"/>
+      <c r="D216" s="10" t="n"/>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B199" s="6" t="n"/>
-      <c r="C199" s="6" t="n"/>
-      <c r="D199" s="6" t="n"/>
-    </row>
-    <row r="200" ht="135" customHeight="1">
-      <c r="A200" s="9" t="inlineStr">
+      <c r="B217" s="6" t="n"/>
+      <c r="C217" s="6" t="n"/>
+      <c r="D217" s="6" t="n"/>
+    </row>
+    <row r="218" ht="144" customHeight="1">
+      <c r="A218" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -6599,125 +6668,125 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B200" s="10" t="n"/>
-      <c r="C200" s="10" t="n"/>
-      <c r="D200" s="10" t="n"/>
-    </row>
-    <row r="201" ht="14" customHeight="1">
-      <c r="A201" s="5" t="inlineStr">
+      <c r="B218" s="10" t="n"/>
+      <c r="C218" s="10" t="n"/>
+      <c r="D218" s="10" t="n"/>
+    </row>
+    <row r="219" ht="14" customHeight="1">
+      <c r="A219" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B201" s="6" t="n"/>
-      <c r="C201" s="6" t="n"/>
-      <c r="D201" s="6" t="n"/>
-    </row>
-    <row r="202" ht="85.5" customHeight="1">
-      <c r="A202" s="10" t="n"/>
-      <c r="B202" s="10" t="n"/>
-      <c r="C202" s="10" t="n"/>
-      <c r="D202" s="10" t="n"/>
-    </row>
-    <row r="203" ht="6" customHeight="1"/>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="1" t="inlineStr">
+      <c r="B219" s="6" t="n"/>
+      <c r="C219" s="6" t="n"/>
+      <c r="D219" s="6" t="n"/>
+    </row>
+    <row r="220" ht="85.5" customHeight="1">
+      <c r="A220" s="10" t="n"/>
+      <c r="B220" s="10" t="n"/>
+      <c r="C220" s="10" t="n"/>
+      <c r="D220" s="10" t="n"/>
+    </row>
+    <row r="221" ht="6" customHeight="1"/>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="1" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B204" s="2" t="n"/>
-      <c r="C204" s="2" t="n"/>
-      <c r="D204" s="2" t="n"/>
-    </row>
-    <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="3" t="inlineStr">
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="2" t="n"/>
+      <c r="D222" s="2" t="n"/>
+    </row>
+    <row r="223" ht="15" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B205" s="3" t="inlineStr">
+      <c r="B223" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="C223" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D205" s="3" t="inlineStr">
+      <c r="D223" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="60" customHeight="1">
-      <c r="A206" s="4" t="inlineStr">
+    <row r="224" ht="64" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="D206" s="4" t="n"/>
-    </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
+      <c r="D224" s="4" t="n"/>
+    </row>
+    <row r="225" ht="32" customHeight="1">
+      <c r="A225" s="4" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B225" s="4" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C225" s="4" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 / →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="D207" s="4" t="n"/>
-    </row>
-    <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="4" t="inlineStr">
+      <c r="D225" s="4" t="n"/>
+    </row>
+    <row r="226" ht="16" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B226" s="4" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="C226" s="4" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="D208" s="4" t="n"/>
-    </row>
-    <row r="209" ht="14" customHeight="1">
-      <c r="A209" s="5" t="inlineStr">
+      <c r="D226" s="4" t="n"/>
+    </row>
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B209" s="6" t="n"/>
-      <c r="C209" s="6" t="n"/>
-      <c r="D209" s="6" t="n"/>
-    </row>
-    <row r="210" ht="465" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
+      <c r="B227" s="6" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+    </row>
+    <row r="228" ht="384" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -6742,8 +6811,14 @@
 샤워로 피부를 충분히 적신다.
 커피 스크럽을 적당량 덜어 원을 그리듯 부드럽게 마사지 (5분 내외),
 팩하듯 5분 정도 두었다가 미지근한 물로 깨끗이 헹굼하세요.
-[주의 사항]
-1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
+[주의 사항]</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="112" customHeight="1">
+      <c r="A229" s="7" t="inlineStr">
+        <is>
+          <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
 특히 민감피부, 여드름 피부는 비추천
 2. 과도한 사용 금지
@@ -6753,18 +6828,18 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="14" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
+    <row r="230" ht="14" customHeight="1">
+      <c r="A230" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B211" s="6" t="n"/>
-      <c r="C211" s="6" t="n"/>
-      <c r="D211" s="6" t="n"/>
-    </row>
-    <row r="212" ht="105" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="B230" s="6" t="n"/>
+      <c r="C230" s="6" t="n"/>
+      <c r="D230" s="6" t="n"/>
+    </row>
+    <row r="231" ht="112" customHeight="1">
+      <c r="A231" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -6776,150 +6851,171 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="14" customHeight="1">
-      <c r="A213" s="5" t="inlineStr">
+    <row r="232" ht="14" customHeight="1">
+      <c r="A232" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B213" s="6" t="n"/>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6" t="n"/>
-    </row>
-    <row r="214" ht="171" customHeight="1"/>
-    <row r="215" ht="6" customHeight="1"/>
+      <c r="B232" s="6" t="n"/>
+      <c r="C232" s="6" t="n"/>
+      <c r="D232" s="6" t="n"/>
+    </row>
+    <row r="233" ht="85.5" customHeight="1"/>
+    <row r="234" ht="85.5" customHeight="1"/>
+    <row r="235" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="111">
-    <mergeCell ref="A150:D150"/>
+  <mergeCells count="131">
     <mergeCell ref="A144:D144"/>
+    <mergeCell ref="A159:D159"/>
+    <mergeCell ref="A215:D215"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A72:D72"/>
-    <mergeCell ref="A200:D200"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A161:D161"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A202:D202"/>
-    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A58:D58"/>
     <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A186:D186"/>
     <mergeCell ref="A73:D73"/>
     <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A228:D228"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A172:D172"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A172:D172"/>
-    <mergeCell ref="A212:D212"/>
     <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A154:D154"/>
-    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A163:D163"/>
     <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A204:D204"/>
+    <mergeCell ref="A195:D195"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A85:D85"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A126:D126"/>
     <mergeCell ref="A141:D141"/>
-    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A206:D206"/>
     <mergeCell ref="A62:D62"/>
     <mergeCell ref="A125:D125"/>
     <mergeCell ref="A190:D190"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A117:D117"/>
-    <mergeCell ref="A199:D199"/>
+    <mergeCell ref="A230:D230"/>
     <mergeCell ref="A111:D111"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A127:D127"/>
+    <mergeCell ref="A167:D167"/>
     <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A232:D232"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A182:D182"/>
+    <mergeCell ref="A216:D216"/>
     <mergeCell ref="A98:D98"/>
+    <mergeCell ref="A191:D191"/>
+    <mergeCell ref="A169:D169"/>
     <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A153:D153"/>
+    <mergeCell ref="A218:D218"/>
+    <mergeCell ref="A227:D227"/>
     <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A208:D208"/>
+    <mergeCell ref="A217:D217"/>
     <mergeCell ref="A192:D192"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A145:D145"/>
+    <mergeCell ref="A139:D139"/>
+    <mergeCell ref="A160:D160"/>
     <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="A71:D71"/>
     <mergeCell ref="A129:D129"/>
+    <mergeCell ref="A194:D194"/>
     <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A116:D116"/>
+    <mergeCell ref="A181:D181"/>
+    <mergeCell ref="A184:D184"/>
+    <mergeCell ref="A131:D131"/>
     <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A140:D140"/>
+    <mergeCell ref="A171:D171"/>
+    <mergeCell ref="A231:D231"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A165:D165"/>
-    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A155:D155"/>
     <mergeCell ref="A102:D102"/>
     <mergeCell ref="A173:D173"/>
+    <mergeCell ref="A229:D229"/>
     <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A83:D83"/>
     <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A157:D157"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A166:D166"/>
     <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A207:D207"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A103:D103"/>
     <mergeCell ref="A168:D168"/>
-    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A205:D205"/>
     <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A193:D193"/>
+    <mergeCell ref="A233:D233"/>
     <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A130:D130"/>
-    <mergeCell ref="A201:D201"/>
-    <mergeCell ref="A132:D132"/>
+    <mergeCell ref="A219:D219"/>
+    <mergeCell ref="A234:D234"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A147:D147"/>
+    <mergeCell ref="A156:D156"/>
+    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="A220:D220"/>
+    <mergeCell ref="A82:D82"/>
+    <mergeCell ref="A222:D222"/>
+    <mergeCell ref="A123:D123"/>
     <mergeCell ref="A197:D197"/>
     <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A146:D146"/>
-    <mergeCell ref="A187:D187"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A183:D183"/>
+    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A118:D118"/>
     <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A189:D189"/>
-    <mergeCell ref="A198:D198"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A158:D158"/>
     <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A55:D55"/>
     <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A213:D213"/>
-    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A47:D47"/>
     <mergeCell ref="A175:D175"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A157" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A175" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A186" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A197" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A222" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="7391400"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="7391400"/>
     <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="10858500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="10858500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="10858500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>14</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="10858500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>14</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>14</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>14</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>14</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>14</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>14</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>14</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>14</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>14</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>14</row>
-      <rowOff>7391400</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="18249900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="20173950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="20173950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="20173950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="20173950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>25</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>25</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="25717500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="25717500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="28187650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="28187650"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="28187650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="28187650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="30035500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>48</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>48</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>48</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>48</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>48</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="36036250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>48</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="36036250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="41573450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="41573450"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="41573450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>60</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="41573450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>60</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="43421300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48977550"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>69</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>69</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56991250"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>80</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>80</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>80</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>80</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>80</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="60686950"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>80</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="60686950"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>102</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="78136749"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>102</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="78136749"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82657950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82657950"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82657950"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>115</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="82657950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>115</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>115</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>115</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>115</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>115</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90290650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90290650"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90290650"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>127</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="90290650"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>137</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="101961950"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>146</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="107765850"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>155</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="112325150"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>166</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="118738650"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>176</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>176</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>176</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>176</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3373,7 +2738,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="1847850"/>
+    <pos x="12934950" y="1847850"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="3695700"/>
+    <pos x="7391400" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="3695700"/>
+    <pos x="9239250" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="3695700"/>
+    <pos x="11087100" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="3695700"/>
+    <pos x="12934950" y="3695700"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="5543550"/>
+    <pos x="7391400" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="5543550"/>
+    <pos x="9239250" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="5543550"/>
+    <pos x="11087100" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="5543550"/>
+    <pos x="12934950" y="5543550"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="7391400"/>
+    <pos x="7391400" y="7391400"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="7391400"/>
+    <pos x="9239250" y="7391400"/>
     <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="10858500"/>
+    <pos x="7391400" y="10858500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="10858500"/>
+    <pos x="9239250" y="10858500"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="10858500"/>
+    <pos x="11087100" y="10858500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="10858500"/>
+    <pos x="12934950" y="10858500"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="12706350"/>
+    <pos x="7391400" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="12706350"/>
+    <pos x="9239250" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="12706350"/>
+    <pos x="11087100" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="12706350"/>
+    <pos x="12934950" y="12706350"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="14554200"/>
+    <pos x="7391400" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="14554200"/>
+    <pos x="9239250" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="14554200"/>
+    <pos x="11087100" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="14554200"/>
+    <pos x="12934950" y="14554200"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="16402050"/>
+    <pos x="7391400" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="16402050"/>
+    <pos x="9239250" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="16402050"/>
+    <pos x="11087100" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="16402050"/>
+    <pos x="12934950" y="16402050"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="18249900"/>
+    <pos x="7391400" y="18249900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="20173950"/>
+    <pos x="7391400" y="20173950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="20173950"/>
+    <pos x="9239250" y="20173950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="20173950"/>
+    <pos x="11087100" y="20173950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="20173950"/>
+    <pos x="12934950" y="20173950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="22021800"/>
+    <pos x="7391400" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="22021800"/>
+    <pos x="9239250" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="22021800"/>
+    <pos x="11087100" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="22021800"/>
+    <pos x="12934950" y="22021800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="23869650"/>
+    <pos x="7391400" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="23869650"/>
+    <pos x="9239250" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="23869650"/>
+    <pos x="11087100" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="23869650"/>
+    <pos x="12934950" y="23869650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="25717500"/>
+    <pos x="7391400" y="25717500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="25717500"/>
+    <pos x="9239250" y="25717500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="28187650"/>
+    <pos x="7391400" y="28187650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="28187650"/>
+    <pos x="9239250" y="28187650"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="28187650"/>
+    <pos x="11087100" y="28187650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="28187650"/>
+    <pos x="12934950" y="28187650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="30035500"/>
+    <pos x="7391400" y="30035500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="32340550"/>
+    <pos x="7391400" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="32340550"/>
+    <pos x="9239250" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="32340550"/>
+    <pos x="11087100" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="32340550"/>
+    <pos x="12934950" y="32340550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="34188400"/>
+    <pos x="7391400" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="34188400"/>
+    <pos x="9239250" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="34188400"/>
+    <pos x="11087100" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="34188400"/>
+    <pos x="12934950" y="34188400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="36036250"/>
+    <pos x="7391400" y="36036250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="36036250"/>
+    <pos x="9239250" y="36036250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="41573450"/>
+    <pos x="7391400" y="41573450"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="41573450"/>
+    <pos x="9239250" y="41573450"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="41573450"/>
+    <pos x="11087100" y="41573450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="41573450"/>
+    <pos x="12934950" y="41573450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="43421300"/>
+    <pos x="7391400" y="43421300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48977550"/>
+    <pos x="7391400" y="48977550"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48977550"/>
+    <pos x="9239250" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48977550"/>
+    <pos x="11087100" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48977550"/>
+    <pos x="12934950" y="48977550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="50825400"/>
+    <pos x="7391400" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="50825400"/>
+    <pos x="9239250" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="50825400"/>
+    <pos x="11087100" y="50825400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56991250"/>
+    <pos x="7391400" y="56991250"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56991250"/>
+    <pos x="9239250" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56991250"/>
+    <pos x="11087100" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="56991250"/>
+    <pos x="12934950" y="56991250"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58839100"/>
+    <pos x="7391400" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="58839100"/>
+    <pos x="9239250" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="58839100"/>
+    <pos x="11087100" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="58839100"/>
+    <pos x="12934950" y="58839100"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="60686950"/>
+    <pos x="7391400" y="60686950"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="60686950"/>
+    <pos x="9239250" y="60686950"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="64192150"/>
+    <pos x="7391400" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="64192150"/>
+    <pos x="9239250" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="64192150"/>
+    <pos x="11087100" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="64192150"/>
+    <pos x="12934950" y="64192150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="74441050"/>
+    <pos x="7391400" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="74441050"/>
+    <pos x="9239250" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="74441050"/>
+    <pos x="11087100" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="74441050"/>
+    <pos x="12934950" y="74441050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="76288900"/>
+    <pos x="7391400" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="76288900"/>
+    <pos x="9239250" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="76288900"/>
+    <pos x="11087100" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="76288900"/>
+    <pos x="12934950" y="76288900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="78136749"/>
+    <pos x="7391400" y="78136749"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="78136749"/>
+    <pos x="9239250" y="78136749"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82657950"/>
+    <pos x="7391400" y="82657950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82657950"/>
+    <pos x="9239250" y="82657950"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82657950"/>
+    <pos x="11087100" y="82657950"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="82657950"/>
+    <pos x="12934950" y="82657950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="84505800"/>
+    <pos x="7391400" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="84505800"/>
+    <pos x="9239250" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="84505800"/>
+    <pos x="11087100" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="84505800"/>
+    <pos x="12934950" y="84505800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86353650"/>
+    <pos x="7391400" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86353650"/>
+    <pos x="9239250" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86353650"/>
+    <pos x="11087100" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86353650"/>
+    <pos x="12934950" y="86353650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90290650"/>
+    <pos x="7391400" y="90290650"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90290650"/>
+    <pos x="9239250" y="90290650"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90290650"/>
+    <pos x="11087100" y="90290650"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="90290650"/>
+    <pos x="12934950" y="90290650"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="101961950"/>
+    <pos x="7391400" y="101961950"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="107765850"/>
+    <pos x="7391400" y="107765850"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="112325150"/>
+    <pos x="7391400" y="112325150"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="118738650"/>
+    <pos x="7391400" y="118738650"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="124313950"/>
+    <pos x="7391400" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="124313950"/>
+    <pos x="9239250" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="124313950"/>
+    <pos x="11087100" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="124313950"/>
+    <pos x="12934950" y="124313950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126161800"/>
+    <pos x="7391400" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126161800"/>
+    <pos x="9239250" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="126161800"/>
+    <pos x="11087100" y="126161800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3038,7 +3038,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -17,13 +17,22 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B5900"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,16 +46,31 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002A4A6B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCEFBE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6DC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -60,7 +84,62 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF3F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,32 +174,80 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -200,7 +327,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7391400" y="0"/>
+    <pos x="7848600" y="1092200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -220,7 +347,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="0"/>
+    <pos x="9696450" y="1092200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +367,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="0"/>
+    <pos x="11544300" y="1092200"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -260,7 +387,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="0"/>
+    <pos x="13392150" y="1092200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +407,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="1847850"/>
+    <pos x="7848600" y="2940050"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +427,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="1847850"/>
+    <pos x="9696450" y="2940050"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +447,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="1847850"/>
+    <pos x="11544300" y="2940050"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +467,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="1847850"/>
+    <pos x="13392150" y="2940050"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +487,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="3695700"/>
+    <pos x="7848600" y="4787900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +507,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="3695700"/>
+    <pos x="9696450" y="4787900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +527,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="3695700"/>
+    <pos x="11544300" y="4787900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +547,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="3695700"/>
+    <pos x="13392150" y="4787900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +567,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="5543550"/>
+    <pos x="7848600" y="6635750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +587,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="5543550"/>
+    <pos x="9696450" y="6635750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +607,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="5543550"/>
+    <pos x="11544300" y="6635750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +627,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="5543550"/>
+    <pos x="13392150" y="6635750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +647,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="7391400"/>
+    <pos x="7848600" y="8483600"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -540,7 +667,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="7391400"/>
+    <pos x="9696450" y="8483600"/>
     <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
@@ -560,7 +687,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="10858500"/>
+    <pos x="7848600" y="12534900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -580,7 +707,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="10858500"/>
+    <pos x="9696450" y="12534900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -600,7 +727,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="10858500"/>
+    <pos x="11544300" y="12534900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +747,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="10858500"/>
+    <pos x="13392150" y="12534900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +767,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="12706350"/>
+    <pos x="7848600" y="14382750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +787,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="12706350"/>
+    <pos x="9696450" y="14382750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +807,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="12706350"/>
+    <pos x="11544300" y="14382750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +827,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="12706350"/>
+    <pos x="13392150" y="14382750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +847,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="14554200"/>
+    <pos x="7848600" y="16230600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +867,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="14554200"/>
+    <pos x="9696450" y="16230600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +887,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="14554200"/>
+    <pos x="11544300" y="16230600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +907,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="14554200"/>
+    <pos x="13392150" y="16230600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +927,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="16402050"/>
+    <pos x="7848600" y="18078450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +947,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="16402050"/>
+    <pos x="9696450" y="18078450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +967,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="16402050"/>
+    <pos x="11544300" y="18078450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +987,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="16402050"/>
+    <pos x="13392150" y="18078450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +1007,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="18249900"/>
+    <pos x="7848600" y="19926300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +1027,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="20173950"/>
+    <pos x="7848600" y="21850350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -920,7 +1047,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="20173950"/>
+    <pos x="9696450" y="21850350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +1067,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="20173950"/>
+    <pos x="11544300" y="21850350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -960,7 +1087,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="20173950"/>
+    <pos x="13392150" y="21850350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -980,7 +1107,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="22021800"/>
+    <pos x="7848600" y="23698200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1127,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="22021800"/>
+    <pos x="9696450" y="23698200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1147,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="22021800"/>
+    <pos x="11544300" y="23698200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1167,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="22021800"/>
+    <pos x="13392150" y="23698200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1187,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="23869650"/>
+    <pos x="7848600" y="25546050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1207,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="23869650"/>
+    <pos x="9696450" y="25546050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1227,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="23869650"/>
+    <pos x="11544300" y="25546050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1247,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="23869650"/>
+    <pos x="13392150" y="25546050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1267,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="25717500"/>
+    <pos x="7848600" y="27393900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1287,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="25717500"/>
+    <pos x="9696450" y="27393900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1307,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="28187650"/>
+    <pos x="7848600" y="30448250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1327,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="28187650"/>
+    <pos x="9696450" y="30448250"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1347,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="28187650"/>
+    <pos x="11544300" y="30448250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1367,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="28187650"/>
+    <pos x="13392150" y="30448250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1387,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="30035500"/>
+    <pos x="7848600" y="32296100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1407,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="32340550"/>
+    <pos x="7848600" y="34778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1427,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="32340550"/>
+    <pos x="9696450" y="34778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1447,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="32340550"/>
+    <pos x="11544300" y="34778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1467,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="32340550"/>
+    <pos x="13392150" y="34778950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1487,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="34188400"/>
+    <pos x="7848600" y="36626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1507,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="34188400"/>
+    <pos x="9696450" y="36626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1527,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="34188400"/>
+    <pos x="11544300" y="36626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1547,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="34188400"/>
+    <pos x="13392150" y="36626800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1567,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="36036250"/>
+    <pos x="7848600" y="38474650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1587,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="36036250"/>
+    <pos x="9696450" y="38474650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1607,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="41573450"/>
+    <pos x="7848600" y="44392850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1627,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="41573450"/>
+    <pos x="9696450" y="44392850"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1647,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="41573450"/>
+    <pos x="11544300" y="44392850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1667,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="41573450"/>
+    <pos x="13392150" y="44392850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1687,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="43421300"/>
+    <pos x="7848600" y="46240700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1707,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="48977550"/>
+    <pos x="7848600" y="52177950"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1727,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="48977550"/>
+    <pos x="9696450" y="52177950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1747,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="48977550"/>
+    <pos x="11544300" y="52177950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1767,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="48977550"/>
+    <pos x="13392150" y="52177950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1787,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="50825400"/>
+    <pos x="7848600" y="54025800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1807,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="50825400"/>
+    <pos x="9696450" y="54025800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1827,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="50825400"/>
+    <pos x="11544300" y="54025800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1847,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="56991250"/>
+    <pos x="7848600" y="60572650"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1867,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="56991250"/>
+    <pos x="9696450" y="60572650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1887,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="56991250"/>
+    <pos x="11544300" y="60572650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1907,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="56991250"/>
+    <pos x="13392150" y="60572650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1927,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="58839100"/>
+    <pos x="7848600" y="62420500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1947,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="58839100"/>
+    <pos x="9696450" y="62420500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1967,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="58839100"/>
+    <pos x="11544300" y="62420500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1987,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="58839100"/>
+    <pos x="13392150" y="62420500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +2007,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="60686950"/>
+    <pos x="7848600" y="64268350"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +2027,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="60686950"/>
+    <pos x="9696450" y="64268350"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +2047,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="64192150"/>
+    <pos x="7848600" y="68154550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +2067,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="64192150"/>
+    <pos x="9696450" y="68154550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +2087,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="64192150"/>
+    <pos x="11544300" y="68154550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +2107,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="64192150"/>
+    <pos x="13392150" y="68154550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2127,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="74441050"/>
+    <pos x="7848600" y="78581250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2147,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="74441050"/>
+    <pos x="9696450" y="78581250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2167,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="74441050"/>
+    <pos x="11544300" y="78581250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2187,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="74441050"/>
+    <pos x="13392150" y="78581250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2207,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="76288900"/>
+    <pos x="7848600" y="80429100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2227,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="76288900"/>
+    <pos x="9696450" y="80429100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2247,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="76288900"/>
+    <pos x="11544300" y="80429100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2267,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="76288900"/>
+    <pos x="13392150" y="80429100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2287,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="78136749"/>
+    <pos x="7848600" y="82276950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2307,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="78136749"/>
+    <pos x="9696450" y="82276950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2327,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="82657950"/>
+    <pos x="7848600" y="87788750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2347,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="82657950"/>
+    <pos x="9696450" y="87788750"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2367,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="82657950"/>
+    <pos x="11544300" y="87788750"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2387,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="82657950"/>
+    <pos x="13392150" y="87788750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2407,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="84505800"/>
+    <pos x="7848600" y="89636600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2427,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="84505800"/>
+    <pos x="9696450" y="89636600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2447,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="84505800"/>
+    <pos x="11544300" y="89636600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2467,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="84505800"/>
+    <pos x="13392150" y="89636600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2487,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="86353650"/>
+    <pos x="7848600" y="91484450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2507,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="86353650"/>
+    <pos x="9696450" y="91484450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2527,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="86353650"/>
+    <pos x="11544300" y="91484450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2547,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="86353650"/>
+    <pos x="13392150" y="91484450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2567,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="90290650"/>
+    <pos x="7848600" y="96208850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2587,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="90290650"/>
+    <pos x="9696450" y="96208850"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2607,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="90290650"/>
+    <pos x="11544300" y="96208850"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2627,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="90290650"/>
+    <pos x="13392150" y="96208850"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2647,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="101961950"/>
+    <pos x="7848600" y="108261150"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2667,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="107765850"/>
+    <pos x="7848600" y="114065050"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2687,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="112325150"/>
+    <pos x="7848600" y="119030750"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2707,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="118738650"/>
+    <pos x="7848600" y="125647450"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2727,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="124313950"/>
+    <pos x="7848600" y="131425950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2747,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="124313950"/>
+    <pos x="9696450" y="131425950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2767,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="124313950"/>
+    <pos x="11544300" y="131425950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2787,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="12934950" y="124313950"/>
+    <pos x="13392150" y="131425950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2807,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7391400" y="126161800"/>
+    <pos x="7848600" y="133273800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2827,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9239250" y="126161800"/>
+    <pos x="9696450" y="133273800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2847,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11087100" y="126161800"/>
+    <pos x="11544300" y="133273800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3031,188 +3158,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:F203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="3" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>초코 버블바스붐 레시피    ↗ 원본</t>
+          <t>━  입욕·스크럽 골격 치트시트  (이 파일 17종 기준)  ━</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>전형 구성(%):  수상 3~23% · 유상 3~40% · 계면 6~14% · 보습 5~5% · 향 1~2% · 점증/pH 68~76% · 기타 10~60%</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>자주 쓰는 원료:  옥수수전분×8 · 구연산×7 · 베이킹소다×5 · 라벤더에센셜오일×3 · 시어버터×3 · SLSA×2 · 아보카도오일×2 · 사해소금×2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="6" customHeight="1"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>초코 버블바스붐 레시피    ↗ 원본</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>400g</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>미네럴, 소금의 일종, 탄산수소나트륨,삼투압으로 노폐뮬제거, 미네럴공급, 피부를 부드럽게</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="F7" s="8" t="n"/>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>감귤류에서 얻은 과일산, pH조절, 각질연화, 항균</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="9" ht="96" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>옥수수에서 얻은 녹말일종, 노폐물흡착, 흡습작용으로 모양이 잘 뭉쳐지게하는 역할</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>카카오분말</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>초콜렛의 원재료,폴리페놀함유</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>초코향</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>8ml</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>초코향,합성향</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>애플계면활성제</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
         <is>
           <t>사과주스에서 순한 계면활성제, 피부자극없음. 생분해율이 아주 높음(이 재료를 빼면 거품은 생기지 않음)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>코코베타인 등 물비누</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="13" ht="14" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 23 · 계면 3 · 향 1 · 점증/pH 68 · 기타 5</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
+      <c r="F13" s="16" t="n"/>
+    </row>
+    <row r="14" ht="14" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="80" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+    </row>
+    <row r="15" ht="80" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>초콜렛음료 속에 잠기는 기분~음?! 재미있겠죠.
 우리는 '이벤트 목욕탕' 가지 않고서도 집에서 초콜렛목욕을 즐길 수 있을 것 같아요.
@@ -3222,18 +3474,20 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="16" ht="14" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="384" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+    </row>
+    <row r="17" ht="384" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 먼저 계량한다. 덩어리지는 경우가 많아 특별히 베이킹소다만 체에 친다. 덩어리는 문질러주세요.
 3-4.나머지 구연산, 옥수수전분, 카카오분말, 초코향을 넣고 골고루 비비면서 섞어주세요.
@@ -3250,165 +3504,241 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>도쿄워커는 “진짜 초콜릿이 들어간 목욕탕”이라며 “초콜릿 속에 있는 폴리페놀은 혈액 촉진과 노폐물 배출 효과가 있고 또 셀룰라이트(울퉁붕툴해 보이는 피하 지방) 분해 효과도 기대할 수 있다”고 설명했다.
 [국민일보 쿠키뉴스 신은정 기자]</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="19" ht="6" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="22" ht="64" customHeight="1">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D17" s="8" t="n"/>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="F22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="80" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="24" ht="96" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
+    <row r="27" ht="14" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="288" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+    </row>
+    <row r="29" ht="288" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -3427,225 +3757,335 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-    </row>
-    <row r="24" ht="164.5" customHeight="1">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="6" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="118.5" customHeight="1">
+      <c r="A30" s="24" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="24" t="n"/>
+      <c r="F30" s="24" t="n"/>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>코치닐+물</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>1g+3g</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>반드시 양조절해서 / 색내기에 사용하세요.</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>원하는 색</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="F35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>주석산</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
         <is>
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n"/>
-    </row>
-    <row r="31" ht="80" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="F36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="96" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="F37" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>코코넛유래, / 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n"/>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="F38" s="8" t="n"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>애플 / 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="80" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="40" ht="80" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="F41" s="8" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="42" ht="14" customHeight="1">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+    </row>
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-    </row>
-    <row r="37" ht="96" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+    </row>
+    <row r="44" ht="96" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -3656,18 +4096,20 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-    </row>
-    <row r="39" ht="192" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+    </row>
+    <row r="46" ht="192" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -3684,69 +4126,105 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="6" customHeight="1"/>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="47" ht="6" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E50" s="20" t="inlineStr">
         <is>
           <t>풍부한 미네랄, / 노폐물제거</t>
         </is>
       </c>
-      <c r="D43" s="8" t="n"/>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="F50" s="20" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 100</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-    </row>
-    <row r="45" ht="176" customHeight="1">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+    </row>
+    <row r="53" ht="176" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -3761,22 +4239,26 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n"/>
-      <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-    </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+    </row>
+    <row r="55" ht="64" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -3784,157 +4266,235 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n"/>
-      <c r="C47" s="10" t="n"/>
-      <c r="D47" s="10" t="n"/>
-    </row>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="24" t="n"/>
+      <c r="F55" s="24" t="n"/>
+    </row>
+    <row r="56" ht="6" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n"/>
+      <c r="F57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="32" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>탄산수소나트륨 / , 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="D51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="80" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="61" ht="96" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="32" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="62" ht="32" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="63" ht="48" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴, / 철함유로 자체 / 핑크색, / 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="D55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="F63" s="8" t="n"/>
+    </row>
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
+      <c r="F64" s="16" t="n"/>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-    </row>
-    <row r="57" ht="240" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+    </row>
+    <row r="66" ht="240" customHeight="1">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -3954,18 +4514,20 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B58" s="6" t="n"/>
-      <c r="C58" s="6" t="n"/>
-      <c r="D58" s="6" t="n"/>
-    </row>
-    <row r="59" ht="208" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+    </row>
+    <row r="68" ht="208" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -3980,69 +4542,105 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="6" customHeight="1"/>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="1" t="inlineStr">
+    <row r="69" ht="6" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B61" s="2" t="n"/>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n"/>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="20" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C72" s="21" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E72" s="20" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="D63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+      <c r="F72" s="20" t="n"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  기타 100</t>
+        </is>
+      </c>
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="16" t="n"/>
+      <c r="D73" s="16" t="n"/>
+      <c r="E73" s="16" t="n"/>
+      <c r="F73" s="16" t="n"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-    </row>
-    <row r="65" ht="384" customHeight="1">
-      <c r="A65" s="9" t="inlineStr">
+      <c r="B74" s="18" t="n"/>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+    </row>
+    <row r="75" ht="384" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -4070,33 +4668,39 @@
 다양한</t>
         </is>
       </c>
-      <c r="B65" s="10" t="n"/>
-      <c r="C65" s="10" t="n"/>
-      <c r="D65" s="10" t="n"/>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="9" t="inlineStr">
+      <c r="B75" s="24" t="n"/>
+      <c r="C75" s="24" t="n"/>
+      <c r="D75" s="24" t="n"/>
+      <c r="E75" s="24" t="n"/>
+      <c r="F75" s="24" t="n"/>
+    </row>
+    <row r="76" ht="32" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>아로마오일을 히말라야 핑크소금에 배합해
 아로마테리피 효과도 함께 누리세요.</t>
         </is>
       </c>
-      <c r="B66" s="10" t="n"/>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="10" t="n"/>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+      <c r="B76" s="24" t="n"/>
+      <c r="C76" s="24" t="n"/>
+      <c r="D76" s="24" t="n"/>
+      <c r="E76" s="24" t="n"/>
+      <c r="F76" s="24" t="n"/>
+    </row>
+    <row r="77" ht="14" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-    </row>
-    <row r="68" ht="80" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
+      <c r="B77" s="18" t="n"/>
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+    </row>
+    <row r="78" ht="80" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -4105,135 +4709,203 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B68" s="10" t="n"/>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="10" t="n"/>
-    </row>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="1" t="inlineStr">
+      <c r="B78" s="24" t="n"/>
+      <c r="C78" s="24" t="n"/>
+      <c r="D78" s="24" t="n"/>
+      <c r="E78" s="24" t="n"/>
+      <c r="F78" s="24" t="n"/>
+    </row>
+    <row r="79" ht="6" customHeight="1"/>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B70" s="2" t="n"/>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n"/>
+      <c r="F80" s="6" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="64" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="82" ht="64" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨, / 산소금=암염, 수분함량 적고 / 미네럴 풍부, / 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="D72" s="4" t="n"/>
-    </row>
-    <row r="73" ht="48" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83" ht="48" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="F83" s="8" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
         <is>
           <t>입,족욕용 또는 / 바디 마사지/ 스크럽 겸용</t>
         </is>
       </c>
-      <c r="D74" s="4" t="n"/>
-    </row>
-    <row r="75" ht="48" customHeight="1">
-      <c r="A75" s="4" t="inlineStr">
+      <c r="F84" s="8" t="n"/>
+    </row>
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C75" s="4" t="inlineStr">
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="n"/>
+      <c r="C86" s="16" t="n"/>
+      <c r="D86" s="16" t="n"/>
+      <c r="E86" s="16" t="n"/>
+      <c r="F86" s="16" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="256" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+      <c r="B87" s="18" t="n"/>
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+    </row>
+    <row r="88" ht="256" customHeight="1">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4254,18 +4926,20 @@
         </is>
       </c>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="n"/>
-    </row>
-    <row r="79" ht="112" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+      <c r="B89" s="18" t="n"/>
+      <c r="C89" s="18" t="n"/>
+      <c r="D89" s="18" t="n"/>
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="18" t="n"/>
+    </row>
+    <row r="90" ht="112" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -4277,135 +4951,201 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="1" t="inlineStr">
+    <row r="91" ht="6" customHeight="1"/>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B81" s="2" t="n"/>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+      <c r="E92" s="6" t="n"/>
+      <c r="F92" s="6" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="48" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C94" s="21" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E94" s="20" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+      <c r="F94" s="20" t="n"/>
+    </row>
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B95" s="20" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E95" s="20" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="F95" s="20" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="96" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+    <row r="96" ht="96" customHeight="1">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B96" s="20" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E96" s="20" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="F96" s="20" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="8" t="inlineStr">
+    <row r="97" ht="80" customHeight="1">
+      <c r="A97" s="20" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E97" s="20" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="F97" s="20" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="5" t="inlineStr">
+    <row r="98" ht="14" customHeight="1">
+      <c r="A98" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
+        </is>
+      </c>
+      <c r="B98" s="16" t="n"/>
+      <c r="C98" s="16" t="n"/>
+      <c r="D98" s="16" t="n"/>
+      <c r="E98" s="16" t="n"/>
+      <c r="F98" s="16" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="64" customHeight="1">
-      <c r="A88" s="9" t="inlineStr">
+      <c r="B99" s="18" t="n"/>
+      <c r="C99" s="18" t="n"/>
+      <c r="D99" s="18" t="n"/>
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="18" t="n"/>
+    </row>
+    <row r="100" ht="64" customHeight="1">
+      <c r="A100" s="23" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -4413,22 +5153,26 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B88" s="10" t="n"/>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="10" t="n"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+      <c r="B100" s="24" t="n"/>
+      <c r="C100" s="24" t="n"/>
+      <c r="D100" s="24" t="n"/>
+      <c r="E100" s="24" t="n"/>
+      <c r="F100" s="24" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="192" customHeight="1">
-      <c r="A90" s="9" t="inlineStr">
+      <c r="B101" s="18" t="n"/>
+      <c r="C101" s="18" t="n"/>
+      <c r="D101" s="18" t="n"/>
+      <c r="E101" s="18" t="n"/>
+      <c r="F101" s="18" t="n"/>
+    </row>
+    <row r="102" ht="192" customHeight="1">
+      <c r="A102" s="23" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -4443,113 +5187,171 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="10" t="n"/>
-    </row>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="1" t="inlineStr">
+      <c r="B102" s="24" t="n"/>
+      <c r="C102" s="24" t="n"/>
+      <c r="D102" s="24" t="n"/>
+      <c r="E102" s="24" t="n"/>
+      <c r="F102" s="24" t="n"/>
+    </row>
+    <row r="103" ht="6" customHeight="1"/>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B92" s="2" t="n"/>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+      <c r="E104" s="6" t="n"/>
+      <c r="F104" s="6" t="n"/>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="8" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="D94" s="4" t="n"/>
-    </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+      <c r="F106" s="8" t="n"/>
+    </row>
+    <row r="107" ht="48" customHeight="1">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D107" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 / 시어버터, 아보카도, 꿀추출물 등 / 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="D95" s="4" t="n"/>
-    </row>
-    <row r="96" ht="64" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="80" customHeight="1">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="D108" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>아로마테라피 / 여드름-티트리, / 바디 용도별 추천오일 / -쿨링 :페파민트, / -다이어트 : 레몬+자몽오일 / -이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="F108" s="8" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
+        </is>
+      </c>
+      <c r="B109" s="16" t="n"/>
+      <c r="C109" s="16" t="n"/>
+      <c r="D109" s="16" t="n"/>
+      <c r="E109" s="16" t="n"/>
+      <c r="F109" s="16" t="n"/>
+    </row>
+    <row r="110" ht="14" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="384" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="B110" s="18" t="n"/>
+      <c r="C110" s="18" t="n"/>
+      <c r="D110" s="18" t="n"/>
+      <c r="E110" s="18" t="n"/>
+      <c r="F110" s="18" t="n"/>
+    </row>
+    <row r="111" ht="384" customHeight="1">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4573,15 +5375,15 @@
 (확실히 사해소금에 비해 수분함량은 낮아요)
 최근 소금에 미세플라스틱이 많다는
 이야기가 있습니다. ㅜㅜ
-히말라야 핑크소금은</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="128" customHeight="1">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>미세플라스틱이 없다, 있을 수 없다고
-알려져있어요.
+히말라야 핑크소금은
+미세플라스틱이 없다, 있을 수 없다고</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="112" customHeight="1">
+      <c r="A112" s="19" t="inlineStr">
+        <is>
+          <t>알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
 잠겨있을 시기에 생성된 소금이고
 지각 변동에 의해 히말라야가 융기되면서
@@ -4591,18 +5393,20 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="5" t="inlineStr">
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-    </row>
-    <row r="101" ht="80" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="B113" s="18" t="n"/>
+      <c r="C113" s="18" t="n"/>
+      <c r="D113" s="18" t="n"/>
+      <c r="E113" s="18" t="n"/>
+      <c r="F113" s="18" t="n"/>
+    </row>
+    <row r="114" ht="80" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -4612,175 +5416,261 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="6" customHeight="1"/>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="1" t="inlineStr">
+    <row r="115" ht="6" customHeight="1"/>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B103" s="2" t="n"/>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n"/>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="6" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B117" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C117" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="8" t="inlineStr">
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="20" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B105" s="8" t="inlineStr">
+      <c r="B118" s="20" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
+      <c r="C118" s="21" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="D118" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E118" s="20" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="D105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+      <c r="F118" s="20" t="n"/>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="20" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B119" s="20" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D119" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E119" s="20" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="F119" s="20" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="80" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="120" ht="96" customHeight="1">
+      <c r="A120" s="20" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B120" s="20" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C120" s="21" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E120" s="20" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="F120" s="20" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="20" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B121" s="20" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E121" s="20" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="D108" s="8" t="n"/>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+      <c r="F121" s="20" t="n"/>
+    </row>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="20" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B122" s="20" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C122" s="21" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="D122" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E122" s="20" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="F122" s="20" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="8" t="inlineStr">
+    <row r="123" ht="64" customHeight="1">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B110" s="8" t="inlineStr">
+      <c r="B123" s="20" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr">
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E123" s="20" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="D110" s="8" t="inlineStr">
+      <c r="F123" s="20" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="5" t="inlineStr">
+    <row r="124" ht="14" customHeight="1">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="n"/>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="16" t="n"/>
+      <c r="F124" s="16" t="n"/>
+    </row>
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-    </row>
-    <row r="112" ht="224" customHeight="1">
-      <c r="A112" s="9" t="inlineStr">
+      <c r="B125" s="18" t="n"/>
+      <c r="C125" s="18" t="n"/>
+      <c r="D125" s="18" t="n"/>
+      <c r="E125" s="18" t="n"/>
+      <c r="F125" s="18" t="n"/>
+    </row>
+    <row r="126" ht="224" customHeight="1">
+      <c r="A126" s="23" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -4798,22 +5688,26 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="10" t="n"/>
-    </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="B126" s="24" t="n"/>
+      <c r="C126" s="24" t="n"/>
+      <c r="D126" s="24" t="n"/>
+      <c r="E126" s="24" t="n"/>
+      <c r="F126" s="24" t="n"/>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-    </row>
-    <row r="114" ht="160" customHeight="1">
-      <c r="A114" s="9" t="inlineStr">
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+    </row>
+    <row r="128" ht="160" customHeight="1">
+      <c r="A128" s="23" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -4827,201 +5721,299 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B114" s="10" t="n"/>
-      <c r="C114" s="10" t="n"/>
-      <c r="D114" s="10" t="n"/>
-    </row>
-    <row r="115" ht="6" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="1" t="inlineStr">
+      <c r="B128" s="24" t="n"/>
+      <c r="C128" s="24" t="n"/>
+      <c r="D128" s="24" t="n"/>
+      <c r="E128" s="24" t="n"/>
+      <c r="F128" s="24" t="n"/>
+    </row>
+    <row r="129" ht="6" customHeight="1"/>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B116" s="2" t="n"/>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+      <c r="E130" s="6" t="n"/>
+      <c r="F130" s="6" t="n"/>
+    </row>
+    <row r="131" ht="15" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="4" t="inlineStr">
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="8" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B132" s="8" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C118" s="4" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="D132" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E132" s="8" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="D118" s="4" t="inlineStr">
+      <c r="F132" s="8" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="8" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D133" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E133" s="8" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="F133" s="8" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="48" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="134" ht="48" customHeight="1">
+      <c r="A134" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D134" s="27" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
         <is>
           <t>에코인증, 물과 오일의 분리를 저지</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="F134" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="48" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="135" ht="64" customHeight="1">
+      <c r="A135" s="8" t="inlineStr">
         <is>
           <t>순한 (샴푸) / 베이스</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>38g</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E135" s="8" t="inlineStr">
         <is>
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="D121" s="4" t="n"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B136" s="8" t="inlineStr">
         <is>
           <t>13g</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C136" s="9" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="D122" s="4" t="inlineStr">
+      <c r="F136" s="8" t="inlineStr">
         <is>
           <t>꿀 등</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+    <row r="137" ht="48" customHeight="1">
+      <c r="A137" s="8" t="inlineStr">
         <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
         <is>
           <t>각질제거, 보습. / 필요에 따라 양을 더 넣어서 / 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="D123" s="4" t="n"/>
-    </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="F137" s="8" t="n"/>
+    </row>
+    <row r="138" ht="32" customHeight="1">
+      <c r="A138" s="8" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B138" s="8" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C138" s="9" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D138" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E138" s="8" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="F138" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="n"/>
+      <c r="C139" s="16" t="n"/>
+      <c r="D139" s="16" t="n"/>
+      <c r="E139" s="16" t="n"/>
+      <c r="F139" s="16" t="n"/>
+    </row>
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-    </row>
-    <row r="126" ht="336" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
+      <c r="B140" s="18" t="n"/>
+      <c r="C140" s="18" t="n"/>
+      <c r="D140" s="18" t="n"/>
+      <c r="E140" s="18" t="n"/>
+      <c r="F140" s="18" t="n"/>
+    </row>
+    <row r="141" ht="336" customHeight="1">
+      <c r="A141" s="19" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -5047,95 +6039,141 @@
         </is>
       </c>
     </row>
-    <row r="127" ht="6" customHeight="1"/>
-    <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="1" t="inlineStr">
+    <row r="142" ht="6" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B128" s="2" t="n"/>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-    </row>
-    <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="B143" s="6" t="n"/>
+      <c r="C143" s="6" t="n"/>
+      <c r="D143" s="6" t="n"/>
+      <c r="E143" s="6" t="n"/>
+      <c r="F143" s="6" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B144" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C144" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="F144" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="64" customHeight="1">
-      <c r="A130" s="8" t="inlineStr">
+    <row r="145" ht="64" customHeight="1">
+      <c r="A145" s="20" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B130" s="8" t="inlineStr">
+      <c r="B145" s="20" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C130" s="8" t="inlineStr">
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="D145" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
         </is>
       </c>
-      <c r="D130" s="8" t="inlineStr">
+      <c r="F145" s="20" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="32" customHeight="1">
-      <c r="A131" s="8" t="inlineStr">
+    <row r="146" ht="48" customHeight="1">
+      <c r="A146" s="20" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B131" s="8" t="inlineStr">
+      <c r="B146" s="20" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr">
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 / 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="D131" s="8" t="inlineStr">
+      <c r="F146" s="20" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="14" customHeight="1">
-      <c r="A132" s="5" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 48 · 향 52</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="n"/>
+      <c r="C147" s="16" t="n"/>
+      <c r="D147" s="16" t="n"/>
+      <c r="E147" s="16" t="n"/>
+      <c r="F147" s="16" t="n"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B132" s="6" t="n"/>
-      <c r="C132" s="6" t="n"/>
-      <c r="D132" s="6" t="n"/>
-    </row>
-    <row r="133" ht="384" customHeight="1">
-      <c r="A133" s="9" t="inlineStr">
+      <c r="B148" s="18" t="n"/>
+      <c r="C148" s="18" t="n"/>
+      <c r="D148" s="18" t="n"/>
+      <c r="E148" s="18" t="n"/>
+      <c r="F148" s="18" t="n"/>
+    </row>
+    <row r="149" ht="384" customHeight="1">
+      <c r="A149" s="23" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -5163,34 +6201,40 @@
 항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
         </is>
       </c>
-      <c r="B133" s="10" t="n"/>
-      <c r="C133" s="10" t="n"/>
-      <c r="D133" s="10" t="n"/>
-    </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="9" t="inlineStr">
+      <c r="B149" s="24" t="n"/>
+      <c r="C149" s="24" t="n"/>
+      <c r="D149" s="24" t="n"/>
+      <c r="E149" s="24" t="n"/>
+      <c r="F149" s="24" t="n"/>
+    </row>
+    <row r="150" ht="48" customHeight="1">
+      <c r="A150" s="23" t="inlineStr">
         <is>
           <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B134" s="10" t="n"/>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="10" t="n"/>
-    </row>
-    <row r="135" ht="14" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+      <c r="B150" s="24" t="n"/>
+      <c r="C150" s="24" t="n"/>
+      <c r="D150" s="24" t="n"/>
+      <c r="E150" s="24" t="n"/>
+      <c r="F150" s="24" t="n"/>
+    </row>
+    <row r="151" ht="14" customHeight="1">
+      <c r="A151" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-    </row>
-    <row r="136" ht="320" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
+      <c r="B151" s="18" t="n"/>
+      <c r="C151" s="18" t="n"/>
+      <c r="D151" s="18" t="n"/>
+      <c r="E151" s="18" t="n"/>
+      <c r="F151" s="18" t="n"/>
+    </row>
+    <row r="152" ht="320" customHeight="1">
+      <c r="A152" s="23" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -5214,135 +6258,175 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B136" s="10" t="n"/>
-      <c r="C136" s="10" t="n"/>
-      <c r="D136" s="10" t="n"/>
-    </row>
-    <row r="137" ht="6" customHeight="1"/>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="1" t="inlineStr">
+      <c r="B152" s="24" t="n"/>
+      <c r="C152" s="24" t="n"/>
+      <c r="D152" s="24" t="n"/>
+      <c r="E152" s="24" t="n"/>
+      <c r="F152" s="24" t="n"/>
+    </row>
+    <row r="153" ht="6" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B138" s="2" t="n"/>
-      <c r="C138" s="2" t="n"/>
-      <c r="D138" s="2" t="n"/>
-    </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B155" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="64" customHeight="1">
-      <c r="A140" s="4" t="inlineStr">
+    <row r="156" ht="64" customHeight="1">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr"/>
+      <c r="D156" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D140" s="4" t="n"/>
-    </row>
-    <row r="141" ht="32" customHeight="1">
-      <c r="A141" s="4" t="inlineStr">
+      <c r="F156" s="8" t="n"/>
+    </row>
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" s="8" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C157" s="9" t="inlineStr"/>
+      <c r="D157" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E157" s="8" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="F157" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="32" customHeight="1">
-      <c r="A142" s="4" t="inlineStr">
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C158" s="9" t="inlineStr"/>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E158" s="8" t="inlineStr">
         <is>
           <t>스크럽, 노폐물, / 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="D142" s="4" t="n"/>
-    </row>
-    <row r="143" ht="96" customHeight="1">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="F158" s="8" t="n"/>
+    </row>
+    <row r="159" ht="96" customHeight="1">
+      <c r="A159" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B143" s="4" t="inlineStr">
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C143" s="4" t="inlineStr">
+      <c r="C159" s="9" t="inlineStr"/>
+      <c r="D159" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E159" s="8" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D143" s="4" t="inlineStr">
+      <c r="F159" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="176" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
+      <c r="B160" s="18" t="n"/>
+      <c r="C160" s="18" t="n"/>
+      <c r="D160" s="18" t="n"/>
+      <c r="E160" s="18" t="n"/>
+      <c r="F160" s="18" t="n"/>
+    </row>
+    <row r="161" ht="176" customHeight="1">
+      <c r="A161" s="19" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -5356,95 +6440,121 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="6" customHeight="1"/>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="1" t="inlineStr">
+    <row r="162" ht="6" customHeight="1"/>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="5" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B147" s="2" t="n"/>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n"/>
-    </row>
-    <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="B163" s="6" t="n"/>
+      <c r="C163" s="6" t="n"/>
+      <c r="D163" s="6" t="n"/>
+      <c r="E163" s="6" t="n"/>
+      <c r="F163" s="6" t="n"/>
+    </row>
+    <row r="164" ht="15" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B164" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="F164" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="8" t="inlineStr">
+    <row r="165" ht="32" customHeight="1">
+      <c r="A165" s="20" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B149" s="8" t="inlineStr">
+      <c r="B165" s="20" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr">
+      <c r="C165" s="21" t="inlineStr"/>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E165" s="20" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="D149" s="8" t="inlineStr">
+      <c r="F165" s="20" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="48" customHeight="1">
-      <c r="A150" s="8" t="inlineStr">
+    <row r="166" ht="64" customHeight="1">
+      <c r="A166" s="20" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B150" s="8" t="inlineStr">
+      <c r="B166" s="20" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr">
+      <c r="C166" s="21" t="inlineStr"/>
+      <c r="D166" s="28" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="E166" s="20" t="inlineStr">
         <is>
           <t>감초의 수/지용성성분추출물.</t>
         </is>
       </c>
-      <c r="D150" s="8" t="inlineStr">
+      <c r="F166" s="20" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="5" t="inlineStr">
+    <row r="167" ht="14" customHeight="1">
+      <c r="A167" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-    </row>
-    <row r="152" ht="112" customHeight="1">
-      <c r="A152" s="9" t="inlineStr">
+      <c r="B167" s="18" t="n"/>
+      <c r="C167" s="18" t="n"/>
+      <c r="D167" s="18" t="n"/>
+      <c r="E167" s="18" t="n"/>
+      <c r="F167" s="18" t="n"/>
+    </row>
+    <row r="168" ht="112" customHeight="1">
+      <c r="A168" s="23" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -5452,22 +6562,26 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B152" s="10" t="n"/>
-      <c r="C152" s="10" t="n"/>
-      <c r="D152" s="10" t="n"/>
-    </row>
-    <row r="153" ht="14" customHeight="1">
-      <c r="A153" s="5" t="inlineStr">
+      <c r="B168" s="24" t="n"/>
+      <c r="C168" s="24" t="n"/>
+      <c r="D168" s="24" t="n"/>
+      <c r="E168" s="24" t="n"/>
+      <c r="F168" s="24" t="n"/>
+    </row>
+    <row r="169" ht="14" customHeight="1">
+      <c r="A169" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B153" s="6" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-    </row>
-    <row r="154" ht="112" customHeight="1">
-      <c r="A154" s="9" t="inlineStr">
+      <c r="B169" s="18" t="n"/>
+      <c r="C169" s="18" t="n"/>
+      <c r="D169" s="18" t="n"/>
+      <c r="E169" s="18" t="n"/>
+      <c r="F169" s="18" t="n"/>
+    </row>
+    <row r="170" ht="112" customHeight="1">
+      <c r="A170" s="23" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -5477,183 +6591,235 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B154" s="10" t="n"/>
-      <c r="C154" s="10" t="n"/>
-      <c r="D154" s="10" t="n"/>
-    </row>
-    <row r="155" ht="6" customHeight="1"/>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="1" t="inlineStr">
+      <c r="B170" s="24" t="n"/>
+      <c r="C170" s="24" t="n"/>
+      <c r="D170" s="24" t="n"/>
+      <c r="E170" s="24" t="n"/>
+      <c r="F170" s="24" t="n"/>
+    </row>
+    <row r="171" ht="6" customHeight="1"/>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="5" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B156" s="2" t="n"/>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n"/>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="3" t="inlineStr">
+      <c r="B172" s="6" t="n"/>
+      <c r="C172" s="6" t="n"/>
+      <c r="D172" s="6" t="n"/>
+      <c r="E172" s="6" t="n"/>
+      <c r="F172" s="6" t="n"/>
+    </row>
+    <row r="173" ht="15" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="F173" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="64" customHeight="1">
-      <c r="A158" s="4" t="inlineStr">
+    <row r="174" ht="64" customHeight="1">
+      <c r="A174" s="8" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B158" s="4" t="inlineStr">
+      <c r="B174" s="8" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C158" s="4" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr"/>
+      <c r="D174" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E174" s="8" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="D158" s="4" t="n"/>
-    </row>
-    <row r="159" ht="32" customHeight="1">
-      <c r="A159" s="4" t="inlineStr">
+      <c r="F174" s="8" t="n"/>
+    </row>
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" s="8" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C159" s="4" t="inlineStr">
+      <c r="C175" s="9" t="inlineStr"/>
+      <c r="D175" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E175" s="8" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="D159" s="4" t="inlineStr">
+      <c r="F175" s="8" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="96" customHeight="1">
-      <c r="A160" s="4" t="inlineStr">
+    <row r="176" ht="96" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C160" s="4" t="inlineStr">
+      <c r="C176" s="9" t="inlineStr"/>
+      <c r="D176" s="10" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="D160" s="4" t="inlineStr">
+      <c r="F176" s="8" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="48" customHeight="1">
-      <c r="A161" s="4" t="inlineStr">
+    <row r="177" ht="48" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C161" s="4" t="inlineStr">
+      <c r="C177" s="9" t="inlineStr"/>
+      <c r="D177" s="11" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="E177" s="8" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="D161" s="4" t="inlineStr">
+      <c r="F177" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="64" customHeight="1">
-      <c r="A162" s="4" t="inlineStr">
+    <row r="178" ht="80" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C162" s="4" t="inlineStr">
+      <c r="C178" s="9" t="inlineStr"/>
+      <c r="D178" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E178" s="8" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D162" s="4" t="inlineStr">
+      <c r="F178" s="8" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="4" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C163" s="4" t="inlineStr">
+      <c r="C179" s="9" t="inlineStr"/>
+      <c r="D179" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="D163" s="4" t="inlineStr">
+      <c r="F179" s="8" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="5" t="inlineStr">
+    <row r="180" ht="14" customHeight="1">
+      <c r="A180" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B164" s="6" t="n"/>
-      <c r="C164" s="6" t="n"/>
-      <c r="D164" s="6" t="n"/>
-    </row>
-    <row r="165" ht="112" customHeight="1">
-      <c r="A165" s="7" t="inlineStr">
+      <c r="B180" s="18" t="n"/>
+      <c r="C180" s="18" t="n"/>
+      <c r="D180" s="18" t="n"/>
+      <c r="E180" s="18" t="n"/>
+      <c r="F180" s="18" t="n"/>
+    </row>
+    <row r="181" ht="112" customHeight="1">
+      <c r="A181" s="19" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -5663,134 +6829,170 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="6" customHeight="1"/>
-    <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="1" t="inlineStr">
+    <row r="182" ht="6" customHeight="1"/>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B167" s="2" t="n"/>
-      <c r="C167" s="2" t="n"/>
-      <c r="D167" s="2" t="n"/>
-    </row>
-    <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="B183" s="6" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+      <c r="E183" s="6" t="n"/>
+      <c r="F183" s="6" t="n"/>
+    </row>
+    <row r="184" ht="15" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B168" s="3" t="inlineStr">
+      <c r="B184" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C168" s="3" t="inlineStr">
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D168" s="3" t="inlineStr">
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="32" customHeight="1">
-      <c r="A169" s="8" t="inlineStr">
+    <row r="185" ht="32" customHeight="1">
+      <c r="A185" s="20" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B169" s="8" t="inlineStr">
+      <c r="B185" s="20" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C169" s="8" t="inlineStr">
+      <c r="C185" s="21" t="inlineStr"/>
+      <c r="D185" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E185" s="20" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="D169" s="8" t="n"/>
-    </row>
-    <row r="170" ht="80" customHeight="1">
-      <c r="A170" s="8" t="inlineStr">
+      <c r="F185" s="20" t="n"/>
+    </row>
+    <row r="186" ht="112" customHeight="1">
+      <c r="A186" s="20" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B170" s="8" t="inlineStr">
+      <c r="B186" s="20" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C170" s="8" t="inlineStr">
+      <c r="C186" s="21" t="inlineStr"/>
+      <c r="D186" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E186" s="20" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="D170" s="8" t="inlineStr">
+      <c r="F186" s="20" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="32" customHeight="1">
-      <c r="A171" s="8" t="inlineStr">
+    <row r="187" ht="32" customHeight="1">
+      <c r="A187" s="20" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B171" s="8" t="inlineStr">
+      <c r="B187" s="20" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr">
+      <c r="C187" s="21" t="inlineStr"/>
+      <c r="D187" s="13" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="E187" s="20" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="D171" s="8" t="inlineStr">
+      <c r="F187" s="20" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="5" t="inlineStr">
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="80" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
+      <c r="B188" s="18" t="n"/>
+      <c r="C188" s="18" t="n"/>
+      <c r="D188" s="18" t="n"/>
+      <c r="E188" s="18" t="n"/>
+      <c r="F188" s="18" t="n"/>
+    </row>
+    <row r="189" ht="80" customHeight="1">
+      <c r="A189" s="23" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B173" s="10" t="n"/>
-      <c r="C173" s="10" t="n"/>
-      <c r="D173" s="10" t="n"/>
-    </row>
-    <row r="174" ht="14" customHeight="1">
-      <c r="A174" s="5" t="inlineStr">
+      <c r="B189" s="24" t="n"/>
+      <c r="C189" s="24" t="n"/>
+      <c r="D189" s="24" t="n"/>
+      <c r="E189" s="24" t="n"/>
+      <c r="F189" s="24" t="n"/>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-    </row>
-    <row r="175" ht="144" customHeight="1">
-      <c r="A175" s="9" t="inlineStr">
+      <c r="B190" s="18" t="n"/>
+      <c r="C190" s="18" t="n"/>
+      <c r="D190" s="18" t="n"/>
+      <c r="E190" s="18" t="n"/>
+      <c r="F190" s="18" t="n"/>
+    </row>
+    <row r="191" ht="128" customHeight="1">
+      <c r="A191" s="23" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -5801,109 +7003,167 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B175" s="10" t="n"/>
-      <c r="C175" s="10" t="n"/>
-      <c r="D175" s="10" t="n"/>
-    </row>
-    <row r="176" ht="6" customHeight="1"/>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="1" t="inlineStr">
+      <c r="B191" s="24" t="n"/>
+      <c r="C191" s="24" t="n"/>
+      <c r="D191" s="24" t="n"/>
+      <c r="E191" s="24" t="n"/>
+      <c r="F191" s="24" t="n"/>
+    </row>
+    <row r="192" ht="6" customHeight="1"/>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="5" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B177" s="2" t="n"/>
-      <c r="C177" s="2" t="n"/>
-      <c r="D177" s="2" t="n"/>
-    </row>
-    <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="3" t="inlineStr">
+      <c r="B193" s="6" t="n"/>
+      <c r="C193" s="6" t="n"/>
+      <c r="D193" s="6" t="n"/>
+      <c r="E193" s="6" t="n"/>
+      <c r="F193" s="6" t="n"/>
+    </row>
+    <row r="194" ht="15" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr">
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C178" s="3" t="inlineStr">
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D178" s="3" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="64" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
+    <row r="195" ht="64" customHeight="1">
+      <c r="A195" s="8" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C195" s="9" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="D195" s="25" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="D179" s="4" t="n"/>
-    </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+      <c r="F195" s="8" t="n"/>
+    </row>
+    <row r="196" ht="32" customHeight="1">
+      <c r="A196" s="8" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B196" s="8" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C196" s="9" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="D196" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E196" s="8" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 / →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="D180" s="4" t="n"/>
-    </row>
-    <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+      <c r="F196" s="8" t="n"/>
+    </row>
+    <row r="197" ht="16" customHeight="1">
+      <c r="A197" s="8" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C197" s="9" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="D197" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E197" s="8" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="D181" s="4" t="n"/>
-    </row>
-    <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="5" t="inlineStr">
+      <c r="F197" s="8" t="n"/>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="15" t="inlineStr">
+        <is>
+          <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
+        </is>
+      </c>
+      <c r="B198" s="16" t="n"/>
+      <c r="C198" s="16" t="n"/>
+      <c r="D198" s="16" t="n"/>
+      <c r="E198" s="16" t="n"/>
+      <c r="F198" s="16" t="n"/>
+    </row>
+    <row r="199" ht="14" customHeight="1">
+      <c r="A199" s="17" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="6" t="n"/>
-      <c r="D182" s="6" t="n"/>
-    </row>
-    <row r="183" ht="384" customHeight="1">
-      <c r="A183" s="7" t="inlineStr">
+      <c r="B199" s="18" t="n"/>
+      <c r="C199" s="18" t="n"/>
+      <c r="D199" s="18" t="n"/>
+      <c r="E199" s="18" t="n"/>
+      <c r="F199" s="18" t="n"/>
+    </row>
+    <row r="200" ht="384" customHeight="1">
+      <c r="A200" s="19" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -5932,8 +7192,8 @@
         </is>
       </c>
     </row>
-    <row r="184" ht="112" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="201" ht="112" customHeight="1">
+      <c r="A201" s="19" t="inlineStr">
         <is>
           <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
@@ -5945,18 +7205,20 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="17" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="112" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
+      <c r="B202" s="18" t="n"/>
+      <c r="C202" s="18" t="n"/>
+      <c r="D202" s="18" t="n"/>
+      <c r="E202" s="18" t="n"/>
+      <c r="F202" s="18" t="n"/>
+    </row>
+    <row r="203" ht="112" customHeight="1">
+      <c r="A203" s="19" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -5968,110 +7230,126 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="6" customHeight="1"/>
+    <row r="204" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="82">
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A81:D81"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A152:D152"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A114:D114"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A172:D172"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A164:D164"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A154:D154"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A126:D126"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A135:D135"/>
-    <mergeCell ref="A125:D125"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A167:D167"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A79:D79"/>
-    <mergeCell ref="A61:D61"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A153:D153"/>
-    <mergeCell ref="A128:D128"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A177:D177"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="A145:D145"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A76:D76"/>
-    <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A184:D184"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A165:D165"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A173:D173"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A103:D103"/>
-    <mergeCell ref="A78:D78"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A113:D113"/>
-    <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A147:D147"/>
-    <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A138:D138"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A151:D151"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A175:D175"/>
+  <mergeCells count="98">
+    <mergeCell ref="A183:F183"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A141:F141"/>
+    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A199:F199"/>
+    <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A139:F139"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A203:F203"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A111:F111"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A89:F89"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A113:F113"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A201:F201"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A110:F110"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A156" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A167" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A177" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,10 @@
     </font>
     <font>
       <color rgb="003A3A3A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="007A4A2A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -55,7 +59,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +74,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECE0"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -184,20 +193,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -212,33 +222,33 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -246,6 +256,9 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -327,7 +340,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1092200"/>
+    <pos x="7848600" y="1854200"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -347,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1092200"/>
+    <pos x="9696450" y="1854200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -367,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1092200"/>
+    <pos x="11544300" y="1854200"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -387,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1092200"/>
+    <pos x="13392150" y="1854200"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -407,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="2940050"/>
+    <pos x="7848600" y="3702049"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -427,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="2940050"/>
+    <pos x="9696450" y="3702049"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -447,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="2940050"/>
+    <pos x="11544300" y="3702049"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -467,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="2940050"/>
+    <pos x="13392150" y="3702049"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -487,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="4787900"/>
+    <pos x="7848600" y="5549900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -507,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="4787900"/>
+    <pos x="9696450" y="5549900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -527,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="4787900"/>
+    <pos x="11544300" y="5549900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -547,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="4787900"/>
+    <pos x="13392150" y="5549900"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -567,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="6635750"/>
+    <pos x="7848600" y="7397750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -587,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="6635750"/>
+    <pos x="9696450" y="7397750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -607,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="6635750"/>
+    <pos x="11544300" y="7397750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -627,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="6635750"/>
+    <pos x="13392150" y="7397750"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -647,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="8483600"/>
+    <pos x="7848600" y="9245600"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -667,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="8483600"/>
+    <pos x="9696450" y="9245600"/>
     <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
@@ -687,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="12534900"/>
+    <pos x="7848600" y="13296900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -707,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="12534900"/>
+    <pos x="9696450" y="13296900"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -727,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="12534900"/>
+    <pos x="11544300" y="13296900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -747,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="12534900"/>
+    <pos x="13392150" y="13296900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -767,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="14382750"/>
+    <pos x="7848600" y="15144750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -787,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="14382750"/>
+    <pos x="9696450" y="15144750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -807,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="14382750"/>
+    <pos x="11544300" y="15144750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -827,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="14382750"/>
+    <pos x="13392150" y="15144750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -847,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="16230600"/>
+    <pos x="7848600" y="16992600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -867,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="16230600"/>
+    <pos x="9696450" y="16992600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -887,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="16230600"/>
+    <pos x="11544300" y="16992600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -907,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="16230600"/>
+    <pos x="13392150" y="16992600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -927,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="18078450"/>
+    <pos x="7848600" y="18840450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -947,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="18078450"/>
+    <pos x="9696450" y="18840450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -967,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="18078450"/>
+    <pos x="11544300" y="18840450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -987,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="18078450"/>
+    <pos x="13392150" y="18840450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1007,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19926300"/>
+    <pos x="7848600" y="20688300"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1027,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="21850350"/>
+    <pos x="7848600" y="22612350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1047,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="21850350"/>
+    <pos x="9696450" y="22612350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1067,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="21850350"/>
+    <pos x="11544300" y="22612350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1087,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="21850350"/>
+    <pos x="13392150" y="22612350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1107,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="23698200"/>
+    <pos x="7848600" y="24460200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1127,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="23698200"/>
+    <pos x="9696450" y="24460200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1147,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="23698200"/>
+    <pos x="11544300" y="24460200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1167,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="23698200"/>
+    <pos x="13392150" y="24460200"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1187,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="25546050"/>
+    <pos x="7848600" y="26308050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1207,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="25546050"/>
+    <pos x="9696450" y="26308050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1227,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="25546050"/>
+    <pos x="11544300" y="26308050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1247,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="25546050"/>
+    <pos x="13392150" y="26308050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1267,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="27393900"/>
+    <pos x="7848600" y="28155900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1287,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="27393900"/>
+    <pos x="9696450" y="28155900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1307,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="30448250"/>
+    <pos x="7848600" y="31210250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1327,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="30448250"/>
+    <pos x="9696450" y="31210250"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1347,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="30448250"/>
+    <pos x="11544300" y="31210250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1367,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="30448250"/>
+    <pos x="13392150" y="31210250"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1387,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="32296100"/>
+    <pos x="7848600" y="33058100"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1407,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34778950"/>
+    <pos x="7848600" y="35540950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1427,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="34778950"/>
+    <pos x="9696450" y="35540950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1447,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="34778950"/>
+    <pos x="11544300" y="35540950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1467,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="34778950"/>
+    <pos x="13392150" y="35540950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1487,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="36626800"/>
+    <pos x="7848600" y="37388800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1507,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="36626800"/>
+    <pos x="9696450" y="37388800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1527,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="36626800"/>
+    <pos x="11544300" y="37388800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1547,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="36626800"/>
+    <pos x="13392150" y="37388800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1567,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="38474650"/>
+    <pos x="7848600" y="39236650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1587,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="38474650"/>
+    <pos x="9696450" y="39236650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1607,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="44392850"/>
+    <pos x="7848600" y="45154850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1627,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="44392850"/>
+    <pos x="9696450" y="45154850"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1647,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="44392850"/>
+    <pos x="11544300" y="45154850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1667,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="44392850"/>
+    <pos x="13392150" y="45154850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1687,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="46240700"/>
+    <pos x="7848600" y="47002700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1707,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="52177950"/>
+    <pos x="7848600" y="52939950"/>
     <ext cx="1809750" cy="1209675"/>
     <pic>
       <nvPicPr>
@@ -1727,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="52177950"/>
+    <pos x="9696450" y="52939950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1747,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="52177950"/>
+    <pos x="11544300" y="52939950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1767,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="52177950"/>
+    <pos x="13392150" y="52939950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1787,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="54025800"/>
+    <pos x="7848600" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1807,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="54025800"/>
+    <pos x="9696450" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1827,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="54025800"/>
+    <pos x="11544300" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1847,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="60572650"/>
+    <pos x="7848600" y="61334650"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -1867,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="60572650"/>
+    <pos x="9696450" y="61334650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1887,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="60572650"/>
+    <pos x="11544300" y="61334650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1907,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="60572650"/>
+    <pos x="13392150" y="61334650"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1927,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="62420500"/>
+    <pos x="7848600" y="63182500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1947,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="62420500"/>
+    <pos x="9696450" y="63182500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1967,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="62420500"/>
+    <pos x="11544300" y="63182500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1987,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="62420500"/>
+    <pos x="13392150" y="63182500"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2007,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="64268350"/>
+    <pos x="7848600" y="65030350"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2027,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="64268350"/>
+    <pos x="9696450" y="65030350"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2047,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68154550"/>
+    <pos x="7848600" y="68916550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2067,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68154550"/>
+    <pos x="9696450" y="68916550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2087,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="68154550"/>
+    <pos x="11544300" y="68916550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2107,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="68154550"/>
+    <pos x="13392150" y="68916550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2127,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="78581250"/>
+    <pos x="7848600" y="79343250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2147,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="78581250"/>
+    <pos x="9696450" y="79343250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2167,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="78581250"/>
+    <pos x="11544300" y="79343250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2187,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="78581250"/>
+    <pos x="13392150" y="79343250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2207,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="80429100"/>
+    <pos x="7848600" y="81191100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2227,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="80429100"/>
+    <pos x="9696450" y="81191100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2247,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="80429100"/>
+    <pos x="11544300" y="81191100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2267,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="80429100"/>
+    <pos x="13392150" y="81191100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2287,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="82276950"/>
+    <pos x="7848600" y="83038950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2307,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="82276950"/>
+    <pos x="9696450" y="83038950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2327,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87788750"/>
+    <pos x="7848600" y="88550750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2347,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="87788750"/>
+    <pos x="9696450" y="88550750"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2367,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="87788750"/>
+    <pos x="11544300" y="88550750"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2387,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="87788750"/>
+    <pos x="13392150" y="88550750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2407,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="89636600"/>
+    <pos x="7848600" y="90398600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2427,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="89636600"/>
+    <pos x="9696450" y="90398600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2447,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="89636600"/>
+    <pos x="11544300" y="90398600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2467,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="89636600"/>
+    <pos x="13392150" y="90398600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2487,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="91484450"/>
+    <pos x="7848600" y="92246450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2507,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="91484450"/>
+    <pos x="9696450" y="92246450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2527,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="91484450"/>
+    <pos x="11544300" y="92246450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2547,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="91484450"/>
+    <pos x="13392150" y="92246450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2567,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="96208850"/>
+    <pos x="7848600" y="96970850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2587,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="96208850"/>
+    <pos x="9696450" y="96970850"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -2607,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="96208850"/>
+    <pos x="11544300" y="96970850"/>
     <ext cx="1809750" cy="1552575"/>
     <pic>
       <nvPicPr>
@@ -2627,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="96208850"/>
+    <pos x="13392150" y="96970850"/>
     <ext cx="1809750" cy="571500"/>
     <pic>
       <nvPicPr>
@@ -2647,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="108261150"/>
+    <pos x="7848600" y="109023150"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2667,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="114065050"/>
+    <pos x="7848600" y="114827050"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2687,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="119030750"/>
+    <pos x="7848600" y="119792750"/>
     <ext cx="1238250" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2707,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="125647450"/>
+    <pos x="7848600" y="126409450"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2727,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="131425950"/>
+    <pos x="7848600" y="132187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2747,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="131425950"/>
+    <pos x="9696450" y="132187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2767,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="131425950"/>
+    <pos x="11544300" y="132187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2787,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="131425950"/>
+    <pos x="13392150" y="132187950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2807,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="133273800"/>
+    <pos x="7848600" y="134035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2827,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="133273800"/>
+    <pos x="9696450" y="134035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2847,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="133273800"/>
+    <pos x="11544300" y="134035800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3158,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3206,255 +3219,258 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
     </row>
-    <row r="4" ht="6" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>⚠ 이 제형 배합 주의·기본원칙
+· 바스밤: 베이킹소다+구연산은 습기에 미리 반응 → 건조·밀봉 보관.
+· 스크럽 입자가 거칠면 피부 손상 → 고운 입자 사용.
+· 오일 함유 제품은 욕조 미끄럼 주의.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5" ht="6" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>초코 버블바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>400g</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>미네럴, 소금의 일종, 탄산수소나트륨,삼투압으로 노폐뮬제거, 미네럴공급, 피부를 부드럽게</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="F8" s="10" t="n"/>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>감귤류에서 얻은 과일산, pH조절, 각질연화, 항균</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="96" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="96" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>옥수수에서 얻은 녹말일종, 노폐물흡착, 흡습작용으로 모양이 잘 뭉쳐지게하는 역할</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>카카오분말</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>초콜렛의 원재료,폴리페놀함유</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>초코향</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>8ml</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>초코향,합성향</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>애플계면활성제</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>사과주스에서 순한 계면활성제, 피부자극없음. 생분해율이 아주 높음(이 재료를 빼면 거품은 생기지 않음)</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>코코베타인 등 물비누</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 23 · 계면 3 · 향 1 · 점증/pH 68 · 기타 5</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
     </row>
     <row r="14" ht="14" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 23 · 계면 3 · 향 1 · 점증/pH 68 · 기타 5</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
@@ -3463,8 +3479,20 @@
       <c r="E14" s="18" t="n"/>
       <c r="F14" s="18" t="n"/>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15" ht="14" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="80" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>초콜렛음료 속에 잠기는 기분~음?! 재미있겠죠.
 우리는 '이벤트 목욕탕' 가지 않고서도 집에서 초콜렛목욕을 즐길 수 있을 것 같아요.
@@ -3474,20 +3502,20 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17" ht="14" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-    </row>
-    <row r="17" ht="384" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="384" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 먼저 계량한다. 덩어리지는 경우가 많아 특별히 베이킹소다만 체에 친다. 덩어리는 문질러주세요.
 3-4.나머지 구연산, 옥수수전분, 카카오분말, 초코향을 넣고 골고루 비비면서 섞어주세요.
@@ -3504,231 +3532,219 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="64" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>도쿄워커는 “진짜 초콜릿이 들어간 목욕탕”이라며 “초콜릿 속에 있는 폴리페놀은 혈액 촉진과 노폐물 배출 효과가 있고 또 셀룰라이트(울퉁붕툴해 보이는 피하 지방) 분해 효과도 기대할 수 있다”고 설명했다.
 [국민일보 쿠키뉴스 신은정 기자]</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="6" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="64" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C22" s="21" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n"/>
-    </row>
-    <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="F23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E23" s="20" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="F23" s="20" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+    <row r="25" ht="96" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="F24" s="20" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C25" s="21" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C26" s="21" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="F26" s="20" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
     </row>
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>— 만들기 —</t>
+          <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
         </is>
       </c>
       <c r="B28" s="18" t="n"/>
@@ -3737,8 +3753,20 @@
       <c r="E28" s="18" t="n"/>
       <c r="F28" s="18" t="n"/>
     </row>
-    <row r="29" ht="288" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>— 만들기 —</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+    </row>
+    <row r="30" ht="288" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -3757,325 +3785,313 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="24" t="n"/>
-      <c r="E29" s="24" t="n"/>
-      <c r="F29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="118.5" customHeight="1">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="24" t="n"/>
-      <c r="F30" s="24" t="n"/>
-    </row>
-    <row r="31" ht="6" customHeight="1"/>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+    </row>
+    <row r="31" ht="118.5" customHeight="1">
+      <c r="A31" s="26" t="n"/>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="26" t="n"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+      <c r="F33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>코치닐+물</t>
         </is>
       </c>
-      <c r="B34" s="8" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>1g+3g</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D35" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="E35" s="10" t="inlineStr">
         <is>
           <t>반드시 양조절해서 / 색내기에 사용하세요.</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>원하는 색</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D35" s="10" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="F36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>주석산</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n"/>
-    </row>
-    <row r="37" ht="96" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="F37" s="10" t="n"/>
+    </row>
+    <row r="38" ht="96" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="32" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D39" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>코코넛유래, / 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n"/>
-    </row>
-    <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="F39" s="10" t="n"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
         <is>
           <t>애플 / 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="80" customHeight="1">
-      <c r="A40" s="8" t="inlineStr">
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D40" s="25" t="inlineStr">
+      <c r="D41" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
     </row>
     <row r="43" ht="14" customHeight="1">
       <c r="A43" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
         </is>
       </c>
       <c r="B43" s="18" t="n"/>
@@ -4084,8 +4100,20 @@
       <c r="E43" s="18" t="n"/>
       <c r="F43" s="18" t="n"/>
     </row>
-    <row r="44" ht="96" customHeight="1">
+    <row r="44" ht="14" customHeight="1">
       <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="20" t="n"/>
+      <c r="F44" s="20" t="n"/>
+    </row>
+    <row r="45" ht="96" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -4096,20 +4124,20 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="46" ht="14" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-    </row>
-    <row r="46" ht="192" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="B46" s="20" t="n"/>
+      <c r="C46" s="20" t="n"/>
+      <c r="D46" s="20" t="n"/>
+      <c r="E46" s="20" t="n"/>
+      <c r="F46" s="20" t="n"/>
+    </row>
+    <row r="47" ht="192" customHeight="1">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -4126,95 +4154,83 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="6" customHeight="1"/>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="48" ht="6" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B48" s="6" t="n"/>
-      <c r="C48" s="6" t="n"/>
-      <c r="D48" s="6" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="B49" s="8" t="n"/>
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="8" t="n"/>
+      <c r="F49" s="8" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D49" s="7" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B51" s="22" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C50" s="21" t="inlineStr">
+      <c r="C51" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E50" s="20" t="inlineStr">
+      <c r="E51" s="22" t="inlineStr">
         <is>
           <t>풍부한 미네랄, / 노폐물제거</t>
         </is>
       </c>
-      <c r="F50" s="20" t="n"/>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 100</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="F51" s="22" t="n"/>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 100</t>
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
@@ -4223,8 +4239,20 @@
       <c r="E52" s="18" t="n"/>
       <c r="F52" s="18" t="n"/>
     </row>
-    <row r="53" ht="176" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="20" t="n"/>
+      <c r="D53" s="20" t="n"/>
+      <c r="E53" s="20" t="n"/>
+      <c r="F53" s="20" t="n"/>
+    </row>
+    <row r="54" ht="176" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -4239,26 +4267,26 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B53" s="24" t="n"/>
-      <c r="C53" s="24" t="n"/>
-      <c r="D53" s="24" t="n"/>
-      <c r="E53" s="24" t="n"/>
-      <c r="F53" s="24" t="n"/>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="B54" s="26" t="n"/>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="26" t="n"/>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="26" t="n"/>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B54" s="18" t="n"/>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-    </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+    </row>
+    <row r="56" ht="64" customHeight="1">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -4266,225 +4294,213 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B55" s="24" t="n"/>
-      <c r="C55" s="24" t="n"/>
-      <c r="D55" s="24" t="n"/>
-      <c r="E55" s="24" t="n"/>
-      <c r="F55" s="24" t="n"/>
-    </row>
-    <row r="56" ht="6" customHeight="1"/>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="B56" s="26" t="n"/>
+      <c r="C56" s="26" t="n"/>
+      <c r="D56" s="26" t="n"/>
+      <c r="E56" s="26" t="n"/>
+      <c r="F56" s="26" t="n"/>
+    </row>
+    <row r="57" ht="6" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B57" s="6" t="n"/>
-      <c r="C57" s="6" t="n"/>
-      <c r="D57" s="6" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="6" t="n"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="B58" s="8" t="n"/>
+      <c r="C58" s="8" t="n"/>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="8" t="n"/>
+      <c r="F58" s="8" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B58" s="7" t="inlineStr">
+      <c r="B59" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
+      <c r="F59" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="8" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D59" s="10" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E60" s="10" t="inlineStr">
         <is>
           <t>탄산수소나트륨 / , 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="F59" s="8" t="n"/>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="8" t="inlineStr">
+      <c r="F60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B60" s="8" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D60" s="10" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F60" s="8" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="96" customHeight="1">
-      <c r="A61" s="8" t="inlineStr">
+    <row r="62" ht="96" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B61" s="8" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="F61" s="8" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B62" s="8" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F62" s="8" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴, / 철함유로 자체 / 핑크색, / 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="F63" s="8" t="n"/>
-    </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="16" t="n"/>
-      <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
+      <c r="F64" s="10" t="n"/>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
         </is>
       </c>
       <c r="B65" s="18" t="n"/>
@@ -4493,8 +4509,20 @@
       <c r="E65" s="18" t="n"/>
       <c r="F65" s="18" t="n"/>
     </row>
-    <row r="66" ht="240" customHeight="1">
+    <row r="66" ht="14" customHeight="1">
       <c r="A66" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="20" t="n"/>
+      <c r="F66" s="20" t="n"/>
+    </row>
+    <row r="67" ht="240" customHeight="1">
+      <c r="A67" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -4514,20 +4542,20 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B67" s="18" t="n"/>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-    </row>
-    <row r="68" ht="208" customHeight="1">
-      <c r="A68" s="19" t="inlineStr">
+      <c r="B68" s="20" t="n"/>
+      <c r="C68" s="20" t="n"/>
+      <c r="D68" s="20" t="n"/>
+      <c r="E68" s="20" t="n"/>
+      <c r="F68" s="20" t="n"/>
+    </row>
+    <row r="69" ht="208" customHeight="1">
+      <c r="A69" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -4542,95 +4570,83 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+    <row r="70" ht="6" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+      <c r="B71" s="8" t="n"/>
+      <c r="C71" s="8" t="n"/>
+      <c r="D71" s="8" t="n"/>
+      <c r="E71" s="8" t="n"/>
+      <c r="F71" s="8" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B72" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="20" t="inlineStr">
+    <row r="73" ht="32" customHeight="1">
+      <c r="A73" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B73" s="22" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C72" s="21" t="inlineStr">
+      <c r="C73" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
+      <c r="D73" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E72" s="20" t="inlineStr">
+      <c r="E73" s="22" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="F72" s="20" t="n"/>
-    </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  기타 100</t>
-        </is>
-      </c>
-      <c r="B73" s="16" t="n"/>
-      <c r="C73" s="16" t="n"/>
-      <c r="D73" s="16" t="n"/>
-      <c r="E73" s="16" t="n"/>
-      <c r="F73" s="16" t="n"/>
+      <c r="F73" s="22" t="n"/>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  기타 100</t>
         </is>
       </c>
       <c r="B74" s="18" t="n"/>
@@ -4639,8 +4655,20 @@
       <c r="E74" s="18" t="n"/>
       <c r="F74" s="18" t="n"/>
     </row>
-    <row r="75" ht="384" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B75" s="20" t="n"/>
+      <c r="C75" s="20" t="n"/>
+      <c r="D75" s="20" t="n"/>
+      <c r="E75" s="20" t="n"/>
+      <c r="F75" s="20" t="n"/>
+    </row>
+    <row r="76" ht="384" customHeight="1">
+      <c r="A76" s="25" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -4668,39 +4696,39 @@
 다양한</t>
         </is>
       </c>
-      <c r="B75" s="24" t="n"/>
-      <c r="C75" s="24" t="n"/>
-      <c r="D75" s="24" t="n"/>
-      <c r="E75" s="24" t="n"/>
-      <c r="F75" s="24" t="n"/>
-    </row>
-    <row r="76" ht="32" customHeight="1">
-      <c r="A76" s="23" t="inlineStr">
+      <c r="B76" s="26" t="n"/>
+      <c r="C76" s="26" t="n"/>
+      <c r="D76" s="26" t="n"/>
+      <c r="E76" s="26" t="n"/>
+      <c r="F76" s="26" t="n"/>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>아로마오일을 히말라야 핑크소금에 배합해
 아로마테리피 효과도 함께 누리세요.</t>
         </is>
       </c>
-      <c r="B76" s="24" t="n"/>
-      <c r="C76" s="24" t="n"/>
-      <c r="D76" s="24" t="n"/>
-      <c r="E76" s="24" t="n"/>
-      <c r="F76" s="24" t="n"/>
-    </row>
-    <row r="77" ht="14" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="B77" s="26" t="n"/>
+      <c r="C77" s="26" t="n"/>
+      <c r="D77" s="26" t="n"/>
+      <c r="E77" s="26" t="n"/>
+      <c r="F77" s="26" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B77" s="18" t="n"/>
-      <c r="C77" s="18" t="n"/>
-      <c r="D77" s="18" t="n"/>
-      <c r="E77" s="18" t="n"/>
-      <c r="F77" s="18" t="n"/>
-    </row>
-    <row r="78" ht="80" customHeight="1">
-      <c r="A78" s="23" t="inlineStr">
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+    </row>
+    <row r="79" ht="80" customHeight="1">
+      <c r="A79" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -4709,193 +4737,181 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B78" s="24" t="n"/>
-      <c r="C78" s="24" t="n"/>
-      <c r="D78" s="24" t="n"/>
-      <c r="E78" s="24" t="n"/>
-      <c r="F78" s="24" t="n"/>
-    </row>
-    <row r="79" ht="6" customHeight="1"/>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="B79" s="26" t="n"/>
+      <c r="C79" s="26" t="n"/>
+      <c r="D79" s="26" t="n"/>
+      <c r="E79" s="26" t="n"/>
+      <c r="F79" s="26" t="n"/>
+    </row>
+    <row r="80" ht="6" customHeight="1"/>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="B81" s="8" t="n"/>
+      <c r="C81" s="8" t="n"/>
+      <c r="D81" s="8" t="n"/>
+      <c r="E81" s="8" t="n"/>
+      <c r="F81" s="8" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B82" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C81" s="7" t="inlineStr">
+      <c r="C82" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D81" s="7" t="inlineStr">
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr">
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="64" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B83" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="11" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D83" s="28" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E83" s="10" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨, / 산소금=암염, 수분함량 적고 / 미네럴 풍부, / 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="48" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+      <c r="F83" s="10" t="n"/>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D84" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="85" ht="32" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D84" s="12" t="inlineStr">
+      <c r="D85" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>입,족욕용 또는 / 바디 마사지/ 스크럽 겸용</t>
         </is>
       </c>
-      <c r="F84" s="8" t="n"/>
-    </row>
-    <row r="85" ht="64" customHeight="1">
-      <c r="A85" s="8" t="inlineStr">
+      <c r="F85" s="10" t="n"/>
+    </row>
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C85" s="9" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D85" s="13" t="inlineStr">
+      <c r="D86" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr">
         <is>
           <t>원하는 / 아로마오일</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
-        </is>
-      </c>
-      <c r="B86" s="16" t="n"/>
-      <c r="C86" s="16" t="n"/>
-      <c r="D86" s="16" t="n"/>
-      <c r="E86" s="16" t="n"/>
-      <c r="F86" s="16" t="n"/>
     </row>
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
         </is>
       </c>
       <c r="B87" s="18" t="n"/>
@@ -4904,8 +4920,20 @@
       <c r="E87" s="18" t="n"/>
       <c r="F87" s="18" t="n"/>
     </row>
-    <row r="88" ht="256" customHeight="1">
+    <row r="88" ht="14" customHeight="1">
       <c r="A88" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B88" s="20" t="n"/>
+      <c r="C88" s="20" t="n"/>
+      <c r="D88" s="20" t="n"/>
+      <c r="E88" s="20" t="n"/>
+      <c r="F88" s="20" t="n"/>
+    </row>
+    <row r="89" ht="256" customHeight="1">
+      <c r="A89" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4926,20 +4954,20 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B89" s="18" t="n"/>
-      <c r="C89" s="18" t="n"/>
-      <c r="D89" s="18" t="n"/>
-      <c r="E89" s="18" t="n"/>
-      <c r="F89" s="18" t="n"/>
-    </row>
-    <row r="90" ht="112" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
+      <c r="B90" s="20" t="n"/>
+      <c r="C90" s="20" t="n"/>
+      <c r="D90" s="20" t="n"/>
+      <c r="E90" s="20" t="n"/>
+      <c r="F90" s="20" t="n"/>
+    </row>
+    <row r="91" ht="112" customHeight="1">
+      <c r="A91" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -4951,191 +4979,179 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="92" ht="6" customHeight="1"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B94" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C94" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D94" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E93" s="7" t="inlineStr">
+      <c r="E94" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="F94" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="48" customHeight="1">
-      <c r="A94" s="20" t="inlineStr">
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="22" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B94" s="20" t="inlineStr">
+      <c r="B95" s="22" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C94" s="21" t="inlineStr">
+      <c r="C95" s="23" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E94" s="20" t="inlineStr">
+      <c r="E95" s="22" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="F94" s="20" t="n"/>
-    </row>
-    <row r="95" ht="32" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
+      <c r="F95" s="22" t="n"/>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="A96" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B96" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C95" s="21" t="inlineStr">
+      <c r="C96" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E95" s="20" t="inlineStr">
+      <c r="E96" s="22" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="F95" s="20" t="inlineStr">
+      <c r="F96" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="96" customHeight="1">
-      <c r="A96" s="20" t="inlineStr">
+    <row r="97" ht="96" customHeight="1">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B96" s="20" t="inlineStr">
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C96" s="21" t="inlineStr">
+      <c r="C97" s="23" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D96" s="10" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E96" s="20" t="inlineStr">
+      <c r="E97" s="22" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F96" s="20" t="inlineStr">
+      <c r="F97" s="22" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="80" customHeight="1">
-      <c r="A97" s="20" t="inlineStr">
+    <row r="98" ht="80" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B97" s="20" t="inlineStr">
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C97" s="21" t="inlineStr">
+      <c r="C98" s="23" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D97" s="13" t="inlineStr">
+      <c r="D98" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E97" s="20" t="inlineStr">
+      <c r="E98" s="22" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F97" s="20" t="inlineStr">
+      <c r="F98" s="22" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
-        </is>
-      </c>
-      <c r="B98" s="16" t="n"/>
-      <c r="C98" s="16" t="n"/>
-      <c r="D98" s="16" t="n"/>
-      <c r="E98" s="16" t="n"/>
-      <c r="F98" s="16" t="n"/>
     </row>
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
         </is>
       </c>
       <c r="B99" s="18" t="n"/>
@@ -5144,8 +5160,20 @@
       <c r="E99" s="18" t="n"/>
       <c r="F99" s="18" t="n"/>
     </row>
-    <row r="100" ht="64" customHeight="1">
-      <c r="A100" s="23" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B100" s="20" t="n"/>
+      <c r="C100" s="20" t="n"/>
+      <c r="D100" s="20" t="n"/>
+      <c r="E100" s="20" t="n"/>
+      <c r="F100" s="20" t="n"/>
+    </row>
+    <row r="101" ht="64" customHeight="1">
+      <c r="A101" s="25" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -5153,26 +5181,26 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B100" s="24" t="n"/>
-      <c r="C100" s="24" t="n"/>
-      <c r="D100" s="24" t="n"/>
-      <c r="E100" s="24" t="n"/>
-      <c r="F100" s="24" t="n"/>
-    </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="B101" s="26" t="n"/>
+      <c r="C101" s="26" t="n"/>
+      <c r="D101" s="26" t="n"/>
+      <c r="E101" s="26" t="n"/>
+      <c r="F101" s="26" t="n"/>
+    </row>
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B101" s="18" t="n"/>
-      <c r="C101" s="18" t="n"/>
-      <c r="D101" s="18" t="n"/>
-      <c r="E101" s="18" t="n"/>
-      <c r="F101" s="18" t="n"/>
-    </row>
-    <row r="102" ht="192" customHeight="1">
-      <c r="A102" s="23" t="inlineStr">
+      <c r="B102" s="20" t="n"/>
+      <c r="C102" s="20" t="n"/>
+      <c r="D102" s="20" t="n"/>
+      <c r="E102" s="20" t="n"/>
+      <c r="F102" s="20" t="n"/>
+    </row>
+    <row r="103" ht="192" customHeight="1">
+      <c r="A103" s="25" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -5187,161 +5215,149 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B102" s="24" t="n"/>
-      <c r="C102" s="24" t="n"/>
-      <c r="D102" s="24" t="n"/>
-      <c r="E102" s="24" t="n"/>
-      <c r="F102" s="24" t="n"/>
-    </row>
-    <row r="103" ht="6" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="5" t="inlineStr">
+      <c r="B103" s="26" t="n"/>
+      <c r="C103" s="26" t="n"/>
+      <c r="D103" s="26" t="n"/>
+      <c r="E103" s="26" t="n"/>
+      <c r="F103" s="26" t="n"/>
+    </row>
+    <row r="104" ht="6" customHeight="1"/>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="B105" s="8" t="n"/>
+      <c r="C105" s="8" t="n"/>
+      <c r="D105" s="8" t="n"/>
+      <c r="E105" s="8" t="n"/>
+      <c r="F105" s="8" t="n"/>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B106" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C106" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D106" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E105" s="7" t="inlineStr">
+      <c r="E106" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
+      <c r="F106" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+    <row r="107" ht="32" customHeight="1">
+      <c r="A107" s="10" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B107" s="10" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C107" s="11" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D106" s="12" t="inlineStr">
+      <c r="D107" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E107" s="10" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F106" s="8" t="n"/>
-    </row>
-    <row r="107" ht="48" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+      <c r="F107" s="10" t="n"/>
+    </row>
+    <row r="108" ht="48" customHeight="1">
+      <c r="A108" s="10" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B108" s="10" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C108" s="11" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D107" s="25" t="inlineStr">
+      <c r="D108" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E108" s="10" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 / 시어버터, 아보카도, 꿀추출물 등 / 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="F107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="80" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+      <c r="F108" s="10" t="n"/>
+    </row>
+    <row r="109" ht="80" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D108" s="13" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>아로마테라피 / 여드름-티트리, / 바디 용도별 추천오일 / -쿨링 :페파민트, / -다이어트 : 레몬+자몽오일 / -이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="F108" s="8" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
-    </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
-        </is>
-      </c>
-      <c r="B109" s="16" t="n"/>
-      <c r="C109" s="16" t="n"/>
-      <c r="D109" s="16" t="n"/>
-      <c r="E109" s="16" t="n"/>
-      <c r="F109" s="16" t="n"/>
     </row>
     <row r="110" ht="14" customHeight="1">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
         </is>
       </c>
       <c r="B110" s="18" t="n"/>
@@ -5350,8 +5366,20 @@
       <c r="E110" s="18" t="n"/>
       <c r="F110" s="18" t="n"/>
     </row>
-    <row r="111" ht="384" customHeight="1">
+    <row r="111" ht="14" customHeight="1">
       <c r="A111" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B111" s="20" t="n"/>
+      <c r="C111" s="20" t="n"/>
+      <c r="D111" s="20" t="n"/>
+      <c r="E111" s="20" t="n"/>
+      <c r="F111" s="20" t="n"/>
+    </row>
+    <row r="112" ht="384" customHeight="1">
+      <c r="A112" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5380,8 +5408,8 @@
         </is>
       </c>
     </row>
-    <row r="112" ht="112" customHeight="1">
-      <c r="A112" s="19" t="inlineStr">
+    <row r="113" ht="112" customHeight="1">
+      <c r="A113" s="21" t="inlineStr">
         <is>
           <t>알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
@@ -5393,20 +5421,20 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="17" t="inlineStr">
+    <row r="114" ht="14" customHeight="1">
+      <c r="A114" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B113" s="18" t="n"/>
-      <c r="C113" s="18" t="n"/>
-      <c r="D113" s="18" t="n"/>
-      <c r="E113" s="18" t="n"/>
-      <c r="F113" s="18" t="n"/>
-    </row>
-    <row r="114" ht="80" customHeight="1">
-      <c r="A114" s="19" t="inlineStr">
+      <c r="B114" s="20" t="n"/>
+      <c r="C114" s="20" t="n"/>
+      <c r="D114" s="20" t="n"/>
+      <c r="E114" s="20" t="n"/>
+      <c r="F114" s="20" t="n"/>
+    </row>
+    <row r="115" ht="80" customHeight="1">
+      <c r="A115" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -5416,251 +5444,239 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="6" customHeight="1"/>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="5" t="inlineStr">
+    <row r="116" ht="6" customHeight="1"/>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="7" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+      <c r="B117" s="8" t="n"/>
+      <c r="C117" s="8" t="n"/>
+      <c r="D117" s="8" t="n"/>
+      <c r="E117" s="8" t="n"/>
+      <c r="F117" s="8" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B118" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C117" s="7" t="inlineStr">
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D118" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E118" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
+      <c r="F118" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="20" t="inlineStr">
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="22" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B118" s="20" t="inlineStr">
+      <c r="B119" s="22" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C118" s="21" t="inlineStr">
+      <c r="C119" s="23" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D118" s="10" t="inlineStr">
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E118" s="20" t="inlineStr">
+      <c r="E119" s="22" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F118" s="20" t="n"/>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="20" t="inlineStr">
+      <c r="F119" s="22" t="n"/>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B119" s="20" t="inlineStr">
+      <c r="B120" s="22" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C119" s="21" t="inlineStr">
+      <c r="C120" s="23" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D119" s="10" t="inlineStr">
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E119" s="20" t="inlineStr">
+      <c r="E120" s="22" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F119" s="20" t="inlineStr">
+      <c r="F120" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="96" customHeight="1">
-      <c r="A120" s="20" t="inlineStr">
+    <row r="121" ht="96" customHeight="1">
+      <c r="A121" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B120" s="20" t="inlineStr">
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C120" s="21" t="inlineStr">
+      <c r="C121" s="23" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D121" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E120" s="20" t="inlineStr">
+      <c r="E121" s="22" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F120" s="20" t="inlineStr">
+      <c r="F121" s="22" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="20" t="inlineStr">
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="22" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B121" s="20" t="inlineStr">
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
+      <c r="C122" s="23" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D121" s="14" t="inlineStr">
+      <c r="D122" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E121" s="20" t="inlineStr">
+      <c r="E122" s="22" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F121" s="20" t="n"/>
-    </row>
-    <row r="122" ht="32" customHeight="1">
-      <c r="A122" s="20" t="inlineStr">
+      <c r="F122" s="22" t="n"/>
+    </row>
+    <row r="123" ht="32" customHeight="1">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B122" s="20" t="inlineStr">
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C122" s="21" t="inlineStr">
+      <c r="C123" s="23" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D122" s="25" t="inlineStr">
+      <c r="D123" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E122" s="20" t="inlineStr">
+      <c r="E123" s="22" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="F122" s="20" t="inlineStr">
+      <c r="F123" s="22" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="64" customHeight="1">
-      <c r="A123" s="20" t="inlineStr">
+    <row r="124" ht="64" customHeight="1">
+      <c r="A124" s="22" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B123" s="20" t="inlineStr">
+      <c r="B124" s="22" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
+      <c r="C124" s="23" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D124" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E123" s="20" t="inlineStr">
+      <c r="E124" s="22" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="F123" s="20" t="inlineStr">
+      <c r="F124" s="22" t="inlineStr">
         <is>
           <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
         </is>
       </c>
-    </row>
-    <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
-        </is>
-      </c>
-      <c r="B124" s="16" t="n"/>
-      <c r="C124" s="16" t="n"/>
-      <c r="D124" s="16" t="n"/>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="16" t="n"/>
     </row>
     <row r="125" ht="14" customHeight="1">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
         </is>
       </c>
       <c r="B125" s="18" t="n"/>
@@ -5669,8 +5685,20 @@
       <c r="E125" s="18" t="n"/>
       <c r="F125" s="18" t="n"/>
     </row>
-    <row r="126" ht="224" customHeight="1">
-      <c r="A126" s="23" t="inlineStr">
+    <row r="126" ht="14" customHeight="1">
+      <c r="A126" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B126" s="20" t="n"/>
+      <c r="C126" s="20" t="n"/>
+      <c r="D126" s="20" t="n"/>
+      <c r="E126" s="20" t="n"/>
+      <c r="F126" s="20" t="n"/>
+    </row>
+    <row r="127" ht="224" customHeight="1">
+      <c r="A127" s="25" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -5688,26 +5716,26 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B126" s="24" t="n"/>
-      <c r="C126" s="24" t="n"/>
-      <c r="D126" s="24" t="n"/>
-      <c r="E126" s="24" t="n"/>
-      <c r="F126" s="24" t="n"/>
-    </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="17" t="inlineStr">
+      <c r="B127" s="26" t="n"/>
+      <c r="C127" s="26" t="n"/>
+      <c r="D127" s="26" t="n"/>
+      <c r="E127" s="26" t="n"/>
+      <c r="F127" s="26" t="n"/>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-    </row>
-    <row r="128" ht="160" customHeight="1">
-      <c r="A128" s="23" t="inlineStr">
+      <c r="B128" s="20" t="n"/>
+      <c r="C128" s="20" t="n"/>
+      <c r="D128" s="20" t="n"/>
+      <c r="E128" s="20" t="n"/>
+      <c r="F128" s="20" t="n"/>
+    </row>
+    <row r="129" ht="160" customHeight="1">
+      <c r="A129" s="25" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -5721,289 +5749,277 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B128" s="24" t="n"/>
-      <c r="C128" s="24" t="n"/>
-      <c r="D128" s="24" t="n"/>
-      <c r="E128" s="24" t="n"/>
-      <c r="F128" s="24" t="n"/>
-    </row>
-    <row r="129" ht="6" customHeight="1"/>
-    <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
+      <c r="B129" s="26" t="n"/>
+      <c r="C129" s="26" t="n"/>
+      <c r="D129" s="26" t="n"/>
+      <c r="E129" s="26" t="n"/>
+      <c r="F129" s="26" t="n"/>
+    </row>
+    <row r="130" ht="6" customHeight="1"/>
+    <row r="131" ht="22" customHeight="1">
+      <c r="A131" s="7" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B130" s="6" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
-    </row>
-    <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="B131" s="8" t="n"/>
+      <c r="C131" s="8" t="n"/>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="8" t="n"/>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="15" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="B132" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C131" s="7" t="inlineStr">
+      <c r="C132" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D131" s="7" t="inlineStr">
+      <c r="D132" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E131" s="7" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F131" s="7" t="inlineStr">
+      <c r="F132" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="8" t="inlineStr">
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="10" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B132" s="8" t="inlineStr">
+      <c r="B133" s="10" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C133" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D132" s="25" t="inlineStr">
+      <c r="D133" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E132" s="8" t="inlineStr">
+      <c r="E133" s="10" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="F132" s="8" t="inlineStr">
+      <c r="F133" s="10" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="32" customHeight="1">
-      <c r="A133" s="8" t="inlineStr">
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="10" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B133" s="8" t="inlineStr">
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C133" s="9" t="inlineStr">
+      <c r="C134" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D133" s="25" t="inlineStr">
+      <c r="D134" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
+      <c r="E134" s="10" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="F133" s="8" t="inlineStr">
+      <c r="F134" s="10" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="48" customHeight="1">
-      <c r="A134" s="8" t="inlineStr">
+    <row r="135" ht="48" customHeight="1">
+      <c r="A135" s="10" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B134" s="8" t="inlineStr">
+      <c r="B135" s="10" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C135" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D134" s="27" t="inlineStr">
+      <c r="D135" s="29" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E134" s="8" t="inlineStr">
+      <c r="E135" s="10" t="inlineStr">
         <is>
           <t>에코인증, 물과 오일의 분리를 저지</t>
         </is>
       </c>
-      <c r="F134" s="8" t="inlineStr">
+      <c r="F135" s="10" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="64" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="136" ht="64" customHeight="1">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>순한 (샴푸) / 베이스</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>38g</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="D135" s="14" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E135" s="8" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
         <is>
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+      <c r="F136" s="10" t="n"/>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>13g</t>
         </is>
       </c>
-      <c r="C136" s="9" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D136" s="22" t="inlineStr">
+      <c r="D137" s="24" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E136" s="8" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="F136" s="8" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>꿀 등</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="48" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="10" t="inlineStr">
         <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B138" s="10" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C137" s="9" t="inlineStr">
+      <c r="C138" s="11" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D137" s="12" t="inlineStr">
+      <c r="D138" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E137" s="8" t="inlineStr">
+      <c r="E138" s="10" t="inlineStr">
         <is>
           <t>각질제거, 보습. / 필요에 따라 양을 더 넣어서 / 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="F137" s="8" t="n"/>
-    </row>
-    <row r="138" ht="32" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+      <c r="F138" s="10" t="n"/>
+    </row>
+    <row r="139" ht="32" customHeight="1">
+      <c r="A139" s="10" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B139" s="10" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C138" s="9" t="inlineStr">
+      <c r="C139" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D138" s="13" t="inlineStr">
+      <c r="D139" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E138" s="8" t="inlineStr">
+      <c r="E139" s="10" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F138" s="8" t="inlineStr">
+      <c r="F139" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
-    </row>
-    <row r="139" ht="14" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
-        </is>
-      </c>
-      <c r="B139" s="16" t="n"/>
-      <c r="C139" s="16" t="n"/>
-      <c r="D139" s="16" t="n"/>
-      <c r="E139" s="16" t="n"/>
-      <c r="F139" s="16" t="n"/>
     </row>
     <row r="140" ht="14" customHeight="1">
       <c r="A140" s="17" t="inlineStr">
         <is>
-          <t>— 만들기 —</t>
+          <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
         </is>
       </c>
       <c r="B140" s="18" t="n"/>
@@ -6012,8 +6028,20 @@
       <c r="E140" s="18" t="n"/>
       <c r="F140" s="18" t="n"/>
     </row>
-    <row r="141" ht="336" customHeight="1">
+    <row r="141" ht="14" customHeight="1">
       <c r="A141" s="19" t="inlineStr">
+        <is>
+          <t>— 만들기 —</t>
+        </is>
+      </c>
+      <c r="B141" s="20" t="n"/>
+      <c r="C141" s="20" t="n"/>
+      <c r="D141" s="20" t="n"/>
+      <c r="E141" s="20" t="n"/>
+      <c r="F141" s="20" t="n"/>
+    </row>
+    <row r="142" ht="336" customHeight="1">
+      <c r="A142" s="21" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -6039,131 +6067,119 @@
         </is>
       </c>
     </row>
-    <row r="142" ht="6" customHeight="1"/>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="5" t="inlineStr">
+    <row r="143" ht="6" customHeight="1"/>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="7" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B143" s="6" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6" t="n"/>
-      <c r="E143" s="6" t="n"/>
-      <c r="F143" s="6" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+      <c r="B144" s="8" t="n"/>
+      <c r="C144" s="8" t="n"/>
+      <c r="D144" s="8" t="n"/>
+      <c r="E144" s="8" t="n"/>
+      <c r="F144" s="8" t="n"/>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B144" s="7" t="inlineStr">
+      <c r="B145" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C144" s="7" t="inlineStr">
+      <c r="C145" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D144" s="7" t="inlineStr">
+      <c r="D145" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E144" s="7" t="inlineStr">
+      <c r="E145" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F144" s="7" t="inlineStr">
+      <c r="F145" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="64" customHeight="1">
-      <c r="A145" s="20" t="inlineStr">
+    <row r="146" ht="64" customHeight="1">
+      <c r="A146" s="22" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B145" s="20" t="inlineStr">
+      <c r="B146" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C145" s="21" t="inlineStr">
+      <c r="C146" s="23" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="D145" s="25" t="inlineStr">
+      <c r="D146" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E145" s="20" t="inlineStr">
+      <c r="E146" s="22" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
         </is>
       </c>
-      <c r="F145" s="20" t="inlineStr">
+      <c r="F146" s="22" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="48" customHeight="1">
-      <c r="A146" s="20" t="inlineStr">
+    <row r="147" ht="48" customHeight="1">
+      <c r="A147" s="22" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B146" s="20" t="inlineStr">
+      <c r="B147" s="22" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C146" s="21" t="inlineStr">
+      <c r="C147" s="23" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="D146" s="13" t="inlineStr">
+      <c r="D147" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E146" s="20" t="inlineStr">
+      <c r="E147" s="22" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 / 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="F146" s="20" t="inlineStr">
+      <c r="F147" s="22" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 48 · 향 52</t>
-        </is>
-      </c>
-      <c r="B147" s="16" t="n"/>
-      <c r="C147" s="16" t="n"/>
-      <c r="D147" s="16" t="n"/>
-      <c r="E147" s="16" t="n"/>
-      <c r="F147" s="16" t="n"/>
     </row>
     <row r="148" ht="14" customHeight="1">
       <c r="A148" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 48 · 향 52</t>
         </is>
       </c>
       <c r="B148" s="18" t="n"/>
@@ -6172,8 +6188,20 @@
       <c r="E148" s="18" t="n"/>
       <c r="F148" s="18" t="n"/>
     </row>
-    <row r="149" ht="384" customHeight="1">
-      <c r="A149" s="23" t="inlineStr">
+    <row r="149" ht="14" customHeight="1">
+      <c r="A149" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B149" s="20" t="n"/>
+      <c r="C149" s="20" t="n"/>
+      <c r="D149" s="20" t="n"/>
+      <c r="E149" s="20" t="n"/>
+      <c r="F149" s="20" t="n"/>
+    </row>
+    <row r="150" ht="384" customHeight="1">
+      <c r="A150" s="25" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -6201,40 +6229,40 @@
 항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
         </is>
       </c>
-      <c r="B149" s="24" t="n"/>
-      <c r="C149" s="24" t="n"/>
-      <c r="D149" s="24" t="n"/>
-      <c r="E149" s="24" t="n"/>
-      <c r="F149" s="24" t="n"/>
-    </row>
-    <row r="150" ht="48" customHeight="1">
-      <c r="A150" s="23" t="inlineStr">
+      <c r="B150" s="26" t="n"/>
+      <c r="C150" s="26" t="n"/>
+      <c r="D150" s="26" t="n"/>
+      <c r="E150" s="26" t="n"/>
+      <c r="F150" s="26" t="n"/>
+    </row>
+    <row r="151" ht="48" customHeight="1">
+      <c r="A151" s="25" t="inlineStr">
         <is>
           <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B150" s="24" t="n"/>
-      <c r="C150" s="24" t="n"/>
-      <c r="D150" s="24" t="n"/>
-      <c r="E150" s="24" t="n"/>
-      <c r="F150" s="24" t="n"/>
-    </row>
-    <row r="151" ht="14" customHeight="1">
-      <c r="A151" s="17" t="inlineStr">
+      <c r="B151" s="26" t="n"/>
+      <c r="C151" s="26" t="n"/>
+      <c r="D151" s="26" t="n"/>
+      <c r="E151" s="26" t="n"/>
+      <c r="F151" s="26" t="n"/>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B151" s="18" t="n"/>
-      <c r="C151" s="18" t="n"/>
-      <c r="D151" s="18" t="n"/>
-      <c r="E151" s="18" t="n"/>
-      <c r="F151" s="18" t="n"/>
-    </row>
-    <row r="152" ht="320" customHeight="1">
-      <c r="A152" s="23" t="inlineStr">
+      <c r="B152" s="20" t="n"/>
+      <c r="C152" s="20" t="n"/>
+      <c r="D152" s="20" t="n"/>
+      <c r="E152" s="20" t="n"/>
+      <c r="F152" s="20" t="n"/>
+    </row>
+    <row r="153" ht="320" customHeight="1">
+      <c r="A153" s="25" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -6258,175 +6286,175 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B152" s="24" t="n"/>
-      <c r="C152" s="24" t="n"/>
-      <c r="D152" s="24" t="n"/>
-      <c r="E152" s="24" t="n"/>
-      <c r="F152" s="24" t="n"/>
-    </row>
-    <row r="153" ht="6" customHeight="1"/>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="5" t="inlineStr">
+      <c r="B153" s="26" t="n"/>
+      <c r="C153" s="26" t="n"/>
+      <c r="D153" s="26" t="n"/>
+      <c r="E153" s="26" t="n"/>
+      <c r="F153" s="26" t="n"/>
+    </row>
+    <row r="154" ht="6" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
+      <c r="B155" s="8" t="n"/>
+      <c r="C155" s="8" t="n"/>
+      <c r="D155" s="8" t="n"/>
+      <c r="E155" s="8" t="n"/>
+      <c r="F155" s="8" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="B156" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C155" s="7" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D155" s="7" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E155" s="7" t="inlineStr">
+      <c r="E156" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F155" s="7" t="inlineStr">
+      <c r="F156" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="64" customHeight="1">
-      <c r="A156" s="8" t="inlineStr">
+    <row r="157" ht="64" customHeight="1">
+      <c r="A157" s="10" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B156" s="8" t="inlineStr">
+      <c r="B157" s="10" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C156" s="9" t="inlineStr"/>
-      <c r="D156" s="10" t="inlineStr">
+      <c r="C157" s="11" t="inlineStr"/>
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E156" s="8" t="inlineStr">
+      <c r="E157" s="10" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F156" s="8" t="n"/>
-    </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="8" t="inlineStr">
+      <c r="F157" s="10" t="n"/>
+    </row>
+    <row r="158" ht="32" customHeight="1">
+      <c r="A158" s="10" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B157" s="8" t="inlineStr">
+      <c r="B158" s="10" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C157" s="9" t="inlineStr"/>
-      <c r="D157" s="10" t="inlineStr">
+      <c r="C158" s="11" t="inlineStr"/>
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E157" s="8" t="inlineStr">
+      <c r="E158" s="10" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F157" s="8" t="inlineStr">
+      <c r="F158" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="8" t="inlineStr">
+    <row r="159" ht="32" customHeight="1">
+      <c r="A159" s="10" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B158" s="8" t="inlineStr">
+      <c r="B159" s="10" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr"/>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="C159" s="11" t="inlineStr"/>
+      <c r="D159" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E158" s="8" t="inlineStr">
+      <c r="E159" s="10" t="inlineStr">
         <is>
           <t>스크럽, 노폐물, / 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="F158" s="8" t="n"/>
-    </row>
-    <row r="159" ht="96" customHeight="1">
-      <c r="A159" s="8" t="inlineStr">
+      <c r="F159" s="10" t="n"/>
+    </row>
+    <row r="160" ht="96" customHeight="1">
+      <c r="A160" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B159" s="8" t="inlineStr">
+      <c r="B160" s="10" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C159" s="9" t="inlineStr"/>
-      <c r="D159" s="10" t="inlineStr">
+      <c r="C160" s="11" t="inlineStr"/>
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E159" s="8" t="inlineStr">
+      <c r="E160" s="10" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F159" s="8" t="inlineStr">
+      <c r="F160" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="14" customHeight="1">
-      <c r="A160" s="17" t="inlineStr">
+    <row r="161" ht="14" customHeight="1">
+      <c r="A161" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B160" s="18" t="n"/>
-      <c r="C160" s="18" t="n"/>
-      <c r="D160" s="18" t="n"/>
-      <c r="E160" s="18" t="n"/>
-      <c r="F160" s="18" t="n"/>
-    </row>
-    <row r="161" ht="176" customHeight="1">
-      <c r="A161" s="19" t="inlineStr">
+      <c r="B161" s="20" t="n"/>
+      <c r="C161" s="20" t="n"/>
+      <c r="D161" s="20" t="n"/>
+      <c r="E161" s="20" t="n"/>
+      <c r="F161" s="20" t="n"/>
+    </row>
+    <row r="162" ht="176" customHeight="1">
+      <c r="A162" s="21" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -6440,121 +6468,121 @@
         </is>
       </c>
     </row>
-    <row r="162" ht="6" customHeight="1"/>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="5" t="inlineStr">
+    <row r="163" ht="6" customHeight="1"/>
+    <row r="164" ht="22" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B163" s="6" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-      <c r="E163" s="6" t="n"/>
-      <c r="F163" s="6" t="n"/>
-    </row>
-    <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
+      <c r="B164" s="8" t="n"/>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+    </row>
+    <row r="165" ht="15" customHeight="1">
+      <c r="A165" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B164" s="7" t="inlineStr">
+      <c r="B165" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C164" s="7" t="inlineStr">
+      <c r="C165" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D164" s="7" t="inlineStr">
+      <c r="D165" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E164" s="7" t="inlineStr">
+      <c r="E165" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F164" s="7" t="inlineStr">
+      <c r="F165" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="32" customHeight="1">
-      <c r="A165" s="20" t="inlineStr">
+    <row r="166" ht="32" customHeight="1">
+      <c r="A166" s="22" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B165" s="20" t="inlineStr">
+      <c r="B166" s="22" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C165" s="21" t="inlineStr"/>
-      <c r="D165" s="12" t="inlineStr">
+      <c r="C166" s="23" t="inlineStr"/>
+      <c r="D166" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E165" s="20" t="inlineStr">
+      <c r="E166" s="22" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="F165" s="20" t="inlineStr">
+      <c r="F166" s="22" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="64" customHeight="1">
-      <c r="A166" s="20" t="inlineStr">
+    <row r="167" ht="64" customHeight="1">
+      <c r="A167" s="22" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B166" s="20" t="inlineStr">
+      <c r="B167" s="22" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C166" s="21" t="inlineStr"/>
-      <c r="D166" s="28" t="inlineStr">
+      <c r="C167" s="23" t="inlineStr"/>
+      <c r="D167" s="30" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E166" s="20" t="inlineStr">
+      <c r="E167" s="22" t="inlineStr">
         <is>
           <t>감초의 수/지용성성분추출물.</t>
         </is>
       </c>
-      <c r="F166" s="20" t="inlineStr">
+      <c r="F167" s="22" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="14" customHeight="1">
-      <c r="A167" s="17" t="inlineStr">
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B167" s="18" t="n"/>
-      <c r="C167" s="18" t="n"/>
-      <c r="D167" s="18" t="n"/>
-      <c r="E167" s="18" t="n"/>
-      <c r="F167" s="18" t="n"/>
-    </row>
-    <row r="168" ht="112" customHeight="1">
-      <c r="A168" s="23" t="inlineStr">
+      <c r="B168" s="20" t="n"/>
+      <c r="C168" s="20" t="n"/>
+      <c r="D168" s="20" t="n"/>
+      <c r="E168" s="20" t="n"/>
+      <c r="F168" s="20" t="n"/>
+    </row>
+    <row r="169" ht="112" customHeight="1">
+      <c r="A169" s="25" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -6562,26 +6590,26 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B168" s="24" t="n"/>
-      <c r="C168" s="24" t="n"/>
-      <c r="D168" s="24" t="n"/>
-      <c r="E168" s="24" t="n"/>
-      <c r="F168" s="24" t="n"/>
-    </row>
-    <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="17" t="inlineStr">
+      <c r="B169" s="26" t="n"/>
+      <c r="C169" s="26" t="n"/>
+      <c r="D169" s="26" t="n"/>
+      <c r="E169" s="26" t="n"/>
+      <c r="F169" s="26" t="n"/>
+    </row>
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B169" s="18" t="n"/>
-      <c r="C169" s="18" t="n"/>
-      <c r="D169" s="18" t="n"/>
-      <c r="E169" s="18" t="n"/>
-      <c r="F169" s="18" t="n"/>
-    </row>
-    <row r="170" ht="112" customHeight="1">
-      <c r="A170" s="23" t="inlineStr">
+      <c r="B170" s="20" t="n"/>
+      <c r="C170" s="20" t="n"/>
+      <c r="D170" s="20" t="n"/>
+      <c r="E170" s="20" t="n"/>
+      <c r="F170" s="20" t="n"/>
+    </row>
+    <row r="171" ht="112" customHeight="1">
+      <c r="A171" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -6591,235 +6619,235 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B170" s="24" t="n"/>
-      <c r="C170" s="24" t="n"/>
-      <c r="D170" s="24" t="n"/>
-      <c r="E170" s="24" t="n"/>
-      <c r="F170" s="24" t="n"/>
-    </row>
-    <row r="171" ht="6" customHeight="1"/>
-    <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="5" t="inlineStr">
+      <c r="B171" s="26" t="n"/>
+      <c r="C171" s="26" t="n"/>
+      <c r="D171" s="26" t="n"/>
+      <c r="E171" s="26" t="n"/>
+      <c r="F171" s="26" t="n"/>
+    </row>
+    <row r="172" ht="6" customHeight="1"/>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
+    </row>
+    <row r="174" ht="15" customHeight="1">
+      <c r="A174" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B174" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C174" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D174" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E174" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F174" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="64" customHeight="1">
-      <c r="A174" s="8" t="inlineStr">
+    <row r="175" ht="64" customHeight="1">
+      <c r="A175" s="10" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B174" s="8" t="inlineStr">
+      <c r="B175" s="10" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr"/>
-      <c r="D174" s="10" t="inlineStr">
+      <c r="C175" s="11" t="inlineStr"/>
+      <c r="D175" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E174" s="8" t="inlineStr">
+      <c r="E175" s="10" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F174" s="8" t="n"/>
-    </row>
-    <row r="175" ht="32" customHeight="1">
-      <c r="A175" s="8" t="inlineStr">
+      <c r="F175" s="10" t="n"/>
+    </row>
+    <row r="176" ht="32" customHeight="1">
+      <c r="A176" s="10" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B175" s="8" t="inlineStr">
+      <c r="B176" s="10" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C175" s="9" t="inlineStr"/>
-      <c r="D175" s="10" t="inlineStr">
+      <c r="C176" s="11" t="inlineStr"/>
+      <c r="D176" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E175" s="8" t="inlineStr">
+      <c r="E176" s="10" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F175" s="8" t="inlineStr">
+      <c r="F176" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="96" customHeight="1">
-      <c r="A176" s="8" t="inlineStr">
+    <row r="177" ht="96" customHeight="1">
+      <c r="A177" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B176" s="8" t="inlineStr">
+      <c r="B177" s="10" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C176" s="9" t="inlineStr"/>
-      <c r="D176" s="10" t="inlineStr">
+      <c r="C177" s="11" t="inlineStr"/>
+      <c r="D177" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E176" s="8" t="inlineStr">
+      <c r="E177" s="10" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F176" s="8" t="inlineStr">
+      <c r="F177" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="48" customHeight="1">
-      <c r="A177" s="8" t="inlineStr">
+    <row r="178" ht="48" customHeight="1">
+      <c r="A178" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B178" s="10" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr"/>
-      <c r="D177" s="11" t="inlineStr">
+      <c r="C178" s="11" t="inlineStr"/>
+      <c r="D178" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E177" s="8" t="inlineStr">
+      <c r="E178" s="10" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F177" s="8" t="inlineStr">
+      <c r="F178" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="80" customHeight="1">
-      <c r="A178" s="8" t="inlineStr">
+    <row r="179" ht="80" customHeight="1">
+      <c r="A179" s="10" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B178" s="8" t="inlineStr">
+      <c r="B179" s="10" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C178" s="9" t="inlineStr"/>
-      <c r="D178" s="25" t="inlineStr">
+      <c r="C179" s="11" t="inlineStr"/>
+      <c r="D179" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E178" s="8" t="inlineStr">
+      <c r="E179" s="10" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F178" s="8" t="inlineStr">
+      <c r="F179" s="10" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="32" customHeight="1">
-      <c r="A179" s="8" t="inlineStr">
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="10" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B179" s="8" t="inlineStr">
+      <c r="B180" s="10" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C179" s="9" t="inlineStr"/>
-      <c r="D179" s="12" t="inlineStr">
+      <c r="C180" s="11" t="inlineStr"/>
+      <c r="D180" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E179" s="8" t="inlineStr">
+      <c r="E180" s="10" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="F179" s="8" t="inlineStr">
+      <c r="F180" s="10" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="14" customHeight="1">
-      <c r="A180" s="17" t="inlineStr">
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B180" s="18" t="n"/>
-      <c r="C180" s="18" t="n"/>
-      <c r="D180" s="18" t="n"/>
-      <c r="E180" s="18" t="n"/>
-      <c r="F180" s="18" t="n"/>
-    </row>
-    <row r="181" ht="112" customHeight="1">
-      <c r="A181" s="19" t="inlineStr">
+      <c r="B181" s="20" t="n"/>
+      <c r="C181" s="20" t="n"/>
+      <c r="D181" s="20" t="n"/>
+      <c r="E181" s="20" t="n"/>
+      <c r="F181" s="20" t="n"/>
+    </row>
+    <row r="182" ht="112" customHeight="1">
+      <c r="A182" s="21" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -6829,170 +6857,170 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="6" customHeight="1"/>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
+    <row r="183" ht="6" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="6" t="n"/>
-    </row>
-    <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+      <c r="B184" s="8" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="8" t="n"/>
+      <c r="E184" s="8" t="n"/>
+      <c r="F184" s="8" t="n"/>
+    </row>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B184" s="7" t="inlineStr">
+      <c r="B185" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C184" s="7" t="inlineStr">
+      <c r="C185" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D184" s="7" t="inlineStr">
+      <c r="D185" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E184" s="7" t="inlineStr">
+      <c r="E185" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F184" s="7" t="inlineStr">
+      <c r="F185" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="32" customHeight="1">
-      <c r="A185" s="20" t="inlineStr">
+    <row r="186" ht="32" customHeight="1">
+      <c r="A186" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B185" s="20" t="inlineStr">
+      <c r="B186" s="22" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C185" s="21" t="inlineStr"/>
-      <c r="D185" s="12" t="inlineStr">
+      <c r="C186" s="23" t="inlineStr"/>
+      <c r="D186" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E185" s="20" t="inlineStr">
+      <c r="E186" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F185" s="20" t="n"/>
-    </row>
-    <row r="186" ht="112" customHeight="1">
-      <c r="A186" s="20" t="inlineStr">
+      <c r="F186" s="22" t="n"/>
+    </row>
+    <row r="187" ht="112" customHeight="1">
+      <c r="A187" s="22" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B186" s="20" t="inlineStr">
+      <c r="B187" s="22" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C186" s="21" t="inlineStr"/>
-      <c r="D186" s="13" t="inlineStr">
+      <c r="C187" s="23" t="inlineStr"/>
+      <c r="D187" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E186" s="20" t="inlineStr">
+      <c r="E187" s="22" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F186" s="20" t="inlineStr">
+      <c r="F187" s="22" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="32" customHeight="1">
-      <c r="A187" s="20" t="inlineStr">
+    <row r="188" ht="32" customHeight="1">
+      <c r="A188" s="22" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B187" s="20" t="inlineStr">
+      <c r="B188" s="22" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C187" s="21" t="inlineStr"/>
-      <c r="D187" s="13" t="inlineStr">
+      <c r="C188" s="23" t="inlineStr"/>
+      <c r="D188" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E187" s="20" t="inlineStr">
+      <c r="E188" s="22" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="F187" s="20" t="inlineStr">
+      <c r="F188" s="22" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="14" customHeight="1">
-      <c r="A188" s="17" t="inlineStr">
+    <row r="189" ht="14" customHeight="1">
+      <c r="A189" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B188" s="18" t="n"/>
-      <c r="C188" s="18" t="n"/>
-      <c r="D188" s="18" t="n"/>
-      <c r="E188" s="18" t="n"/>
-      <c r="F188" s="18" t="n"/>
-    </row>
-    <row r="189" ht="80" customHeight="1">
-      <c r="A189" s="23" t="inlineStr">
+      <c r="B189" s="20" t="n"/>
+      <c r="C189" s="20" t="n"/>
+      <c r="D189" s="20" t="n"/>
+      <c r="E189" s="20" t="n"/>
+      <c r="F189" s="20" t="n"/>
+    </row>
+    <row r="190" ht="80" customHeight="1">
+      <c r="A190" s="25" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B189" s="24" t="n"/>
-      <c r="C189" s="24" t="n"/>
-      <c r="D189" s="24" t="n"/>
-      <c r="E189" s="24" t="n"/>
-      <c r="F189" s="24" t="n"/>
-    </row>
-    <row r="190" ht="14" customHeight="1">
-      <c r="A190" s="17" t="inlineStr">
+      <c r="B190" s="26" t="n"/>
+      <c r="C190" s="26" t="n"/>
+      <c r="D190" s="26" t="n"/>
+      <c r="E190" s="26" t="n"/>
+      <c r="F190" s="26" t="n"/>
+    </row>
+    <row r="191" ht="14" customHeight="1">
+      <c r="A191" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B190" s="18" t="n"/>
-      <c r="C190" s="18" t="n"/>
-      <c r="D190" s="18" t="n"/>
-      <c r="E190" s="18" t="n"/>
-      <c r="F190" s="18" t="n"/>
-    </row>
-    <row r="191" ht="128" customHeight="1">
-      <c r="A191" s="23" t="inlineStr">
+      <c r="B191" s="20" t="n"/>
+      <c r="C191" s="20" t="n"/>
+      <c r="D191" s="20" t="n"/>
+      <c r="E191" s="20" t="n"/>
+      <c r="F191" s="20" t="n"/>
+    </row>
+    <row r="192" ht="128" customHeight="1">
+      <c r="A192" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -7003,157 +7031,145 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B191" s="24" t="n"/>
-      <c r="C191" s="24" t="n"/>
-      <c r="D191" s="24" t="n"/>
-      <c r="E191" s="24" t="n"/>
-      <c r="F191" s="24" t="n"/>
-    </row>
-    <row r="192" ht="6" customHeight="1"/>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="5" t="inlineStr">
+      <c r="B192" s="26" t="n"/>
+      <c r="C192" s="26" t="n"/>
+      <c r="D192" s="26" t="n"/>
+      <c r="E192" s="26" t="n"/>
+      <c r="F192" s="26" t="n"/>
+    </row>
+    <row r="193" ht="6" customHeight="1"/>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B193" s="6" t="n"/>
-      <c r="C193" s="6" t="n"/>
-      <c r="D193" s="6" t="n"/>
-      <c r="E193" s="6" t="n"/>
-      <c r="F193" s="6" t="n"/>
-    </row>
-    <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
+    </row>
+    <row r="195" ht="15" customHeight="1">
+      <c r="A195" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B195" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C194" s="7" t="inlineStr">
+      <c r="C195" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D195" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E195" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F195" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="64" customHeight="1">
-      <c r="A195" s="8" t="inlineStr">
+    <row r="196" ht="64" customHeight="1">
+      <c r="A196" s="10" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B196" s="10" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C195" s="9" t="inlineStr">
+      <c r="C196" s="11" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D195" s="25" t="inlineStr">
+      <c r="D196" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E195" s="8" t="inlineStr">
+      <c r="E196" s="10" t="inlineStr">
         <is>
           <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="F195" s="8" t="n"/>
-    </row>
-    <row r="196" ht="32" customHeight="1">
-      <c r="A196" s="8" t="inlineStr">
+      <c r="F196" s="10" t="n"/>
+    </row>
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="10" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B196" s="8" t="inlineStr">
+      <c r="B197" s="10" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C196" s="9" t="inlineStr">
+      <c r="C197" s="11" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D196" s="12" t="inlineStr">
+      <c r="D197" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E196" s="8" t="inlineStr">
+      <c r="E197" s="10" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 / →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="F196" s="8" t="n"/>
-    </row>
-    <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="8" t="inlineStr">
+      <c r="F197" s="10" t="n"/>
+    </row>
+    <row r="198" ht="16" customHeight="1">
+      <c r="A198" s="10" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B197" s="8" t="inlineStr">
+      <c r="B198" s="10" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C197" s="9" t="inlineStr">
+      <c r="C198" s="11" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="D197" s="12" t="inlineStr">
+      <c r="D198" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E197" s="8" t="inlineStr">
+      <c r="E198" s="10" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="F197" s="8" t="n"/>
-    </row>
-    <row r="198" ht="14" customHeight="1">
-      <c r="A198" s="15" t="inlineStr">
-        <is>
-          <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
-        </is>
-      </c>
-      <c r="B198" s="16" t="n"/>
-      <c r="C198" s="16" t="n"/>
-      <c r="D198" s="16" t="n"/>
-      <c r="E198" s="16" t="n"/>
-      <c r="F198" s="16" t="n"/>
+      <c r="F198" s="10" t="n"/>
     </row>
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="17" t="inlineStr">
         <is>
-          <t>— 상세내용 —</t>
+          <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
         </is>
       </c>
       <c r="B199" s="18" t="n"/>
@@ -7162,8 +7178,20 @@
       <c r="E199" s="18" t="n"/>
       <c r="F199" s="18" t="n"/>
     </row>
-    <row r="200" ht="384" customHeight="1">
+    <row r="200" ht="14" customHeight="1">
       <c r="A200" s="19" t="inlineStr">
+        <is>
+          <t>— 상세내용 —</t>
+        </is>
+      </c>
+      <c r="B200" s="20" t="n"/>
+      <c r="C200" s="20" t="n"/>
+      <c r="D200" s="20" t="n"/>
+      <c r="E200" s="20" t="n"/>
+      <c r="F200" s="20" t="n"/>
+    </row>
+    <row r="201" ht="384" customHeight="1">
+      <c r="A201" s="21" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -7192,8 +7220,8 @@
         </is>
       </c>
     </row>
-    <row r="201" ht="112" customHeight="1">
-      <c r="A201" s="19" t="inlineStr">
+    <row r="202" ht="112" customHeight="1">
+      <c r="A202" s="21" t="inlineStr">
         <is>
           <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
@@ -7205,20 +7233,20 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="14" customHeight="1">
-      <c r="A202" s="17" t="inlineStr">
+    <row r="203" ht="14" customHeight="1">
+      <c r="A203" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B202" s="18" t="n"/>
-      <c r="C202" s="18" t="n"/>
-      <c r="D202" s="18" t="n"/>
-      <c r="E202" s="18" t="n"/>
-      <c r="F202" s="18" t="n"/>
-    </row>
-    <row r="203" ht="112" customHeight="1">
-      <c r="A203" s="19" t="inlineStr">
+      <c r="B203" s="20" t="n"/>
+      <c r="C203" s="20" t="n"/>
+      <c r="D203" s="20" t="n"/>
+      <c r="E203" s="20" t="n"/>
+      <c r="F203" s="20" t="n"/>
+    </row>
+    <row r="204" ht="112" customHeight="1">
+      <c r="A204" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -7230,47 +7258,35 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="6" customHeight="1"/>
+    <row r="205" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="98">
-    <mergeCell ref="A183:F183"/>
+  <mergeCells count="99">
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A75:F75"/>
     <mergeCell ref="A189:F189"/>
-    <mergeCell ref="A198:F198"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A160:F160"/>
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A150:F150"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A144:F144"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A200:F200"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A152:F152"/>
     <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="A202:F202"/>
+    <mergeCell ref="A58:F58"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A73:F73"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A124:F124"/>
-    <mergeCell ref="A172:F172"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A149:F149"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A101:F101"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A204:F204"/>
     <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A188:F188"/>
     <mergeCell ref="A126:F126"/>
     <mergeCell ref="A141:F141"/>
     <mergeCell ref="A125:F125"/>
@@ -7279,77 +7295,90 @@
     <mergeCell ref="A112:F112"/>
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A167:F167"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A142:F142"/>
+    <mergeCell ref="A182:F182"/>
     <mergeCell ref="A191:F191"/>
     <mergeCell ref="A169:F169"/>
+    <mergeCell ref="A79:F79"/>
     <mergeCell ref="A88:F88"/>
+    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A162:F162"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A90:F90"/>
+    <mergeCell ref="A164:F164"/>
     <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A76:F76"/>
     <mergeCell ref="A203:F203"/>
-    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A181:F181"/>
     <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A131:F131"/>
     <mergeCell ref="A100:F100"/>
     <mergeCell ref="A140:F140"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A171:F171"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A102:F102"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A173:F173"/>
     <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A143:F143"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A103:F103"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A87:F87"/>
     <mergeCell ref="A65:F65"/>
     <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A193:F193"/>
-    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="A170:F170"/>
     <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A130:F130"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A201:F201"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A163" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A183" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -3305,7 +3305,7 @@
           <t>미네럴, 소금의 일종, 탄산수소나트륨,삼투압으로 노폐뮬제거, 미네럴공급, 피부를 부드럽게</t>
         </is>
       </c>
-      <c r="F8" s="10" t="n"/>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -3608,10 +3608,10 @@
       </c>
       <c r="E23" s="22" t="inlineStr">
         <is>
-          <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="n"/>
+          <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr"/>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="22" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>반드시 양조절해서 / 색내기에 사용하세요.</t>
+          <t>반드시 양조절해서 · 색내기에 사용하세요.</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -3902,7 +3902,7 @@
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F36" s="10" t="n"/>
+      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
@@ -3930,7 +3930,7 @@
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="F37" s="10" t="n"/>
+      <c r="F37" s="10" t="inlineStr"/>
     </row>
     <row r="38" ht="96" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -3987,10 +3987,10 @@
       </c>
       <c r="E39" s="10" t="inlineStr">
         <is>
-          <t>코코넛유래, / 거품, 세정, 음이온</t>
-        </is>
-      </c>
-      <c r="F39" s="10" t="n"/>
+          <t>코코넛유래 · 거품, 세정, 음이온</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr"/>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>애플 / 계면활성제</t>
+          <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
@@ -4222,10 +4222,10 @@
       </c>
       <c r="E51" s="22" t="inlineStr">
         <is>
-          <t>풍부한 미네랄, / 노폐물제거</t>
-        </is>
-      </c>
-      <c r="F51" s="22" t="n"/>
+          <t>풍부한 미네랄 · 노폐물제거</t>
+        </is>
+      </c>
+      <c r="F51" s="22" t="inlineStr"/>
     </row>
     <row r="52" ht="14" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
@@ -4368,10 +4368,10 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>탄산수소나트륨 / , 미네럴공급, 연수효과</t>
-        </is>
-      </c>
-      <c r="F60" s="10" t="n"/>
+          <t>탄산수소나트륨 · 미네럴공급, 연수효과</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr"/>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="10" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F62" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -4492,10 +4492,10 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>히말라얀 암염, 풍부한 미네럴, / 철함유로 자체 / 핑크색, / 아로마를 입힌 핑크솔트도 가능</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="n"/>
+          <t>히말라얀 암염, 풍부한 미네럴 · 철함유로 자체 · 핑크색 · 아로마를 입힌 핑크솔트도 가능</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr"/>
     </row>
     <row r="65" ht="14" customHeight="1">
       <c r="A65" s="17" t="inlineStr">
@@ -4641,7 +4641,7 @@
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="F73" s="22" t="n"/>
+      <c r="F73" s="22" t="inlineStr"/>
     </row>
     <row r="74" ht="14" customHeight="1">
       <c r="A74" s="17" t="inlineStr">
@@ -4811,10 +4811,10 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>바다가 융기해 산이 됨, / 산소금=암염, 수분함량 적고 / 미네럴 풍부, / 산화철 함유로 색상 발현(핑크색)</t>
-        </is>
-      </c>
-      <c r="F83" s="10" t="n"/>
+          <t>바다가 융기해 산이 됨 · 산소금=암염, 수분함량 적고 · 미네럴 풍부 · 산화철 함유로 색상 발현(핑크색)</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr"/>
     </row>
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="10" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 아로마오일</t>
+          <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
@@ -4871,10 +4871,10 @@
       </c>
       <c r="E85" s="10" t="inlineStr">
         <is>
-          <t>입,족욕용 또는 / 바디 마사지/ 스크럽 겸용</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="n"/>
+          <t>입,족욕용 또는 · 바디 마사지 · 스크럽 겸용</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr"/>
     </row>
     <row r="86" ht="64" customHeight="1">
       <c r="A86" s="10" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F86" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 아로마오일</t>
+          <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="F95" s="22" t="n"/>
+      <c r="F95" s="22" t="inlineStr"/>
     </row>
     <row r="96" ht="32" customHeight="1">
       <c r="A96" s="22" t="inlineStr">
@@ -5289,10 +5289,10 @@
       </c>
       <c r="E107" s="10" t="inlineStr">
         <is>
-          <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
-        </is>
-      </c>
-      <c r="F107" s="10" t="n"/>
+          <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr"/>
     </row>
     <row r="108" ht="48" customHeight="1">
       <c r="A108" s="10" t="inlineStr">
@@ -5317,10 +5317,10 @@
       </c>
       <c r="E108" s="10" t="inlineStr">
         <is>
-          <t>DIY 스크럽 만들기 최적의 베이스 / 시어버터, 아보카도, 꿀추출물 등 / 함유, 보습+ 세정</t>
-        </is>
-      </c>
-      <c r="F108" s="10" t="n"/>
+          <t>DIY 스크럽 만들기 최적의 베이스 · 시어버터, 아보카도, 꿀추출물 등 · 함유, 보습+ 세정</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr"/>
     </row>
     <row r="109" ht="80" customHeight="1">
       <c r="A109" s="10" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="E109" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피 / 여드름-티트리, / 바디 용도별 추천오일 / -쿨링 :페파민트, / -다이어트 : 레몬+자몽오일 / -이완 : 라벤더오일 등</t>
+          <t>아로마테라피 · 여드름-티트리 · 바디 용도별 추천오일 · 쿨링 :페파민트 · 다이어트 : 레몬+자몽오일 · 이완 : 라벤더오일 등</t>
         </is>
       </c>
       <c r="F109" s="10" t="inlineStr">
@@ -5515,7 +5515,7 @@
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F119" s="22" t="n"/>
+      <c r="F119" s="22" t="inlineStr"/>
     </row>
     <row r="120" ht="16" customHeight="1">
       <c r="A120" s="22" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="F121" s="22" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F122" s="22" t="n"/>
+      <c r="F122" s="22" t="inlineStr"/>
     </row>
     <row r="123" ht="32" customHeight="1">
       <c r="A123" s="22" t="inlineStr">
@@ -5669,7 +5669,7 @@
       </c>
       <c r="F124" s="22" t="inlineStr">
         <is>
-          <t>카보머 프리젤 / 28g 적용 가능. / 적용시 가열과정 없음</t>
+          <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
@@ -5892,7 +5892,7 @@
       </c>
       <c r="F135" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="F136" s="10" t="n"/>
+      <c r="F136" s="10" t="inlineStr"/>
     </row>
     <row r="137" ht="16" customHeight="1">
       <c r="A137" s="10" t="inlineStr">
@@ -5979,10 +5979,10 @@
       </c>
       <c r="E138" s="10" t="inlineStr">
         <is>
-          <t>각질제거, 보습. / 필요에 따라 양을 더 넣어서 / 비벼도 됩니다.</t>
-        </is>
-      </c>
-      <c r="F138" s="10" t="n"/>
+          <t>각질제거, 보습. · 필요에 따라 양을 더 넣어서 · 비벼도 됩니다.</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr"/>
     </row>
     <row r="139" ht="32" customHeight="1">
       <c r="A139" s="10" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="E146" s="22" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 / 최적의 베이스</t>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
       <c r="F146" s="22" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="E147" s="22" t="inlineStr">
         <is>
-          <t>유기농 설탕+ 카카오분말 / 폴리페놀 풍부, 카카오의 달콤한 향</t>
+          <t>유기농 설탕+ 카카오분말 · 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
       <c r="F147" s="22" t="inlineStr">
@@ -6356,10 +6356,10 @@
       </c>
       <c r="E157" s="10" t="inlineStr">
         <is>
-          <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
-        </is>
-      </c>
-      <c r="F157" s="10" t="n"/>
+          <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
+        </is>
+      </c>
+      <c r="F157" s="10" t="inlineStr"/>
     </row>
     <row r="158" ht="32" customHeight="1">
       <c r="A158" s="10" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="E158" s="10" t="inlineStr">
         <is>
-          <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
+          <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
       <c r="F158" s="10" t="inlineStr">
@@ -6408,10 +6408,10 @@
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>스크럽, 노폐물, / 피지 삼투압으로 제거 도움</t>
-        </is>
-      </c>
-      <c r="F159" s="10" t="n"/>
+          <t>스크럽, 노폐물 · 피지 삼투압으로 제거 도움</t>
+        </is>
+      </c>
+      <c r="F159" s="10" t="inlineStr"/>
     </row>
     <row r="160" ht="96" customHeight="1">
       <c r="A160" s="10" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="F160" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="E167" s="22" t="inlineStr">
         <is>
-          <t>감초의 수/지용성성분추출물.</t>
+          <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
       <c r="F167" s="22" t="inlineStr">
@@ -6689,10 +6689,10 @@
       </c>
       <c r="E175" s="10" t="inlineStr">
         <is>
-          <t>베이킹소다=중조=중탄산나트륨 / 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
-        </is>
-      </c>
-      <c r="F175" s="10" t="n"/>
+          <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
+        </is>
+      </c>
+      <c r="F175" s="10" t="inlineStr"/>
     </row>
     <row r="176" ht="32" customHeight="1">
       <c r="A176" s="10" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>구연산: 정제수=1:9 pH 조절 / (주방세제는 pH 10~6 가능)</t>
+          <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
       <c r="F176" s="10" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F177" s="10" t="inlineStr">
         <is>
-          <t>라벤더, 유칼립튜스 등 / 천연 에센셜오일 / 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
@@ -6802,7 +6802,7 @@
       </c>
       <c r="F179" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -6921,10 +6921,10 @@
       </c>
       <c r="E186" s="22" t="inlineStr">
         <is>
-          <t>히말라야 핑크소금, 암염, / 미세입자, 미네럴 풍부</t>
-        </is>
-      </c>
-      <c r="F186" s="22" t="n"/>
+          <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
+        </is>
+      </c>
+      <c r="F186" s="22" t="inlineStr"/>
     </row>
     <row r="187" ht="112" customHeight="1">
       <c r="A187" s="22" t="inlineStr">
@@ -7105,10 +7105,10 @@
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>6 IN ONE / 피부결 개선, 보습, 맑은 피부, / 윤기, 영양공급, 피부정화 / 스크럽제를 만들기 위한 최적의 베이스</t>
-        </is>
-      </c>
-      <c r="F196" s="10" t="n"/>
+          <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 최적의 베이스</t>
+        </is>
+      </c>
+      <c r="F196" s="10" t="inlineStr"/>
     </row>
     <row r="197" ht="32" customHeight="1">
       <c r="A197" s="10" t="inlineStr">
@@ -7133,10 +7133,10 @@
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>커피에 포함된 폴리페놀 / →피부 활력, 탄력 도움</t>
-        </is>
-      </c>
-      <c r="F197" s="10" t="n"/>
+          <t>커피에 포함된 폴리페놀 · →피부 활력, 탄력 도움</t>
+        </is>
+      </c>
+      <c r="F197" s="10" t="inlineStr"/>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="10" t="inlineStr">
@@ -7164,7 +7164,7 @@
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="F198" s="10" t="n"/>
+      <c r="F198" s="10" t="inlineStr"/>
     </row>
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="17" t="inlineStr">

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -341,7 +341,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
     <pos x="7848600" y="1854200"/>
-    <ext cx="1809750" cy="1409700"/>
+    <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -361,27 +361,27 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="9696450" y="1854200"/>
+    <ext cx="1809750" cy="1323975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="1854200"/>
     <ext cx="1295400" cy="1428750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="1854200"/>
-    <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -561,7 +561,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="13392150" y="5549900"/>
-    <ext cx="1295400" cy="1428750"/>
+    <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -641,7 +641,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="13392150" y="7397750"/>
-    <ext cx="1285875" cy="1428750"/>
+    <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -661,7 +661,7 @@
   </absoluteAnchor>
   <absoluteAnchor>
     <pos x="7848600" y="9245600"/>
-    <ext cx="1809750" cy="1409700"/>
+    <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -680,8 +680,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="9245600"/>
-    <ext cx="1809750" cy="990600"/>
+    <pos x="7848600" y="13303249"/>
+    <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="13296900"/>
+    <pos x="7848600" y="17437100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -720,8 +720,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="13296900"/>
-    <ext cx="1809750" cy="1504950"/>
+    <pos x="9696450" y="17437100"/>
+    <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="13296900"/>
+    <pos x="11544300" y="17437100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="13296900"/>
+    <pos x="13392150" y="17437100"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="15144750"/>
+    <pos x="7848600" y="19284950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="15144750"/>
+    <pos x="9696450" y="19284950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="15144750"/>
+    <pos x="11544300" y="19284950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="15144750"/>
+    <pos x="13392150" y="19284950"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="16992600"/>
+    <pos x="7848600" y="21132800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="16992600"/>
+    <pos x="9696450" y="21132800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="16992600"/>
+    <pos x="11544300" y="21132800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="16992600"/>
+    <pos x="13392150" y="21132800"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="18840450"/>
+    <pos x="7848600" y="22980650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="18840450"/>
+    <pos x="9696450" y="22980650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="18840450"/>
+    <pos x="11544300" y="22980650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="18840450"/>
+    <pos x="13392150" y="22980650"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,8 +1020,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="20688300"/>
-    <ext cx="1724025" cy="1809750"/>
+    <pos x="7848600" y="24828500"/>
+    <ext cx="5143500" cy="4286250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="35" name="Image 35" descr="Picture"/>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="22612350"/>
+    <pos x="7848600" y="29229050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="22612350"/>
+    <pos x="9696450" y="29229050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="22612350"/>
+    <pos x="11544300" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="22612350"/>
+    <pos x="13392150" y="29229050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="24460200"/>
+    <pos x="7848600" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="24460200"/>
+    <pos x="9696450" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="24460200"/>
+    <pos x="11544300" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="24460200"/>
+    <pos x="13392150" y="31076900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="26308050"/>
+    <pos x="7848600" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="26308050"/>
+    <pos x="9696450" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="26308050"/>
+    <pos x="11544300" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="26308050"/>
+    <pos x="13392150" y="32924750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="28155900"/>
+    <pos x="7848600" y="34772600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="28155900"/>
+    <pos x="9696450" y="34772600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31210250"/>
+    <pos x="7848600" y="37826950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31210250"/>
+    <pos x="9696450" y="37826950"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31210250"/>
+    <pos x="11544300" y="37826950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31210250"/>
+    <pos x="13392150" y="37826950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="33058100"/>
+    <pos x="7848600" y="39674800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="35540950"/>
+    <pos x="7848600" y="42157650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="35540950"/>
+    <pos x="9696450" y="42157650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="35540950"/>
+    <pos x="11544300" y="42157650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="35540950"/>
+    <pos x="13392150" y="42157650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37388800"/>
+    <pos x="7848600" y="44005500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37388800"/>
+    <pos x="9696450" y="44005500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37388800"/>
+    <pos x="11544300" y="44005500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="37388800"/>
+    <pos x="13392150" y="44005500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39236650"/>
+    <pos x="7848600" y="45853350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="39236650"/>
+    <pos x="9696450" y="45853350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45154850"/>
+    <pos x="7848600" y="51771550"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45154850"/>
+    <pos x="9696450" y="51771550"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45154850"/>
+    <pos x="11544300" y="51771550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45154850"/>
+    <pos x="13392150" y="51771550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47002700"/>
+    <pos x="7848600" y="53619400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,8 +1720,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="52939950"/>
-    <ext cx="1809750" cy="1209675"/>
+    <pos x="7848600" y="59556650"/>
+    <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="52939950"/>
+    <pos x="9696450" y="59556650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="52939950"/>
+    <pos x="11544300" y="59556650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="52939950"/>
+    <pos x="13392150" y="59556650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="54787800"/>
+    <pos x="7848600" y="61404500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="54787800"/>
+    <pos x="9696450" y="61404500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,1010 +1840,1010 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="54787800"/>
+    <pos x="7848600" y="63252350"/>
+    <ext cx="5143500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="67951350"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="67951350"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="67951350"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="67951350"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="69799200"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="69799200"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="69799200"/>
+    <ext cx="1428750" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="69799200"/>
+    <ext cx="1809750" cy="1647825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="71647050"/>
+    <ext cx="1809750" cy="1647825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="73494900"/>
+    <ext cx="5143500" cy="4286250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="77895450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="61334650"/>
-    <ext cx="1809750" cy="1504950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="61334650"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="61334650"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="61334650"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="63182500"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="63182500"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="63182500"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="63182500"/>
-    <ext cx="1428750" cy="1257300"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="65030350"/>
-    <ext cx="1809750" cy="1647825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="65030350"/>
-    <ext cx="1809750" cy="1647825"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="68916550"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="77895450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="68916550"/>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="77895450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="68916550"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="79743300"/>
+    <ext cx="5143500" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="88322150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="68916550"/>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="88322150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="79343250"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="88322150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="79343250"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="88322150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="79343250"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="90170000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="79343250"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="90170000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="81191100"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="90170000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="81191100"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="90170000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="81191100"/>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="92017850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="81191100"/>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="93865700"/>
+    <ext cx="5143500" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="99123500"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="99123500"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="99123500"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="99123500"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="100971350"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="100971350"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="100971350"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="100971350"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="102819200"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="102819200"/>
+    <ext cx="1809750" cy="1714500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="104667050"/>
+    <ext cx="5143500" cy="4352925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="109058075"/>
+    <ext cx="5143500" cy="1628775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="110801150"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="112649000"/>
+    <ext cx="5143500" cy="4352925"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="117040025"/>
+    <ext cx="5143500" cy="4419600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="121497725"/>
+    <ext cx="5143500" cy="1628775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="123240800"/>
+    <ext cx="3200400" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="129044700"/>
+    <ext cx="3200400" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="134302500"/>
+    <ext cx="3505200" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="140919200"/>
+    <ext cx="3200400" cy="5143500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="146697700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="83038950"/>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="146697700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="83038950"/>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11544300" y="146697700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="88550750"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="88550750"/>
-    <ext cx="1809750" cy="1533525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="88550750"/>
-    <ext cx="1809750" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="88550750"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="90398600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="105" name="Image 105" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="90398600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="106" name="Image 106" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="90398600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="107" name="Image 107" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="90398600"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="108" name="Image 108" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="92246450"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="109" name="Image 109" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="92246450"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="110" name="Image 110" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="92246450"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="111" name="Image 111" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="92246450"/>
-    <ext cx="1809750" cy="1714500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="112" name="Image 112" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId112"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="96970850"/>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="113" name="Image 113" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="96970850"/>
-    <ext cx="1809750" cy="1533525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="114" name="Image 114" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="96970850"/>
-    <ext cx="1809750" cy="1552575"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="115" name="Image 115" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId115"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="96970850"/>
-    <ext cx="1809750" cy="571500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="116" name="Image 116" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId116"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="109023150"/>
-    <ext cx="1123950" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="117" name="Image 117" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId117"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="114827050"/>
-    <ext cx="1123950" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="118" name="Image 118" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId118"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="119792750"/>
-    <ext cx="1238250" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="119" name="Image 119" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId119"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="126409450"/>
-    <ext cx="1123950" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="120" name="Image 120" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId120"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="132187950"/>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="13392150" y="146697700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="121" name="Image 121" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId121"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="132187950"/>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId124"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="7848600" y="148545550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="122" name="Image 122" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId122"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="11544300" y="132187950"/>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId125"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9696450" y="148545550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="123" name="Image 123" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId123"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="13392150" y="132187950"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="124" name="Image 124" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId124"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="7848600" y="134035800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="125" name="Image 125" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId125"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </absoluteAnchor>
-  <absoluteAnchor>
-    <pos x="9696450" y="134035800"/>
-    <ext cx="1809750" cy="1809750"/>
-    <pic>
-      <nvPicPr>
         <cNvPr id="126" name="Image 126" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -2860,8 +2860,8 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="134035800"/>
-    <ext cx="1809750" cy="1809750"/>
+    <pos x="7848600" y="150393400"/>
+    <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="127" name="Image 127" descr="Picture"/>
@@ -3171,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3540,233 +3540,234 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="20" ht="325.9999999999999" customHeight="1"/>
+    <row r="21" ht="6" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
+    <row r="24" ht="64" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+    <row r="26" ht="96" customHeight="1">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D26" s="24" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F27" s="22" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="29" ht="14" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-    </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+    </row>
+    <row r="30" ht="14" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="20" t="n"/>
-    </row>
-    <row r="30" ht="288" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+    </row>
+    <row r="31" ht="288" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -3785,335 +3786,335 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-    </row>
-    <row r="31" ht="118.5" customHeight="1">
-      <c r="A31" s="26" t="n"/>
       <c r="B31" s="26" t="n"/>
       <c r="C31" s="26" t="n"/>
       <c r="D31" s="26" t="n"/>
       <c r="E31" s="26" t="n"/>
       <c r="F31" s="26" t="n"/>
     </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="32" ht="313.5000000000002" customHeight="1">
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
+      <c r="F32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F34" s="9" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
-      <c r="A35" s="10" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>코치닐+물</t>
         </is>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>1g+3g</t>
         </is>
       </c>
-      <c r="C35" s="11" t="inlineStr">
+      <c r="C36" s="11" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>반드시 양조절해서 · 색내기에 사용하세요.</t>
         </is>
       </c>
-      <c r="F35" s="10" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>원하는 색</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>베이킹소다</t>
-        </is>
-      </c>
-      <c r="B36" s="10" t="inlineStr">
-        <is>
-          <t>250g</t>
-        </is>
-      </c>
-      <c r="C36" s="11" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>점증/pH</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>미네럴 공급, 연수화</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="10" t="inlineStr">
         <is>
+          <t>베이킹소다</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>미네럴 공급, 연수화</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
           <t>주석산</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C38" s="11" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="96" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr"/>
+    </row>
+    <row r="39" ht="96" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E39" s="10" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr">
+      <c r="F39" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+    <row r="40" ht="32" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C40" s="11" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D39" s="16" t="inlineStr">
+      <c r="D40" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E40" s="10" t="inlineStr">
         <is>
           <t>코코넛유래 · 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr"/>
-    </row>
-    <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
         <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E41" s="10" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr">
+      <c r="F41" s="10" t="inlineStr">
         <is>
           <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="80" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+    <row r="42" ht="80" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C42" s="11" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D41" s="27" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F43" s="10" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+    <row r="44" ht="14" customHeight="1">
+      <c r="A44" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="19" t="inlineStr">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+    </row>
+    <row r="45" ht="14" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B44" s="20" t="n"/>
-      <c r="C44" s="20" t="n"/>
-      <c r="D44" s="20" t="n"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="20" t="n"/>
-    </row>
-    <row r="45" ht="96" customHeight="1">
-      <c r="A45" s="21" t="inlineStr">
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="20" t="n"/>
+    </row>
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -4124,20 +4125,20 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="19" t="inlineStr">
+    <row r="47" ht="14" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="20" t="n"/>
-      <c r="D46" s="20" t="n"/>
-      <c r="E46" s="20" t="n"/>
-      <c r="F46" s="20" t="n"/>
-    </row>
-    <row r="47" ht="192" customHeight="1">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="20" t="n"/>
+    </row>
+    <row r="48" ht="192" customHeight="1">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -4154,105 +4155,105 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="6" customHeight="1"/>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+    <row r="49" ht="6" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B49" s="8" t="n"/>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="8" t="n"/>
+      <c r="F50" s="8" t="n"/>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C50" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D50" s="9" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="22" t="inlineStr">
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B51" s="22" t="inlineStr">
+      <c r="B52" s="22" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C51" s="23" t="inlineStr">
+      <c r="C52" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D52" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E51" s="22" t="inlineStr">
+      <c r="E52" s="22" t="inlineStr">
         <is>
           <t>풍부한 미네랄 · 노폐물제거</t>
         </is>
       </c>
-      <c r="F51" s="22" t="inlineStr"/>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="F52" s="22" t="inlineStr"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 100</t>
         </is>
       </c>
-      <c r="B52" s="18" t="n"/>
-      <c r="C52" s="18" t="n"/>
-      <c r="D52" s="18" t="n"/>
-      <c r="E52" s="18" t="n"/>
-      <c r="F52" s="18" t="n"/>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-    </row>
-    <row r="54" ht="176" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="20" t="n"/>
+      <c r="D54" s="20" t="n"/>
+      <c r="E54" s="20" t="n"/>
+      <c r="F54" s="20" t="n"/>
+    </row>
+    <row r="55" ht="176" customHeight="1">
+      <c r="A55" s="25" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -4267,26 +4268,26 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B54" s="26" t="n"/>
-      <c r="C54" s="26" t="n"/>
-      <c r="D54" s="26" t="n"/>
-      <c r="E54" s="26" t="n"/>
-      <c r="F54" s="26" t="n"/>
-    </row>
-    <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="26" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-    </row>
-    <row r="56" ht="64" customHeight="1">
-      <c r="A56" s="25" t="inlineStr">
+      <c r="B56" s="20" t="n"/>
+      <c r="C56" s="20" t="n"/>
+      <c r="D56" s="20" t="n"/>
+      <c r="E56" s="20" t="n"/>
+      <c r="F56" s="20" t="n"/>
+    </row>
+    <row r="57" ht="64" customHeight="1">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -4294,235 +4295,235 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B56" s="26" t="n"/>
-      <c r="C56" s="26" t="n"/>
-      <c r="D56" s="26" t="n"/>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="26" t="n"/>
-    </row>
-    <row r="57" ht="6" customHeight="1"/>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="B57" s="26" t="n"/>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="26" t="n"/>
+      <c r="E57" s="26" t="n"/>
+      <c r="F57" s="26" t="n"/>
+    </row>
+    <row r="58" ht="6" customHeight="1"/>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="9" t="inlineStr">
+      <c r="B59" s="8" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="8" t="n"/>
+      <c r="F59" s="8" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B59" s="9" t="inlineStr">
+      <c r="B60" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C60" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F60" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B61" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr">
+      <c r="E61" s="10" t="inlineStr">
         <is>
           <t>탄산수소나트륨 · 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="F60" s="10" t="inlineStr"/>
-    </row>
-    <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+      <c r="F61" s="10" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E62" s="10" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr">
+      <c r="F62" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="96" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+    <row r="63" ht="96" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D62" s="13" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="32" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C64" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="D64" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E64" s="10" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F64" s="10" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="65" ht="48" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B65" s="10" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C65" s="11" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D64" s="14" t="inlineStr">
+      <c r="D65" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E65" s="10" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴 · 철함유로 자체 · 핑크색 · 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr"/>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr"/>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
         </is>
       </c>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-    </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="19" t="inlineStr">
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+    </row>
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B66" s="20" t="n"/>
-      <c r="C66" s="20" t="n"/>
-      <c r="D66" s="20" t="n"/>
-      <c r="E66" s="20" t="n"/>
-      <c r="F66" s="20" t="n"/>
-    </row>
-    <row r="67" ht="240" customHeight="1">
-      <c r="A67" s="21" t="inlineStr">
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+    </row>
+    <row r="68" ht="240" customHeight="1">
+      <c r="A68" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -4542,20 +4543,20 @@
         </is>
       </c>
     </row>
-    <row r="68" ht="14" customHeight="1">
-      <c r="A68" s="19" t="inlineStr">
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B68" s="20" t="n"/>
-      <c r="C68" s="20" t="n"/>
-      <c r="D68" s="20" t="n"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="20" t="n"/>
-    </row>
-    <row r="69" ht="208" customHeight="1">
-      <c r="A69" s="21" t="inlineStr">
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+    </row>
+    <row r="70" ht="208" customHeight="1">
+      <c r="A70" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -4570,105 +4571,105 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="6" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="71" ht="6" customHeight="1"/>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B71" s="8" t="n"/>
-      <c r="C71" s="8" t="n"/>
-      <c r="D71" s="8" t="n"/>
-      <c r="E71" s="8" t="n"/>
-      <c r="F71" s="8" t="n"/>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B73" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
+      <c r="C73" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="D73" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E72" s="9" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
+      <c r="F73" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="32" customHeight="1">
-      <c r="A73" s="22" t="inlineStr">
+    <row r="74" ht="32" customHeight="1">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B73" s="22" t="inlineStr">
+      <c r="B74" s="22" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C73" s="23" t="inlineStr">
+      <c r="C74" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D73" s="14" t="inlineStr">
+      <c r="D74" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E73" s="22" t="inlineStr">
+      <c r="E74" s="22" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="F73" s="22" t="inlineStr"/>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="F74" s="22" t="inlineStr"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  기타 100</t>
         </is>
       </c>
-      <c r="B74" s="18" t="n"/>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="19" t="inlineStr">
+      <c r="B75" s="18" t="n"/>
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B75" s="20" t="n"/>
-      <c r="C75" s="20" t="n"/>
-      <c r="D75" s="20" t="n"/>
-      <c r="E75" s="20" t="n"/>
-      <c r="F75" s="20" t="n"/>
-    </row>
-    <row r="76" ht="384" customHeight="1">
-      <c r="A76" s="25" t="inlineStr">
+      <c r="B76" s="20" t="n"/>
+      <c r="C76" s="20" t="n"/>
+      <c r="D76" s="20" t="n"/>
+      <c r="E76" s="20" t="n"/>
+      <c r="F76" s="20" t="n"/>
+    </row>
+    <row r="77" ht="384" customHeight="1">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -4696,39 +4697,39 @@
 다양한</t>
         </is>
       </c>
-      <c r="B76" s="26" t="n"/>
-      <c r="C76" s="26" t="n"/>
-      <c r="D76" s="26" t="n"/>
-      <c r="E76" s="26" t="n"/>
-      <c r="F76" s="26" t="n"/>
-    </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>아로마오일을 히말라야 핑크소금에 배합해
-아로마테리피 효과도 함께 누리세요.</t>
-        </is>
-      </c>
       <c r="B77" s="26" t="n"/>
       <c r="C77" s="26" t="n"/>
       <c r="D77" s="26" t="n"/>
       <c r="E77" s="26" t="n"/>
       <c r="F77" s="26" t="n"/>
     </row>
-    <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="19" t="inlineStr">
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="25" t="inlineStr">
+        <is>
+          <t>아로마오일을 히말라야 핑크소금에 배합해
+아로마테리피 효과도 함께 누리세요.</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="n"/>
+      <c r="C78" s="26" t="n"/>
+      <c r="D78" s="26" t="n"/>
+      <c r="E78" s="26" t="n"/>
+      <c r="F78" s="26" t="n"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B78" s="20" t="n"/>
-      <c r="C78" s="20" t="n"/>
-      <c r="D78" s="20" t="n"/>
-      <c r="E78" s="20" t="n"/>
-      <c r="F78" s="20" t="n"/>
-    </row>
-    <row r="79" ht="80" customHeight="1">
-      <c r="A79" s="25" t="inlineStr">
+      <c r="B79" s="20" t="n"/>
+      <c r="C79" s="20" t="n"/>
+      <c r="D79" s="20" t="n"/>
+      <c r="E79" s="20" t="n"/>
+      <c r="F79" s="20" t="n"/>
+    </row>
+    <row r="80" ht="80" customHeight="1">
+      <c r="A80" s="25" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -4737,203 +4738,203 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B79" s="26" t="n"/>
-      <c r="C79" s="26" t="n"/>
-      <c r="D79" s="26" t="n"/>
-      <c r="E79" s="26" t="n"/>
-      <c r="F79" s="26" t="n"/>
-    </row>
-    <row r="80" ht="6" customHeight="1"/>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+      <c r="B80" s="26" t="n"/>
+      <c r="C80" s="26" t="n"/>
+      <c r="D80" s="26" t="n"/>
+      <c r="E80" s="26" t="n"/>
+      <c r="F80" s="26" t="n"/>
+    </row>
+    <row r="81" ht="6" customHeight="1"/>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B81" s="8" t="n"/>
-      <c r="C81" s="8" t="n"/>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="8" t="n"/>
-      <c r="F81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="9" t="inlineStr">
+      <c r="B82" s="8" t="n"/>
+      <c r="C82" s="8" t="n"/>
+      <c r="D82" s="8" t="n"/>
+      <c r="E82" s="8" t="n"/>
+      <c r="F82" s="8" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="B83" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D82" s="9" t="inlineStr">
+      <c r="D83" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E82" s="9" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F82" s="9" t="inlineStr">
+      <c r="F83" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1">
-      <c r="A83" s="10" t="inlineStr">
+    <row r="84" ht="64" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C83" s="11" t="inlineStr">
+      <c r="C84" s="11" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D83" s="28" t="inlineStr">
+      <c r="D84" s="28" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨 · 산소금=암염, 수분함량 적고 · 미네럴 풍부 · 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="F83" s="10" t="inlineStr"/>
-    </row>
-    <row r="84" ht="48" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+      <c r="F84" s="10" t="inlineStr"/>
+    </row>
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C85" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D84" s="15" t="inlineStr">
+      <c r="D85" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr">
+      <c r="F85" s="10" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C86" s="11" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D85" s="14" t="inlineStr">
+      <c r="D86" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>입,족욕용 또는 · 바디 마사지 · 스크럽 겸용</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr"/>
-    </row>
-    <row r="86" ht="64" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
+      <c r="F86" s="10" t="inlineStr"/>
+    </row>
+    <row r="87" ht="64" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C87" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D86" s="15" t="inlineStr">
+      <c r="D87" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr">
+      <c r="F87" s="10" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="17" t="inlineStr">
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
         </is>
       </c>
-      <c r="B87" s="18" t="n"/>
-      <c r="C87" s="18" t="n"/>
-      <c r="D87" s="18" t="n"/>
-      <c r="E87" s="18" t="n"/>
-      <c r="F87" s="18" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="19" t="inlineStr">
+      <c r="B88" s="18" t="n"/>
+      <c r="C88" s="18" t="n"/>
+      <c r="D88" s="18" t="n"/>
+      <c r="E88" s="18" t="n"/>
+      <c r="F88" s="18" t="n"/>
+    </row>
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B88" s="20" t="n"/>
-      <c r="C88" s="20" t="n"/>
-      <c r="D88" s="20" t="n"/>
-      <c r="E88" s="20" t="n"/>
-      <c r="F88" s="20" t="n"/>
-    </row>
-    <row r="89" ht="256" customHeight="1">
-      <c r="A89" s="21" t="inlineStr">
+      <c r="B89" s="20" t="n"/>
+      <c r="C89" s="20" t="n"/>
+      <c r="D89" s="20" t="n"/>
+      <c r="E89" s="20" t="n"/>
+      <c r="F89" s="20" t="n"/>
+    </row>
+    <row r="90" ht="256" customHeight="1">
+      <c r="A90" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4954,20 +4955,20 @@
         </is>
       </c>
     </row>
-    <row r="90" ht="14" customHeight="1">
-      <c r="A90" s="19" t="inlineStr">
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B90" s="20" t="n"/>
-      <c r="C90" s="20" t="n"/>
-      <c r="D90" s="20" t="n"/>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="20" t="n"/>
-    </row>
-    <row r="91" ht="112" customHeight="1">
-      <c r="A91" s="21" t="inlineStr">
+      <c r="B91" s="20" t="n"/>
+      <c r="C91" s="20" t="n"/>
+      <c r="D91" s="20" t="n"/>
+      <c r="E91" s="20" t="n"/>
+      <c r="F91" s="20" t="n"/>
+    </row>
+    <row r="92" ht="112" customHeight="1">
+      <c r="A92" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -4979,201 +4980,201 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="6" customHeight="1"/>
-    <row r="93" ht="22" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+    <row r="93" ht="6" customHeight="1"/>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="7" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B93" s="8" t="n"/>
-      <c r="C93" s="8" t="n"/>
-      <c r="D93" s="8" t="n"/>
-      <c r="E93" s="8" t="n"/>
-      <c r="F93" s="8" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="9" t="inlineStr">
+      <c r="B94" s="8" t="n"/>
+      <c r="C94" s="8" t="n"/>
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="8" t="n"/>
+      <c r="F94" s="8" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="B95" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C94" s="9" t="inlineStr">
+      <c r="C95" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D94" s="9" t="inlineStr">
+      <c r="D95" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F94" s="9" t="inlineStr">
+      <c r="F95" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="48" customHeight="1">
-      <c r="A95" s="22" t="inlineStr">
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="22" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B95" s="22" t="inlineStr">
+      <c r="B96" s="22" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C95" s="23" t="inlineStr">
+      <c r="C96" s="23" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D95" s="12" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E95" s="22" t="inlineStr">
+      <c r="E96" s="22" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="F95" s="22" t="inlineStr"/>
-    </row>
-    <row r="96" ht="32" customHeight="1">
-      <c r="A96" s="22" t="inlineStr">
+      <c r="F96" s="22" t="inlineStr"/>
+    </row>
+    <row r="97" ht="32" customHeight="1">
+      <c r="A97" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B96" s="22" t="inlineStr">
+      <c r="B97" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C96" s="23" t="inlineStr">
+      <c r="C97" s="23" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E96" s="22" t="inlineStr">
+      <c r="E97" s="22" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="F96" s="22" t="inlineStr">
+      <c r="F97" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="96" customHeight="1">
-      <c r="A97" s="22" t="inlineStr">
+    <row r="98" ht="96" customHeight="1">
+      <c r="A98" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B97" s="22" t="inlineStr">
+      <c r="B98" s="22" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C97" s="23" t="inlineStr">
+      <c r="C98" s="23" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E97" s="22" t="inlineStr">
+      <c r="E98" s="22" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F97" s="22" t="inlineStr">
+      <c r="F98" s="22" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="80" customHeight="1">
-      <c r="A98" s="22" t="inlineStr">
+    <row r="99" ht="80" customHeight="1">
+      <c r="A99" s="22" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B98" s="22" t="inlineStr">
+      <c r="B99" s="22" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C98" s="23" t="inlineStr">
+      <c r="C99" s="23" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D98" s="15" t="inlineStr">
+      <c r="D99" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
+      <c r="E99" s="22" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F98" s="22" t="inlineStr">
+      <c r="F99" s="22" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="17" t="inlineStr">
+    <row r="100" ht="14" customHeight="1">
+      <c r="A100" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
         </is>
       </c>
-      <c r="B99" s="18" t="n"/>
-      <c r="C99" s="18" t="n"/>
-      <c r="D99" s="18" t="n"/>
-      <c r="E99" s="18" t="n"/>
-      <c r="F99" s="18" t="n"/>
-    </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="19" t="inlineStr">
+      <c r="B100" s="18" t="n"/>
+      <c r="C100" s="18" t="n"/>
+      <c r="D100" s="18" t="n"/>
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="18" t="n"/>
+    </row>
+    <row r="101" ht="14" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B100" s="20" t="n"/>
-      <c r="C100" s="20" t="n"/>
-      <c r="D100" s="20" t="n"/>
-      <c r="E100" s="20" t="n"/>
-      <c r="F100" s="20" t="n"/>
-    </row>
-    <row r="101" ht="64" customHeight="1">
-      <c r="A101" s="25" t="inlineStr">
+      <c r="B101" s="20" t="n"/>
+      <c r="C101" s="20" t="n"/>
+      <c r="D101" s="20" t="n"/>
+      <c r="E101" s="20" t="n"/>
+      <c r="F101" s="20" t="n"/>
+    </row>
+    <row r="102" ht="64" customHeight="1">
+      <c r="A102" s="25" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -5181,26 +5182,26 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B101" s="26" t="n"/>
-      <c r="C101" s="26" t="n"/>
-      <c r="D101" s="26" t="n"/>
-      <c r="E101" s="26" t="n"/>
-      <c r="F101" s="26" t="n"/>
-    </row>
-    <row r="102" ht="14" customHeight="1">
-      <c r="A102" s="19" t="inlineStr">
+      <c r="B102" s="26" t="n"/>
+      <c r="C102" s="26" t="n"/>
+      <c r="D102" s="26" t="n"/>
+      <c r="E102" s="26" t="n"/>
+      <c r="F102" s="26" t="n"/>
+    </row>
+    <row r="103" ht="14" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B102" s="20" t="n"/>
-      <c r="C102" s="20" t="n"/>
-      <c r="D102" s="20" t="n"/>
-      <c r="E102" s="20" t="n"/>
-      <c r="F102" s="20" t="n"/>
-    </row>
-    <row r="103" ht="192" customHeight="1">
-      <c r="A103" s="25" t="inlineStr">
+      <c r="B103" s="20" t="n"/>
+      <c r="C103" s="20" t="n"/>
+      <c r="D103" s="20" t="n"/>
+      <c r="E103" s="20" t="n"/>
+      <c r="F103" s="20" t="n"/>
+    </row>
+    <row r="104" ht="192" customHeight="1">
+      <c r="A104" s="25" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -5215,171 +5216,179 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B103" s="26" t="n"/>
-      <c r="C103" s="26" t="n"/>
-      <c r="D103" s="26" t="n"/>
-      <c r="E103" s="26" t="n"/>
-      <c r="F103" s="26" t="n"/>
-    </row>
-    <row r="104" ht="6" customHeight="1"/>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="7" t="inlineStr">
+      <c r="B104" s="26" t="n"/>
+      <c r="C104" s="26" t="n"/>
+      <c r="D104" s="26" t="n"/>
+      <c r="E104" s="26" t="n"/>
+      <c r="F104" s="26" t="n"/>
+    </row>
+    <row r="105" ht="186" customHeight="1">
+      <c r="A105" s="26" t="n"/>
+      <c r="B105" s="26" t="n"/>
+      <c r="C105" s="26" t="n"/>
+      <c r="D105" s="26" t="n"/>
+      <c r="E105" s="26" t="n"/>
+      <c r="F105" s="26" t="n"/>
+    </row>
+    <row r="106" ht="6" customHeight="1"/>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="9" t="inlineStr">
+      <c r="B107" s="8" t="n"/>
+      <c r="C107" s="8" t="n"/>
+      <c r="D107" s="8" t="n"/>
+      <c r="E107" s="8" t="n"/>
+      <c r="F107" s="8" t="n"/>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B106" s="9" t="inlineStr">
+      <c r="B108" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C106" s="9" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D106" s="9" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E106" s="9" t="inlineStr">
+      <c r="E108" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F106" s="9" t="inlineStr">
+      <c r="F108" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="32" customHeight="1">
-      <c r="A107" s="10" t="inlineStr">
+    <row r="109" ht="32" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B109" s="10" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C107" s="11" t="inlineStr">
+      <c r="C109" s="11" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D107" s="14" t="inlineStr">
+      <c r="D109" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E107" s="10" t="inlineStr">
+      <c r="E109" s="10" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F107" s="10" t="inlineStr"/>
-    </row>
-    <row r="108" ht="48" customHeight="1">
-      <c r="A108" s="10" t="inlineStr">
+      <c r="F109" s="10" t="inlineStr"/>
+    </row>
+    <row r="110" ht="48" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C108" s="11" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D108" s="27" t="inlineStr">
+      <c r="D110" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E108" s="10" t="inlineStr">
+      <c r="E110" s="10" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 · 시어버터, 아보카도, 꿀추출물 등 · 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="F108" s="10" t="inlineStr"/>
-    </row>
-    <row r="109" ht="80" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
+      <c r="F110" s="10" t="inlineStr"/>
+    </row>
+    <row r="111" ht="80" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B111" s="10" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr">
+      <c r="C111" s="11" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E111" s="10" t="inlineStr">
         <is>
           <t>아로마테라피 · 여드름-티트리 · 바디 용도별 추천오일 · 쿨링 :페파민트 · 다이어트 : 레몬+자몽오일 · 이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr">
+      <c r="F111" s="10" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="17" t="inlineStr">
+    <row r="112" ht="14" customHeight="1">
+      <c r="A112" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
         </is>
       </c>
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
-      <c r="E110" s="18" t="n"/>
-      <c r="F110" s="18" t="n"/>
-    </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="19" t="inlineStr">
+      <c r="B112" s="18" t="n"/>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+    </row>
+    <row r="113" ht="14" customHeight="1">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B111" s="20" t="n"/>
-      <c r="C111" s="20" t="n"/>
-      <c r="D111" s="20" t="n"/>
-      <c r="E111" s="20" t="n"/>
-      <c r="F111" s="20" t="n"/>
-    </row>
-    <row r="112" ht="384" customHeight="1">
-      <c r="A112" s="21" t="inlineStr">
+      <c r="B113" s="20" t="n"/>
+      <c r="C113" s="20" t="n"/>
+      <c r="D113" s="20" t="n"/>
+      <c r="E113" s="20" t="n"/>
+      <c r="F113" s="20" t="n"/>
+    </row>
+    <row r="114" ht="384" customHeight="1">
+      <c r="A114" s="21" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5408,8 +5417,8 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="112" customHeight="1">
-      <c r="A113" s="21" t="inlineStr">
+    <row r="115" ht="112" customHeight="1">
+      <c r="A115" s="21" t="inlineStr">
         <is>
           <t>알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
@@ -5421,20 +5430,20 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="19" t="inlineStr">
+    <row r="116" ht="14" customHeight="1">
+      <c r="A116" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B114" s="20" t="n"/>
-      <c r="C114" s="20" t="n"/>
-      <c r="D114" s="20" t="n"/>
-      <c r="E114" s="20" t="n"/>
-      <c r="F114" s="20" t="n"/>
-    </row>
-    <row r="115" ht="80" customHeight="1">
-      <c r="A115" s="21" t="inlineStr">
+      <c r="B116" s="20" t="n"/>
+      <c r="C116" s="20" t="n"/>
+      <c r="D116" s="20" t="n"/>
+      <c r="E116" s="20" t="n"/>
+      <c r="F116" s="20" t="n"/>
+    </row>
+    <row r="117" ht="80" customHeight="1">
+      <c r="A117" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -5444,261 +5453,261 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="6" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="7" t="inlineStr">
+    <row r="118" ht="6" customHeight="1"/>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="7" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B117" s="8" t="n"/>
-      <c r="C117" s="8" t="n"/>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="B119" s="8" t="n"/>
+      <c r="C119" s="8" t="n"/>
+      <c r="D119" s="8" t="n"/>
+      <c r="E119" s="8" t="n"/>
+      <c r="F119" s="8" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr">
+      <c r="B120" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C118" s="9" t="inlineStr">
+      <c r="C120" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D118" s="9" t="inlineStr">
+      <c r="D120" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E118" s="9" t="inlineStr">
+      <c r="E120" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F118" s="9" t="inlineStr">
+      <c r="F120" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="22" t="inlineStr">
+    <row r="121" ht="16" customHeight="1">
+      <c r="A121" s="22" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B119" s="22" t="inlineStr">
+      <c r="B121" s="22" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C119" s="23" t="inlineStr">
+      <c r="C121" s="23" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D119" s="12" t="inlineStr">
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E119" s="22" t="inlineStr">
+      <c r="E121" s="22" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F119" s="22" t="inlineStr"/>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="22" t="inlineStr">
+      <c r="F121" s="22" t="inlineStr"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="22" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B120" s="22" t="inlineStr">
+      <c r="B122" s="22" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C120" s="23" t="inlineStr">
+      <c r="C122" s="23" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D120" s="12" t="inlineStr">
+      <c r="D122" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E120" s="22" t="inlineStr">
+      <c r="E122" s="22" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F120" s="22" t="inlineStr">
+      <c r="F122" s="22" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="96" customHeight="1">
-      <c r="A121" s="22" t="inlineStr">
+    <row r="123" ht="96" customHeight="1">
+      <c r="A123" s="22" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B121" s="22" t="inlineStr">
+      <c r="B123" s="22" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
+      <c r="C123" s="23" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D121" s="14" t="inlineStr">
+      <c r="D123" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E121" s="22" t="inlineStr">
+      <c r="E123" s="22" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F121" s="22" t="inlineStr">
+      <c r="F123" s="22" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="32" customHeight="1">
-      <c r="A122" s="22" t="inlineStr">
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="22" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B122" s="22" t="inlineStr">
+      <c r="B124" s="22" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C122" s="23" t="inlineStr">
+      <c r="C124" s="23" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D122" s="16" t="inlineStr">
+      <c r="D124" s="16" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E124" s="22" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F122" s="22" t="inlineStr"/>
-    </row>
-    <row r="123" ht="32" customHeight="1">
-      <c r="A123" s="22" t="inlineStr">
+      <c r="F124" s="22" t="inlineStr"/>
+    </row>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="22" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B123" s="22" t="inlineStr">
+      <c r="B125" s="22" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C123" s="23" t="inlineStr">
+      <c r="C125" s="23" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D123" s="27" t="inlineStr">
+      <c r="D125" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E123" s="22" t="inlineStr">
+      <c r="E125" s="22" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="F123" s="22" t="inlineStr">
+      <c r="F125" s="22" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="64" customHeight="1">
-      <c r="A124" s="22" t="inlineStr">
+    <row r="126" ht="64" customHeight="1">
+      <c r="A126" s="22" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B126" s="22" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
+      <c r="C126" s="23" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D124" s="13" t="inlineStr">
+      <c r="D126" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E124" s="22" t="inlineStr">
+      <c r="E126" s="22" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="F124" s="22" t="inlineStr">
+      <c r="F126" s="22" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="17" t="inlineStr">
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
         </is>
       </c>
-      <c r="B125" s="18" t="n"/>
-      <c r="C125" s="18" t="n"/>
-      <c r="D125" s="18" t="n"/>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-    </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="19" t="inlineStr">
+      <c r="B127" s="18" t="n"/>
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+    </row>
+    <row r="128" ht="14" customHeight="1">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B126" s="20" t="n"/>
-      <c r="C126" s="20" t="n"/>
-      <c r="D126" s="20" t="n"/>
-      <c r="E126" s="20" t="n"/>
-      <c r="F126" s="20" t="n"/>
-    </row>
-    <row r="127" ht="224" customHeight="1">
-      <c r="A127" s="25" t="inlineStr">
+      <c r="B128" s="20" t="n"/>
+      <c r="C128" s="20" t="n"/>
+      <c r="D128" s="20" t="n"/>
+      <c r="E128" s="20" t="n"/>
+      <c r="F128" s="20" t="n"/>
+    </row>
+    <row r="129" ht="224" customHeight="1">
+      <c r="A129" s="25" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -5716,26 +5725,26 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B127" s="26" t="n"/>
-      <c r="C127" s="26" t="n"/>
-      <c r="D127" s="26" t="n"/>
-      <c r="E127" s="26" t="n"/>
-      <c r="F127" s="26" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="B129" s="26" t="n"/>
+      <c r="C129" s="26" t="n"/>
+      <c r="D129" s="26" t="n"/>
+      <c r="E129" s="26" t="n"/>
+      <c r="F129" s="26" t="n"/>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B128" s="20" t="n"/>
-      <c r="C128" s="20" t="n"/>
-      <c r="D128" s="20" t="n"/>
-      <c r="E128" s="20" t="n"/>
-      <c r="F128" s="20" t="n"/>
-    </row>
-    <row r="129" ht="160" customHeight="1">
-      <c r="A129" s="25" t="inlineStr">
+      <c r="B130" s="20" t="n"/>
+      <c r="C130" s="20" t="n"/>
+      <c r="D130" s="20" t="n"/>
+      <c r="E130" s="20" t="n"/>
+      <c r="F130" s="20" t="n"/>
+    </row>
+    <row r="131" ht="160" customHeight="1">
+      <c r="A131" s="25" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -5749,299 +5758,307 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B129" s="26" t="n"/>
-      <c r="C129" s="26" t="n"/>
-      <c r="D129" s="26" t="n"/>
-      <c r="E129" s="26" t="n"/>
-      <c r="F129" s="26" t="n"/>
-    </row>
-    <row r="130" ht="6" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="7" t="inlineStr">
+      <c r="B131" s="26" t="n"/>
+      <c r="C131" s="26" t="n"/>
+      <c r="D131" s="26" t="n"/>
+      <c r="E131" s="26" t="n"/>
+      <c r="F131" s="26" t="n"/>
+    </row>
+    <row r="132" ht="125.4999999999999" customHeight="1">
+      <c r="A132" s="26" t="n"/>
+      <c r="B132" s="26" t="n"/>
+      <c r="C132" s="26" t="n"/>
+      <c r="D132" s="26" t="n"/>
+      <c r="E132" s="26" t="n"/>
+      <c r="F132" s="26" t="n"/>
+    </row>
+    <row r="133" ht="6" customHeight="1"/>
+    <row r="134" ht="22" customHeight="1">
+      <c r="A134" s="7" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="8" t="n"/>
-    </row>
-    <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="9" t="inlineStr">
+      <c r="B134" s="8" t="n"/>
+      <c r="C134" s="8" t="n"/>
+      <c r="D134" s="8" t="n"/>
+      <c r="E134" s="8" t="n"/>
+      <c r="F134" s="8" t="n"/>
+    </row>
+    <row r="135" ht="15" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B132" s="9" t="inlineStr">
+      <c r="B135" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C132" s="9" t="inlineStr">
+      <c r="C135" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D132" s="9" t="inlineStr">
+      <c r="D135" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E132" s="9" t="inlineStr">
+      <c r="E135" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F132" s="9" t="inlineStr">
+      <c r="F135" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="10" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="10" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B133" s="10" t="inlineStr">
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C133" s="11" t="inlineStr">
+      <c r="C136" s="11" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D133" s="27" t="inlineStr">
+      <c r="D136" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E133" s="10" t="inlineStr">
+      <c r="E136" s="10" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="F133" s="10" t="inlineStr">
+      <c r="F136" s="10" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="32" customHeight="1">
-      <c r="A134" s="10" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="10" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B134" s="10" t="inlineStr">
+      <c r="B137" s="10" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C134" s="11" t="inlineStr">
+      <c r="C137" s="11" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D134" s="27" t="inlineStr">
+      <c r="D137" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E134" s="10" t="inlineStr">
+      <c r="E137" s="10" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="F134" s="10" t="inlineStr">
+      <c r="F137" s="10" t="inlineStr">
         <is>
           <t>버터류</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="48" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
-        <is>
-          <t>올리브유화왁스</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>12g</t>
-        </is>
-      </c>
-      <c r="C135" s="11" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="D135" s="29" t="inlineStr">
-        <is>
-          <t>유화</t>
-        </is>
-      </c>
-      <c r="E135" s="10" t="inlineStr">
-        <is>
-          <t>에코인증, 물과 오일의 분리를 저지</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="inlineStr">
-        <is>
-          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="64" customHeight="1">
-      <c r="A136" s="10" t="inlineStr">
-        <is>
-          <t>순한 (샴푸) / 베이스</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>38g</t>
-        </is>
-      </c>
-      <c r="C136" s="11" t="inlineStr">
-        <is>
-          <t>14%</t>
-        </is>
-      </c>
-      <c r="D136" s="16" t="inlineStr">
-        <is>
-          <t>계면</t>
-        </is>
-      </c>
-      <c r="E136" s="10" t="inlineStr">
-        <is>
-          <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
-        </is>
-      </c>
-      <c r="F136" s="10" t="inlineStr"/>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
-        <is>
-          <t>식물성 글리세린</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>13g</t>
-        </is>
-      </c>
-      <c r="C137" s="11" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D137" s="24" t="inlineStr">
-        <is>
-          <t>보습</t>
-        </is>
-      </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>보습제</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
-        <is>
-          <t>꿀 등</t>
         </is>
       </c>
     </row>
     <row r="138" ht="48" customHeight="1">
       <c r="A138" s="10" t="inlineStr">
         <is>
+          <t>올리브유화왁스</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>12g</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="D138" s="29" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>에코인증, 물과 오일의 분리를 저지</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="64" customHeight="1">
+      <c r="A139" s="10" t="inlineStr">
+        <is>
+          <t>순한 (샴푸) / 베이스</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="inlineStr">
+        <is>
+          <t>38g</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="D139" s="16" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E139" s="10" t="inlineStr">
+        <is>
+          <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
+        </is>
+      </c>
+      <c r="F139" s="10" t="inlineStr"/>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="10" t="inlineStr">
+        <is>
+          <t>식물성 글리세린</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>13g</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D140" s="24" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="E140" s="10" t="inlineStr">
+        <is>
+          <t>보습제</t>
+        </is>
+      </c>
+      <c r="F140" s="10" t="inlineStr">
+        <is>
+          <t>꿀 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="48" customHeight="1">
+      <c r="A141" s="10" t="inlineStr">
+        <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C141" s="11" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D138" s="14" t="inlineStr">
+      <c r="D141" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E141" s="10" t="inlineStr">
         <is>
           <t>각질제거, 보습. · 필요에 따라 양을 더 넣어서 · 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="F138" s="10" t="inlineStr"/>
-    </row>
-    <row r="139" ht="32" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
+      <c r="F141" s="10" t="inlineStr"/>
+    </row>
+    <row r="142" ht="32" customHeight="1">
+      <c r="A142" s="10" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B142" s="10" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C142" s="11" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D139" s="15" t="inlineStr">
+      <c r="D142" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E142" s="10" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr">
+      <c r="F142" s="10" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="17" t="inlineStr">
+    <row r="143" ht="14" customHeight="1">
+      <c r="A143" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
         </is>
       </c>
-      <c r="B140" s="18" t="n"/>
-      <c r="C140" s="18" t="n"/>
-      <c r="D140" s="18" t="n"/>
-      <c r="E140" s="18" t="n"/>
-      <c r="F140" s="18" t="n"/>
-    </row>
-    <row r="141" ht="14" customHeight="1">
-      <c r="A141" s="19" t="inlineStr">
+      <c r="B143" s="18" t="n"/>
+      <c r="C143" s="18" t="n"/>
+      <c r="D143" s="18" t="n"/>
+      <c r="E143" s="18" t="n"/>
+      <c r="F143" s="18" t="n"/>
+    </row>
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B141" s="20" t="n"/>
-      <c r="C141" s="20" t="n"/>
-      <c r="D141" s="20" t="n"/>
-      <c r="E141" s="20" t="n"/>
-      <c r="F141" s="20" t="n"/>
-    </row>
-    <row r="142" ht="336" customHeight="1">
-      <c r="A142" s="21" t="inlineStr">
+      <c r="B144" s="20" t="n"/>
+      <c r="C144" s="20" t="n"/>
+      <c r="D144" s="20" t="n"/>
+      <c r="E144" s="20" t="n"/>
+      <c r="F144" s="20" t="n"/>
+    </row>
+    <row r="145" ht="336" customHeight="1">
+      <c r="A145" s="21" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -6067,141 +6084,142 @@
         </is>
       </c>
     </row>
-    <row r="143" ht="6" customHeight="1"/>
-    <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="7" t="inlineStr">
+    <row r="146" ht="256.5" customHeight="1"/>
+    <row r="147" ht="6" customHeight="1"/>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="7" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B144" s="8" t="n"/>
-      <c r="C144" s="8" t="n"/>
-      <c r="D144" s="8" t="n"/>
-      <c r="E144" s="8" t="n"/>
-      <c r="F144" s="8" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="B148" s="8" t="n"/>
+      <c r="C148" s="8" t="n"/>
+      <c r="D148" s="8" t="n"/>
+      <c r="E148" s="8" t="n"/>
+      <c r="F148" s="8" t="n"/>
+    </row>
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B145" s="9" t="inlineStr">
+      <c r="B149" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C145" s="9" t="inlineStr">
+      <c r="C149" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D145" s="9" t="inlineStr">
+      <c r="D149" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E145" s="9" t="inlineStr">
+      <c r="E149" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F145" s="9" t="inlineStr">
+      <c r="F149" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="64" customHeight="1">
-      <c r="A146" s="22" t="inlineStr">
+    <row r="150" ht="64" customHeight="1">
+      <c r="A150" s="22" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B146" s="22" t="inlineStr">
+      <c r="B150" s="22" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C146" s="23" t="inlineStr">
+      <c r="C150" s="23" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="D146" s="27" t="inlineStr">
+      <c r="D150" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E146" s="22" t="inlineStr">
+      <c r="E150" s="22" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
-      <c r="F146" s="22" t="inlineStr">
+      <c r="F150" s="22" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="48" customHeight="1">
-      <c r="A147" s="22" t="inlineStr">
+    <row r="151" ht="48" customHeight="1">
+      <c r="A151" s="22" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B147" s="22" t="inlineStr">
+      <c r="B151" s="22" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C147" s="23" t="inlineStr">
+      <c r="C151" s="23" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="D147" s="15" t="inlineStr">
+      <c r="D151" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E147" s="22" t="inlineStr">
+      <c r="E151" s="22" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 · 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="F147" s="22" t="inlineStr">
+      <c r="F151" s="22" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="17" t="inlineStr">
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 48 · 향 52</t>
         </is>
       </c>
-      <c r="B148" s="18" t="n"/>
-      <c r="C148" s="18" t="n"/>
-      <c r="D148" s="18" t="n"/>
-      <c r="E148" s="18" t="n"/>
-      <c r="F148" s="18" t="n"/>
-    </row>
-    <row r="149" ht="14" customHeight="1">
-      <c r="A149" s="19" t="inlineStr">
+      <c r="B152" s="18" t="n"/>
+      <c r="C152" s="18" t="n"/>
+      <c r="D152" s="18" t="n"/>
+      <c r="E152" s="18" t="n"/>
+      <c r="F152" s="18" t="n"/>
+    </row>
+    <row r="153" ht="14" customHeight="1">
+      <c r="A153" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B149" s="20" t="n"/>
-      <c r="C149" s="20" t="n"/>
-      <c r="D149" s="20" t="n"/>
-      <c r="E149" s="20" t="n"/>
-      <c r="F149" s="20" t="n"/>
-    </row>
-    <row r="150" ht="384" customHeight="1">
-      <c r="A150" s="25" t="inlineStr">
+      <c r="B153" s="20" t="n"/>
+      <c r="C153" s="20" t="n"/>
+      <c r="D153" s="20" t="n"/>
+      <c r="E153" s="20" t="n"/>
+      <c r="F153" s="20" t="n"/>
+    </row>
+    <row r="154" ht="384" customHeight="1">
+      <c r="A154" s="25" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -6229,40 +6247,40 @@
 항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
         </is>
       </c>
-      <c r="B150" s="26" t="n"/>
-      <c r="C150" s="26" t="n"/>
-      <c r="D150" s="26" t="n"/>
-      <c r="E150" s="26" t="n"/>
-      <c r="F150" s="26" t="n"/>
-    </row>
-    <row r="151" ht="48" customHeight="1">
-      <c r="A151" s="25" t="inlineStr">
+      <c r="B154" s="26" t="n"/>
+      <c r="C154" s="26" t="n"/>
+      <c r="D154" s="26" t="n"/>
+      <c r="E154" s="26" t="n"/>
+      <c r="F154" s="26" t="n"/>
+    </row>
+    <row r="155" ht="48" customHeight="1">
+      <c r="A155" s="25" t="inlineStr">
         <is>
           <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B151" s="26" t="n"/>
-      <c r="C151" s="26" t="n"/>
-      <c r="D151" s="26" t="n"/>
-      <c r="E151" s="26" t="n"/>
-      <c r="F151" s="26" t="n"/>
-    </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="19" t="inlineStr">
+      <c r="B155" s="26" t="n"/>
+      <c r="C155" s="26" t="n"/>
+      <c r="D155" s="26" t="n"/>
+      <c r="E155" s="26" t="n"/>
+      <c r="F155" s="26" t="n"/>
+    </row>
+    <row r="156" ht="14" customHeight="1">
+      <c r="A156" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B152" s="20" t="n"/>
-      <c r="C152" s="20" t="n"/>
-      <c r="D152" s="20" t="n"/>
-      <c r="E152" s="20" t="n"/>
-      <c r="F152" s="20" t="n"/>
-    </row>
-    <row r="153" ht="320" customHeight="1">
-      <c r="A153" s="25" t="inlineStr">
+      <c r="B156" s="20" t="n"/>
+      <c r="C156" s="20" t="n"/>
+      <c r="D156" s="20" t="n"/>
+      <c r="E156" s="20" t="n"/>
+      <c r="F156" s="20" t="n"/>
+    </row>
+    <row r="157" ht="320" customHeight="1">
+      <c r="A157" s="25" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -6286,175 +6304,183 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B153" s="26" t="n"/>
-      <c r="C153" s="26" t="n"/>
-      <c r="D153" s="26" t="n"/>
-      <c r="E153" s="26" t="n"/>
-      <c r="F153" s="26" t="n"/>
-    </row>
-    <row r="154" ht="6" customHeight="1"/>
-    <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
+      <c r="B157" s="26" t="n"/>
+      <c r="C157" s="26" t="n"/>
+      <c r="D157" s="26" t="n"/>
+      <c r="E157" s="26" t="n"/>
+      <c r="F157" s="26" t="n"/>
+    </row>
+    <row r="158" ht="30.50000000000006" customHeight="1">
+      <c r="A158" s="26" t="n"/>
+      <c r="B158" s="26" t="n"/>
+      <c r="C158" s="26" t="n"/>
+      <c r="D158" s="26" t="n"/>
+      <c r="E158" s="26" t="n"/>
+      <c r="F158" s="26" t="n"/>
+    </row>
+    <row r="159" ht="6" customHeight="1"/>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="7" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B155" s="8" t="n"/>
-      <c r="C155" s="8" t="n"/>
-      <c r="D155" s="8" t="n"/>
-      <c r="E155" s="8" t="n"/>
-      <c r="F155" s="8" t="n"/>
-    </row>
-    <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="9" t="inlineStr">
+      <c r="B160" s="8" t="n"/>
+      <c r="C160" s="8" t="n"/>
+      <c r="D160" s="8" t="n"/>
+      <c r="E160" s="8" t="n"/>
+      <c r="F160" s="8" t="n"/>
+    </row>
+    <row r="161" ht="15" customHeight="1">
+      <c r="A161" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B156" s="9" t="inlineStr">
+      <c r="B161" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C156" s="9" t="inlineStr">
+      <c r="C161" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D156" s="9" t="inlineStr">
+      <c r="D161" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E156" s="9" t="inlineStr">
+      <c r="E161" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F156" s="9" t="inlineStr">
+      <c r="F161" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="64" customHeight="1">
-      <c r="A157" s="10" t="inlineStr">
+    <row r="162" ht="64" customHeight="1">
+      <c r="A162" s="10" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B157" s="10" t="inlineStr">
+      <c r="B162" s="10" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C157" s="11" t="inlineStr"/>
-      <c r="D157" s="12" t="inlineStr">
+      <c r="C162" s="11" t="inlineStr"/>
+      <c r="D162" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E157" s="10" t="inlineStr">
+      <c r="E162" s="10" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F157" s="10" t="inlineStr"/>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="F162" s="10" t="inlineStr"/>
+    </row>
+    <row r="163" ht="32" customHeight="1">
+      <c r="A163" s="10" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B158" s="10" t="inlineStr">
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C158" s="11" t="inlineStr"/>
-      <c r="D158" s="12" t="inlineStr">
+      <c r="C163" s="11" t="inlineStr"/>
+      <c r="D163" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E158" s="10" t="inlineStr">
+      <c r="E163" s="10" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F158" s="10" t="inlineStr">
+      <c r="F163" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="32" customHeight="1">
-      <c r="A159" s="10" t="inlineStr">
+    <row r="164" ht="32" customHeight="1">
+      <c r="A164" s="10" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B159" s="10" t="inlineStr">
+      <c r="B164" s="10" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C159" s="11" t="inlineStr"/>
-      <c r="D159" s="13" t="inlineStr">
+      <c r="C164" s="11" t="inlineStr"/>
+      <c r="D164" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E159" s="10" t="inlineStr">
+      <c r="E164" s="10" t="inlineStr">
         <is>
           <t>스크럽, 노폐물 · 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="F159" s="10" t="inlineStr"/>
-    </row>
-    <row r="160" ht="96" customHeight="1">
-      <c r="A160" s="10" t="inlineStr">
+      <c r="F164" s="10" t="inlineStr"/>
+    </row>
+    <row r="165" ht="96" customHeight="1">
+      <c r="A165" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B160" s="10" t="inlineStr">
+      <c r="B165" s="10" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C160" s="11" t="inlineStr"/>
-      <c r="D160" s="12" t="inlineStr">
+      <c r="C165" s="11" t="inlineStr"/>
+      <c r="D165" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E160" s="10" t="inlineStr">
+      <c r="E165" s="10" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F160" s="10" t="inlineStr">
+      <c r="F165" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="14" customHeight="1">
-      <c r="A161" s="19" t="inlineStr">
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B161" s="20" t="n"/>
-      <c r="C161" s="20" t="n"/>
-      <c r="D161" s="20" t="n"/>
-      <c r="E161" s="20" t="n"/>
-      <c r="F161" s="20" t="n"/>
-    </row>
-    <row r="162" ht="176" customHeight="1">
-      <c r="A162" s="21" t="inlineStr">
+      <c r="B166" s="20" t="n"/>
+      <c r="C166" s="20" t="n"/>
+      <c r="D166" s="20" t="n"/>
+      <c r="E166" s="20" t="n"/>
+      <c r="F166" s="20" t="n"/>
+    </row>
+    <row r="167" ht="176" customHeight="1">
+      <c r="A167" s="21" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -6468,121 +6494,121 @@
         </is>
       </c>
     </row>
-    <row r="163" ht="6" customHeight="1"/>
-    <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="7" t="inlineStr">
+    <row r="168" ht="6" customHeight="1"/>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="8" t="n"/>
-      <c r="D164" s="8" t="n"/>
-      <c r="E164" s="8" t="n"/>
-      <c r="F164" s="8" t="n"/>
-    </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="9" t="inlineStr">
+      <c r="B169" s="8" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="8" t="n"/>
+      <c r="F169" s="8" t="n"/>
+    </row>
+    <row r="170" ht="15" customHeight="1">
+      <c r="A170" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B165" s="9" t="inlineStr">
+      <c r="B170" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C165" s="9" t="inlineStr">
+      <c r="C170" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D165" s="9" t="inlineStr">
+      <c r="D170" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E165" s="9" t="inlineStr">
+      <c r="E170" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F165" s="9" t="inlineStr">
+      <c r="F170" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="32" customHeight="1">
-      <c r="A166" s="22" t="inlineStr">
+    <row r="171" ht="32" customHeight="1">
+      <c r="A171" s="22" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B166" s="22" t="inlineStr">
+      <c r="B171" s="22" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C166" s="23" t="inlineStr"/>
-      <c r="D166" s="14" t="inlineStr">
+      <c r="C171" s="23" t="inlineStr"/>
+      <c r="D171" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E166" s="22" t="inlineStr">
+      <c r="E171" s="22" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="F166" s="22" t="inlineStr">
+      <c r="F171" s="22" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="64" customHeight="1">
-      <c r="A167" s="22" t="inlineStr">
+    <row r="172" ht="64" customHeight="1">
+      <c r="A172" s="22" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B167" s="22" t="inlineStr">
+      <c r="B172" s="22" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C167" s="23" t="inlineStr"/>
-      <c r="D167" s="30" t="inlineStr">
+      <c r="C172" s="23" t="inlineStr"/>
+      <c r="D172" s="30" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E167" s="22" t="inlineStr">
+      <c r="E172" s="22" t="inlineStr">
         <is>
           <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
-      <c r="F167" s="22" t="inlineStr">
+      <c r="F172" s="22" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="14" customHeight="1">
-      <c r="A168" s="19" t="inlineStr">
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B168" s="20" t="n"/>
-      <c r="C168" s="20" t="n"/>
-      <c r="D168" s="20" t="n"/>
-      <c r="E168" s="20" t="n"/>
-      <c r="F168" s="20" t="n"/>
-    </row>
-    <row r="169" ht="112" customHeight="1">
-      <c r="A169" s="25" t="inlineStr">
+      <c r="B173" s="20" t="n"/>
+      <c r="C173" s="20" t="n"/>
+      <c r="D173" s="20" t="n"/>
+      <c r="E173" s="20" t="n"/>
+      <c r="F173" s="20" t="n"/>
+    </row>
+    <row r="174" ht="112" customHeight="1">
+      <c r="A174" s="25" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -6590,26 +6616,26 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B169" s="26" t="n"/>
-      <c r="C169" s="26" t="n"/>
-      <c r="D169" s="26" t="n"/>
-      <c r="E169" s="26" t="n"/>
-      <c r="F169" s="26" t="n"/>
-    </row>
-    <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="19" t="inlineStr">
+      <c r="B174" s="26" t="n"/>
+      <c r="C174" s="26" t="n"/>
+      <c r="D174" s="26" t="n"/>
+      <c r="E174" s="26" t="n"/>
+      <c r="F174" s="26" t="n"/>
+    </row>
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B170" s="20" t="n"/>
-      <c r="C170" s="20" t="n"/>
-      <c r="D170" s="20" t="n"/>
-      <c r="E170" s="20" t="n"/>
-      <c r="F170" s="20" t="n"/>
-    </row>
-    <row r="171" ht="112" customHeight="1">
-      <c r="A171" s="25" t="inlineStr">
+      <c r="B175" s="20" t="n"/>
+      <c r="C175" s="20" t="n"/>
+      <c r="D175" s="20" t="n"/>
+      <c r="E175" s="20" t="n"/>
+      <c r="F175" s="20" t="n"/>
+    </row>
+    <row r="176" ht="112" customHeight="1">
+      <c r="A176" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -6619,235 +6645,243 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B171" s="26" t="n"/>
-      <c r="C171" s="26" t="n"/>
-      <c r="D171" s="26" t="n"/>
-      <c r="E171" s="26" t="n"/>
-      <c r="F171" s="26" t="n"/>
-    </row>
-    <row r="172" ht="6" customHeight="1"/>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
+      <c r="B176" s="26" t="n"/>
+      <c r="C176" s="26" t="n"/>
+      <c r="D176" s="26" t="n"/>
+      <c r="E176" s="26" t="n"/>
+      <c r="F176" s="26" t="n"/>
+    </row>
+    <row r="177" ht="22.99999999999997" customHeight="1">
+      <c r="A177" s="26" t="n"/>
+      <c r="B177" s="26" t="n"/>
+      <c r="C177" s="26" t="n"/>
+      <c r="D177" s="26" t="n"/>
+      <c r="E177" s="26" t="n"/>
+      <c r="F177" s="26" t="n"/>
+    </row>
+    <row r="178" ht="6" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="7" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B173" s="8" t="n"/>
-      <c r="C173" s="8" t="n"/>
-      <c r="D173" s="8" t="n"/>
-      <c r="E173" s="8" t="n"/>
-      <c r="F173" s="8" t="n"/>
-    </row>
-    <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="9" t="inlineStr">
+      <c r="B179" s="8" t="n"/>
+      <c r="C179" s="8" t="n"/>
+      <c r="D179" s="8" t="n"/>
+      <c r="E179" s="8" t="n"/>
+      <c r="F179" s="8" t="n"/>
+    </row>
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B174" s="9" t="inlineStr">
+      <c r="B180" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D174" s="9" t="inlineStr">
+      <c r="D180" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E174" s="9" t="inlineStr">
+      <c r="E180" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F174" s="9" t="inlineStr">
+      <c r="F180" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="64" customHeight="1">
-      <c r="A175" s="10" t="inlineStr">
+    <row r="181" ht="64" customHeight="1">
+      <c r="A181" s="10" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B175" s="10" t="inlineStr">
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C175" s="11" t="inlineStr"/>
-      <c r="D175" s="12" t="inlineStr">
+      <c r="C181" s="11" t="inlineStr"/>
+      <c r="D181" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E175" s="10" t="inlineStr">
+      <c r="E181" s="10" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F175" s="10" t="inlineStr"/>
-    </row>
-    <row r="176" ht="32" customHeight="1">
-      <c r="A176" s="10" t="inlineStr">
+      <c r="F181" s="10" t="inlineStr"/>
+    </row>
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="10" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B176" s="10" t="inlineStr">
+      <c r="B182" s="10" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C176" s="11" t="inlineStr"/>
-      <c r="D176" s="12" t="inlineStr">
+      <c r="C182" s="11" t="inlineStr"/>
+      <c r="D182" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E176" s="10" t="inlineStr">
+      <c r="E182" s="10" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F176" s="10" t="inlineStr">
+      <c r="F182" s="10" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="96" customHeight="1">
-      <c r="A177" s="10" t="inlineStr">
+    <row r="183" ht="96" customHeight="1">
+      <c r="A183" s="10" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B177" s="10" t="inlineStr">
+      <c r="B183" s="10" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C177" s="11" t="inlineStr"/>
-      <c r="D177" s="12" t="inlineStr">
+      <c r="C183" s="11" t="inlineStr"/>
+      <c r="D183" s="12" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E177" s="10" t="inlineStr">
+      <c r="E183" s="10" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F177" s="10" t="inlineStr">
+      <c r="F183" s="10" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="48" customHeight="1">
-      <c r="A178" s="10" t="inlineStr">
+    <row r="184" ht="48" customHeight="1">
+      <c r="A184" s="10" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B178" s="10" t="inlineStr">
+      <c r="B184" s="10" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C178" s="11" t="inlineStr"/>
-      <c r="D178" s="13" t="inlineStr">
+      <c r="C184" s="11" t="inlineStr"/>
+      <c r="D184" s="13" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E178" s="10" t="inlineStr">
+      <c r="E184" s="10" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F178" s="10" t="inlineStr">
+      <c r="F184" s="10" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="80" customHeight="1">
-      <c r="A179" s="10" t="inlineStr">
+    <row r="185" ht="80" customHeight="1">
+      <c r="A185" s="10" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B179" s="10" t="inlineStr">
+      <c r="B185" s="10" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C179" s="11" t="inlineStr"/>
-      <c r="D179" s="27" t="inlineStr">
+      <c r="C185" s="11" t="inlineStr"/>
+      <c r="D185" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E179" s="10" t="inlineStr">
+      <c r="E185" s="10" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F179" s="10" t="inlineStr">
+      <c r="F185" s="10" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="32" customHeight="1">
-      <c r="A180" s="10" t="inlineStr">
+    <row r="186" ht="32" customHeight="1">
+      <c r="A186" s="10" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B180" s="10" t="inlineStr">
+      <c r="B186" s="10" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C180" s="11" t="inlineStr"/>
-      <c r="D180" s="14" t="inlineStr">
+      <c r="C186" s="11" t="inlineStr"/>
+      <c r="D186" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E180" s="10" t="inlineStr">
+      <c r="E186" s="10" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="F180" s="10" t="inlineStr">
+      <c r="F186" s="10" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="14" customHeight="1">
-      <c r="A181" s="19" t="inlineStr">
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B181" s="20" t="n"/>
-      <c r="C181" s="20" t="n"/>
-      <c r="D181" s="20" t="n"/>
-      <c r="E181" s="20" t="n"/>
-      <c r="F181" s="20" t="n"/>
-    </row>
-    <row r="182" ht="112" customHeight="1">
-      <c r="A182" s="21" t="inlineStr">
+      <c r="B187" s="20" t="n"/>
+      <c r="C187" s="20" t="n"/>
+      <c r="D187" s="20" t="n"/>
+      <c r="E187" s="20" t="n"/>
+      <c r="F187" s="20" t="n"/>
+    </row>
+    <row r="188" ht="112" customHeight="1">
+      <c r="A188" s="21" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -6857,170 +6891,170 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="6" customHeight="1"/>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="189" ht="6" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="8" t="n"/>
-      <c r="D184" s="8" t="n"/>
-      <c r="E184" s="8" t="n"/>
-      <c r="F184" s="8" t="n"/>
-    </row>
-    <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
+      <c r="B190" s="8" t="n"/>
+      <c r="C190" s="8" t="n"/>
+      <c r="D190" s="8" t="n"/>
+      <c r="E190" s="8" t="n"/>
+      <c r="F190" s="8" t="n"/>
+    </row>
+    <row r="191" ht="15" customHeight="1">
+      <c r="A191" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B185" s="9" t="inlineStr">
+      <c r="B191" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C185" s="9" t="inlineStr">
+      <c r="C191" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D185" s="9" t="inlineStr">
+      <c r="D191" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E185" s="9" t="inlineStr">
+      <c r="E191" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F185" s="9" t="inlineStr">
+      <c r="F191" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="22" t="inlineStr">
+    <row r="192" ht="32" customHeight="1">
+      <c r="A192" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B186" s="22" t="inlineStr">
+      <c r="B192" s="22" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C186" s="23" t="inlineStr"/>
-      <c r="D186" s="14" t="inlineStr">
+      <c r="C192" s="23" t="inlineStr"/>
+      <c r="D192" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E186" s="22" t="inlineStr">
+      <c r="E192" s="22" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F186" s="22" t="inlineStr"/>
-    </row>
-    <row r="187" ht="112" customHeight="1">
-      <c r="A187" s="22" t="inlineStr">
+      <c r="F192" s="22" t="inlineStr"/>
+    </row>
+    <row r="193" ht="112" customHeight="1">
+      <c r="A193" s="22" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B187" s="22" t="inlineStr">
+      <c r="B193" s="22" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C187" s="23" t="inlineStr"/>
-      <c r="D187" s="15" t="inlineStr">
+      <c r="C193" s="23" t="inlineStr"/>
+      <c r="D193" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E187" s="22" t="inlineStr">
+      <c r="E193" s="22" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F187" s="22" t="inlineStr">
+      <c r="F193" s="22" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="32" customHeight="1">
-      <c r="A188" s="22" t="inlineStr">
+    <row r="194" ht="32" customHeight="1">
+      <c r="A194" s="22" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B188" s="22" t="inlineStr">
+      <c r="B194" s="22" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C188" s="23" t="inlineStr"/>
-      <c r="D188" s="15" t="inlineStr">
+      <c r="C194" s="23" t="inlineStr"/>
+      <c r="D194" s="15" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E188" s="22" t="inlineStr">
+      <c r="E194" s="22" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="F188" s="22" t="inlineStr">
+      <c r="F194" s="22" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="14" customHeight="1">
-      <c r="A189" s="19" t="inlineStr">
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B189" s="20" t="n"/>
-      <c r="C189" s="20" t="n"/>
-      <c r="D189" s="20" t="n"/>
-      <c r="E189" s="20" t="n"/>
-      <c r="F189" s="20" t="n"/>
-    </row>
-    <row r="190" ht="80" customHeight="1">
-      <c r="A190" s="25" t="inlineStr">
+      <c r="B195" s="20" t="n"/>
+      <c r="C195" s="20" t="n"/>
+      <c r="D195" s="20" t="n"/>
+      <c r="E195" s="20" t="n"/>
+      <c r="F195" s="20" t="n"/>
+    </row>
+    <row r="196" ht="80" customHeight="1">
+      <c r="A196" s="25" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B190" s="26" t="n"/>
-      <c r="C190" s="26" t="n"/>
-      <c r="D190" s="26" t="n"/>
-      <c r="E190" s="26" t="n"/>
-      <c r="F190" s="26" t="n"/>
-    </row>
-    <row r="191" ht="14" customHeight="1">
-      <c r="A191" s="19" t="inlineStr">
+      <c r="B196" s="26" t="n"/>
+      <c r="C196" s="26" t="n"/>
+      <c r="D196" s="26" t="n"/>
+      <c r="E196" s="26" t="n"/>
+      <c r="F196" s="26" t="n"/>
+    </row>
+    <row r="197" ht="14" customHeight="1">
+      <c r="A197" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B191" s="20" t="n"/>
-      <c r="C191" s="20" t="n"/>
-      <c r="D191" s="20" t="n"/>
-      <c r="E191" s="20" t="n"/>
-      <c r="F191" s="20" t="n"/>
-    </row>
-    <row r="192" ht="128" customHeight="1">
-      <c r="A192" s="25" t="inlineStr">
+      <c r="B197" s="20" t="n"/>
+      <c r="C197" s="20" t="n"/>
+      <c r="D197" s="20" t="n"/>
+      <c r="E197" s="20" t="n"/>
+      <c r="F197" s="20" t="n"/>
+    </row>
+    <row r="198" ht="128" customHeight="1">
+      <c r="A198" s="25" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -7031,167 +7065,167 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B192" s="26" t="n"/>
-      <c r="C192" s="26" t="n"/>
-      <c r="D192" s="26" t="n"/>
-      <c r="E192" s="26" t="n"/>
-      <c r="F192" s="26" t="n"/>
-    </row>
-    <row r="193" ht="6" customHeight="1"/>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="B198" s="26" t="n"/>
+      <c r="C198" s="26" t="n"/>
+      <c r="D198" s="26" t="n"/>
+      <c r="E198" s="26" t="n"/>
+      <c r="F198" s="26" t="n"/>
+    </row>
+    <row r="199" ht="6" customHeight="1"/>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="7" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="8" t="n"/>
-      <c r="D194" s="8" t="n"/>
-      <c r="E194" s="8" t="n"/>
-      <c r="F194" s="8" t="n"/>
-    </row>
-    <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="9" t="inlineStr">
+      <c r="B200" s="8" t="n"/>
+      <c r="C200" s="8" t="n"/>
+      <c r="D200" s="8" t="n"/>
+      <c r="E200" s="8" t="n"/>
+      <c r="F200" s="8" t="n"/>
+    </row>
+    <row r="201" ht="15" customHeight="1">
+      <c r="A201" s="9" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B195" s="9" t="inlineStr">
+      <c r="B201" s="9" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C195" s="9" t="inlineStr">
+      <c r="C201" s="9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D195" s="9" t="inlineStr">
+      <c r="D201" s="9" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E195" s="9" t="inlineStr">
+      <c r="E201" s="9" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F195" s="9" t="inlineStr">
+      <c r="F201" s="9" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="64" customHeight="1">
-      <c r="A196" s="10" t="inlineStr">
+    <row r="202" ht="64" customHeight="1">
+      <c r="A202" s="10" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B196" s="10" t="inlineStr">
+      <c r="B202" s="10" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C196" s="11" t="inlineStr">
+      <c r="C202" s="11" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D196" s="27" t="inlineStr">
+      <c r="D202" s="27" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E196" s="10" t="inlineStr">
+      <c r="E202" s="10" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="F196" s="10" t="inlineStr"/>
-    </row>
-    <row r="197" ht="32" customHeight="1">
-      <c r="A197" s="10" t="inlineStr">
+      <c r="F202" s="10" t="inlineStr"/>
+    </row>
+    <row r="203" ht="32" customHeight="1">
+      <c r="A203" s="10" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B197" s="10" t="inlineStr">
+      <c r="B203" s="10" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C197" s="11" t="inlineStr">
+      <c r="C203" s="11" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D197" s="14" t="inlineStr">
+      <c r="D203" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E197" s="10" t="inlineStr">
+      <c r="E203" s="10" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 · →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="F197" s="10" t="inlineStr"/>
-    </row>
-    <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="10" t="inlineStr">
+      <c r="F203" s="10" t="inlineStr"/>
+    </row>
+    <row r="204" ht="16" customHeight="1">
+      <c r="A204" s="10" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
+      <c r="B204" s="10" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C198" s="11" t="inlineStr">
+      <c r="C204" s="11" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="D198" s="14" t="inlineStr">
+      <c r="D204" s="14" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E198" s="10" t="inlineStr">
+      <c r="E204" s="10" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="F198" s="10" t="inlineStr"/>
-    </row>
-    <row r="199" ht="14" customHeight="1">
-      <c r="A199" s="17" t="inlineStr">
+      <c r="F204" s="10" t="inlineStr"/>
+    </row>
+    <row r="205" ht="14" customHeight="1">
+      <c r="A205" s="17" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
         </is>
       </c>
-      <c r="B199" s="18" t="n"/>
-      <c r="C199" s="18" t="n"/>
-      <c r="D199" s="18" t="n"/>
-      <c r="E199" s="18" t="n"/>
-      <c r="F199" s="18" t="n"/>
-    </row>
-    <row r="200" ht="14" customHeight="1">
-      <c r="A200" s="19" t="inlineStr">
+      <c r="B205" s="18" t="n"/>
+      <c r="C205" s="18" t="n"/>
+      <c r="D205" s="18" t="n"/>
+      <c r="E205" s="18" t="n"/>
+      <c r="F205" s="18" t="n"/>
+    </row>
+    <row r="206" ht="14" customHeight="1">
+      <c r="A206" s="19" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B200" s="20" t="n"/>
-      <c r="C200" s="20" t="n"/>
-      <c r="D200" s="20" t="n"/>
-      <c r="E200" s="20" t="n"/>
-      <c r="F200" s="20" t="n"/>
-    </row>
-    <row r="201" ht="384" customHeight="1">
-      <c r="A201" s="21" t="inlineStr">
+      <c r="B206" s="20" t="n"/>
+      <c r="C206" s="20" t="n"/>
+      <c r="D206" s="20" t="n"/>
+      <c r="E206" s="20" t="n"/>
+      <c r="F206" s="20" t="n"/>
+    </row>
+    <row r="207" ht="384" customHeight="1">
+      <c r="A207" s="21" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -7220,8 +7254,8 @@
         </is>
       </c>
     </row>
-    <row r="202" ht="112" customHeight="1">
-      <c r="A202" s="21" t="inlineStr">
+    <row r="208" ht="112" customHeight="1">
+      <c r="A208" s="21" t="inlineStr">
         <is>
           <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
@@ -7233,20 +7267,20 @@
         </is>
       </c>
     </row>
-    <row r="203" ht="14" customHeight="1">
-      <c r="A203" s="19" t="inlineStr">
+    <row r="209" ht="14" customHeight="1">
+      <c r="A209" s="19" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B203" s="20" t="n"/>
-      <c r="C203" s="20" t="n"/>
-      <c r="D203" s="20" t="n"/>
-      <c r="E203" s="20" t="n"/>
-      <c r="F203" s="20" t="n"/>
-    </row>
-    <row r="204" ht="112" customHeight="1">
-      <c r="A204" s="21" t="inlineStr">
+      <c r="B209" s="20" t="n"/>
+      <c r="C209" s="20" t="n"/>
+      <c r="D209" s="20" t="n"/>
+      <c r="E209" s="20" t="n"/>
+      <c r="F209" s="20" t="n"/>
+    </row>
+    <row r="210" ht="112" customHeight="1">
+      <c r="A210" s="21" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -7258,127 +7292,127 @@
         </is>
       </c>
     </row>
-    <row r="205" ht="6" customHeight="1"/>
+    <row r="211" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="99">
+    <mergeCell ref="A174:F174"/>
+    <mergeCell ref="A205:F205"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A189:F189"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A144:F144"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A134:F134"/>
     <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A161:F161"/>
     <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A202:F202"/>
-    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A70:F70"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A149:F149"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A204:F204"/>
-    <mergeCell ref="A151:F151"/>
-    <mergeCell ref="A126:F126"/>
-    <mergeCell ref="A141:F141"/>
-    <mergeCell ref="A125:F125"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A206:F206"/>
     <mergeCell ref="A190:F190"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A127:F127"/>
+    <mergeCell ref="A167:F167"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A176:F176"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A182:F182"/>
-    <mergeCell ref="A191:F191"/>
+    <mergeCell ref="A59:F59"/>
     <mergeCell ref="A169:F169"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A88:F88"/>
     <mergeCell ref="A153:F153"/>
-    <mergeCell ref="A162:F162"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A90:F90"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="A208:F208"/>
     <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A154:F154"/>
+    <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A179:F179"/>
     <mergeCell ref="A129:F129"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A203:F203"/>
-    <mergeCell ref="A181:F181"/>
+    <mergeCell ref="A116:F116"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A131:F131"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A140:F140"/>
     <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A171:F171"/>
     <mergeCell ref="A115:F115"/>
-    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A102:F102"/>
     <mergeCell ref="A117:F117"/>
     <mergeCell ref="A173:F173"/>
-    <mergeCell ref="A111:F111"/>
-    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A143:F143"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A157:F157"/>
+    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A168:F168"/>
     <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A65:F65"/>
     <mergeCell ref="A128:F128"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="A57:F57"/>
     <mergeCell ref="A113:F113"/>
     <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A209:F209"/>
     <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="A170:F170"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A156:F156"/>
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A130:F130"/>
     <mergeCell ref="A77:F77"/>
-    <mergeCell ref="A201:F201"/>
     <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="A197:F197"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A187:F187"/>
     <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A164" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A173" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A184" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,13 +40,25 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001155CC"/>
-      <sz val="12"/>
-      <u val="single"/>
+      <color rgb="0033475B"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="003A3A3A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001155CC"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
     <font>
       <b val="1"/>
@@ -59,7 +71,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +95,76 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF4FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCEBFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8F5D8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E0D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6DAF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFF3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAD9F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5D9C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9F0D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FAFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8EEF7"/>
       </patternFill>
     </fill>
@@ -93,62 +175,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E9F0D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCEBFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBD9E8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E6DAF5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00EEF3F8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F7FAFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CFF3F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5D9C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D8F5D8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAD9F7"/>
       </patternFill>
     </fill>
   </fills>
@@ -159,11 +186,6 @@
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="008A94A6"/>
-      </top>
     </border>
     <border>
       <left style="thin">
@@ -179,11 +201,16 @@
         <color rgb="00D0D5DD"/>
       </bottom>
     </border>
+    <border>
+      <top style="medium">
+        <color rgb="008A94A6"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -197,68 +224,114 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -340,7 +413,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="7848600" y="1854200"/>
+    <pos x="7848600" y="9398000"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +433,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="1854200"/>
+    <pos x="9696450" y="9398000"/>
     <ext cx="1809750" cy="1323975"/>
     <pic>
       <nvPicPr>
@@ -380,7 +453,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="1854200"/>
+    <pos x="11544300" y="9398000"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +473,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="1854200"/>
+    <pos x="13392150" y="9398000"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +493,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="3702049"/>
+    <pos x="7848600" y="11245849"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +513,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="3702049"/>
+    <pos x="9696450" y="11245849"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +533,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="3702049"/>
+    <pos x="11544300" y="11245849"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +553,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="3702049"/>
+    <pos x="13392150" y="11245849"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +573,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="5549900"/>
+    <pos x="7848600" y="13093699"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +593,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="5549900"/>
+    <pos x="9696450" y="13093699"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +613,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="5549900"/>
+    <pos x="11544300" y="13093699"/>
     <ext cx="1295400" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +633,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="5549900"/>
+    <pos x="13392150" y="13093699"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +653,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="7397750"/>
+    <pos x="7848600" y="14941549"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +673,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="7397750"/>
+    <pos x="9696450" y="14941549"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +693,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="7397750"/>
+    <pos x="11544300" y="14941549"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +713,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="7397750"/>
+    <pos x="13392150" y="14941549"/>
     <ext cx="1809750" cy="990600"/>
     <pic>
       <nvPicPr>
@@ -660,7 +733,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="9245600"/>
+    <pos x="7848600" y="16789400"/>
     <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
@@ -680,7 +753,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="13303249"/>
+    <pos x="7848600" y="20847050"/>
     <ext cx="5143500" cy="4019550"/>
     <pic>
       <nvPicPr>
@@ -700,7 +773,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="17437100"/>
+    <pos x="7848600" y="24980900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -720,7 +793,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="17437100"/>
+    <pos x="9696450" y="24980900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +813,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="17437100"/>
+    <pos x="11544300" y="24980900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +833,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="17437100"/>
+    <pos x="13392150" y="24980900"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +853,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="19284950"/>
+    <pos x="7848600" y="26828750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -800,7 +873,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="19284950"/>
+    <pos x="9696450" y="26828750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +893,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="19284950"/>
+    <pos x="11544300" y="26828750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +913,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="19284950"/>
+    <pos x="13392150" y="26828750"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +933,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="21132800"/>
+    <pos x="7848600" y="28676600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +953,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="21132800"/>
+    <pos x="9696450" y="28676600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +973,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="21132800"/>
+    <pos x="11544300" y="28676600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +993,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="21132800"/>
+    <pos x="13392150" y="28676600"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -940,7 +1013,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="22980650"/>
+    <pos x="7848600" y="30524450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -960,7 +1033,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="22980650"/>
+    <pos x="9696450" y="30524450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -980,7 +1053,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="22980650"/>
+    <pos x="11544300" y="30524450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1073,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="22980650"/>
+    <pos x="13392150" y="30524450"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1093,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="24828500"/>
+    <pos x="7848600" y="32372300"/>
     <ext cx="5143500" cy="4286250"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1113,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="29229050"/>
+    <pos x="7848600" y="36772850"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1133,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="29229050"/>
+    <pos x="9696450" y="36772850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1153,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="29229050"/>
+    <pos x="11544300" y="36772850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1173,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="29229050"/>
+    <pos x="13392150" y="36772850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1193,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="31076900"/>
+    <pos x="7848600" y="38620700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1213,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="31076900"/>
+    <pos x="9696450" y="38620700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1233,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="31076900"/>
+    <pos x="11544300" y="38620700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1253,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="31076900"/>
+    <pos x="13392150" y="38620700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1273,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="32924750"/>
+    <pos x="7848600" y="40468549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1293,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="32924750"/>
+    <pos x="9696450" y="40468549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1313,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="32924750"/>
+    <pos x="11544300" y="40468549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1333,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="32924750"/>
+    <pos x="13392150" y="40468549"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1353,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="34772600"/>
+    <pos x="7848600" y="42316399"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1373,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="34772600"/>
+    <pos x="9696450" y="42316399"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1393,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="37826950"/>
+    <pos x="7848600" y="45370750"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1413,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="37826950"/>
+    <pos x="9696450" y="45370750"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1433,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="37826950"/>
+    <pos x="11544300" y="45370750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1453,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="37826950"/>
+    <pos x="13392150" y="45370750"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1473,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="39674800"/>
+    <pos x="7848600" y="47218600"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1493,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="42157650"/>
+    <pos x="7848600" y="49701450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1513,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="42157650"/>
+    <pos x="9696450" y="49701450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1533,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="42157650"/>
+    <pos x="11544300" y="49701450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1553,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="42157650"/>
+    <pos x="13392150" y="49701450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1573,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="44005500"/>
+    <pos x="7848600" y="51549300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1593,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="44005500"/>
+    <pos x="9696450" y="51549300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1613,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="44005500"/>
+    <pos x="11544300" y="51549300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1633,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="44005500"/>
+    <pos x="13392150" y="51549300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1653,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45853350"/>
+    <pos x="7848600" y="53397150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1673,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45853350"/>
+    <pos x="9696450" y="53397150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1693,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="51771550"/>
+    <pos x="7848600" y="59315350"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1713,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="51771550"/>
+    <pos x="9696450" y="59315350"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1733,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="51771550"/>
+    <pos x="11544300" y="59315350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1753,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="51771550"/>
+    <pos x="13392150" y="59315350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1773,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="53619400"/>
+    <pos x="7848600" y="61163200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1793,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="59556650"/>
+    <pos x="7848600" y="67100450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1813,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="59556650"/>
+    <pos x="9696450" y="67100450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1833,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="59556650"/>
+    <pos x="11544300" y="67100450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1853,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="59556650"/>
+    <pos x="13392150" y="67100450"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1873,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61404500"/>
+    <pos x="7848600" y="68948300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1893,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="61404500"/>
+    <pos x="9696450" y="68948300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1913,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="63252350"/>
+    <pos x="7848600" y="70796150"/>
     <ext cx="5143500" cy="3429000"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1933,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="67951350"/>
+    <pos x="7848600" y="75495150"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1953,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="67951350"/>
+    <pos x="9696450" y="75495150"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1973,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="67951350"/>
+    <pos x="11544300" y="75495150"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1993,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="67951350"/>
+    <pos x="13392150" y="75495150"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +2013,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="69799200"/>
+    <pos x="7848600" y="77343000"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +2033,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="69799200"/>
+    <pos x="9696450" y="77343000"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +2053,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="69799200"/>
+    <pos x="11544300" y="77343000"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2073,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="69799200"/>
+    <pos x="13392150" y="77343000"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2093,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="71647050"/>
+    <pos x="7848600" y="79190850"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2113,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="73494900"/>
+    <pos x="7848600" y="81038700"/>
     <ext cx="5143500" cy="4286250"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2133,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="77895450"/>
+    <pos x="7848600" y="85439250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2153,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="77895450"/>
+    <pos x="9696450" y="85439250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2173,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="77895450"/>
+    <pos x="11544300" y="85439250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2193,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79743300"/>
+    <pos x="7848600" y="87287100"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2213,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="88322150"/>
+    <pos x="7848600" y="95865950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2233,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="88322150"/>
+    <pos x="9696450" y="95865950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2253,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="88322150"/>
+    <pos x="11544300" y="95865950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2273,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="88322150"/>
+    <pos x="13392150" y="95865950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2293,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="90170000"/>
+    <pos x="7848600" y="97713800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2313,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="90170000"/>
+    <pos x="9696450" y="97713800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2333,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="90170000"/>
+    <pos x="11544300" y="97713800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2353,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="90170000"/>
+    <pos x="13392150" y="97713800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2373,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="92017850"/>
+    <pos x="7848600" y="99561650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2393,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="93865700"/>
+    <pos x="7848600" y="101409500"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2413,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="99123500"/>
+    <pos x="7848600" y="106667300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2433,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="99123500"/>
+    <pos x="9696450" y="106667300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2453,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="99123500"/>
+    <pos x="11544300" y="106667300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2473,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="99123500"/>
+    <pos x="13392150" y="106667300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2493,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="100971350"/>
+    <pos x="7848600" y="108515150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2513,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="100971350"/>
+    <pos x="9696450" y="108515150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2533,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="100971350"/>
+    <pos x="11544300" y="108515150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2553,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="100971350"/>
+    <pos x="13392150" y="108515150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2573,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="102819200"/>
+    <pos x="7848600" y="110363000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2593,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="102819200"/>
+    <pos x="9696450" y="110363000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2613,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="104667050"/>
+    <pos x="7848600" y="112210850"/>
     <ext cx="5143500" cy="4352925"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2633,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="109058075"/>
+    <pos x="7848600" y="116601875"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2653,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="110801150"/>
+    <pos x="7848600" y="118344950"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2673,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="112649000"/>
+    <pos x="7848600" y="120192800"/>
     <ext cx="5143500" cy="4352925"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2693,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="117040025"/>
+    <pos x="7848600" y="124583825"/>
     <ext cx="5143500" cy="4419600"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2713,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="121497725"/>
+    <pos x="7848600" y="129041525"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2733,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="123240800"/>
+    <pos x="7848600" y="130784600"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2753,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="129044700"/>
+    <pos x="7848600" y="136588500"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2773,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="134302500"/>
+    <pos x="7848600" y="141846300"/>
     <ext cx="3505200" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2793,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="140919200"/>
+    <pos x="7848600" y="148463000"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2813,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="146697700"/>
+    <pos x="7848600" y="154241500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2833,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="146697700"/>
+    <pos x="9696450" y="154241500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2853,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="146697700"/>
+    <pos x="11544300" y="154241500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2873,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="146697700"/>
+    <pos x="13392150" y="154241500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2893,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="148545550"/>
+    <pos x="7848600" y="156089350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2913,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="148545550"/>
+    <pos x="9696450" y="156089350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2933,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="150393400"/>
+    <pos x="7848600" y="157937200"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -3171,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3234,265 +3307,511 @@
       <c r="E4" s="6" t="n"/>
       <c r="F4" s="6" t="n"/>
     </row>
-    <row r="5" ht="6" customHeight="1"/>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>🎨 역할(phase) 읽는 법 — 아래 미니표 '역할' 색상의 뜻</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="8" t="n"/>
+      <c r="F5" s="8" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>수상</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>물·수용성 베이스. 제형의 대부분을 차지하는 뼈대이고, 수용성 활성·보습제가 여기 녹는다.   예) 정제수, 로즈워터, 알로에워터</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>유상</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>오일·버터 등 지용성. 피부에 유연·보습막·영양을 주고 발림성·리치함을 결정한다.   예) 호호바오일, 시어버터, 스쿠알란</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>유화</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>안 섞이는 물과 오일을 하나로 묶는 '다리'. 없으면 분리된다. 양으로 로션↔크림 점도도 좌우.   예) 올리브유화왁스, 몬타노브68</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>경화</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>왁스·고형. 제형을 굳혀 밤·스틱 형태를 만든다. 비율로 말랑↔단단이 갈린다.   예) 밀랍, 칸데릴라왁스</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>피지·노폐물을 물에 씻겨나가게 하는 세정 성분. 거품·세정력을 담당.   예) 코코베타인, 데실글루코사이드</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>보습</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>공기·진피의 수분을 끌어와 붙잡는 습윤제. 촉촉함을 유지.   예) 글리세린, 프로판다이올, 솔비톨</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>특정 효능(미백·진정·탄력 등)을 노리는 기능 성분. '이 제품의 컨셉'을 만든다.   예) 나이아신아마이드, 세라마이드, 추출물</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>향</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>향·아로마(에센셜오일 등). 소량(보통 ≤1%)으로 감성·아로마테라피.   예) 라벤더EO, 네롤리</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>색소</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>색을 내는 안료·펄. 색조·틴트 제형의 핵심.   예) 마이카, 산화철, 이산화티탄</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>방부</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>세균·곰팡이 번식을 억제. 물 있는 제형엔 사실상 필수.   예) 1,2-헥산디올, 천연한방보존제</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>점도 조절(젤화)과 산도(pH) 조절. 사용감·안정성·방부 효력에 영향.   예) 잔탄검, 카보머, 구연산</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>위 분류에 안 잡힌 것(완제 베이스·충전제 등).   예) 크림베이스, 옥수수전분</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>📖 배합 기본원리 — 왜 그렇게 하나</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Q. 유화는 왜 같은 온도(65~75℃)에서?
+→ 오일상 왁스가 녹아 액체이고 수상도 같은 온도여야 미세하게 섞인다. 온도차가 크면 닿는 순간 왁스가 굳어 알갱이·분리가 생긴다.</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 식으며 저어주나 / 핸드블렌더?
+→ 유화 입자를 더 잘고 고르게 쪼개면 분리가 줄고 발림·안정성이 좋아진다. 찬물에 받쳐 식히면 유화가 빨리·안정적으로 잡힌다.</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Q. 물 있는 제형은 왜 방부 필수?
+→ 물은 세균·곰팡이의 번식 배지다. 무방부는 수일 내 변질 → 냉장·소량 제조만. 방부력은 실제 챌린지(방부력) 테스트로 확인해야 한다.</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Q. 왜 약산성(pH 5~6)?
+→ 건강한 피부는 pH 4.5~5.5. 알칼리는 장벽을 들뜨게 하고, 적정 산성은 방부 효력과 일부 활성(산성 영역) 안정에 유리하다.</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Q. 가루(점증·활성)는 왜 미리 분산?
+→ 가루가 물에 닿자마자 겉만 수화돼 '덩어리(fish-eye)'가 진다. 글리세린 등에 미리 적셔 분산하거나 천천히 뿌리며 교반해야 곱게 풀린다.</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Q. 무수(오일·밤)는 왜 방부 불필요하지만 물 유입 금지?
+→ 물이 없으면 미생물이 못 큰다. 대신 사용 중 물이 들어가면 그 지점부터 상한다. 산패는 비타민E 등 항산화와 차광·밀폐로 늦춘다.</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+    </row>
+    <row r="25" ht="6" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>초코 버블바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="25" t="n"/>
+      <c r="F26" s="25" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D27" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E27" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F27" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>400g</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C28" s="28" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D28" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>미네럴, 소금의 일종, 탄산수소나트륨,삼투압으로 노폐뮬제거, 미네럴공급, 피부를 부드럽게</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="F28" s="27" t="inlineStr"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D29" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>감귤류에서 얻은 과일산, pH조절, 각질연화, 항균</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F29" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="96" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="30" ht="96" customHeight="1">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C30" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>옥수수에서 얻은 녹말일종, 노폐물흡착, 흡습작용으로 모양이 잘 뭉쳐지게하는 역할</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F30" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>카카오분말</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C31" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D31" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E31" s="27" t="inlineStr">
         <is>
           <t>초콜렛의 원재료,폴리페놀함유</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F31" s="27" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>초코향</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>8ml</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C32" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D32" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E32" s="27" t="inlineStr">
         <is>
           <t>초코향,합성향</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F32" s="27" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>애플계면활성제</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C33" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D33" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E33" s="27" t="inlineStr">
         <is>
           <t>사과주스에서 순한 계면활성제, 피부자극없음. 생분해율이 아주 높음(이 재료를 빼면 거품은 생기지 않음)</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F33" s="27" t="inlineStr">
         <is>
           <t>코코베타인 등 물비누</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+    <row r="34" ht="14" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 계면 3 · 향 1 · 점증/pH 68 · 기타 5</t>
         </is>
       </c>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="18" t="n"/>
-      <c r="E14" s="18" t="n"/>
-      <c r="F14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="B34" s="35" t="n"/>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="14" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-    </row>
-    <row r="16" ht="80" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="37" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
+    </row>
+    <row r="36" ht="80" customHeight="1">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>초콜렛음료 속에 잠기는 기분~음?! 재미있겠죠.
 우리는 '이벤트 목욕탕' 가지 않고서도 집에서 초콜렛목욕을 즐길 수 있을 것 같아요.
@@ -3502,20 +3821,20 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+    <row r="37" ht="14" customHeight="1">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-    </row>
-    <row r="18" ht="384" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="37" t="n"/>
+      <c r="D37" s="37" t="n"/>
+      <c r="E37" s="37" t="n"/>
+      <c r="F37" s="37" t="n"/>
+    </row>
+    <row r="38" ht="384" customHeight="1">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 먼저 계량한다. 덩어리지는 경우가 많아 특별히 베이킹소다만 체에 친다. 덩어리는 문질러주세요.
 3-4.나머지 구연산, 옥수수전분, 카카오분말, 초코향을 넣고 골고루 비비면서 섞어주세요.
@@ -3532,242 +3851,242 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="64" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>도쿄워커는 “진짜 초콜릿이 들어간 목욕탕”이라며 “초콜릿 속에 있는 폴리페놀은 혈액 촉진과 노폐물 배출 효과가 있고 또 셀룰라이트(울퉁붕툴해 보이는 피하 지방) 분해 효과도 기대할 수 있다”고 설명했다.
 [국민일보 쿠키뉴스 신은정 기자]</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="325.9999999999999" customHeight="1"/>
-    <row r="21" ht="6" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="40" ht="326.0000000000001" customHeight="1"/>
+    <row r="41" ht="6" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="25" t="n"/>
+      <c r="F42" s="25" t="n"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D43" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E43" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F43" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="64" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" s="39" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C44" s="40" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D44" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E44" s="39" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr"/>
-    </row>
-    <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="F44" s="39" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="39" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C45" s="40" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D45" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E45" s="39" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F45" s="39" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="96" customHeight="1">
-      <c r="A26" s="22" t="inlineStr">
+    <row r="46" ht="96" customHeight="1">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C46" s="40" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D46" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E46" s="39" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F46" s="39" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
+    <row r="47" ht="48" customHeight="1">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C47" s="40" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D27" s="24" t="inlineStr">
+      <c r="D47" s="41" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E47" s="39" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F47" s="39" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="22" t="inlineStr">
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="39" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C48" s="40" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D48" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E48" s="39" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F48" s="39" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="49" ht="14" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
         </is>
       </c>
-      <c r="B29" s="18" t="n"/>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="B49" s="35" t="n"/>
+      <c r="C49" s="35" t="n"/>
+      <c r="D49" s="35" t="n"/>
+      <c r="E49" s="35" t="n"/>
+      <c r="F49" s="35" t="n"/>
+    </row>
+    <row r="50" ht="14" customHeight="1">
+      <c r="A50" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-    </row>
-    <row r="31" ht="288" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="37" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="37" t="n"/>
+    </row>
+    <row r="51" ht="288" customHeight="1">
+      <c r="A51" s="42" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -3786,335 +4105,335 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-    </row>
-    <row r="32" ht="313.5000000000002" customHeight="1">
-      <c r="A32" s="26" t="n"/>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="6" customHeight="1"/>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="23" t="n"/>
+      <c r="F51" s="23" t="n"/>
+    </row>
+    <row r="52" ht="313.5" customHeight="1">
+      <c r="A52" s="23" t="n"/>
+      <c r="B52" s="23" t="n"/>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="23" t="n"/>
+      <c r="F52" s="23" t="n"/>
+    </row>
+    <row r="53" ht="6" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="24" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="n"/>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B55" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D55" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E55" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F35" s="9" t="inlineStr">
+      <c r="F55" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="32" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="27" t="inlineStr">
         <is>
           <t>코치닐+물</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>1g+3g</t>
         </is>
       </c>
-      <c r="C36" s="11" t="inlineStr">
+      <c r="C56" s="28" t="inlineStr">
         <is>
           <t>&lt;1%</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E56" s="27" t="inlineStr">
         <is>
           <t>반드시 양조절해서 · 색내기에 사용하세요.</t>
         </is>
       </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="F56" s="27" t="inlineStr">
         <is>
           <t>원하는 색</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B57" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C37" s="11" t="inlineStr">
+      <c r="C57" s="28" t="inlineStr">
         <is>
           <t>39%</t>
         </is>
       </c>
-      <c r="D37" s="12" t="inlineStr">
+      <c r="D57" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E57" s="27" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="inlineStr">
+      <c r="F57" s="27" t="inlineStr"/>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="27" t="inlineStr">
         <is>
           <t>주석산</t>
         </is>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C38" s="11" t="inlineStr">
+      <c r="C58" s="28" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D58" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>각질연화, pH조절</t>
         </is>
       </c>
-      <c r="F38" s="10" t="inlineStr"/>
-    </row>
-    <row r="39" ht="96" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="F58" s="27" t="inlineStr"/>
+    </row>
+    <row r="59" ht="96" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B59" s="27" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C39" s="11" t="inlineStr">
+      <c r="C59" s="28" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D59" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E39" s="10" t="inlineStr">
+      <c r="E59" s="27" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F39" s="10" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="32" customHeight="1">
-      <c r="A40" s="10" t="inlineStr">
+    <row r="60" ht="32" customHeight="1">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C40" s="11" t="inlineStr">
+      <c r="C60" s="28" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="D60" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>코코넛유래 · 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F40" s="10" t="inlineStr"/>
-    </row>
-    <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="10" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr"/>
+    </row>
+    <row r="61" ht="16" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B61" s="27" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C41" s="11" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D61" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E61" s="27" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="F41" s="10" t="inlineStr">
+      <c r="F61" s="27" t="inlineStr">
         <is>
           <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="80" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="62" ht="80" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C42" s="11" t="inlineStr">
+      <c r="C62" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D42" s="27" t="inlineStr">
+      <c r="D62" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="F42" s="10" t="inlineStr">
+      <c r="F62" s="27" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+    <row r="63" ht="16" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B63" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C43" s="11" t="inlineStr">
+      <c r="C63" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="D63" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E63" s="27" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F43" s="10" t="inlineStr">
+      <c r="F63" s="27" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="64" ht="14" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
         </is>
       </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-    </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="B64" s="35" t="n"/>
+      <c r="C64" s="35" t="n"/>
+      <c r="D64" s="35" t="n"/>
+      <c r="E64" s="35" t="n"/>
+      <c r="F64" s="35" t="n"/>
+    </row>
+    <row r="65" ht="14" customHeight="1">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="20" t="n"/>
-      <c r="D45" s="20" t="n"/>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="20" t="n"/>
-    </row>
-    <row r="46" ht="96" customHeight="1">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="B65" s="37" t="n"/>
+      <c r="C65" s="37" t="n"/>
+      <c r="D65" s="37" t="n"/>
+      <c r="E65" s="37" t="n"/>
+      <c r="F65" s="37" t="n"/>
+    </row>
+    <row r="66" ht="96" customHeight="1">
+      <c r="A66" s="38" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -4125,20 +4444,20 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
+    <row r="67" ht="14" customHeight="1">
+      <c r="A67" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="20" t="n"/>
-    </row>
-    <row r="48" ht="192" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="B67" s="37" t="n"/>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="37" t="n"/>
+      <c r="E67" s="37" t="n"/>
+      <c r="F67" s="37" t="n"/>
+    </row>
+    <row r="68" ht="192" customHeight="1">
+      <c r="A68" s="38" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -4155,105 +4474,105 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="6" customHeight="1"/>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+    <row r="69" ht="6" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="24" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B70" s="25" t="n"/>
+      <c r="C70" s="25" t="n"/>
+      <c r="D70" s="25" t="n"/>
+      <c r="E70" s="25" t="n"/>
+      <c r="F70" s="25" t="n"/>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B51" s="9" t="inlineStr">
+      <c r="B71" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C71" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D71" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr">
+      <c r="E71" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F51" s="9" t="inlineStr">
+      <c r="F71" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="22" t="inlineStr">
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="39" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B52" s="22" t="inlineStr">
+      <c r="B72" s="39" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C52" s="23" t="inlineStr">
+      <c r="C72" s="40" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E52" s="22" t="inlineStr">
+      <c r="E72" s="39" t="inlineStr">
         <is>
           <t>풍부한 미네랄 · 노폐물제거</t>
         </is>
       </c>
-      <c r="F52" s="22" t="inlineStr"/>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="F72" s="39" t="inlineStr"/>
+    </row>
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 100</t>
         </is>
       </c>
-      <c r="B53" s="18" t="n"/>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="B73" s="35" t="n"/>
+      <c r="C73" s="35" t="n"/>
+      <c r="D73" s="35" t="n"/>
+      <c r="E73" s="35" t="n"/>
+      <c r="F73" s="35" t="n"/>
+    </row>
+    <row r="74" ht="14" customHeight="1">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B54" s="20" t="n"/>
-      <c r="C54" s="20" t="n"/>
-      <c r="D54" s="20" t="n"/>
-      <c r="E54" s="20" t="n"/>
-      <c r="F54" s="20" t="n"/>
-    </row>
-    <row r="55" ht="176" customHeight="1">
-      <c r="A55" s="25" t="inlineStr">
+      <c r="B74" s="37" t="n"/>
+      <c r="C74" s="37" t="n"/>
+      <c r="D74" s="37" t="n"/>
+      <c r="E74" s="37" t="n"/>
+      <c r="F74" s="37" t="n"/>
+    </row>
+    <row r="75" ht="176" customHeight="1">
+      <c r="A75" s="42" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -4268,26 +4587,26 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B55" s="26" t="n"/>
-      <c r="C55" s="26" t="n"/>
-      <c r="D55" s="26" t="n"/>
-      <c r="E55" s="26" t="n"/>
-      <c r="F55" s="26" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="19" t="inlineStr">
+      <c r="B75" s="23" t="n"/>
+      <c r="C75" s="23" t="n"/>
+      <c r="D75" s="23" t="n"/>
+      <c r="E75" s="23" t="n"/>
+      <c r="F75" s="23" t="n"/>
+    </row>
+    <row r="76" ht="14" customHeight="1">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B56" s="20" t="n"/>
-      <c r="C56" s="20" t="n"/>
-      <c r="D56" s="20" t="n"/>
-      <c r="E56" s="20" t="n"/>
-      <c r="F56" s="20" t="n"/>
-    </row>
-    <row r="57" ht="64" customHeight="1">
-      <c r="A57" s="25" t="inlineStr">
+      <c r="B76" s="37" t="n"/>
+      <c r="C76" s="37" t="n"/>
+      <c r="D76" s="37" t="n"/>
+      <c r="E76" s="37" t="n"/>
+      <c r="F76" s="37" t="n"/>
+    </row>
+    <row r="77" ht="64" customHeight="1">
+      <c r="A77" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -4295,235 +4614,235 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B57" s="26" t="n"/>
-      <c r="C57" s="26" t="n"/>
-      <c r="D57" s="26" t="n"/>
-      <c r="E57" s="26" t="n"/>
-      <c r="F57" s="26" t="n"/>
-    </row>
-    <row r="58" ht="6" customHeight="1"/>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="B77" s="23" t="n"/>
+      <c r="C77" s="23" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="23" t="n"/>
+      <c r="F77" s="23" t="n"/>
+    </row>
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="24" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="9" t="inlineStr">
+      <c r="B79" s="25" t="n"/>
+      <c r="C79" s="25" t="n"/>
+      <c r="D79" s="25" t="n"/>
+      <c r="E79" s="25" t="n"/>
+      <c r="F79" s="25" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B80" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C60" s="9" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D60" s="9" t="inlineStr">
+      <c r="D80" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E60" s="9" t="inlineStr">
+      <c r="E80" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F60" s="9" t="inlineStr">
+      <c r="F80" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="32" customHeight="1">
-      <c r="A61" s="10" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B81" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C81" s="28" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E61" s="10" t="inlineStr">
+      <c r="E81" s="27" t="inlineStr">
         <is>
           <t>탄산수소나트륨 · 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="F61" s="10" t="inlineStr"/>
-    </row>
-    <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="10" t="inlineStr">
+      <c r="F81" s="27" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="27" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C62" s="11" t="inlineStr">
+      <c r="C82" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D62" s="12" t="inlineStr">
+      <c r="D82" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr">
+      <c r="E82" s="27" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F62" s="10" t="inlineStr">
+      <c r="F82" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="96" customHeight="1">
-      <c r="A63" s="10" t="inlineStr">
+    <row r="83" ht="96" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B83" s="27" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C63" s="11" t="inlineStr">
+      <c r="C83" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D83" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E63" s="10" t="inlineStr">
+      <c r="E83" s="27" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="F63" s="10" t="inlineStr">
+      <c r="F83" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="10" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="27" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C64" s="11" t="inlineStr">
+      <c r="C84" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D64" s="15" t="inlineStr">
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E84" s="27" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F84" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B85" s="27" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C65" s="11" t="inlineStr">
+      <c r="C85" s="28" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D65" s="14" t="inlineStr">
+      <c r="D85" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E65" s="10" t="inlineStr">
+      <c r="E85" s="27" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴 · 철함유로 자체 · 핑크색 · 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="F65" s="10" t="inlineStr"/>
-    </row>
-    <row r="66" ht="14" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="F85" s="27" t="inlineStr"/>
+    </row>
+    <row r="86" ht="14" customHeight="1">
+      <c r="A86" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
         </is>
       </c>
-      <c r="B66" s="18" t="n"/>
-      <c r="C66" s="18" t="n"/>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="18" t="n"/>
-      <c r="F66" s="18" t="n"/>
-    </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="19" t="inlineStr">
+      <c r="B86" s="35" t="n"/>
+      <c r="C86" s="35" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="35" t="n"/>
+    </row>
+    <row r="87" ht="14" customHeight="1">
+      <c r="A87" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B67" s="20" t="n"/>
-      <c r="C67" s="20" t="n"/>
-      <c r="D67" s="20" t="n"/>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="20" t="n"/>
-    </row>
-    <row r="68" ht="240" customHeight="1">
-      <c r="A68" s="21" t="inlineStr">
+      <c r="B87" s="37" t="n"/>
+      <c r="C87" s="37" t="n"/>
+      <c r="D87" s="37" t="n"/>
+      <c r="E87" s="37" t="n"/>
+      <c r="F87" s="37" t="n"/>
+    </row>
+    <row r="88" ht="240" customHeight="1">
+      <c r="A88" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -4543,20 +4862,20 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="19" t="inlineStr">
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B69" s="20" t="n"/>
-      <c r="C69" s="20" t="n"/>
-      <c r="D69" s="20" t="n"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="20" t="n"/>
-    </row>
-    <row r="70" ht="208" customHeight="1">
-      <c r="A70" s="21" t="inlineStr">
+      <c r="B89" s="37" t="n"/>
+      <c r="C89" s="37" t="n"/>
+      <c r="D89" s="37" t="n"/>
+      <c r="E89" s="37" t="n"/>
+      <c r="F89" s="37" t="n"/>
+    </row>
+    <row r="90" ht="208" customHeight="1">
+      <c r="A90" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -4571,105 +4890,105 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="6" customHeight="1"/>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="91" ht="6" customHeight="1"/>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="24" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
-      <c r="F72" s="8" t="n"/>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="B92" s="25" t="n"/>
+      <c r="C92" s="25" t="n"/>
+      <c r="D92" s="25" t="n"/>
+      <c r="E92" s="25" t="n"/>
+      <c r="F92" s="25" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B73" s="9" t="inlineStr">
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr">
+      <c r="E93" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
+      <c r="F93" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="22" t="inlineStr">
+    <row r="94" ht="32" customHeight="1">
+      <c r="A94" s="39" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B74" s="22" t="inlineStr">
+      <c r="B94" s="39" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C74" s="23" t="inlineStr">
+      <c r="C94" s="40" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D74" s="14" t="inlineStr">
+      <c r="D94" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E74" s="22" t="inlineStr">
+      <c r="E94" s="39" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="F74" s="22" t="inlineStr"/>
-    </row>
-    <row r="75" ht="14" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="F94" s="39" t="inlineStr"/>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  기타 100</t>
         </is>
       </c>
-      <c r="B75" s="18" t="n"/>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="19" t="inlineStr">
+      <c r="B95" s="35" t="n"/>
+      <c r="C95" s="35" t="n"/>
+      <c r="D95" s="35" t="n"/>
+      <c r="E95" s="35" t="n"/>
+      <c r="F95" s="35" t="n"/>
+    </row>
+    <row r="96" ht="14" customHeight="1">
+      <c r="A96" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B76" s="20" t="n"/>
-      <c r="C76" s="20" t="n"/>
-      <c r="D76" s="20" t="n"/>
-      <c r="E76" s="20" t="n"/>
-      <c r="F76" s="20" t="n"/>
-    </row>
-    <row r="77" ht="384" customHeight="1">
-      <c r="A77" s="25" t="inlineStr">
+      <c r="B96" s="37" t="n"/>
+      <c r="C96" s="37" t="n"/>
+      <c r="D96" s="37" t="n"/>
+      <c r="E96" s="37" t="n"/>
+      <c r="F96" s="37" t="n"/>
+    </row>
+    <row r="97" ht="384" customHeight="1">
+      <c r="A97" s="42" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -4697,39 +5016,39 @@
 다양한</t>
         </is>
       </c>
-      <c r="B77" s="26" t="n"/>
-      <c r="C77" s="26" t="n"/>
-      <c r="D77" s="26" t="n"/>
-      <c r="E77" s="26" t="n"/>
-      <c r="F77" s="26" t="n"/>
-    </row>
-    <row r="78" ht="32" customHeight="1">
-      <c r="A78" s="25" t="inlineStr">
+      <c r="B97" s="23" t="n"/>
+      <c r="C97" s="23" t="n"/>
+      <c r="D97" s="23" t="n"/>
+      <c r="E97" s="23" t="n"/>
+      <c r="F97" s="23" t="n"/>
+    </row>
+    <row r="98" ht="32" customHeight="1">
+      <c r="A98" s="42" t="inlineStr">
         <is>
           <t>아로마오일을 히말라야 핑크소금에 배합해
 아로마테리피 효과도 함께 누리세요.</t>
         </is>
       </c>
-      <c r="B78" s="26" t="n"/>
-      <c r="C78" s="26" t="n"/>
-      <c r="D78" s="26" t="n"/>
-      <c r="E78" s="26" t="n"/>
-      <c r="F78" s="26" t="n"/>
-    </row>
-    <row r="79" ht="14" customHeight="1">
-      <c r="A79" s="19" t="inlineStr">
+      <c r="B98" s="23" t="n"/>
+      <c r="C98" s="23" t="n"/>
+      <c r="D98" s="23" t="n"/>
+      <c r="E98" s="23" t="n"/>
+      <c r="F98" s="23" t="n"/>
+    </row>
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B79" s="20" t="n"/>
-      <c r="C79" s="20" t="n"/>
-      <c r="D79" s="20" t="n"/>
-      <c r="E79" s="20" t="n"/>
-      <c r="F79" s="20" t="n"/>
-    </row>
-    <row r="80" ht="80" customHeight="1">
-      <c r="A80" s="25" t="inlineStr">
+      <c r="B99" s="37" t="n"/>
+      <c r="C99" s="37" t="n"/>
+      <c r="D99" s="37" t="n"/>
+      <c r="E99" s="37" t="n"/>
+      <c r="F99" s="37" t="n"/>
+    </row>
+    <row r="100" ht="80" customHeight="1">
+      <c r="A100" s="42" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -4738,203 +5057,203 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B80" s="26" t="n"/>
-      <c r="C80" s="26" t="n"/>
-      <c r="D80" s="26" t="n"/>
-      <c r="E80" s="26" t="n"/>
-      <c r="F80" s="26" t="n"/>
-    </row>
-    <row r="81" ht="6" customHeight="1"/>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="7" t="inlineStr">
+      <c r="B100" s="23" t="n"/>
+      <c r="C100" s="23" t="n"/>
+      <c r="D100" s="23" t="n"/>
+      <c r="E100" s="23" t="n"/>
+      <c r="F100" s="23" t="n"/>
+    </row>
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="24" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B82" s="8" t="n"/>
-      <c r="C82" s="8" t="n"/>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="8" t="n"/>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
+      <c r="B102" s="25" t="n"/>
+      <c r="C102" s="25" t="n"/>
+      <c r="D102" s="25" t="n"/>
+      <c r="E102" s="25" t="n"/>
+      <c r="F102" s="25" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B83" s="9" t="inlineStr">
+      <c r="B103" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C83" s="9" t="inlineStr">
+      <c r="C103" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D83" s="9" t="inlineStr">
+      <c r="D103" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr">
+      <c r="E103" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
+      <c r="F103" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="64" customHeight="1">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" s="27" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B104" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C84" s="11" t="inlineStr">
+      <c r="C104" s="28" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D84" s="28" t="inlineStr">
+      <c r="D104" s="44" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E84" s="10" t="inlineStr">
+      <c r="E104" s="27" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨 · 산소금=암염, 수분함량 적고 · 미네럴 풍부 · 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="F84" s="10" t="inlineStr"/>
-    </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="F104" s="27" t="inlineStr"/>
+    </row>
+    <row r="105" ht="48" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B105" s="27" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C85" s="11" t="inlineStr">
+      <c r="C105" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
+      <c r="D105" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
+      <c r="E105" s="27" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="F105" s="27" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="32" customHeight="1">
-      <c r="A86" s="10" t="inlineStr">
+    <row r="106" ht="32" customHeight="1">
+      <c r="A106" s="27" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B106" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C86" s="11" t="inlineStr">
+      <c r="C106" s="28" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
+      <c r="D106" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr">
+      <c r="E106" s="27" t="inlineStr">
         <is>
           <t>입,족욕용 또는 · 바디 마사지 · 스크럽 겸용</t>
         </is>
       </c>
-      <c r="F86" s="10" t="inlineStr"/>
-    </row>
-    <row r="87" ht="64" customHeight="1">
-      <c r="A87" s="10" t="inlineStr">
+      <c r="F106" s="27" t="inlineStr"/>
+    </row>
+    <row r="107" ht="64" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B107" s="27" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C87" s="11" t="inlineStr">
+      <c r="C107" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D87" s="15" t="inlineStr">
+      <c r="D107" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E87" s="10" t="inlineStr">
+      <c r="E107" s="27" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="F87" s="10" t="inlineStr">
+      <c r="F107" s="27" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="17" t="inlineStr">
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
         </is>
       </c>
-      <c r="B88" s="18" t="n"/>
-      <c r="C88" s="18" t="n"/>
-      <c r="D88" s="18" t="n"/>
-      <c r="E88" s="18" t="n"/>
-      <c r="F88" s="18" t="n"/>
-    </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="19" t="inlineStr">
+      <c r="B108" s="35" t="n"/>
+      <c r="C108" s="35" t="n"/>
+      <c r="D108" s="35" t="n"/>
+      <c r="E108" s="35" t="n"/>
+      <c r="F108" s="35" t="n"/>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B89" s="20" t="n"/>
-      <c r="C89" s="20" t="n"/>
-      <c r="D89" s="20" t="n"/>
-      <c r="E89" s="20" t="n"/>
-      <c r="F89" s="20" t="n"/>
-    </row>
-    <row r="90" ht="256" customHeight="1">
-      <c r="A90" s="21" t="inlineStr">
+      <c r="B109" s="37" t="n"/>
+      <c r="C109" s="37" t="n"/>
+      <c r="D109" s="37" t="n"/>
+      <c r="E109" s="37" t="n"/>
+      <c r="F109" s="37" t="n"/>
+    </row>
+    <row r="110" ht="256" customHeight="1">
+      <c r="A110" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -4955,20 +5274,20 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="14" customHeight="1">
-      <c r="A91" s="19" t="inlineStr">
+    <row r="111" ht="14" customHeight="1">
+      <c r="A111" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B91" s="20" t="n"/>
-      <c r="C91" s="20" t="n"/>
-      <c r="D91" s="20" t="n"/>
-      <c r="E91" s="20" t="n"/>
-      <c r="F91" s="20" t="n"/>
-    </row>
-    <row r="92" ht="112" customHeight="1">
-      <c r="A92" s="21" t="inlineStr">
+      <c r="B111" s="37" t="n"/>
+      <c r="C111" s="37" t="n"/>
+      <c r="D111" s="37" t="n"/>
+      <c r="E111" s="37" t="n"/>
+      <c r="F111" s="37" t="n"/>
+    </row>
+    <row r="112" ht="112" customHeight="1">
+      <c r="A112" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -4980,201 +5299,201 @@
         </is>
       </c>
     </row>
-    <row r="93" ht="6" customHeight="1"/>
-    <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="113" ht="6" customHeight="1"/>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="24" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="8" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="B114" s="25" t="n"/>
+      <c r="C114" s="25" t="n"/>
+      <c r="D114" s="25" t="n"/>
+      <c r="E114" s="25" t="n"/>
+      <c r="F114" s="25" t="n"/>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B95" s="9" t="inlineStr">
+      <c r="B115" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C95" s="9" t="inlineStr">
+      <c r="C115" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D95" s="9" t="inlineStr">
+      <c r="D115" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E95" s="9" t="inlineStr">
+      <c r="E115" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="F115" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="22" t="inlineStr">
+    <row r="116" ht="48" customHeight="1">
+      <c r="A116" s="39" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B96" s="22" t="inlineStr">
+      <c r="B116" s="39" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C96" s="23" t="inlineStr">
+      <c r="C116" s="40" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D96" s="12" t="inlineStr">
+      <c r="D116" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E96" s="22" t="inlineStr">
+      <c r="E116" s="39" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="F96" s="22" t="inlineStr"/>
-    </row>
-    <row r="97" ht="32" customHeight="1">
-      <c r="A97" s="22" t="inlineStr">
+      <c r="F116" s="39" t="inlineStr"/>
+    </row>
+    <row r="117" ht="32" customHeight="1">
+      <c r="A117" s="39" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B97" s="22" t="inlineStr">
+      <c r="B117" s="39" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C97" s="23" t="inlineStr">
+      <c r="C117" s="40" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D117" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E97" s="22" t="inlineStr">
+      <c r="E117" s="39" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="F97" s="22" t="inlineStr">
+      <c r="F117" s="39" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="98" ht="96" customHeight="1">
-      <c r="A98" s="22" t="inlineStr">
+    <row r="118" ht="96" customHeight="1">
+      <c r="A118" s="39" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B98" s="22" t="inlineStr">
+      <c r="B118" s="39" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C98" s="23" t="inlineStr">
+      <c r="C118" s="40" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D98" s="12" t="inlineStr">
+      <c r="D118" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E98" s="22" t="inlineStr">
+      <c r="E118" s="39" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F98" s="22" t="inlineStr">
+      <c r="F118" s="39" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="80" customHeight="1">
-      <c r="A99" s="22" t="inlineStr">
+    <row r="119" ht="80" customHeight="1">
+      <c r="A119" s="39" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B99" s="22" t="inlineStr">
+      <c r="B119" s="39" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C99" s="23" t="inlineStr">
+      <c r="C119" s="40" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D99" s="15" t="inlineStr">
+      <c r="D119" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E99" s="22" t="inlineStr">
+      <c r="E119" s="39" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F99" s="22" t="inlineStr">
+      <c r="F119" s="39" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="17" t="inlineStr">
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
         </is>
       </c>
-      <c r="B100" s="18" t="n"/>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="18" t="n"/>
-      <c r="F100" s="18" t="n"/>
-    </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="19" t="inlineStr">
+      <c r="B120" s="35" t="n"/>
+      <c r="C120" s="35" t="n"/>
+      <c r="D120" s="35" t="n"/>
+      <c r="E120" s="35" t="n"/>
+      <c r="F120" s="35" t="n"/>
+    </row>
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B101" s="20" t="n"/>
-      <c r="C101" s="20" t="n"/>
-      <c r="D101" s="20" t="n"/>
-      <c r="E101" s="20" t="n"/>
-      <c r="F101" s="20" t="n"/>
-    </row>
-    <row r="102" ht="64" customHeight="1">
-      <c r="A102" s="25" t="inlineStr">
+      <c r="B121" s="37" t="n"/>
+      <c r="C121" s="37" t="n"/>
+      <c r="D121" s="37" t="n"/>
+      <c r="E121" s="37" t="n"/>
+      <c r="F121" s="37" t="n"/>
+    </row>
+    <row r="122" ht="64" customHeight="1">
+      <c r="A122" s="42" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -5182,26 +5501,26 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B102" s="26" t="n"/>
-      <c r="C102" s="26" t="n"/>
-      <c r="D102" s="26" t="n"/>
-      <c r="E102" s="26" t="n"/>
-      <c r="F102" s="26" t="n"/>
-    </row>
-    <row r="103" ht="14" customHeight="1">
-      <c r="A103" s="19" t="inlineStr">
+      <c r="B122" s="23" t="n"/>
+      <c r="C122" s="23" t="n"/>
+      <c r="D122" s="23" t="n"/>
+      <c r="E122" s="23" t="n"/>
+      <c r="F122" s="23" t="n"/>
+    </row>
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B103" s="20" t="n"/>
-      <c r="C103" s="20" t="n"/>
-      <c r="D103" s="20" t="n"/>
-      <c r="E103" s="20" t="n"/>
-      <c r="F103" s="20" t="n"/>
-    </row>
-    <row r="104" ht="192" customHeight="1">
-      <c r="A104" s="25" t="inlineStr">
+      <c r="B123" s="37" t="n"/>
+      <c r="C123" s="37" t="n"/>
+      <c r="D123" s="37" t="n"/>
+      <c r="E123" s="37" t="n"/>
+      <c r="F123" s="37" t="n"/>
+    </row>
+    <row r="124" ht="192" customHeight="1">
+      <c r="A124" s="42" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -5216,179 +5535,179 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B104" s="26" t="n"/>
-      <c r="C104" s="26" t="n"/>
-      <c r="D104" s="26" t="n"/>
-      <c r="E104" s="26" t="n"/>
-      <c r="F104" s="26" t="n"/>
-    </row>
-    <row r="105" ht="186" customHeight="1">
-      <c r="A105" s="26" t="n"/>
-      <c r="B105" s="26" t="n"/>
-      <c r="C105" s="26" t="n"/>
-      <c r="D105" s="26" t="n"/>
-      <c r="E105" s="26" t="n"/>
-      <c r="F105" s="26" t="n"/>
-    </row>
-    <row r="106" ht="6" customHeight="1"/>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="7" t="inlineStr">
+      <c r="B124" s="23" t="n"/>
+      <c r="C124" s="23" t="n"/>
+      <c r="D124" s="23" t="n"/>
+      <c r="E124" s="23" t="n"/>
+      <c r="F124" s="23" t="n"/>
+    </row>
+    <row r="125" ht="186" customHeight="1">
+      <c r="A125" s="23" t="n"/>
+      <c r="B125" s="23" t="n"/>
+      <c r="C125" s="23" t="n"/>
+      <c r="D125" s="23" t="n"/>
+      <c r="E125" s="23" t="n"/>
+      <c r="F125" s="23" t="n"/>
+    </row>
+    <row r="126" ht="6" customHeight="1"/>
+    <row r="127" ht="22" customHeight="1">
+      <c r="A127" s="24" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="8" t="n"/>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="9" t="inlineStr">
+      <c r="B127" s="25" t="n"/>
+      <c r="C127" s="25" t="n"/>
+      <c r="D127" s="25" t="n"/>
+      <c r="E127" s="25" t="n"/>
+      <c r="F127" s="25" t="n"/>
+    </row>
+    <row r="128" ht="15" customHeight="1">
+      <c r="A128" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B108" s="9" t="inlineStr">
+      <c r="B128" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C108" s="9" t="inlineStr">
+      <c r="C128" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D108" s="9" t="inlineStr">
+      <c r="D128" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E108" s="9" t="inlineStr">
+      <c r="E128" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="F128" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="32" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B129" s="27" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C109" s="11" t="inlineStr">
+      <c r="C129" s="28" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D109" s="14" t="inlineStr">
+      <c r="D129" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E109" s="10" t="inlineStr">
+      <c r="E129" s="27" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F109" s="10" t="inlineStr"/>
-    </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="10" t="inlineStr">
+      <c r="F129" s="27" t="inlineStr"/>
+    </row>
+    <row r="130" ht="48" customHeight="1">
+      <c r="A130" s="27" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B130" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C110" s="11" t="inlineStr">
+      <c r="C130" s="28" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D110" s="27" t="inlineStr">
+      <c r="D130" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E110" s="10" t="inlineStr">
+      <c r="E130" s="27" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 · 시어버터, 아보카도, 꿀추출물 등 · 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="F110" s="10" t="inlineStr"/>
-    </row>
-    <row r="111" ht="80" customHeight="1">
-      <c r="A111" s="10" t="inlineStr">
+      <c r="F130" s="27" t="inlineStr"/>
+    </row>
+    <row r="131" ht="80" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B111" s="10" t="inlineStr">
+      <c r="B131" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C111" s="11" t="inlineStr">
+      <c r="C131" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D111" s="15" t="inlineStr">
+      <c r="D131" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E111" s="10" t="inlineStr">
+      <c r="E131" s="27" t="inlineStr">
         <is>
           <t>아로마테라피 · 여드름-티트리 · 바디 용도별 추천오일 · 쿨링 :페파민트 · 다이어트 : 레몬+자몽오일 · 이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="F111" s="10" t="inlineStr">
+      <c r="F131" s="27" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="17" t="inlineStr">
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
         </is>
       </c>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-    </row>
-    <row r="113" ht="14" customHeight="1">
-      <c r="A113" s="19" t="inlineStr">
+      <c r="B132" s="35" t="n"/>
+      <c r="C132" s="35" t="n"/>
+      <c r="D132" s="35" t="n"/>
+      <c r="E132" s="35" t="n"/>
+      <c r="F132" s="35" t="n"/>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B113" s="20" t="n"/>
-      <c r="C113" s="20" t="n"/>
-      <c r="D113" s="20" t="n"/>
-      <c r="E113" s="20" t="n"/>
-      <c r="F113" s="20" t="n"/>
-    </row>
-    <row r="114" ht="384" customHeight="1">
-      <c r="A114" s="21" t="inlineStr">
+      <c r="B133" s="37" t="n"/>
+      <c r="C133" s="37" t="n"/>
+      <c r="D133" s="37" t="n"/>
+      <c r="E133" s="37" t="n"/>
+      <c r="F133" s="37" t="n"/>
+    </row>
+    <row r="134" ht="384" customHeight="1">
+      <c r="A134" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5417,8 +5736,8 @@
         </is>
       </c>
     </row>
-    <row r="115" ht="112" customHeight="1">
-      <c r="A115" s="21" t="inlineStr">
+    <row r="135" ht="112" customHeight="1">
+      <c r="A135" s="38" t="inlineStr">
         <is>
           <t>알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
@@ -5430,20 +5749,20 @@
         </is>
       </c>
     </row>
-    <row r="116" ht="14" customHeight="1">
-      <c r="A116" s="19" t="inlineStr">
+    <row r="136" ht="14" customHeight="1">
+      <c r="A136" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B116" s="20" t="n"/>
-      <c r="C116" s="20" t="n"/>
-      <c r="D116" s="20" t="n"/>
-      <c r="E116" s="20" t="n"/>
-      <c r="F116" s="20" t="n"/>
-    </row>
-    <row r="117" ht="80" customHeight="1">
-      <c r="A117" s="21" t="inlineStr">
+      <c r="B136" s="37" t="n"/>
+      <c r="C136" s="37" t="n"/>
+      <c r="D136" s="37" t="n"/>
+      <c r="E136" s="37" t="n"/>
+      <c r="F136" s="37" t="n"/>
+    </row>
+    <row r="137" ht="80" customHeight="1">
+      <c r="A137" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -5453,261 +5772,261 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="6" customHeight="1"/>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="7" t="inlineStr">
+    <row r="138" ht="6" customHeight="1"/>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="24" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="9" t="inlineStr">
+      <c r="B139" s="25" t="n"/>
+      <c r="C139" s="25" t="n"/>
+      <c r="D139" s="25" t="n"/>
+      <c r="E139" s="25" t="n"/>
+      <c r="F139" s="25" t="n"/>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B120" s="9" t="inlineStr">
+      <c r="B140" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C140" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D140" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="E140" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F120" s="9" t="inlineStr">
+      <c r="F140" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="22" t="inlineStr">
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="39" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B121" s="22" t="inlineStr">
+      <c r="B141" s="39" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C121" s="23" t="inlineStr">
+      <c r="C141" s="40" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D121" s="12" t="inlineStr">
+      <c r="D141" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E121" s="22" t="inlineStr">
+      <c r="E141" s="39" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F121" s="22" t="inlineStr"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="22" t="inlineStr">
+      <c r="F141" s="39" t="inlineStr"/>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="39" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B122" s="22" t="inlineStr">
+      <c r="B142" s="39" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C122" s="23" t="inlineStr">
+      <c r="C142" s="40" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D122" s="12" t="inlineStr">
+      <c r="D142" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E122" s="22" t="inlineStr">
+      <c r="E142" s="39" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F122" s="22" t="inlineStr">
+      <c r="F142" s="39" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="96" customHeight="1">
-      <c r="A123" s="22" t="inlineStr">
+    <row r="143" ht="96" customHeight="1">
+      <c r="A143" s="39" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B123" s="22" t="inlineStr">
+      <c r="B143" s="39" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C123" s="23" t="inlineStr">
+      <c r="C143" s="40" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D123" s="14" t="inlineStr">
+      <c r="D143" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E123" s="22" t="inlineStr">
+      <c r="E143" s="39" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F123" s="22" t="inlineStr">
+      <c r="F143" s="39" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="32" customHeight="1">
-      <c r="A124" s="22" t="inlineStr">
+    <row r="144" ht="32" customHeight="1">
+      <c r="A144" s="39" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B124" s="22" t="inlineStr">
+      <c r="B144" s="39" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C124" s="23" t="inlineStr">
+      <c r="C144" s="40" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D124" s="16" t="inlineStr">
+      <c r="D144" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E124" s="22" t="inlineStr">
+      <c r="E144" s="39" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F124" s="22" t="inlineStr"/>
-    </row>
-    <row r="125" ht="32" customHeight="1">
-      <c r="A125" s="22" t="inlineStr">
+      <c r="F144" s="39" t="inlineStr"/>
+    </row>
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" s="39" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B125" s="22" t="inlineStr">
+      <c r="B145" s="39" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C125" s="23" t="inlineStr">
+      <c r="C145" s="40" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D125" s="27" t="inlineStr">
+      <c r="D145" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E125" s="22" t="inlineStr">
+      <c r="E145" s="39" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="F125" s="22" t="inlineStr">
+      <c r="F145" s="39" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="64" customHeight="1">
-      <c r="A126" s="22" t="inlineStr">
+    <row r="146" ht="64" customHeight="1">
+      <c r="A146" s="39" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B126" s="22" t="inlineStr">
+      <c r="B146" s="39" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C126" s="23" t="inlineStr">
+      <c r="C146" s="40" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D126" s="13" t="inlineStr">
+      <c r="D146" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E126" s="22" t="inlineStr">
+      <c r="E146" s="39" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="F126" s="22" t="inlineStr">
+      <c r="F146" s="39" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="17" t="inlineStr">
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
         </is>
       </c>
-      <c r="B127" s="18" t="n"/>
-      <c r="C127" s="18" t="n"/>
-      <c r="D127" s="18" t="n"/>
-      <c r="E127" s="18" t="n"/>
-      <c r="F127" s="18" t="n"/>
-    </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="19" t="inlineStr">
+      <c r="B147" s="35" t="n"/>
+      <c r="C147" s="35" t="n"/>
+      <c r="D147" s="35" t="n"/>
+      <c r="E147" s="35" t="n"/>
+      <c r="F147" s="35" t="n"/>
+    </row>
+    <row r="148" ht="14" customHeight="1">
+      <c r="A148" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B128" s="20" t="n"/>
-      <c r="C128" s="20" t="n"/>
-      <c r="D128" s="20" t="n"/>
-      <c r="E128" s="20" t="n"/>
-      <c r="F128" s="20" t="n"/>
-    </row>
-    <row r="129" ht="224" customHeight="1">
-      <c r="A129" s="25" t="inlineStr">
+      <c r="B148" s="37" t="n"/>
+      <c r="C148" s="37" t="n"/>
+      <c r="D148" s="37" t="n"/>
+      <c r="E148" s="37" t="n"/>
+      <c r="F148" s="37" t="n"/>
+    </row>
+    <row r="149" ht="224" customHeight="1">
+      <c r="A149" s="42" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -5725,26 +6044,26 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B129" s="26" t="n"/>
-      <c r="C129" s="26" t="n"/>
-      <c r="D129" s="26" t="n"/>
-      <c r="E129" s="26" t="n"/>
-      <c r="F129" s="26" t="n"/>
-    </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="19" t="inlineStr">
+      <c r="B149" s="23" t="n"/>
+      <c r="C149" s="23" t="n"/>
+      <c r="D149" s="23" t="n"/>
+      <c r="E149" s="23" t="n"/>
+      <c r="F149" s="23" t="n"/>
+    </row>
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B130" s="20" t="n"/>
-      <c r="C130" s="20" t="n"/>
-      <c r="D130" s="20" t="n"/>
-      <c r="E130" s="20" t="n"/>
-      <c r="F130" s="20" t="n"/>
-    </row>
-    <row r="131" ht="160" customHeight="1">
-      <c r="A131" s="25" t="inlineStr">
+      <c r="B150" s="37" t="n"/>
+      <c r="C150" s="37" t="n"/>
+      <c r="D150" s="37" t="n"/>
+      <c r="E150" s="37" t="n"/>
+      <c r="F150" s="37" t="n"/>
+    </row>
+    <row r="151" ht="160" customHeight="1">
+      <c r="A151" s="42" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -5758,307 +6077,307 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B131" s="26" t="n"/>
-      <c r="C131" s="26" t="n"/>
-      <c r="D131" s="26" t="n"/>
-      <c r="E131" s="26" t="n"/>
-      <c r="F131" s="26" t="n"/>
-    </row>
-    <row r="132" ht="125.4999999999999" customHeight="1">
-      <c r="A132" s="26" t="n"/>
-      <c r="B132" s="26" t="n"/>
-      <c r="C132" s="26" t="n"/>
-      <c r="D132" s="26" t="n"/>
-      <c r="E132" s="26" t="n"/>
-      <c r="F132" s="26" t="n"/>
-    </row>
-    <row r="133" ht="6" customHeight="1"/>
-    <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="7" t="inlineStr">
+      <c r="B151" s="23" t="n"/>
+      <c r="C151" s="23" t="n"/>
+      <c r="D151" s="23" t="n"/>
+      <c r="E151" s="23" t="n"/>
+      <c r="F151" s="23" t="n"/>
+    </row>
+    <row r="152" ht="125.4999999999999" customHeight="1">
+      <c r="A152" s="23" t="n"/>
+      <c r="B152" s="23" t="n"/>
+      <c r="C152" s="23" t="n"/>
+      <c r="D152" s="23" t="n"/>
+      <c r="E152" s="23" t="n"/>
+      <c r="F152" s="23" t="n"/>
+    </row>
+    <row r="153" ht="6" customHeight="1"/>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="24" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B134" s="8" t="n"/>
-      <c r="C134" s="8" t="n"/>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="8" t="n"/>
-      <c r="F134" s="8" t="n"/>
-    </row>
-    <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
+      <c r="B154" s="25" t="n"/>
+      <c r="C154" s="25" t="n"/>
+      <c r="D154" s="25" t="n"/>
+      <c r="E154" s="25" t="n"/>
+      <c r="F154" s="25" t="n"/>
+    </row>
+    <row r="155" ht="15" customHeight="1">
+      <c r="A155" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B135" s="9" t="inlineStr">
+      <c r="B155" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C135" s="9" t="inlineStr">
+      <c r="C155" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D135" s="9" t="inlineStr">
+      <c r="D155" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E135" s="9" t="inlineStr">
+      <c r="E155" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F135" s="9" t="inlineStr">
+      <c r="F155" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="10" t="inlineStr">
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="27" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B136" s="10" t="inlineStr">
+      <c r="B156" s="27" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C136" s="11" t="inlineStr">
+      <c r="C156" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D136" s="27" t="inlineStr">
+      <c r="D156" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E136" s="10" t="inlineStr">
+      <c r="E156" s="27" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="F136" s="10" t="inlineStr">
+      <c r="F156" s="27" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="32" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
+    <row r="157" ht="32" customHeight="1">
+      <c r="A157" s="27" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B157" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C137" s="11" t="inlineStr">
+      <c r="C157" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D137" s="27" t="inlineStr">
+      <c r="D157" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
+      <c r="E157" s="27" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="F157" s="27" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="48" customHeight="1">
-      <c r="A138" s="10" t="inlineStr">
+    <row r="158" ht="48" customHeight="1">
+      <c r="A158" s="27" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B138" s="10" t="inlineStr">
+      <c r="B158" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C138" s="11" t="inlineStr">
+      <c r="C158" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D138" s="29" t="inlineStr">
+      <c r="D158" s="45" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E138" s="10" t="inlineStr">
+      <c r="E158" s="27" t="inlineStr">
         <is>
           <t>에코인증, 물과 오일의 분리를 저지</t>
         </is>
       </c>
-      <c r="F138" s="10" t="inlineStr">
+      <c r="F158" s="27" t="inlineStr">
         <is>
           <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="64" customHeight="1">
-      <c r="A139" s="10" t="inlineStr">
+    <row r="159" ht="64" customHeight="1">
+      <c r="A159" s="27" t="inlineStr">
         <is>
           <t>순한 (샴푸) / 베이스</t>
         </is>
       </c>
-      <c r="B139" s="10" t="inlineStr">
+      <c r="B159" s="27" t="inlineStr">
         <is>
           <t>38g</t>
         </is>
       </c>
-      <c r="C139" s="11" t="inlineStr">
+      <c r="C159" s="28" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="D139" s="16" t="inlineStr">
+      <c r="D159" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E139" s="10" t="inlineStr">
+      <c r="E159" s="27" t="inlineStr">
         <is>
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="F139" s="10" t="inlineStr"/>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="10" t="inlineStr">
+      <c r="F159" s="27" t="inlineStr"/>
+    </row>
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="27" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B140" s="10" t="inlineStr">
+      <c r="B160" s="27" t="inlineStr">
         <is>
           <t>13g</t>
         </is>
       </c>
-      <c r="C140" s="11" t="inlineStr">
+      <c r="C160" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D140" s="24" t="inlineStr">
+      <c r="D160" s="41" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E140" s="10" t="inlineStr">
+      <c r="E160" s="27" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="F140" s="10" t="inlineStr">
+      <c r="F160" s="27" t="inlineStr">
         <is>
           <t>꿀 등</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="48" customHeight="1">
-      <c r="A141" s="10" t="inlineStr">
+    <row r="161" ht="48" customHeight="1">
+      <c r="A161" s="27" t="inlineStr">
         <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B141" s="10" t="inlineStr">
+      <c r="B161" s="27" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C141" s="11" t="inlineStr">
+      <c r="C161" s="28" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D141" s="14" t="inlineStr">
+      <c r="D161" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E141" s="10" t="inlineStr">
+      <c r="E161" s="27" t="inlineStr">
         <is>
           <t>각질제거, 보습. · 필요에 따라 양을 더 넣어서 · 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="F141" s="10" t="inlineStr"/>
-    </row>
-    <row r="142" ht="32" customHeight="1">
-      <c r="A142" s="10" t="inlineStr">
+      <c r="F161" s="27" t="inlineStr"/>
+    </row>
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="27" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B142" s="10" t="inlineStr">
+      <c r="B162" s="27" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C142" s="11" t="inlineStr">
+      <c r="C162" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D142" s="15" t="inlineStr">
+      <c r="D162" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E142" s="10" t="inlineStr">
+      <c r="E162" s="27" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F142" s="10" t="inlineStr">
+      <c r="F162" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="14" customHeight="1">
-      <c r="A143" s="17" t="inlineStr">
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
         </is>
       </c>
-      <c r="B143" s="18" t="n"/>
-      <c r="C143" s="18" t="n"/>
-      <c r="D143" s="18" t="n"/>
-      <c r="E143" s="18" t="n"/>
-      <c r="F143" s="18" t="n"/>
-    </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="19" t="inlineStr">
+      <c r="B163" s="35" t="n"/>
+      <c r="C163" s="35" t="n"/>
+      <c r="D163" s="35" t="n"/>
+      <c r="E163" s="35" t="n"/>
+      <c r="F163" s="35" t="n"/>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B144" s="20" t="n"/>
-      <c r="C144" s="20" t="n"/>
-      <c r="D144" s="20" t="n"/>
-      <c r="E144" s="20" t="n"/>
-      <c r="F144" s="20" t="n"/>
-    </row>
-    <row r="145" ht="336" customHeight="1">
-      <c r="A145" s="21" t="inlineStr">
+      <c r="B164" s="37" t="n"/>
+      <c r="C164" s="37" t="n"/>
+      <c r="D164" s="37" t="n"/>
+      <c r="E164" s="37" t="n"/>
+      <c r="F164" s="37" t="n"/>
+    </row>
+    <row r="165" ht="336" customHeight="1">
+      <c r="A165" s="38" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -6084,142 +6403,142 @@
         </is>
       </c>
     </row>
-    <row r="146" ht="256.5" customHeight="1"/>
-    <row r="147" ht="6" customHeight="1"/>
-    <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="7" t="inlineStr">
+    <row r="166" ht="256.5" customHeight="1"/>
+    <row r="167" ht="6" customHeight="1"/>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="24" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="8" t="n"/>
-      <c r="D148" s="8" t="n"/>
-      <c r="E148" s="8" t="n"/>
-      <c r="F148" s="8" t="n"/>
-    </row>
-    <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="9" t="inlineStr">
+      <c r="B168" s="25" t="n"/>
+      <c r="C168" s="25" t="n"/>
+      <c r="D168" s="25" t="n"/>
+      <c r="E168" s="25" t="n"/>
+      <c r="F168" s="25" t="n"/>
+    </row>
+    <row r="169" ht="15" customHeight="1">
+      <c r="A169" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B149" s="9" t="inlineStr">
+      <c r="B169" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C149" s="9" t="inlineStr">
+      <c r="C169" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D149" s="9" t="inlineStr">
+      <c r="D169" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E149" s="9" t="inlineStr">
+      <c r="E169" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F149" s="9" t="inlineStr">
+      <c r="F169" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="64" customHeight="1">
-      <c r="A150" s="22" t="inlineStr">
+    <row r="170" ht="64" customHeight="1">
+      <c r="A170" s="39" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B150" s="22" t="inlineStr">
+      <c r="B170" s="39" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C150" s="23" t="inlineStr">
+      <c r="C170" s="40" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="D150" s="27" t="inlineStr">
+      <c r="D170" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E150" s="22" t="inlineStr">
+      <c r="E170" s="39" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
-      <c r="F150" s="22" t="inlineStr">
+      <c r="F170" s="39" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="48" customHeight="1">
-      <c r="A151" s="22" t="inlineStr">
+    <row r="171" ht="48" customHeight="1">
+      <c r="A171" s="39" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B151" s="22" t="inlineStr">
+      <c r="B171" s="39" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C151" s="23" t="inlineStr">
+      <c r="C171" s="40" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="D151" s="15" t="inlineStr">
+      <c r="D171" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E151" s="22" t="inlineStr">
+      <c r="E171" s="39" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 · 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="F151" s="22" t="inlineStr">
+      <c r="F171" s="39" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="17" t="inlineStr">
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 48 · 향 52</t>
         </is>
       </c>
-      <c r="B152" s="18" t="n"/>
-      <c r="C152" s="18" t="n"/>
-      <c r="D152" s="18" t="n"/>
-      <c r="E152" s="18" t="n"/>
-      <c r="F152" s="18" t="n"/>
-    </row>
-    <row r="153" ht="14" customHeight="1">
-      <c r="A153" s="19" t="inlineStr">
+      <c r="B172" s="35" t="n"/>
+      <c r="C172" s="35" t="n"/>
+      <c r="D172" s="35" t="n"/>
+      <c r="E172" s="35" t="n"/>
+      <c r="F172" s="35" t="n"/>
+    </row>
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B153" s="20" t="n"/>
-      <c r="C153" s="20" t="n"/>
-      <c r="D153" s="20" t="n"/>
-      <c r="E153" s="20" t="n"/>
-      <c r="F153" s="20" t="n"/>
-    </row>
-    <row r="154" ht="384" customHeight="1">
-      <c r="A154" s="25" t="inlineStr">
+      <c r="B173" s="37" t="n"/>
+      <c r="C173" s="37" t="n"/>
+      <c r="D173" s="37" t="n"/>
+      <c r="E173" s="37" t="n"/>
+      <c r="F173" s="37" t="n"/>
+    </row>
+    <row r="174" ht="384" customHeight="1">
+      <c r="A174" s="42" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -6247,40 +6566,40 @@
 항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
         </is>
       </c>
-      <c r="B154" s="26" t="n"/>
-      <c r="C154" s="26" t="n"/>
-      <c r="D154" s="26" t="n"/>
-      <c r="E154" s="26" t="n"/>
-      <c r="F154" s="26" t="n"/>
-    </row>
-    <row r="155" ht="48" customHeight="1">
-      <c r="A155" s="25" t="inlineStr">
+      <c r="B174" s="23" t="n"/>
+      <c r="C174" s="23" t="n"/>
+      <c r="D174" s="23" t="n"/>
+      <c r="E174" s="23" t="n"/>
+      <c r="F174" s="23" t="n"/>
+    </row>
+    <row r="175" ht="48" customHeight="1">
+      <c r="A175" s="42" t="inlineStr">
         <is>
           <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B155" s="26" t="n"/>
-      <c r="C155" s="26" t="n"/>
-      <c r="D155" s="26" t="n"/>
-      <c r="E155" s="26" t="n"/>
-      <c r="F155" s="26" t="n"/>
-    </row>
-    <row r="156" ht="14" customHeight="1">
-      <c r="A156" s="19" t="inlineStr">
+      <c r="B175" s="23" t="n"/>
+      <c r="C175" s="23" t="n"/>
+      <c r="D175" s="23" t="n"/>
+      <c r="E175" s="23" t="n"/>
+      <c r="F175" s="23" t="n"/>
+    </row>
+    <row r="176" ht="14" customHeight="1">
+      <c r="A176" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B156" s="20" t="n"/>
-      <c r="C156" s="20" t="n"/>
-      <c r="D156" s="20" t="n"/>
-      <c r="E156" s="20" t="n"/>
-      <c r="F156" s="20" t="n"/>
-    </row>
-    <row r="157" ht="320" customHeight="1">
-      <c r="A157" s="25" t="inlineStr">
+      <c r="B176" s="37" t="n"/>
+      <c r="C176" s="37" t="n"/>
+      <c r="D176" s="37" t="n"/>
+      <c r="E176" s="37" t="n"/>
+      <c r="F176" s="37" t="n"/>
+    </row>
+    <row r="177" ht="320" customHeight="1">
+      <c r="A177" s="42" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -6304,183 +6623,183 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B157" s="26" t="n"/>
-      <c r="C157" s="26" t="n"/>
-      <c r="D157" s="26" t="n"/>
-      <c r="E157" s="26" t="n"/>
-      <c r="F157" s="26" t="n"/>
-    </row>
-    <row r="158" ht="30.50000000000006" customHeight="1">
-      <c r="A158" s="26" t="n"/>
-      <c r="B158" s="26" t="n"/>
-      <c r="C158" s="26" t="n"/>
-      <c r="D158" s="26" t="n"/>
-      <c r="E158" s="26" t="n"/>
-      <c r="F158" s="26" t="n"/>
-    </row>
-    <row r="159" ht="6" customHeight="1"/>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
+      <c r="B177" s="23" t="n"/>
+      <c r="C177" s="23" t="n"/>
+      <c r="D177" s="23" t="n"/>
+      <c r="E177" s="23" t="n"/>
+      <c r="F177" s="23" t="n"/>
+    </row>
+    <row r="178" ht="30.50000000000006" customHeight="1">
+      <c r="A178" s="23" t="n"/>
+      <c r="B178" s="23" t="n"/>
+      <c r="C178" s="23" t="n"/>
+      <c r="D178" s="23" t="n"/>
+      <c r="E178" s="23" t="n"/>
+      <c r="F178" s="23" t="n"/>
+    </row>
+    <row r="179" ht="6" customHeight="1"/>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="24" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="8" t="n"/>
-      <c r="D160" s="8" t="n"/>
-      <c r="E160" s="8" t="n"/>
-      <c r="F160" s="8" t="n"/>
-    </row>
-    <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="9" t="inlineStr">
+      <c r="B180" s="25" t="n"/>
+      <c r="C180" s="25" t="n"/>
+      <c r="D180" s="25" t="n"/>
+      <c r="E180" s="25" t="n"/>
+      <c r="F180" s="25" t="n"/>
+    </row>
+    <row r="181" ht="15" customHeight="1">
+      <c r="A181" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B161" s="9" t="inlineStr">
+      <c r="B181" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C161" s="9" t="inlineStr">
+      <c r="C181" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D161" s="9" t="inlineStr">
+      <c r="D181" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E161" s="9" t="inlineStr">
+      <c r="E181" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F161" s="9" t="inlineStr">
+      <c r="F181" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="64" customHeight="1">
-      <c r="A162" s="10" t="inlineStr">
+    <row r="182" ht="64" customHeight="1">
+      <c r="A182" s="27" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B162" s="10" t="inlineStr">
+      <c r="B182" s="27" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C162" s="11" t="inlineStr"/>
-      <c r="D162" s="12" t="inlineStr">
+      <c r="C182" s="28" t="inlineStr"/>
+      <c r="D182" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E162" s="10" t="inlineStr">
+      <c r="E182" s="27" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F162" s="10" t="inlineStr"/>
-    </row>
-    <row r="163" ht="32" customHeight="1">
-      <c r="A163" s="10" t="inlineStr">
+      <c r="F182" s="27" t="inlineStr"/>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="27" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B163" s="10" t="inlineStr">
+      <c r="B183" s="27" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C163" s="11" t="inlineStr"/>
-      <c r="D163" s="12" t="inlineStr">
+      <c r="C183" s="28" t="inlineStr"/>
+      <c r="D183" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E163" s="10" t="inlineStr">
+      <c r="E183" s="27" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F163" s="10" t="inlineStr">
+      <c r="F183" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="32" customHeight="1">
-      <c r="A164" s="10" t="inlineStr">
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="27" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B164" s="10" t="inlineStr">
+      <c r="B184" s="27" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C164" s="11" t="inlineStr"/>
-      <c r="D164" s="13" t="inlineStr">
+      <c r="C184" s="28" t="inlineStr"/>
+      <c r="D184" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E164" s="10" t="inlineStr">
+      <c r="E184" s="27" t="inlineStr">
         <is>
           <t>스크럽, 노폐물 · 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="F164" s="10" t="inlineStr"/>
-    </row>
-    <row r="165" ht="96" customHeight="1">
-      <c r="A165" s="10" t="inlineStr">
+      <c r="F184" s="27" t="inlineStr"/>
+    </row>
+    <row r="185" ht="96" customHeight="1">
+      <c r="A185" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B165" s="10" t="inlineStr">
+      <c r="B185" s="27" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C165" s="11" t="inlineStr"/>
-      <c r="D165" s="12" t="inlineStr">
+      <c r="C185" s="28" t="inlineStr"/>
+      <c r="D185" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E165" s="10" t="inlineStr">
+      <c r="E185" s="27" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F165" s="10" t="inlineStr">
+      <c r="F185" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="14" customHeight="1">
-      <c r="A166" s="19" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B166" s="20" t="n"/>
-      <c r="C166" s="20" t="n"/>
-      <c r="D166" s="20" t="n"/>
-      <c r="E166" s="20" t="n"/>
-      <c r="F166" s="20" t="n"/>
-    </row>
-    <row r="167" ht="176" customHeight="1">
-      <c r="A167" s="21" t="inlineStr">
+      <c r="B186" s="37" t="n"/>
+      <c r="C186" s="37" t="n"/>
+      <c r="D186" s="37" t="n"/>
+      <c r="E186" s="37" t="n"/>
+      <c r="F186" s="37" t="n"/>
+    </row>
+    <row r="187" ht="176" customHeight="1">
+      <c r="A187" s="38" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -6494,121 +6813,121 @@
         </is>
       </c>
     </row>
-    <row r="168" ht="6" customHeight="1"/>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
+    <row r="188" ht="6" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="24" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="8" t="n"/>
-      <c r="D169" s="8" t="n"/>
-      <c r="E169" s="8" t="n"/>
-      <c r="F169" s="8" t="n"/>
-    </row>
-    <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="B189" s="25" t="n"/>
+      <c r="C189" s="25" t="n"/>
+      <c r="D189" s="25" t="n"/>
+      <c r="E189" s="25" t="n"/>
+      <c r="F189" s="25" t="n"/>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B170" s="9" t="inlineStr">
+      <c r="B190" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C170" s="9" t="inlineStr">
+      <c r="C190" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D170" s="9" t="inlineStr">
+      <c r="D190" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E170" s="9" t="inlineStr">
+      <c r="E190" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F170" s="9" t="inlineStr">
+      <c r="F190" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="32" customHeight="1">
-      <c r="A171" s="22" t="inlineStr">
+    <row r="191" ht="32" customHeight="1">
+      <c r="A191" s="39" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B171" s="22" t="inlineStr">
+      <c r="B191" s="39" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C171" s="23" t="inlineStr"/>
-      <c r="D171" s="14" t="inlineStr">
+      <c r="C191" s="40" t="inlineStr"/>
+      <c r="D191" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E171" s="22" t="inlineStr">
+      <c r="E191" s="39" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="F171" s="22" t="inlineStr">
+      <c r="F191" s="39" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="64" customHeight="1">
-      <c r="A172" s="22" t="inlineStr">
+    <row r="192" ht="64" customHeight="1">
+      <c r="A192" s="39" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B172" s="22" t="inlineStr">
+      <c r="B192" s="39" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C172" s="23" t="inlineStr"/>
-      <c r="D172" s="30" t="inlineStr">
+      <c r="C192" s="40" t="inlineStr"/>
+      <c r="D192" s="46" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E172" s="22" t="inlineStr">
+      <c r="E192" s="39" t="inlineStr">
         <is>
           <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
-      <c r="F172" s="22" t="inlineStr">
+      <c r="F192" s="39" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="19" t="inlineStr">
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B173" s="20" t="n"/>
-      <c r="C173" s="20" t="n"/>
-      <c r="D173" s="20" t="n"/>
-      <c r="E173" s="20" t="n"/>
-      <c r="F173" s="20" t="n"/>
-    </row>
-    <row r="174" ht="112" customHeight="1">
-      <c r="A174" s="25" t="inlineStr">
+      <c r="B193" s="37" t="n"/>
+      <c r="C193" s="37" t="n"/>
+      <c r="D193" s="37" t="n"/>
+      <c r="E193" s="37" t="n"/>
+      <c r="F193" s="37" t="n"/>
+    </row>
+    <row r="194" ht="112" customHeight="1">
+      <c r="A194" s="42" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -6616,26 +6935,26 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B174" s="26" t="n"/>
-      <c r="C174" s="26" t="n"/>
-      <c r="D174" s="26" t="n"/>
-      <c r="E174" s="26" t="n"/>
-      <c r="F174" s="26" t="n"/>
-    </row>
-    <row r="175" ht="14" customHeight="1">
-      <c r="A175" s="19" t="inlineStr">
+      <c r="B194" s="23" t="n"/>
+      <c r="C194" s="23" t="n"/>
+      <c r="D194" s="23" t="n"/>
+      <c r="E194" s="23" t="n"/>
+      <c r="F194" s="23" t="n"/>
+    </row>
+    <row r="195" ht="14" customHeight="1">
+      <c r="A195" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B175" s="20" t="n"/>
-      <c r="C175" s="20" t="n"/>
-      <c r="D175" s="20" t="n"/>
-      <c r="E175" s="20" t="n"/>
-      <c r="F175" s="20" t="n"/>
-    </row>
-    <row r="176" ht="112" customHeight="1">
-      <c r="A176" s="25" t="inlineStr">
+      <c r="B195" s="37" t="n"/>
+      <c r="C195" s="37" t="n"/>
+      <c r="D195" s="37" t="n"/>
+      <c r="E195" s="37" t="n"/>
+      <c r="F195" s="37" t="n"/>
+    </row>
+    <row r="196" ht="112" customHeight="1">
+      <c r="A196" s="42" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -6645,243 +6964,243 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B176" s="26" t="n"/>
-      <c r="C176" s="26" t="n"/>
-      <c r="D176" s="26" t="n"/>
-      <c r="E176" s="26" t="n"/>
-      <c r="F176" s="26" t="n"/>
-    </row>
-    <row r="177" ht="22.99999999999997" customHeight="1">
-      <c r="A177" s="26" t="n"/>
-      <c r="B177" s="26" t="n"/>
-      <c r="C177" s="26" t="n"/>
-      <c r="D177" s="26" t="n"/>
-      <c r="E177" s="26" t="n"/>
-      <c r="F177" s="26" t="n"/>
-    </row>
-    <row r="178" ht="6" customHeight="1"/>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="7" t="inlineStr">
+      <c r="B196" s="23" t="n"/>
+      <c r="C196" s="23" t="n"/>
+      <c r="D196" s="23" t="n"/>
+      <c r="E196" s="23" t="n"/>
+      <c r="F196" s="23" t="n"/>
+    </row>
+    <row r="197" ht="22.99999999999997" customHeight="1">
+      <c r="A197" s="23" t="n"/>
+      <c r="B197" s="23" t="n"/>
+      <c r="C197" s="23" t="n"/>
+      <c r="D197" s="23" t="n"/>
+      <c r="E197" s="23" t="n"/>
+      <c r="F197" s="23" t="n"/>
+    </row>
+    <row r="198" ht="6" customHeight="1"/>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="24" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B179" s="8" t="n"/>
-      <c r="C179" s="8" t="n"/>
-      <c r="D179" s="8" t="n"/>
-      <c r="E179" s="8" t="n"/>
-      <c r="F179" s="8" t="n"/>
-    </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="9" t="inlineStr">
+      <c r="B199" s="25" t="n"/>
+      <c r="C199" s="25" t="n"/>
+      <c r="D199" s="25" t="n"/>
+      <c r="E199" s="25" t="n"/>
+      <c r="F199" s="25" t="n"/>
+    </row>
+    <row r="200" ht="15" customHeight="1">
+      <c r="A200" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B180" s="9" t="inlineStr">
+      <c r="B200" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C180" s="9" t="inlineStr">
+      <c r="C200" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D180" s="9" t="inlineStr">
+      <c r="D200" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E180" s="9" t="inlineStr">
+      <c r="E200" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F180" s="9" t="inlineStr">
+      <c r="F200" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="64" customHeight="1">
-      <c r="A181" s="10" t="inlineStr">
+    <row r="201" ht="64" customHeight="1">
+      <c r="A201" s="27" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B181" s="10" t="inlineStr">
+      <c r="B201" s="27" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C181" s="11" t="inlineStr"/>
-      <c r="D181" s="12" t="inlineStr">
+      <c r="C201" s="28" t="inlineStr"/>
+      <c r="D201" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E181" s="10" t="inlineStr">
+      <c r="E201" s="27" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F181" s="10" t="inlineStr"/>
-    </row>
-    <row r="182" ht="32" customHeight="1">
-      <c r="A182" s="10" t="inlineStr">
+      <c r="F201" s="27" t="inlineStr"/>
+    </row>
+    <row r="202" ht="32" customHeight="1">
+      <c r="A202" s="27" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B182" s="10" t="inlineStr">
+      <c r="B202" s="27" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C182" s="11" t="inlineStr"/>
-      <c r="D182" s="12" t="inlineStr">
+      <c r="C202" s="28" t="inlineStr"/>
+      <c r="D202" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E182" s="10" t="inlineStr">
+      <c r="E202" s="27" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F182" s="10" t="inlineStr">
+      <c r="F202" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="96" customHeight="1">
-      <c r="A183" s="10" t="inlineStr">
+    <row r="203" ht="96" customHeight="1">
+      <c r="A203" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B183" s="10" t="inlineStr">
+      <c r="B203" s="27" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C183" s="11" t="inlineStr"/>
-      <c r="D183" s="12" t="inlineStr">
+      <c r="C203" s="28" t="inlineStr"/>
+      <c r="D203" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E183" s="10" t="inlineStr">
+      <c r="E203" s="27" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F183" s="10" t="inlineStr">
+      <c r="F203" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="48" customHeight="1">
-      <c r="A184" s="10" t="inlineStr">
+    <row r="204" ht="48" customHeight="1">
+      <c r="A204" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B184" s="10" t="inlineStr">
+      <c r="B204" s="27" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C184" s="11" t="inlineStr"/>
-      <c r="D184" s="13" t="inlineStr">
+      <c r="C204" s="28" t="inlineStr"/>
+      <c r="D204" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E184" s="10" t="inlineStr">
+      <c r="E204" s="27" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F184" s="10" t="inlineStr">
+      <c r="F204" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="185" ht="80" customHeight="1">
-      <c r="A185" s="10" t="inlineStr">
+    <row r="205" ht="80" customHeight="1">
+      <c r="A205" s="27" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B185" s="10" t="inlineStr">
+      <c r="B205" s="27" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C185" s="11" t="inlineStr"/>
-      <c r="D185" s="27" t="inlineStr">
+      <c r="C205" s="28" t="inlineStr"/>
+      <c r="D205" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E185" s="10" t="inlineStr">
+      <c r="E205" s="27" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F185" s="10" t="inlineStr">
+      <c r="F205" s="27" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="32" customHeight="1">
-      <c r="A186" s="10" t="inlineStr">
+    <row r="206" ht="32" customHeight="1">
+      <c r="A206" s="27" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B186" s="10" t="inlineStr">
+      <c r="B206" s="27" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C186" s="11" t="inlineStr"/>
-      <c r="D186" s="14" t="inlineStr">
+      <c r="C206" s="28" t="inlineStr"/>
+      <c r="D206" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E186" s="10" t="inlineStr">
+      <c r="E206" s="27" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="F186" s="10" t="inlineStr">
+      <c r="F206" s="27" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="19" t="inlineStr">
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B187" s="20" t="n"/>
-      <c r="C187" s="20" t="n"/>
-      <c r="D187" s="20" t="n"/>
-      <c r="E187" s="20" t="n"/>
-      <c r="F187" s="20" t="n"/>
-    </row>
-    <row r="188" ht="112" customHeight="1">
-      <c r="A188" s="21" t="inlineStr">
+      <c r="B207" s="37" t="n"/>
+      <c r="C207" s="37" t="n"/>
+      <c r="D207" s="37" t="n"/>
+      <c r="E207" s="37" t="n"/>
+      <c r="F207" s="37" t="n"/>
+    </row>
+    <row r="208" ht="112" customHeight="1">
+      <c r="A208" s="38" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -6891,170 +7210,170 @@
         </is>
       </c>
     </row>
-    <row r="189" ht="6" customHeight="1"/>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="7" t="inlineStr">
+    <row r="209" ht="6" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="24" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B190" s="8" t="n"/>
-      <c r="C190" s="8" t="n"/>
-      <c r="D190" s="8" t="n"/>
-      <c r="E190" s="8" t="n"/>
-      <c r="F190" s="8" t="n"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="9" t="inlineStr">
+      <c r="B210" s="25" t="n"/>
+      <c r="C210" s="25" t="n"/>
+      <c r="D210" s="25" t="n"/>
+      <c r="E210" s="25" t="n"/>
+      <c r="F210" s="25" t="n"/>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B191" s="9" t="inlineStr">
+      <c r="B211" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C191" s="9" t="inlineStr">
+      <c r="C211" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D191" s="9" t="inlineStr">
+      <c r="D211" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E191" s="9" t="inlineStr">
+      <c r="E211" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F191" s="9" t="inlineStr">
+      <c r="F211" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="32" customHeight="1">
-      <c r="A192" s="22" t="inlineStr">
+    <row r="212" ht="32" customHeight="1">
+      <c r="A212" s="39" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B192" s="22" t="inlineStr">
+      <c r="B212" s="39" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C192" s="23" t="inlineStr"/>
-      <c r="D192" s="14" t="inlineStr">
+      <c r="C212" s="40" t="inlineStr"/>
+      <c r="D212" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E192" s="22" t="inlineStr">
+      <c r="E212" s="39" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F192" s="22" t="inlineStr"/>
-    </row>
-    <row r="193" ht="112" customHeight="1">
-      <c r="A193" s="22" t="inlineStr">
+      <c r="F212" s="39" t="inlineStr"/>
+    </row>
+    <row r="213" ht="112" customHeight="1">
+      <c r="A213" s="39" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B193" s="22" t="inlineStr">
+      <c r="B213" s="39" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C193" s="23" t="inlineStr"/>
-      <c r="D193" s="15" t="inlineStr">
+      <c r="C213" s="40" t="inlineStr"/>
+      <c r="D213" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E193" s="22" t="inlineStr">
+      <c r="E213" s="39" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F193" s="22" t="inlineStr">
+      <c r="F213" s="39" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="32" customHeight="1">
-      <c r="A194" s="22" t="inlineStr">
+    <row r="214" ht="32" customHeight="1">
+      <c r="A214" s="39" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B194" s="22" t="inlineStr">
+      <c r="B214" s="39" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C194" s="23" t="inlineStr"/>
-      <c r="D194" s="15" t="inlineStr">
+      <c r="C214" s="40" t="inlineStr"/>
+      <c r="D214" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E194" s="22" t="inlineStr">
+      <c r="E214" s="39" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="F194" s="22" t="inlineStr">
+      <c r="F214" s="39" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="14" customHeight="1">
-      <c r="A195" s="19" t="inlineStr">
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B195" s="20" t="n"/>
-      <c r="C195" s="20" t="n"/>
-      <c r="D195" s="20" t="n"/>
-      <c r="E195" s="20" t="n"/>
-      <c r="F195" s="20" t="n"/>
-    </row>
-    <row r="196" ht="80" customHeight="1">
-      <c r="A196" s="25" t="inlineStr">
+      <c r="B215" s="37" t="n"/>
+      <c r="C215" s="37" t="n"/>
+      <c r="D215" s="37" t="n"/>
+      <c r="E215" s="37" t="n"/>
+      <c r="F215" s="37" t="n"/>
+    </row>
+    <row r="216" ht="80" customHeight="1">
+      <c r="A216" s="42" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B196" s="26" t="n"/>
-      <c r="C196" s="26" t="n"/>
-      <c r="D196" s="26" t="n"/>
-      <c r="E196" s="26" t="n"/>
-      <c r="F196" s="26" t="n"/>
-    </row>
-    <row r="197" ht="14" customHeight="1">
-      <c r="A197" s="19" t="inlineStr">
+      <c r="B216" s="23" t="n"/>
+      <c r="C216" s="23" t="n"/>
+      <c r="D216" s="23" t="n"/>
+      <c r="E216" s="23" t="n"/>
+      <c r="F216" s="23" t="n"/>
+    </row>
+    <row r="217" ht="14" customHeight="1">
+      <c r="A217" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B197" s="20" t="n"/>
-      <c r="C197" s="20" t="n"/>
-      <c r="D197" s="20" t="n"/>
-      <c r="E197" s="20" t="n"/>
-      <c r="F197" s="20" t="n"/>
-    </row>
-    <row r="198" ht="128" customHeight="1">
-      <c r="A198" s="25" t="inlineStr">
+      <c r="B217" s="37" t="n"/>
+      <c r="C217" s="37" t="n"/>
+      <c r="D217" s="37" t="n"/>
+      <c r="E217" s="37" t="n"/>
+      <c r="F217" s="37" t="n"/>
+    </row>
+    <row r="218" ht="128" customHeight="1">
+      <c r="A218" s="42" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -7065,167 +7384,167 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B198" s="26" t="n"/>
-      <c r="C198" s="26" t="n"/>
-      <c r="D198" s="26" t="n"/>
-      <c r="E198" s="26" t="n"/>
-      <c r="F198" s="26" t="n"/>
-    </row>
-    <row r="199" ht="6" customHeight="1"/>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="7" t="inlineStr">
+      <c r="B218" s="23" t="n"/>
+      <c r="C218" s="23" t="n"/>
+      <c r="D218" s="23" t="n"/>
+      <c r="E218" s="23" t="n"/>
+      <c r="F218" s="23" t="n"/>
+    </row>
+    <row r="219" ht="6" customHeight="1"/>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="24" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B200" s="8" t="n"/>
-      <c r="C200" s="8" t="n"/>
-      <c r="D200" s="8" t="n"/>
-      <c r="E200" s="8" t="n"/>
-      <c r="F200" s="8" t="n"/>
-    </row>
-    <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="9" t="inlineStr">
+      <c r="B220" s="25" t="n"/>
+      <c r="C220" s="25" t="n"/>
+      <c r="D220" s="25" t="n"/>
+      <c r="E220" s="25" t="n"/>
+      <c r="F220" s="25" t="n"/>
+    </row>
+    <row r="221" ht="15" customHeight="1">
+      <c r="A221" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B201" s="9" t="inlineStr">
+      <c r="B221" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C201" s="9" t="inlineStr">
+      <c r="C221" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D201" s="9" t="inlineStr">
+      <c r="D221" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E201" s="9" t="inlineStr">
+      <c r="E221" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F201" s="9" t="inlineStr">
+      <c r="F221" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="64" customHeight="1">
-      <c r="A202" s="10" t="inlineStr">
+    <row r="222" ht="64" customHeight="1">
+      <c r="A222" s="27" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B202" s="10" t="inlineStr">
+      <c r="B222" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C202" s="11" t="inlineStr">
+      <c r="C222" s="28" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D202" s="27" t="inlineStr">
+      <c r="D222" s="43" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E202" s="10" t="inlineStr">
+      <c r="E222" s="27" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="F202" s="10" t="inlineStr"/>
-    </row>
-    <row r="203" ht="32" customHeight="1">
-      <c r="A203" s="10" t="inlineStr">
+      <c r="F222" s="27" t="inlineStr"/>
+    </row>
+    <row r="223" ht="32" customHeight="1">
+      <c r="A223" s="27" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B203" s="10" t="inlineStr">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C203" s="11" t="inlineStr">
+      <c r="C223" s="28" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D203" s="14" t="inlineStr">
+      <c r="D223" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E203" s="10" t="inlineStr">
+      <c r="E223" s="27" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 · →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="F203" s="10" t="inlineStr"/>
-    </row>
-    <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="10" t="inlineStr">
+      <c r="F223" s="27" t="inlineStr"/>
+    </row>
+    <row r="224" ht="16" customHeight="1">
+      <c r="A224" s="27" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B204" s="10" t="inlineStr">
+      <c r="B224" s="27" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C204" s="11" t="inlineStr">
+      <c r="C224" s="28" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="D204" s="14" t="inlineStr">
+      <c r="D224" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E204" s="10" t="inlineStr">
+      <c r="E224" s="27" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="F204" s="10" t="inlineStr"/>
-    </row>
-    <row r="205" ht="14" customHeight="1">
-      <c r="A205" s="17" t="inlineStr">
+      <c r="F224" s="27" t="inlineStr"/>
+    </row>
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
         </is>
       </c>
-      <c r="B205" s="18" t="n"/>
-      <c r="C205" s="18" t="n"/>
-      <c r="D205" s="18" t="n"/>
-      <c r="E205" s="18" t="n"/>
-      <c r="F205" s="18" t="n"/>
-    </row>
-    <row r="206" ht="14" customHeight="1">
-      <c r="A206" s="19" t="inlineStr">
+      <c r="B225" s="35" t="n"/>
+      <c r="C225" s="35" t="n"/>
+      <c r="D225" s="35" t="n"/>
+      <c r="E225" s="35" t="n"/>
+      <c r="F225" s="35" t="n"/>
+    </row>
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B206" s="20" t="n"/>
-      <c r="C206" s="20" t="n"/>
-      <c r="D206" s="20" t="n"/>
-      <c r="E206" s="20" t="n"/>
-      <c r="F206" s="20" t="n"/>
-    </row>
-    <row r="207" ht="384" customHeight="1">
-      <c r="A207" s="21" t="inlineStr">
+      <c r="B226" s="37" t="n"/>
+      <c r="C226" s="37" t="n"/>
+      <c r="D226" s="37" t="n"/>
+      <c r="E226" s="37" t="n"/>
+      <c r="F226" s="37" t="n"/>
+    </row>
+    <row r="227" ht="384" customHeight="1">
+      <c r="A227" s="38" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -7254,8 +7573,8 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="112" customHeight="1">
-      <c r="A208" s="21" t="inlineStr">
+    <row r="228" ht="112" customHeight="1">
+      <c r="A228" s="38" t="inlineStr">
         <is>
           <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
@@ -7267,20 +7586,20 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="14" customHeight="1">
-      <c r="A209" s="19" t="inlineStr">
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B209" s="20" t="n"/>
-      <c r="C209" s="20" t="n"/>
-      <c r="D209" s="20" t="n"/>
-      <c r="E209" s="20" t="n"/>
-      <c r="F209" s="20" t="n"/>
-    </row>
-    <row r="210" ht="112" customHeight="1">
-      <c r="A210" s="21" t="inlineStr">
+      <c r="B229" s="37" t="n"/>
+      <c r="C229" s="37" t="n"/>
+      <c r="D229" s="37" t="n"/>
+      <c r="E229" s="37" t="n"/>
+      <c r="F229" s="37" t="n"/>
+    </row>
+    <row r="230" ht="112" customHeight="1">
+      <c r="A230" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -7292,127 +7611,147 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="6" customHeight="1"/>
+    <row r="231" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="99">
+  <mergeCells count="119">
     <mergeCell ref="A174:F174"/>
-    <mergeCell ref="A205:F205"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B16:F16"/>
     <mergeCell ref="A66:F66"/>
     <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="A189:F189"/>
     <mergeCell ref="A50:F50"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A55:F55"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A160:F160"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A95:F95"/>
     <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A144:F144"/>
-    <mergeCell ref="A72:F72"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A150:F150"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A134:F134"/>
-    <mergeCell ref="A200:F200"/>
-    <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A70:F70"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A228:F228"/>
+    <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A149:F149"/>
     <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="A163:F163"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A151:F151"/>
     <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A206:F206"/>
-    <mergeCell ref="A190:F190"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A215:F215"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="A199:F199"/>
     <mergeCell ref="A112:F112"/>
+    <mergeCell ref="A230:F230"/>
+    <mergeCell ref="B10:F10"/>
     <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A167:F167"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A114:F114"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A216:F216"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A225:F225"/>
     <mergeCell ref="A79:F79"/>
     <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A153:F153"/>
+    <mergeCell ref="A218:F218"/>
+    <mergeCell ref="A227:F227"/>
     <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A137:F137"/>
+    <mergeCell ref="A177:F177"/>
     <mergeCell ref="A90:F90"/>
     <mergeCell ref="A208:F208"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A145:F145"/>
+    <mergeCell ref="A217:F217"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A139:F139"/>
     <mergeCell ref="A154:F154"/>
     <mergeCell ref="A210:F210"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="A129:F129"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A131:F131"/>
     <mergeCell ref="A100:F100"/>
-    <mergeCell ref="A53:F53"/>
-    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A165:F165"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A180:F180"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A117:F117"/>
     <mergeCell ref="A173:F173"/>
+    <mergeCell ref="A229:F229"/>
+    <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A157:F157"/>
-    <mergeCell ref="A166:F166"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="A78:F78"/>
-    <mergeCell ref="A128:F128"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A37:F37"/>
     <mergeCell ref="A89:F89"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A113:F113"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A194:F194"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A209:F209"/>
-    <mergeCell ref="A91:F91"/>
-    <mergeCell ref="A156:F156"/>
-    <mergeCell ref="A155:F155"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A147:F147"/>
     <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A130:F130"/>
+    <mergeCell ref="A220:F220"/>
     <mergeCell ref="A77:F77"/>
     <mergeCell ref="A148:F148"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A110:F110"/>
     <mergeCell ref="A187:F187"/>
-    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A160" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A169" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A200" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>

--- a/카드_아키타입/13_입욕·스크럽.xlsx
+++ b/카드_아키타입/13_입욕·스크럽.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,13 @@
       <color rgb="0055606E"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B3A7A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -178,6 +183,16 @@
         <fgColor rgb="00EEF3F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3EEFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF8FD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -210,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -308,6 +323,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1393,7 +1415,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="45370750"/>
+    <pos x="7848600" y="46120050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1413,7 +1435,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="45370750"/>
+    <pos x="9696450" y="46120050"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1433,7 +1455,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="45370750"/>
+    <pos x="11544300" y="46120050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1453,7 +1475,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="45370750"/>
+    <pos x="13392150" y="46120050"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1473,7 +1495,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="47218600"/>
+    <pos x="7848600" y="47967900"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1493,7 +1515,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="49701450"/>
+    <pos x="7848600" y="51009550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1513,7 +1535,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="49701450"/>
+    <pos x="9696450" y="51009550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1533,7 +1555,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="49701450"/>
+    <pos x="11544300" y="51009550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1553,7 +1575,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="49701450"/>
+    <pos x="13392150" y="51009550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,7 +1595,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="51549300"/>
+    <pos x="7848600" y="52857400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1593,7 +1615,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="51549300"/>
+    <pos x="9696450" y="52857400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1613,7 +1635,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="51549300"/>
+    <pos x="11544300" y="52857400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1633,7 +1655,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="51549300"/>
+    <pos x="13392150" y="52857400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1653,7 +1675,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="53397150"/>
+    <pos x="7848600" y="54705250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,7 +1695,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="53397150"/>
+    <pos x="9696450" y="54705250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1693,7 +1715,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="59315350"/>
+    <pos x="7848600" y="61182250"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1713,7 +1735,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="59315350"/>
+    <pos x="9696450" y="61182250"/>
     <ext cx="1600200" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1733,7 +1755,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="59315350"/>
+    <pos x="11544300" y="61182250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1753,7 +1775,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="59315350"/>
+    <pos x="13392150" y="61182250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,7 +1795,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="61163200"/>
+    <pos x="7848600" y="63030100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1793,7 +1815,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="67100450"/>
+    <pos x="7848600" y="68967350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1813,7 +1835,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="67100450"/>
+    <pos x="9696450" y="68967350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1833,7 +1855,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="67100450"/>
+    <pos x="11544300" y="68967350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1853,7 +1875,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="67100450"/>
+    <pos x="13392150" y="68967350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1873,7 +1895,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="68948300"/>
+    <pos x="7848600" y="70815200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1893,7 +1915,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="68948300"/>
+    <pos x="9696450" y="70815200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1913,7 +1935,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="70796150"/>
+    <pos x="7848600" y="72663050"/>
     <ext cx="5143500" cy="3429000"/>
     <pic>
       <nvPicPr>
@@ -1933,7 +1955,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="75495150"/>
+    <pos x="7848600" y="77895450"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1953,7 +1975,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="75495150"/>
+    <pos x="9696450" y="77895450"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1973,7 +1995,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="75495150"/>
+    <pos x="11544300" y="77895450"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -1993,7 +2015,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="75495150"/>
+    <pos x="13392150" y="77895450"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2013,7 +2035,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="77343000"/>
+    <pos x="7848600" y="79743300"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2033,7 +2055,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="77343000"/>
+    <pos x="9696450" y="79743300"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2053,7 +2075,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="77343000"/>
+    <pos x="11544300" y="79743300"/>
     <ext cx="1428750" cy="1257300"/>
     <pic>
       <nvPicPr>
@@ -2073,7 +2095,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="77343000"/>
+    <pos x="13392150" y="79743300"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2093,7 +2115,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="79190850"/>
+    <pos x="7848600" y="81591150"/>
     <ext cx="1809750" cy="1647825"/>
     <pic>
       <nvPicPr>
@@ -2113,7 +2135,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="81038700"/>
+    <pos x="7848600" y="83439000"/>
     <ext cx="5143500" cy="4286250"/>
     <pic>
       <nvPicPr>
@@ -2133,7 +2155,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="85439250"/>
+    <pos x="7848600" y="87839550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2153,7 +2175,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="85439250"/>
+    <pos x="9696450" y="87839550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2173,7 +2195,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="85439250"/>
+    <pos x="11544300" y="87839550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2193,7 +2215,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="87287100"/>
+    <pos x="7848600" y="89687400"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2213,7 +2235,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="95865950"/>
+    <pos x="7848600" y="98825050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2233,7 +2255,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="95865950"/>
+    <pos x="9696450" y="98825050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2253,7 +2275,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="95865950"/>
+    <pos x="11544300" y="98825050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2273,7 +2295,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="95865950"/>
+    <pos x="13392150" y="98825050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2293,7 +2315,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="97713800"/>
+    <pos x="7848600" y="100672900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2313,7 +2335,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="97713800"/>
+    <pos x="9696450" y="100672900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2333,7 +2355,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="97713800"/>
+    <pos x="11544300" y="100672900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2353,7 +2375,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="97713800"/>
+    <pos x="13392150" y="100672900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2373,7 +2395,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="99561650"/>
+    <pos x="7848600" y="102520750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2393,7 +2415,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="101409500"/>
+    <pos x="7848600" y="104368600"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2413,7 +2435,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="106667300"/>
+    <pos x="7848600" y="109626400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2433,7 +2455,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="106667300"/>
+    <pos x="9696450" y="109626400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2453,7 +2475,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="106667300"/>
+    <pos x="11544300" y="109626400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2473,7 +2495,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="106667300"/>
+    <pos x="13392150" y="109626400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2493,7 +2515,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="108515150"/>
+    <pos x="7848600" y="111474250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2513,7 +2535,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="108515150"/>
+    <pos x="9696450" y="111474250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2533,7 +2555,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="108515150"/>
+    <pos x="11544300" y="111474250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2553,7 +2575,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="108515150"/>
+    <pos x="13392150" y="111474250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2573,7 +2595,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="110363000"/>
+    <pos x="7848600" y="113322100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2593,7 +2615,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="110363000"/>
+    <pos x="9696450" y="113322100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2613,7 +2635,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="112210850"/>
+    <pos x="7848600" y="115169950"/>
     <ext cx="5143500" cy="4352925"/>
     <pic>
       <nvPicPr>
@@ -2633,7 +2655,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="116601875"/>
+    <pos x="7848600" y="119560975"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2653,7 +2675,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="118344950"/>
+    <pos x="7848600" y="121304050"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2673,7 +2695,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="120192800"/>
+    <pos x="7848600" y="123151900"/>
     <ext cx="5143500" cy="4352925"/>
     <pic>
       <nvPicPr>
@@ -2693,7 +2715,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="124583825"/>
+    <pos x="7848600" y="127542925"/>
     <ext cx="5143500" cy="4419600"/>
     <pic>
       <nvPicPr>
@@ -2713,7 +2735,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="129041525"/>
+    <pos x="7848600" y="132000625"/>
     <ext cx="5143500" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -2733,7 +2755,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="130784600"/>
+    <pos x="7848600" y="133915150"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2753,7 +2775,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="136588500"/>
+    <pos x="7848600" y="139719050"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2773,7 +2795,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="141846300"/>
+    <pos x="7848600" y="144976850"/>
     <ext cx="3505200" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2793,7 +2815,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="148463000"/>
+    <pos x="7848600" y="151593550"/>
     <ext cx="3200400" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -2813,7 +2835,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="154241500"/>
+    <pos x="7848600" y="157372050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2833,7 +2855,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="154241500"/>
+    <pos x="9696450" y="157372050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2853,7 +2875,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="154241500"/>
+    <pos x="11544300" y="157372050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,7 +2895,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="154241500"/>
+    <pos x="13392150" y="157372050"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2893,7 +2915,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="156089350"/>
+    <pos x="7848600" y="159219900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2913,7 +2935,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="156089350"/>
+    <pos x="9696450" y="159219900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2933,7 +2955,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="157937200"/>
+    <pos x="7848600" y="161067750"/>
     <ext cx="5143500" cy="5143500"/>
     <pic>
       <nvPicPr>
@@ -3244,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F230"/>
+  <dimension ref="A1:F253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3859,234 +3881,254 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="326.0000000000001" customHeight="1"/>
-    <row r="41" ht="6" customHeight="1"/>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="24" t="inlineStr">
+    <row r="40" ht="14" customHeight="1">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B40" s="40" t="n"/>
+      <c r="C40" s="40" t="n"/>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="40" t="n"/>
+      <c r="F40" s="40" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 23%(옥수수전분 23%)가 제형의 뼈대·수분 공급.
+· 마무리: 점증·pH 68% · 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="282" customHeight="1"/>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
         <is>
           <t>아로마 바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="B44" s="25" t="n"/>
+      <c r="C44" s="25" t="n"/>
+      <c r="D44" s="25" t="n"/>
+      <c r="E44" s="25" t="n"/>
+      <c r="F44" s="25" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B43" s="26" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="39" t="inlineStr">
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" s="42" t="inlineStr">
         <is>
           <t>베이킹 소다</t>
         </is>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B46" s="42" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="D46" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E44" s="39" t="inlineStr">
+      <c r="E46" s="42" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F44" s="39" t="inlineStr"/>
-    </row>
-    <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="39" t="inlineStr">
+      <c r="F46" s="42" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="42" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B47" s="42" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C45" s="40" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D45" s="29" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E45" s="39" t="inlineStr">
+      <c r="E47" s="42" t="inlineStr">
         <is>
           <t>pH조절 ,균형, 각질 연화</t>
         </is>
       </c>
-      <c r="F45" s="39" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="96" customHeight="1">
-      <c r="A46" s="39" t="inlineStr">
+    <row r="48" ht="96" customHeight="1">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B48" s="42" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C46" s="40" t="inlineStr">
+      <c r="C48" s="43" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D46" s="31" t="inlineStr">
+      <c r="D48" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E46" s="39" t="inlineStr">
+      <c r="E48" s="42" t="inlineStr">
         <is>
           <t>흡착</t>
         </is>
       </c>
-      <c r="F46" s="39" t="inlineStr">
+      <c r="F48" s="42" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="39" t="inlineStr">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="42" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B49" s="42" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C47" s="40" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D47" s="41" t="inlineStr">
+      <c r="D49" s="44" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E47" s="39" t="inlineStr">
+      <c r="E49" s="42" t="inlineStr">
         <is>
           <t>보습, 잘 뭉쳐지게</t>
         </is>
       </c>
-      <c r="F47" s="39" t="inlineStr">
+      <c r="F49" s="42" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="39" t="inlineStr">
+    <row r="50" ht="32" customHeight="1">
+      <c r="A50" s="42" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B50" s="42" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C48" s="40" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D48" s="32" t="inlineStr">
+      <c r="D50" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E48" s="39" t="inlineStr">
+      <c r="E50" s="42" t="inlineStr">
         <is>
           <t>허브의 여왕</t>
         </is>
       </c>
-      <c r="F48" s="39" t="inlineStr">
+      <c r="F50" s="42" t="inlineStr">
         <is>
           <t>레몬, 오렌지 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="34" t="inlineStr">
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  보습 5 · 향 1 · 점증/pH 71 · 기타 24</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="35" t="n"/>
-      <c r="E49" s="35" t="n"/>
-      <c r="F49" s="35" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="36" t="inlineStr">
+      <c r="B51" s="35" t="n"/>
+      <c r="C51" s="35" t="n"/>
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="35" t="n"/>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B50" s="37" t="n"/>
-      <c r="C50" s="37" t="n"/>
-      <c r="D50" s="37" t="n"/>
-      <c r="E50" s="37" t="n"/>
-      <c r="F50" s="37" t="n"/>
-    </row>
-    <row r="51" ht="288" customHeight="1">
-      <c r="A51" s="42" t="inlineStr">
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="37" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="37" t="n"/>
+    </row>
+    <row r="53" ht="288" customHeight="1">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>만들기과정
 1.베이킹소다와 구연산, 옥수수전분을 넓은 볼에 계량하세요.
@@ -4105,335 +4147,354 @@
 15.건초 양을 달리하여 만들기해보세요. 완성. 글리세린 덕분에 부서지지 않고 모양은 잘 잡히지만 금방 단단해지지 않습니다.</t>
         </is>
       </c>
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="23" t="n"/>
-      <c r="F51" s="23" t="n"/>
-    </row>
-    <row r="52" ht="313.5" customHeight="1">
-      <c r="A52" s="23" t="n"/>
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="23" t="n"/>
-      <c r="F52" s="23" t="n"/>
-    </row>
-    <row r="53" ht="6" customHeight="1"/>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="23" t="n"/>
+      <c r="F53" s="23" t="n"/>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B54" s="40" t="n"/>
+      <c r="C54" s="40" t="n"/>
+      <c r="D54" s="40" t="n"/>
+      <c r="E54" s="40" t="n"/>
+      <c r="F54" s="40" t="n"/>
+    </row>
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="41" t="inlineStr">
+        <is>
+          <t>· 마무리: 보습 5% · 점증·pH 71% · 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="271.5" customHeight="1">
+      <c r="A56" s="23" t="n"/>
+      <c r="B56" s="23" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="23" t="n"/>
+      <c r="F56" s="23" t="n"/>
+    </row>
+    <row r="57" ht="6" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>버블바스붐    [색내기 / (액상)]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="n"/>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="n"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="B58" s="25" t="n"/>
+      <c r="C58" s="25" t="n"/>
+      <c r="D58" s="25" t="n"/>
+      <c r="E58" s="25" t="n"/>
+      <c r="F58" s="25" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B55" s="26" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
+      <c r="C59" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D55" s="26" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E55" s="26" t="inlineStr">
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="F59" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="27" t="inlineStr">
-        <is>
-          <t>코치닐+물</t>
-        </is>
-      </c>
-      <c r="B56" s="27" t="inlineStr">
-        <is>
-          <t>1g+3g</t>
-        </is>
-      </c>
-      <c r="C56" s="28" t="inlineStr">
-        <is>
-          <t>&lt;1%</t>
-        </is>
-      </c>
-      <c r="D56" s="30" t="inlineStr">
-        <is>
-          <t>수상</t>
-        </is>
-      </c>
-      <c r="E56" s="27" t="inlineStr">
-        <is>
-          <t>반드시 양조절해서 · 색내기에 사용하세요.</t>
-        </is>
-      </c>
-      <c r="F56" s="27" t="inlineStr">
-        <is>
-          <t>원하는 색</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="27" t="inlineStr">
-        <is>
-          <t>베이킹소다</t>
-        </is>
-      </c>
-      <c r="B57" s="27" t="inlineStr">
-        <is>
-          <t>250g</t>
-        </is>
-      </c>
-      <c r="C57" s="28" t="inlineStr">
-        <is>
-          <t>39%</t>
-        </is>
-      </c>
-      <c r="D57" s="29" t="inlineStr">
-        <is>
-          <t>점증/pH</t>
-        </is>
-      </c>
-      <c r="E57" s="27" t="inlineStr">
-        <is>
-          <t>미네럴 공급, 연수화</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="inlineStr"/>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="27" t="inlineStr">
-        <is>
-          <t>주석산</t>
-        </is>
-      </c>
-      <c r="B58" s="27" t="inlineStr">
-        <is>
-          <t>125g</t>
-        </is>
-      </c>
-      <c r="C58" s="28" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="D58" s="29" t="inlineStr">
-        <is>
-          <t>점증/pH</t>
-        </is>
-      </c>
-      <c r="E58" s="27" t="inlineStr">
-        <is>
-          <t>각질연화, pH조절</t>
-        </is>
-      </c>
-      <c r="F58" s="27" t="inlineStr"/>
-    </row>
-    <row r="59" ht="96" customHeight="1">
-      <c r="A59" s="27" t="inlineStr">
-        <is>
-          <t>옥수수전분</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="inlineStr">
-        <is>
-          <t>63g</t>
-        </is>
-      </c>
-      <c r="C59" s="28" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D59" s="31" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="E59" s="27" t="inlineStr">
-        <is>
-          <t>흡착, 모양만들기</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>SLSA</t>
+          <t>코치닐+물</t>
         </is>
       </c>
       <c r="B60" s="27" t="inlineStr">
         <is>
-          <t>83g</t>
+          <t>1g+3g</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
         <is>
-          <t>13%</t>
-        </is>
-      </c>
-      <c r="D60" s="33" t="inlineStr">
-        <is>
-          <t>계면</t>
+          <t>&lt;1%</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>수상</t>
         </is>
       </c>
       <c r="E60" s="27" t="inlineStr">
         <is>
-          <t>코코넛유래 · 거품, 세정, 음이온</t>
-        </is>
-      </c>
-      <c r="F60" s="27" t="inlineStr"/>
+          <t>반드시 양조절해서 · 색내기에 사용하세요.</t>
+        </is>
+      </c>
+      <c r="F60" s="27" t="inlineStr">
+        <is>
+          <t>원하는 색</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="16" customHeight="1">
       <c r="A61" s="27" t="inlineStr">
         <is>
+          <t>베이킹소다</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>250g</t>
+        </is>
+      </c>
+      <c r="C61" s="28" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="D61" s="29" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>미네럴 공급, 연수화</t>
+        </is>
+      </c>
+      <c r="F61" s="27" t="inlineStr"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="27" t="inlineStr">
+        <is>
+          <t>주석산</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>125g</t>
+        </is>
+      </c>
+      <c r="C62" s="28" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D62" s="29" t="inlineStr">
+        <is>
+          <t>점증/pH</t>
+        </is>
+      </c>
+      <c r="E62" s="27" t="inlineStr">
+        <is>
+          <t>각질연화, pH조절</t>
+        </is>
+      </c>
+      <c r="F62" s="27" t="inlineStr"/>
+    </row>
+    <row r="63" ht="96" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>옥수수전분</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>63g</t>
+        </is>
+      </c>
+      <c r="C63" s="28" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>흡착, 모양만들기</t>
+        </is>
+      </c>
+      <c r="F63" s="27" t="inlineStr">
+        <is>
+          <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
+          <t>SLSA</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>83g</t>
+        </is>
+      </c>
+      <c r="C64" s="28" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="D64" s="33" t="inlineStr">
+        <is>
+          <t>계면</t>
+        </is>
+      </c>
+      <c r="E64" s="27" t="inlineStr">
+        <is>
+          <t>코코넛유래 · 거품, 세정, 음이온</t>
+        </is>
+      </c>
+      <c r="F64" s="27" t="inlineStr"/>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
           <t>코코-베타인</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B65" s="27" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C61" s="28" t="inlineStr">
+      <c r="C65" s="28" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D61" s="33" t="inlineStr">
+      <c r="D65" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E61" s="27" t="inlineStr">
+      <c r="E65" s="27" t="inlineStr">
         <is>
           <t>코코넛 유래, 양쪽성 이온</t>
         </is>
       </c>
-      <c r="F61" s="27" t="inlineStr">
+      <c r="F65" s="27" t="inlineStr">
         <is>
           <t>애플 · 계면활성제</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="80" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+    <row r="66" ht="80" customHeight="1">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C62" s="28" t="inlineStr">
+      <c r="C66" s="28" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D62" s="43" t="inlineStr">
+      <c r="D66" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>보습, 오일</t>
         </is>
       </c>
-      <c r="F62" s="27" t="inlineStr">
+      <c r="F66" s="27" t="inlineStr">
         <is>
           <t>붉은 색을 원하면 자초인퓨즈오일사용, 호호바, 마카다미아넛, 동백, 햄프 베이스오일 등등</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="27" t="inlineStr">
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>라벤더EO</t>
         </is>
       </c>
-      <c r="B63" s="27" t="inlineStr">
+      <c r="B67" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C63" s="28" t="inlineStr">
+      <c r="C67" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D63" s="32" t="inlineStr">
+      <c r="D67" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E63" s="27" t="inlineStr">
+      <c r="E67" s="27" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="F63" s="27" t="inlineStr">
+      <c r="F67" s="27" t="inlineStr">
         <is>
           <t>원하는 향</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="34" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 0 · 유상 3 · 계면 26 · 향 2 · 점증/pH 59 · 기타 10</t>
         </is>
       </c>
-      <c r="B64" s="35" t="n"/>
-      <c r="C64" s="35" t="n"/>
-      <c r="D64" s="35" t="n"/>
-      <c r="E64" s="35" t="n"/>
-      <c r="F64" s="35" t="n"/>
-    </row>
-    <row r="65" ht="14" customHeight="1">
-      <c r="A65" s="36" t="inlineStr">
+      <c r="B68" s="35" t="n"/>
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="35" t="n"/>
+    </row>
+    <row r="69" ht="14" customHeight="1">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B65" s="37" t="n"/>
-      <c r="C65" s="37" t="n"/>
-      <c r="D65" s="37" t="n"/>
-      <c r="E65" s="37" t="n"/>
-      <c r="F65" s="37" t="n"/>
-    </row>
-    <row r="66" ht="96" customHeight="1">
-      <c r="A66" s="38" t="inlineStr">
+      <c r="B69" s="37" t="n"/>
+      <c r="C69" s="37" t="n"/>
+      <c r="D69" s="37" t="n"/>
+      <c r="E69" s="37" t="n"/>
+      <c r="F69" s="37" t="n"/>
+    </row>
+    <row r="70" ht="96" customHeight="1">
+      <c r="A70" s="38" t="inlineStr">
         <is>
           <t>버블바스붐은 풍성한 거품이 나는 입욕제로
 피부 속 노폐물 제거, 촉촉하고 부드러운 피부로 가꿔줍니다.
@@ -4444,20 +4505,20 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="36" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B67" s="37" t="n"/>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="37" t="n"/>
-      <c r="E67" s="37" t="n"/>
-      <c r="F67" s="37" t="n"/>
-    </row>
-    <row r="68" ht="192" customHeight="1">
-      <c r="A68" s="38" t="inlineStr">
+      <c r="B71" s="37" t="n"/>
+      <c r="C71" s="37" t="n"/>
+      <c r="D71" s="37" t="n"/>
+      <c r="E71" s="37" t="n"/>
+      <c r="F71" s="37" t="n"/>
+    </row>
+    <row r="72" ht="192" customHeight="1">
+      <c r="A72" s="38" t="inlineStr">
         <is>
           <t>1. 색소를 미리 만들어 놓습니다.
 2. 넓은 용기에 2번 분말 재료를 계량하고 골고루 섞어주세요.
@@ -4474,105 +4535,126 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="6" customHeight="1"/>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="24" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B73" s="40" t="n"/>
+      <c r="C73" s="40" t="n"/>
+      <c r="D73" s="40" t="n"/>
+      <c r="E73" s="40" t="n"/>
+      <c r="F73" s="40" t="n"/>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="41" t="inlineStr">
+        <is>
+          <t>· 제형: 계면활성제 26% → 세정 제형. 농도가 세정력·자극을 좌우(높을수록 강하고 건조).
+· 베이스: 유상 중심, 주 오일 아보카도오일(3%)로 보습막·발림 설계.
+· 마무리: 점증·pH 59% · 향 2% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="6" customHeight="1"/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>아로마 바스솔트    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B70" s="25" t="n"/>
-      <c r="C70" s="25" t="n"/>
-      <c r="D70" s="25" t="n"/>
-      <c r="E70" s="25" t="n"/>
-      <c r="F70" s="25" t="n"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="26" t="inlineStr">
+      <c r="B76" s="25" t="n"/>
+      <c r="C76" s="25" t="n"/>
+      <c r="D76" s="25" t="n"/>
+      <c r="E76" s="25" t="n"/>
+      <c r="F76" s="25" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B71" s="26" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D71" s="26" t="inlineStr">
+      <c r="D77" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E71" s="26" t="inlineStr">
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F71" s="26" t="inlineStr">
+      <c r="F77" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="39" t="inlineStr">
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="42" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B78" s="42" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C72" s="40" t="inlineStr">
+      <c r="C78" s="43" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E72" s="39" t="inlineStr">
+      <c r="E78" s="42" t="inlineStr">
         <is>
           <t>풍부한 미네랄 · 노폐물제거</t>
         </is>
       </c>
-      <c r="F72" s="39" t="inlineStr"/>
-    </row>
-    <row r="73" ht="14" customHeight="1">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="F78" s="42" t="inlineStr"/>
+    </row>
+    <row r="79" ht="14" customHeight="1">
+      <c r="A79" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 100</t>
         </is>
       </c>
-      <c r="B73" s="35" t="n"/>
-      <c r="C73" s="35" t="n"/>
-      <c r="D73" s="35" t="n"/>
-      <c r="E73" s="35" t="n"/>
-      <c r="F73" s="35" t="n"/>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="36" t="inlineStr">
+      <c r="B79" s="35" t="n"/>
+      <c r="C79" s="35" t="n"/>
+      <c r="D79" s="35" t="n"/>
+      <c r="E79" s="35" t="n"/>
+      <c r="F79" s="35" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B74" s="37" t="n"/>
-      <c r="C74" s="37" t="n"/>
-      <c r="D74" s="37" t="n"/>
-      <c r="E74" s="37" t="n"/>
-      <c r="F74" s="37" t="n"/>
-    </row>
-    <row r="75" ht="176" customHeight="1">
-      <c r="A75" s="42" t="inlineStr">
+      <c r="B80" s="37" t="n"/>
+      <c r="C80" s="37" t="n"/>
+      <c r="D80" s="37" t="n"/>
+      <c r="E80" s="37" t="n"/>
+      <c r="F80" s="37" t="n"/>
+    </row>
+    <row r="81" ht="176" customHeight="1">
+      <c r="A81" s="45" t="inlineStr">
         <is>
           <t>사해소금은
 삼투압으로 노폐물을 제거하고
@@ -4587,26 +4669,26 @@
 물온도 38~40℃추천, 마지막에 미온수로 헹굼하세요</t>
         </is>
       </c>
-      <c r="B75" s="23" t="n"/>
-      <c r="C75" s="23" t="n"/>
-      <c r="D75" s="23" t="n"/>
-      <c r="E75" s="23" t="n"/>
-      <c r="F75" s="23" t="n"/>
-    </row>
-    <row r="76" ht="14" customHeight="1">
-      <c r="A76" s="36" t="inlineStr">
+      <c r="B81" s="23" t="n"/>
+      <c r="C81" s="23" t="n"/>
+      <c r="D81" s="23" t="n"/>
+      <c r="E81" s="23" t="n"/>
+      <c r="F81" s="23" t="n"/>
+    </row>
+    <row r="82" ht="14" customHeight="1">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B76" s="37" t="n"/>
-      <c r="C76" s="37" t="n"/>
-      <c r="D76" s="37" t="n"/>
-      <c r="E76" s="37" t="n"/>
-      <c r="F76" s="37" t="n"/>
-    </row>
-    <row r="77" ht="64" customHeight="1">
-      <c r="A77" s="42" t="inlineStr">
+      <c r="B82" s="37" t="n"/>
+      <c r="C82" s="37" t="n"/>
+      <c r="D82" s="37" t="n"/>
+      <c r="E82" s="37" t="n"/>
+      <c r="F82" s="37" t="n"/>
+    </row>
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 위생비닐에 분량의 사해 소금을 넣고
@@ -4614,235 +4696,255 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B77" s="23" t="n"/>
-      <c r="C77" s="23" t="n"/>
-      <c r="D77" s="23" t="n"/>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="23" t="n"/>
-    </row>
-    <row r="78" ht="6" customHeight="1"/>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="24" t="inlineStr">
+      <c r="B83" s="23" t="n"/>
+      <c r="C83" s="23" t="n"/>
+      <c r="D83" s="23" t="n"/>
+      <c r="E83" s="23" t="n"/>
+      <c r="F83" s="23" t="n"/>
+    </row>
+    <row r="84" ht="14" customHeight="1">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B84" s="40" t="n"/>
+      <c r="C84" s="40" t="n"/>
+      <c r="D84" s="40" t="n"/>
+      <c r="E84" s="40" t="n"/>
+      <c r="F84" s="40" t="n"/>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="41" t="inlineStr">
+        <is>
+          <t>· 제형: 수상 100% 중심 → 토너·미스트·젤 등 수상 제형(오일 넣으려면 가용화 필요).
+· 베이스: 수상 100%(사해소금 100%)가 제형의 뼈대·수분 공급.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="6" customHeight="1"/>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="24" t="inlineStr">
         <is>
           <t>핑크솔트 바쓰붐(완전 딱딱!)    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B79" s="25" t="n"/>
-      <c r="C79" s="25" t="n"/>
-      <c r="D79" s="25" t="n"/>
-      <c r="E79" s="25" t="n"/>
-      <c r="F79" s="25" t="n"/>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="B87" s="25" t="n"/>
+      <c r="C87" s="25" t="n"/>
+      <c r="D87" s="25" t="n"/>
+      <c r="E87" s="25" t="n"/>
+      <c r="F87" s="25" t="n"/>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B80" s="26" t="inlineStr">
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C80" s="26" t="inlineStr">
+      <c r="C88" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="D88" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E80" s="26" t="inlineStr">
+      <c r="E88" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F80" s="26" t="inlineStr">
+      <c r="F88" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="32" customHeight="1">
-      <c r="A81" s="27" t="inlineStr">
+    <row r="89" ht="32" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B81" s="27" t="inlineStr">
+      <c r="B89" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C81" s="28" t="inlineStr">
+      <c r="C89" s="28" t="inlineStr">
         <is>
           <t>46%</t>
         </is>
       </c>
-      <c r="D81" s="29" t="inlineStr">
+      <c r="D89" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E81" s="27" t="inlineStr">
+      <c r="E89" s="27" t="inlineStr">
         <is>
           <t>탄산수소나트륨 · 미네럴공급, 연수효과</t>
         </is>
       </c>
-      <c r="F81" s="27" t="inlineStr"/>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="27" t="inlineStr">
+      <c r="F89" s="27" t="inlineStr"/>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="27" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B82" s="27" t="inlineStr">
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C82" s="28" t="inlineStr">
+      <c r="C90" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D82" s="29" t="inlineStr">
+      <c r="D90" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E82" s="27" t="inlineStr">
+      <c r="E90" s="27" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F82" s="27" t="inlineStr">
+      <c r="F90" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="96" customHeight="1">
-      <c r="A83" s="27" t="inlineStr">
+    <row r="91" ht="96" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B83" s="27" t="inlineStr">
+      <c r="B91" s="27" t="inlineStr">
         <is>
           <t>125g</t>
         </is>
       </c>
-      <c r="C83" s="28" t="inlineStr">
+      <c r="C91" s="28" t="inlineStr">
         <is>
           <t>23%</t>
         </is>
       </c>
-      <c r="D83" s="30" t="inlineStr">
+      <c r="D91" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E83" s="27" t="inlineStr">
+      <c r="E91" s="27" t="inlineStr">
         <is>
           <t>결합 UP, 노폐물 흡착</t>
         </is>
       </c>
-      <c r="F83" s="27" t="inlineStr">
+      <c r="F91" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="A84" s="27" t="inlineStr">
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="27" t="inlineStr">
         <is>
           <t>레몬 EO</t>
         </is>
       </c>
-      <c r="B84" s="27" t="inlineStr">
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>8g / (10ml)</t>
         </is>
       </c>
-      <c r="C84" s="28" t="inlineStr">
+      <c r="C92" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D84" s="32" t="inlineStr">
+      <c r="D92" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E84" s="27" t="inlineStr">
+      <c r="E92" s="27" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F84" s="27" t="inlineStr">
+      <c r="F92" s="27" t="inlineStr">
         <is>
           <t>원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="27" t="inlineStr">
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>핑크솔트</t>
         </is>
       </c>
-      <c r="B85" s="27" t="inlineStr">
+      <c r="B93" s="27" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C85" s="28" t="inlineStr">
+      <c r="C93" s="28" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D85" s="31" t="inlineStr">
+      <c r="D93" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E85" s="27" t="inlineStr">
+      <c r="E93" s="27" t="inlineStr">
         <is>
           <t>히말라얀 암염, 풍부한 미네럴 · 철함유로 자체 · 핑크색 · 아로마를 입힌 핑크솔트도 가능</t>
         </is>
       </c>
-      <c r="F85" s="27" t="inlineStr"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="F93" s="27" t="inlineStr"/>
+    </row>
+    <row r="94" ht="14" customHeight="1">
+      <c r="A94" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 23 · 향 1 · 점증/pH 70 · 기타 6</t>
         </is>
       </c>
-      <c r="B86" s="35" t="n"/>
-      <c r="C86" s="35" t="n"/>
-      <c r="D86" s="35" t="n"/>
-      <c r="E86" s="35" t="n"/>
-      <c r="F86" s="35" t="n"/>
-    </row>
-    <row r="87" ht="14" customHeight="1">
-      <c r="A87" s="36" t="inlineStr">
+      <c r="B94" s="35" t="n"/>
+      <c r="C94" s="35" t="n"/>
+      <c r="D94" s="35" t="n"/>
+      <c r="E94" s="35" t="n"/>
+      <c r="F94" s="35" t="n"/>
+    </row>
+    <row r="95" ht="14" customHeight="1">
+      <c r="A95" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B87" s="37" t="n"/>
-      <c r="C87" s="37" t="n"/>
-      <c r="D87" s="37" t="n"/>
-      <c r="E87" s="37" t="n"/>
-      <c r="F87" s="37" t="n"/>
-    </row>
-    <row r="88" ht="240" customHeight="1">
-      <c r="A88" s="38" t="inlineStr">
+      <c r="B95" s="37" t="n"/>
+      <c r="C95" s="37" t="n"/>
+      <c r="D95" s="37" t="n"/>
+      <c r="E95" s="37" t="n"/>
+      <c r="F95" s="37" t="n"/>
+    </row>
+    <row r="96" ht="240" customHeight="1">
+      <c r="A96" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 바스붐과 핑크솔트가 만나서
@@ -4862,20 +4964,20 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="14" customHeight="1">
-      <c r="A89" s="36" t="inlineStr">
+    <row r="97" ht="14" customHeight="1">
+      <c r="A97" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B89" s="37" t="n"/>
-      <c r="C89" s="37" t="n"/>
-      <c r="D89" s="37" t="n"/>
-      <c r="E89" s="37" t="n"/>
-      <c r="F89" s="37" t="n"/>
-    </row>
-    <row r="90" ht="208" customHeight="1">
-      <c r="A90" s="38" t="inlineStr">
+      <c r="B97" s="37" t="n"/>
+      <c r="C97" s="37" t="n"/>
+      <c r="D97" s="37" t="n"/>
+      <c r="E97" s="37" t="n"/>
+      <c r="F97" s="37" t="n"/>
+    </row>
+    <row r="98" ht="208" customHeight="1">
+      <c r="A98" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1.베이스를 개량하고
@@ -4890,105 +4992,125 @@
         </is>
       </c>
     </row>
-    <row r="91" ht="6" customHeight="1"/>
-    <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
+    <row r="99" ht="14" customHeight="1">
+      <c r="A99" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B99" s="40" t="n"/>
+      <c r="C99" s="40" t="n"/>
+      <c r="D99" s="40" t="n"/>
+      <c r="E99" s="40" t="n"/>
+      <c r="F99" s="40" t="n"/>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 수상 23%(옥수수전분 23%)가 제형의 뼈대·수분 공급.
+· 마무리: 점증·pH 70% · 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="6" customHeight="1"/>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="24" t="inlineStr">
         <is>
           <t>바스솔트 (히말라야 핑크솔트)    [공통재료]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B92" s="25" t="n"/>
-      <c r="C92" s="25" t="n"/>
-      <c r="D92" s="25" t="n"/>
-      <c r="E92" s="25" t="n"/>
-      <c r="F92" s="25" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="26" t="inlineStr">
+      <c r="B102" s="25" t="n"/>
+      <c r="C102" s="25" t="n"/>
+      <c r="D102" s="25" t="n"/>
+      <c r="E102" s="25" t="n"/>
+      <c r="F102" s="25" t="n"/>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B93" s="26" t="inlineStr">
+      <c r="B103" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C93" s="26" t="inlineStr">
+      <c r="C103" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D93" s="26" t="inlineStr">
+      <c r="D103" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E93" s="26" t="inlineStr">
+      <c r="E103" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F93" s="26" t="inlineStr">
+      <c r="F103" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="39" t="inlineStr">
+    <row r="104" ht="32" customHeight="1">
+      <c r="A104" s="42" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B94" s="39" t="inlineStr">
+      <c r="B104" s="42" t="inlineStr">
         <is>
           <t>500g</t>
         </is>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C104" s="43" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D94" s="31" t="inlineStr">
+      <c r="D104" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E94" s="39" t="inlineStr">
+      <c r="E104" s="42" t="inlineStr">
         <is>
           <t>풍부한 미네럴, 미세플라스틱 OUT</t>
         </is>
       </c>
-      <c r="F94" s="39" t="inlineStr"/>
-    </row>
-    <row r="95" ht="14" customHeight="1">
-      <c r="A95" s="34" t="inlineStr">
+      <c r="F104" s="42" t="inlineStr"/>
+    </row>
+    <row r="105" ht="14" customHeight="1">
+      <c r="A105" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  기타 100</t>
         </is>
       </c>
-      <c r="B95" s="35" t="n"/>
-      <c r="C95" s="35" t="n"/>
-      <c r="D95" s="35" t="n"/>
-      <c r="E95" s="35" t="n"/>
-      <c r="F95" s="35" t="n"/>
-    </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="36" t="inlineStr">
+      <c r="B105" s="35" t="n"/>
+      <c r="C105" s="35" t="n"/>
+      <c r="D105" s="35" t="n"/>
+      <c r="E105" s="35" t="n"/>
+      <c r="F105" s="35" t="n"/>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B96" s="37" t="n"/>
-      <c r="C96" s="37" t="n"/>
-      <c r="D96" s="37" t="n"/>
-      <c r="E96" s="37" t="n"/>
-      <c r="F96" s="37" t="n"/>
-    </row>
-    <row r="97" ht="384" customHeight="1">
-      <c r="A97" s="42" t="inlineStr">
+      <c r="B106" s="37" t="n"/>
+      <c r="C106" s="37" t="n"/>
+      <c r="D106" s="37" t="n"/>
+      <c r="E106" s="37" t="n"/>
+      <c r="F106" s="37" t="n"/>
+    </row>
+    <row r="107" ht="384" customHeight="1">
+      <c r="A107" s="45" t="inlineStr">
         <is>
           <t>핑크소금은
 건강한 소금,
@@ -5016,39 +5138,39 @@
 다양한</t>
         </is>
       </c>
-      <c r="B97" s="23" t="n"/>
-      <c r="C97" s="23" t="n"/>
-      <c r="D97" s="23" t="n"/>
-      <c r="E97" s="23" t="n"/>
-      <c r="F97" s="23" t="n"/>
-    </row>
-    <row r="98" ht="32" customHeight="1">
-      <c r="A98" s="42" t="inlineStr">
+      <c r="B107" s="23" t="n"/>
+      <c r="C107" s="23" t="n"/>
+      <c r="D107" s="23" t="n"/>
+      <c r="E107" s="23" t="n"/>
+      <c r="F107" s="23" t="n"/>
+    </row>
+    <row r="108" ht="32" customHeight="1">
+      <c r="A108" s="45" t="inlineStr">
         <is>
           <t>아로마오일을 히말라야 핑크소금에 배합해
 아로마테리피 효과도 함께 누리세요.</t>
         </is>
       </c>
-      <c r="B98" s="23" t="n"/>
-      <c r="C98" s="23" t="n"/>
-      <c r="D98" s="23" t="n"/>
-      <c r="E98" s="23" t="n"/>
-      <c r="F98" s="23" t="n"/>
-    </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="36" t="inlineStr">
+      <c r="B108" s="23" t="n"/>
+      <c r="C108" s="23" t="n"/>
+      <c r="D108" s="23" t="n"/>
+      <c r="E108" s="23" t="n"/>
+      <c r="F108" s="23" t="n"/>
+    </row>
+    <row r="109" ht="14" customHeight="1">
+      <c r="A109" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B99" s="37" t="n"/>
-      <c r="C99" s="37" t="n"/>
-      <c r="D99" s="37" t="n"/>
-      <c r="E99" s="37" t="n"/>
-      <c r="F99" s="37" t="n"/>
-    </row>
-    <row r="100" ht="80" customHeight="1">
-      <c r="A100" s="42" t="inlineStr">
+      <c r="B109" s="37" t="n"/>
+      <c r="C109" s="37" t="n"/>
+      <c r="D109" s="37" t="n"/>
+      <c r="E109" s="37" t="n"/>
+      <c r="F109" s="37" t="n"/>
+    </row>
+    <row r="110" ht="80" customHeight="1">
+      <c r="A110" s="45" t="inlineStr">
         <is>
           <t>만들기 과정
 1. (지퍼)비닐이나 통에
@@ -5057,203 +5179,203 @@
 3. 골고루 잘 섞이도록 흔들고 비벼 주면 완성.</t>
         </is>
       </c>
-      <c r="B100" s="23" t="n"/>
-      <c r="C100" s="23" t="n"/>
-      <c r="D100" s="23" t="n"/>
-      <c r="E100" s="23" t="n"/>
-      <c r="F100" s="23" t="n"/>
-    </row>
-    <row r="101" ht="6" customHeight="1"/>
-    <row r="102" ht="22" customHeight="1">
-      <c r="A102" s="24" t="inlineStr">
+      <c r="B110" s="23" t="n"/>
+      <c r="C110" s="23" t="n"/>
+      <c r="D110" s="23" t="n"/>
+      <c r="E110" s="23" t="n"/>
+      <c r="F110" s="23" t="n"/>
+    </row>
+    <row r="111" ht="6" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="24" t="inlineStr">
         <is>
           <t>아로마 바스솔트 (핑크)    [족욕, 입욕, 세안시]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B102" s="25" t="n"/>
-      <c r="C102" s="25" t="n"/>
-      <c r="D102" s="25" t="n"/>
-      <c r="E102" s="25" t="n"/>
-      <c r="F102" s="25" t="n"/>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="26" t="inlineStr">
+      <c r="B112" s="25" t="n"/>
+      <c r="C112" s="25" t="n"/>
+      <c r="D112" s="25" t="n"/>
+      <c r="E112" s="25" t="n"/>
+      <c r="F112" s="25" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B103" s="26" t="inlineStr">
+      <c r="B113" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C103" s="26" t="inlineStr">
+      <c r="C113" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D103" s="26" t="inlineStr">
+      <c r="D113" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E103" s="26" t="inlineStr">
+      <c r="E113" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F103" s="26" t="inlineStr">
+      <c r="F113" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="64" customHeight="1">
-      <c r="A104" s="27" t="inlineStr">
+    <row r="114" ht="64" customHeight="1">
+      <c r="A114" s="27" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (굵은 소금)</t>
         </is>
       </c>
-      <c r="B104" s="27" t="inlineStr">
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C104" s="28" t="inlineStr">
+      <c r="C114" s="28" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D104" s="44" t="inlineStr">
+      <c r="D114" s="47" t="inlineStr">
         <is>
           <t>색소</t>
         </is>
       </c>
-      <c r="E104" s="27" t="inlineStr">
+      <c r="E114" s="27" t="inlineStr">
         <is>
           <t>바다가 융기해 산이 됨 · 산소금=암염, 수분함량 적고 · 미네럴 풍부 · 산화철 함유로 색상 발현(핑크색)</t>
         </is>
       </c>
-      <c r="F104" s="27" t="inlineStr"/>
-    </row>
-    <row r="105" ht="48" customHeight="1">
-      <c r="A105" s="27" t="inlineStr">
+      <c r="F114" s="27" t="inlineStr"/>
+    </row>
+    <row r="115" ht="48" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B105" s="27" t="inlineStr">
+      <c r="B115" s="27" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울)내외</t>
         </is>
       </c>
-      <c r="C105" s="28" t="inlineStr">
+      <c r="C115" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D105" s="32" t="inlineStr">
+      <c r="D115" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E105" s="27" t="inlineStr">
+      <c r="E115" s="27" t="inlineStr">
         <is>
           <t>심신 이완</t>
         </is>
       </c>
-      <c r="F105" s="27" t="inlineStr">
+      <c r="F115" s="27" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="32" customHeight="1">
-      <c r="A106" s="27" t="inlineStr">
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="27" t="inlineStr">
         <is>
           <t>히말라아 핑크솔트 / (가는 소금)</t>
         </is>
       </c>
-      <c r="B106" s="27" t="inlineStr">
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>250g</t>
         </is>
       </c>
-      <c r="C106" s="28" t="inlineStr">
+      <c r="C116" s="28" t="inlineStr">
         <is>
           <t>49%</t>
         </is>
       </c>
-      <c r="D106" s="31" t="inlineStr">
+      <c r="D116" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E106" s="27" t="inlineStr">
+      <c r="E116" s="27" t="inlineStr">
         <is>
           <t>입,족욕용 또는 · 바디 마사지 · 스크럽 겸용</t>
         </is>
       </c>
-      <c r="F106" s="27" t="inlineStr"/>
-    </row>
-    <row r="107" ht="64" customHeight="1">
-      <c r="A107" s="27" t="inlineStr">
+      <c r="F116" s="27" t="inlineStr"/>
+    </row>
+    <row r="117" ht="64" customHeight="1">
+      <c r="A117" s="27" t="inlineStr">
         <is>
           <t>페파민트에센셜오일(EO)</t>
         </is>
       </c>
-      <c r="B107" s="27" t="inlineStr">
+      <c r="B117" s="27" t="inlineStr">
         <is>
           <t>3~5ml / (60~100방울) 내외</t>
         </is>
       </c>
-      <c r="C107" s="28" t="inlineStr">
+      <c r="C117" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D107" s="32" t="inlineStr">
+      <c r="D117" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E107" s="27" t="inlineStr">
+      <c r="E117" s="27" t="inlineStr">
         <is>
           <t>피로회복, 혈액순환</t>
         </is>
       </c>
-      <c r="F107" s="27" t="inlineStr">
+      <c r="F117" s="27" t="inlineStr">
         <is>
           <t>원하는 · 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="14" customHeight="1">
-      <c r="A108" s="34" t="inlineStr">
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 2 · 색소 49 · 기타 49</t>
         </is>
       </c>
-      <c r="B108" s="35" t="n"/>
-      <c r="C108" s="35" t="n"/>
-      <c r="D108" s="35" t="n"/>
-      <c r="E108" s="35" t="n"/>
-      <c r="F108" s="35" t="n"/>
-    </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="36" t="inlineStr">
+      <c r="B118" s="35" t="n"/>
+      <c r="C118" s="35" t="n"/>
+      <c r="D118" s="35" t="n"/>
+      <c r="E118" s="35" t="n"/>
+      <c r="F118" s="35" t="n"/>
+    </row>
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B109" s="37" t="n"/>
-      <c r="C109" s="37" t="n"/>
-      <c r="D109" s="37" t="n"/>
-      <c r="E109" s="37" t="n"/>
-      <c r="F109" s="37" t="n"/>
-    </row>
-    <row r="110" ht="256" customHeight="1">
-      <c r="A110" s="38" t="inlineStr">
+      <c r="B119" s="37" t="n"/>
+      <c r="C119" s="37" t="n"/>
+      <c r="D119" s="37" t="n"/>
+      <c r="E119" s="37" t="n"/>
+      <c r="F119" s="37" t="n"/>
+    </row>
+    <row r="120" ht="256" customHeight="1">
+      <c r="A120" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5274,20 +5396,20 @@
         </is>
       </c>
     </row>
-    <row r="111" ht="14" customHeight="1">
-      <c r="A111" s="36" t="inlineStr">
+    <row r="121" ht="14" customHeight="1">
+      <c r="A121" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B111" s="37" t="n"/>
-      <c r="C111" s="37" t="n"/>
-      <c r="D111" s="37" t="n"/>
-      <c r="E111" s="37" t="n"/>
-      <c r="F111" s="37" t="n"/>
-    </row>
-    <row r="112" ht="112" customHeight="1">
-      <c r="A112" s="38" t="inlineStr">
+      <c r="B121" s="37" t="n"/>
+      <c r="C121" s="37" t="n"/>
+      <c r="D121" s="37" t="n"/>
+      <c r="E121" s="37" t="n"/>
+      <c r="F121" s="37" t="n"/>
+    </row>
+    <row r="122" ht="112" customHeight="1">
+      <c r="A122" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 지퍼백에 핑크소금(미세소금) 에센셜오일을 떨어뜨려주세요.
@@ -5299,201 +5421,220 @@
         </is>
       </c>
     </row>
-    <row r="113" ht="6" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="24" t="inlineStr">
+    <row r="123" ht="14" customHeight="1">
+      <c r="A123" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B123" s="40" t="n"/>
+      <c r="C123" s="40" t="n"/>
+      <c r="D123" s="40" t="n"/>
+      <c r="E123" s="40" t="n"/>
+      <c r="F123" s="40" t="n"/>
+    </row>
+    <row r="124" ht="28" customHeight="1">
+      <c r="A124" s="41" t="inlineStr">
+        <is>
+          <t>· 마무리: 향 2% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="6" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="24" t="inlineStr">
         <is>
           <t>Pure 가루바스붐 레시피    ↗ 원본</t>
         </is>
       </c>
-      <c r="B114" s="25" t="n"/>
-      <c r="C114" s="25" t="n"/>
-      <c r="D114" s="25" t="n"/>
-      <c r="E114" s="25" t="n"/>
-      <c r="F114" s="25" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="26" t="inlineStr">
+      <c r="B126" s="25" t="n"/>
+      <c r="C126" s="25" t="n"/>
+      <c r="D126" s="25" t="n"/>
+      <c r="E126" s="25" t="n"/>
+      <c r="F126" s="25" t="n"/>
+    </row>
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B115" s="26" t="inlineStr">
+      <c r="B127" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C115" s="26" t="inlineStr">
+      <c r="C127" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D115" s="26" t="inlineStr">
+      <c r="D127" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E115" s="26" t="inlineStr">
+      <c r="E127" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F115" s="26" t="inlineStr">
+      <c r="F127" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="116" ht="48" customHeight="1">
-      <c r="A116" s="39" t="inlineStr">
+    <row r="128" ht="48" customHeight="1">
+      <c r="A128" s="42" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B116" s="39" t="inlineStr">
+      <c r="B128" s="42" t="inlineStr">
         <is>
           <t>200g</t>
         </is>
       </c>
-      <c r="C116" s="40" t="inlineStr">
+      <c r="C128" s="43" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D116" s="29" t="inlineStr">
+      <c r="D128" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E116" s="39" t="inlineStr">
+      <c r="E128" s="42" t="inlineStr">
         <is>
           <t>탄산수소나트륨, 중조, 중탄산나트륨.베이킹파우더와는 다르다. 약알카리, 미네럴공급</t>
         </is>
       </c>
-      <c r="F116" s="39" t="inlineStr"/>
-    </row>
-    <row r="117" ht="32" customHeight="1">
-      <c r="A117" s="39" t="inlineStr">
+      <c r="F128" s="42" t="inlineStr"/>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="42" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B117" s="39" t="inlineStr">
+      <c r="B129" s="42" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C117" s="40" t="inlineStr">
+      <c r="C129" s="43" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D117" s="29" t="inlineStr">
+      <c r="D129" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E117" s="39" t="inlineStr">
+      <c r="E129" s="42" t="inlineStr">
         <is>
           <t>산성, PH조절, 과일산, 묵은각질을 관리, 살균 등</t>
         </is>
       </c>
-      <c r="F117" s="39" t="inlineStr">
+      <c r="F129" s="42" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="96" customHeight="1">
-      <c r="A118" s="39" t="inlineStr">
+    <row r="130" ht="96" customHeight="1">
+      <c r="A130" s="42" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B118" s="39" t="inlineStr">
+      <c r="B130" s="42" t="inlineStr">
         <is>
           <t>120g</t>
         </is>
       </c>
-      <c r="C118" s="40" t="inlineStr">
+      <c r="C130" s="43" t="inlineStr">
         <is>
           <t>28%</t>
         </is>
       </c>
-      <c r="D118" s="29" t="inlineStr">
+      <c r="D130" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E118" s="39" t="inlineStr">
+      <c r="E130" s="42" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F118" s="39" t="inlineStr">
+      <c r="F130" s="42" t="inlineStr">
         <is>
           <t>쌀가루, 감자전분,고구마전분</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="80" customHeight="1">
-      <c r="A119" s="39" t="inlineStr">
+    <row r="131" ht="80" customHeight="1">
+      <c r="A131" s="42" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B119" s="39" t="inlineStr">
+      <c r="B131" s="42" t="inlineStr">
         <is>
           <t>4ml(1%이하)</t>
         </is>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C131" s="43" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D119" s="32" t="inlineStr">
+      <c r="D131" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E119" s="39" t="inlineStr">
+      <c r="E131" s="42" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F119" s="39" t="inlineStr">
+      <c r="F131" s="42" t="inlineStr">
         <is>
           <t>만다린, 오렌지 등 원하는 에센셜오일. 전체양의 1%</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="14" customHeight="1">
-      <c r="A120" s="34" t="inlineStr">
+    <row r="132" ht="14" customHeight="1">
+      <c r="A132" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  향 1 · 점증/pH 99</t>
         </is>
       </c>
-      <c r="B120" s="35" t="n"/>
-      <c r="C120" s="35" t="n"/>
-      <c r="D120" s="35" t="n"/>
-      <c r="E120" s="35" t="n"/>
-      <c r="F120" s="35" t="n"/>
-    </row>
-    <row r="121" ht="14" customHeight="1">
-      <c r="A121" s="36" t="inlineStr">
+      <c r="B132" s="35" t="n"/>
+      <c r="C132" s="35" t="n"/>
+      <c r="D132" s="35" t="n"/>
+      <c r="E132" s="35" t="n"/>
+      <c r="F132" s="35" t="n"/>
+    </row>
+    <row r="133" ht="14" customHeight="1">
+      <c r="A133" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B121" s="37" t="n"/>
-      <c r="C121" s="37" t="n"/>
-      <c r="D121" s="37" t="n"/>
-      <c r="E121" s="37" t="n"/>
-      <c r="F121" s="37" t="n"/>
-    </row>
-    <row r="122" ht="64" customHeight="1">
-      <c r="A122" s="42" t="inlineStr">
+      <c r="B133" s="37" t="n"/>
+      <c r="C133" s="37" t="n"/>
+      <c r="D133" s="37" t="n"/>
+      <c r="E133" s="37" t="n"/>
+      <c r="F133" s="37" t="n"/>
+    </row>
+    <row r="134" ht="64" customHeight="1">
+      <c r="A134" s="45" t="inlineStr">
         <is>
           <t>바스붐은 베이킹소다, 구연산, 아로마오일이 들어가서 물을 연수화시켜서
 피부에 미네럴공급, 각질관리, 보습, 아로마테라피, 노폐물흡착 등의 효과가 있답니다.
@@ -5501,26 +5642,26 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B122" s="23" t="n"/>
-      <c r="C122" s="23" t="n"/>
-      <c r="D122" s="23" t="n"/>
-      <c r="E122" s="23" t="n"/>
-      <c r="F122" s="23" t="n"/>
-    </row>
-    <row r="123" ht="14" customHeight="1">
-      <c r="A123" s="36" t="inlineStr">
+      <c r="B134" s="23" t="n"/>
+      <c r="C134" s="23" t="n"/>
+      <c r="D134" s="23" t="n"/>
+      <c r="E134" s="23" t="n"/>
+      <c r="F134" s="23" t="n"/>
+    </row>
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B123" s="37" t="n"/>
-      <c r="C123" s="37" t="n"/>
-      <c r="D123" s="37" t="n"/>
-      <c r="E123" s="37" t="n"/>
-      <c r="F123" s="37" t="n"/>
-    </row>
-    <row r="124" ht="192" customHeight="1">
-      <c r="A124" s="42" t="inlineStr">
+      <c r="B135" s="37" t="n"/>
+      <c r="C135" s="37" t="n"/>
+      <c r="D135" s="37" t="n"/>
+      <c r="E135" s="37" t="n"/>
+      <c r="F135" s="37" t="n"/>
+    </row>
+    <row r="136" ht="192" customHeight="1">
+      <c r="A136" s="45" t="inlineStr">
         <is>
           <t>1-2.베이킹소다를 체에 쳐주세요. 덩어리진것을 깨주시면 전체 재료가 잘 섞여요
 3.그용기에 구연산을 계량하고
@@ -5535,179 +5676,198 @@
 한개씩 꺼내쓰는 재미도 있을 것 같아요. 꼭 어릴때 먹던 삼각형 비닐 우유같네요^^</t>
         </is>
       </c>
-      <c r="B124" s="23" t="n"/>
-      <c r="C124" s="23" t="n"/>
-      <c r="D124" s="23" t="n"/>
-      <c r="E124" s="23" t="n"/>
-      <c r="F124" s="23" t="n"/>
-    </row>
-    <row r="125" ht="186" customHeight="1">
-      <c r="A125" s="23" t="n"/>
-      <c r="B125" s="23" t="n"/>
-      <c r="C125" s="23" t="n"/>
-      <c r="D125" s="23" t="n"/>
-      <c r="E125" s="23" t="n"/>
-      <c r="F125" s="23" t="n"/>
-    </row>
-    <row r="126" ht="6" customHeight="1"/>
-    <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="24" t="inlineStr">
+      <c r="B136" s="23" t="n"/>
+      <c r="C136" s="23" t="n"/>
+      <c r="D136" s="23" t="n"/>
+      <c r="E136" s="23" t="n"/>
+      <c r="F136" s="23" t="n"/>
+    </row>
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B137" s="40" t="n"/>
+      <c r="C137" s="40" t="n"/>
+      <c r="D137" s="40" t="n"/>
+      <c r="E137" s="40" t="n"/>
+      <c r="F137" s="40" t="n"/>
+    </row>
+    <row r="138" ht="28" customHeight="1">
+      <c r="A138" s="41" t="inlineStr">
+        <is>
+          <t>· 마무리: 점증·pH 99% · 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="144" customHeight="1">
+      <c r="A139" s="23" t="n"/>
+      <c r="B139" s="23" t="n"/>
+      <c r="C139" s="23" t="n"/>
+      <c r="D139" s="23" t="n"/>
+      <c r="E139" s="23" t="n"/>
+      <c r="F139" s="23" t="n"/>
+    </row>
+    <row r="140" ht="6" customHeight="1"/>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="24" t="inlineStr">
         <is>
           <t>(핑크) 솔트 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B127" s="25" t="n"/>
-      <c r="C127" s="25" t="n"/>
-      <c r="D127" s="25" t="n"/>
-      <c r="E127" s="25" t="n"/>
-      <c r="F127" s="25" t="n"/>
-    </row>
-    <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="26" t="inlineStr">
+      <c r="B141" s="25" t="n"/>
+      <c r="C141" s="25" t="n"/>
+      <c r="D141" s="25" t="n"/>
+      <c r="E141" s="25" t="n"/>
+      <c r="F141" s="25" t="n"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B128" s="26" t="inlineStr">
+      <c r="B142" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C128" s="26" t="inlineStr">
+      <c r="C142" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D128" s="26" t="inlineStr">
+      <c r="D142" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E128" s="26" t="inlineStr">
+      <c r="E142" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F128" s="26" t="inlineStr">
+      <c r="F142" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="32" customHeight="1">
-      <c r="A129" s="27" t="inlineStr">
+    <row r="143" ht="32" customHeight="1">
+      <c r="A143" s="27" t="inlineStr">
         <is>
           <t>핑크소금</t>
         </is>
       </c>
-      <c r="B129" s="27" t="inlineStr">
+      <c r="B143" s="27" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C129" s="28" t="inlineStr">
+      <c r="C143" s="28" t="inlineStr">
         <is>
           <t>60%</t>
         </is>
       </c>
-      <c r="D129" s="31" t="inlineStr">
+      <c r="D143" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E129" s="27" t="inlineStr">
+      <c r="E143" s="27" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F129" s="27" t="inlineStr"/>
-    </row>
-    <row r="130" ht="48" customHeight="1">
-      <c r="A130" s="27" t="inlineStr">
+      <c r="F143" s="27" t="inlineStr"/>
+    </row>
+    <row r="144" ht="48" customHeight="1">
+      <c r="A144" s="27" t="inlineStr">
         <is>
           <t>시어버터 스크럽베이스</t>
         </is>
       </c>
-      <c r="B130" s="27" t="inlineStr">
+      <c r="B144" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C130" s="28" t="inlineStr">
+      <c r="C144" s="28" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="D130" s="43" t="inlineStr">
+      <c r="D144" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E130" s="27" t="inlineStr">
+      <c r="E144" s="27" t="inlineStr">
         <is>
           <t>DIY 스크럽 만들기 최적의 베이스 · 시어버터, 아보카도, 꿀추출물 등 · 함유, 보습+ 세정</t>
         </is>
       </c>
-      <c r="F130" s="27" t="inlineStr"/>
-    </row>
-    <row r="131" ht="80" customHeight="1">
-      <c r="A131" s="27" t="inlineStr">
+      <c r="F144" s="27" t="inlineStr"/>
+    </row>
+    <row r="145" ht="80" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
         <is>
           <t>아로마오일</t>
         </is>
       </c>
-      <c r="B131" s="27" t="inlineStr">
+      <c r="B145" s="27" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C131" s="28" t="inlineStr">
+      <c r="C145" s="28" t="inlineStr">
         <is>
           <t>1%</t>
         </is>
       </c>
-      <c r="D131" s="32" t="inlineStr">
+      <c r="D145" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E131" s="27" t="inlineStr">
+      <c r="E145" s="27" t="inlineStr">
         <is>
           <t>아로마테라피 · 여드름-티트리 · 바디 용도별 추천오일 · 쿨링 :페파민트 · 다이어트 : 레몬+자몽오일 · 이완 : 라벤더오일 등</t>
         </is>
       </c>
-      <c r="F131" s="27" t="inlineStr">
+      <c r="F145" s="27" t="inlineStr">
         <is>
           <t>허니향,원하는 에센셜오일이나 향</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="14" customHeight="1">
-      <c r="A132" s="34" t="inlineStr">
+    <row r="146" ht="14" customHeight="1">
+      <c r="A146" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 40 · 향 1 · 기타 60</t>
         </is>
       </c>
-      <c r="B132" s="35" t="n"/>
-      <c r="C132" s="35" t="n"/>
-      <c r="D132" s="35" t="n"/>
-      <c r="E132" s="35" t="n"/>
-      <c r="F132" s="35" t="n"/>
-    </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="36" t="inlineStr">
+      <c r="B146" s="35" t="n"/>
+      <c r="C146" s="35" t="n"/>
+      <c r="D146" s="35" t="n"/>
+      <c r="E146" s="35" t="n"/>
+      <c r="F146" s="35" t="n"/>
+    </row>
+    <row r="147" ht="14" customHeight="1">
+      <c r="A147" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B133" s="37" t="n"/>
-      <c r="C133" s="37" t="n"/>
-      <c r="D133" s="37" t="n"/>
-      <c r="E133" s="37" t="n"/>
-      <c r="F133" s="37" t="n"/>
-    </row>
-    <row r="134" ht="384" customHeight="1">
-      <c r="A134" s="38" t="inlineStr">
+      <c r="B147" s="37" t="n"/>
+      <c r="C147" s="37" t="n"/>
+      <c r="D147" s="37" t="n"/>
+      <c r="E147" s="37" t="n"/>
+      <c r="F147" s="37" t="n"/>
+    </row>
+    <row r="148" ht="384" customHeight="1">
+      <c r="A148" s="38" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -5736,8 +5896,8 @@
         </is>
       </c>
     </row>
-    <row r="135" ht="112" customHeight="1">
-      <c r="A135" s="38" t="inlineStr">
+    <row r="149" ht="112" customHeight="1">
+      <c r="A149" s="38" t="inlineStr">
         <is>
           <t>알려져있어요.
 이유는.. 약 2억 5000만 년 전에 히말라야 바다 아래로
@@ -5749,20 +5909,20 @@
         </is>
       </c>
     </row>
-    <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="36" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B136" s="37" t="n"/>
-      <c r="C136" s="37" t="n"/>
-      <c r="D136" s="37" t="n"/>
-      <c r="E136" s="37" t="n"/>
-      <c r="F136" s="37" t="n"/>
-    </row>
-    <row r="137" ht="80" customHeight="1">
-      <c r="A137" s="38" t="inlineStr">
+      <c r="B150" s="37" t="n"/>
+      <c r="C150" s="37" t="n"/>
+      <c r="D150" s="37" t="n"/>
+      <c r="E150" s="37" t="n"/>
+      <c r="F150" s="37" t="n"/>
+    </row>
+    <row r="151" ht="80" customHeight="1">
+      <c r="A151" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 에센셜오일 50방울을 넣고
@@ -5772,261 +5932,281 @@
         </is>
       </c>
     </row>
-    <row r="138" ht="6" customHeight="1"/>
-    <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="24" t="inlineStr">
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B152" s="40" t="n"/>
+      <c r="C152" s="40" t="n"/>
+      <c r="D152" s="40" t="n"/>
+      <c r="E152" s="40" t="n"/>
+      <c r="F152" s="40" t="n"/>
+    </row>
+    <row r="153" ht="30" customHeight="1">
+      <c r="A153" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 시어버터 스크럽베이스(40%)로 보습막·발림 설계.
+· 마무리: 향 1% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="6" customHeight="1"/>
+    <row r="155" ht="22" customHeight="1">
+      <c r="A155" s="24" t="inlineStr">
         <is>
           <t>냥이 거품 입욕제    [베이스]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B139" s="25" t="n"/>
-      <c r="C139" s="25" t="n"/>
-      <c r="D139" s="25" t="n"/>
-      <c r="E139" s="25" t="n"/>
-      <c r="F139" s="25" t="n"/>
-    </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="26" t="inlineStr">
+      <c r="B155" s="25" t="n"/>
+      <c r="C155" s="25" t="n"/>
+      <c r="D155" s="25" t="n"/>
+      <c r="E155" s="25" t="n"/>
+      <c r="F155" s="25" t="n"/>
+    </row>
+    <row r="156" ht="15" customHeight="1">
+      <c r="A156" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B140" s="26" t="inlineStr">
+      <c r="B156" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C140" s="26" t="inlineStr">
+      <c r="C156" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D140" s="26" t="inlineStr">
+      <c r="D156" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E140" s="26" t="inlineStr">
+      <c r="E156" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F140" s="26" t="inlineStr">
+      <c r="F156" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="39" t="inlineStr">
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="42" t="inlineStr">
         <is>
           <t>베이킹소다</t>
         </is>
       </c>
-      <c r="B141" s="39" t="inlineStr">
+      <c r="B157" s="42" t="inlineStr">
         <is>
           <t>300g</t>
         </is>
       </c>
-      <c r="C141" s="40" t="inlineStr">
+      <c r="C157" s="43" t="inlineStr">
         <is>
           <t>51%</t>
         </is>
       </c>
-      <c r="D141" s="29" t="inlineStr">
+      <c r="D157" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E141" s="39" t="inlineStr">
+      <c r="E157" s="42" t="inlineStr">
         <is>
           <t>미네럴 공급, 연수화</t>
         </is>
       </c>
-      <c r="F141" s="39" t="inlineStr"/>
-    </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="39" t="inlineStr">
+      <c r="F157" s="42" t="inlineStr"/>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="42" t="inlineStr">
         <is>
           <t>구연산</t>
         </is>
       </c>
-      <c r="B142" s="39" t="inlineStr">
+      <c r="B158" s="42" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C142" s="40" t="inlineStr">
+      <c r="C158" s="43" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="D142" s="29" t="inlineStr">
+      <c r="D158" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E142" s="39" t="inlineStr">
+      <c r="E158" s="42" t="inlineStr">
         <is>
           <t>과일산, pH 조절, 각질연화</t>
         </is>
       </c>
-      <c r="F142" s="39" t="inlineStr">
+      <c r="F158" s="42" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="96" customHeight="1">
-      <c r="A143" s="39" t="inlineStr">
+    <row r="159" ht="96" customHeight="1">
+      <c r="A159" s="42" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B143" s="39" t="inlineStr">
+      <c r="B159" s="42" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C143" s="40" t="inlineStr">
+      <c r="C159" s="43" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="D143" s="31" t="inlineStr">
+      <c r="D159" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E143" s="39" t="inlineStr">
+      <c r="E159" s="42" t="inlineStr">
         <is>
           <t>흡착, 모양만들기</t>
         </is>
       </c>
-      <c r="F143" s="39" t="inlineStr">
+      <c r="F159" s="42" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="39" t="inlineStr">
+    <row r="160" ht="32" customHeight="1">
+      <c r="A160" s="42" t="inlineStr">
         <is>
           <t>SLSA</t>
         </is>
       </c>
-      <c r="B144" s="39" t="inlineStr">
+      <c r="B160" s="42" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C144" s="40" t="inlineStr">
+      <c r="C160" s="43" t="inlineStr">
         <is>
           <t>6%</t>
         </is>
       </c>
-      <c r="D144" s="33" t="inlineStr">
+      <c r="D160" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E144" s="39" t="inlineStr">
+      <c r="E160" s="42" t="inlineStr">
         <is>
           <t>코코넛유래, 거품, 세정, 음이온</t>
         </is>
       </c>
-      <c r="F144" s="39" t="inlineStr"/>
-    </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="39" t="inlineStr">
+      <c r="F160" s="42" t="inlineStr"/>
+    </row>
+    <row r="161" ht="32" customHeight="1">
+      <c r="A161" s="42" t="inlineStr">
         <is>
           <t>라임캔디블렌딩오일</t>
         </is>
       </c>
-      <c r="B145" s="39" t="inlineStr">
+      <c r="B161" s="42" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C145" s="40" t="inlineStr">
+      <c r="C161" s="43" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D145" s="43" t="inlineStr">
+      <c r="D161" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E145" s="39" t="inlineStr">
+      <c r="E161" s="42" t="inlineStr">
         <is>
           <t>아로마 테라피</t>
         </is>
       </c>
-      <c r="F145" s="39" t="inlineStr">
+      <c r="F161" s="42" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="64" customHeight="1">
-      <c r="A146" s="39" t="inlineStr">
+    <row r="162" ht="64" customHeight="1">
+      <c r="A162" s="42" t="inlineStr">
         <is>
           <t>워터</t>
         </is>
       </c>
-      <c r="B146" s="39" t="inlineStr">
+      <c r="B162" s="42" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C146" s="40" t="inlineStr">
+      <c r="C162" s="43" t="inlineStr">
         <is>
           <t>3%</t>
         </is>
       </c>
-      <c r="D146" s="30" t="inlineStr">
+      <c r="D162" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E146" s="39" t="inlineStr">
+      <c r="E162" s="42" t="inlineStr">
         <is>
           <t>잘뭉치게</t>
         </is>
       </c>
-      <c r="F146" s="39" t="inlineStr">
+      <c r="F162" s="42" t="inlineStr">
         <is>
           <t>카보머 프리젤 · 28g 적용 가능. · 적용시 가열과정 없음</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="14" customHeight="1">
-      <c r="A147" s="34" t="inlineStr">
+    <row r="163" ht="14" customHeight="1">
+      <c r="A163" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  수상 3 · 유상 2 · 계면 6 · 점증/pH 76 · 기타 13</t>
         </is>
       </c>
-      <c r="B147" s="35" t="n"/>
-      <c r="C147" s="35" t="n"/>
-      <c r="D147" s="35" t="n"/>
-      <c r="E147" s="35" t="n"/>
-      <c r="F147" s="35" t="n"/>
-    </row>
-    <row r="148" ht="14" customHeight="1">
-      <c r="A148" s="36" t="inlineStr">
+      <c r="B163" s="35" t="n"/>
+      <c r="C163" s="35" t="n"/>
+      <c r="D163" s="35" t="n"/>
+      <c r="E163" s="35" t="n"/>
+      <c r="F163" s="35" t="n"/>
+    </row>
+    <row r="164" ht="14" customHeight="1">
+      <c r="A164" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B148" s="37" t="n"/>
-      <c r="C148" s="37" t="n"/>
-      <c r="D148" s="37" t="n"/>
-      <c r="E148" s="37" t="n"/>
-      <c r="F148" s="37" t="n"/>
-    </row>
-    <row r="149" ht="224" customHeight="1">
-      <c r="A149" s="42" t="inlineStr">
+      <c r="B164" s="37" t="n"/>
+      <c r="C164" s="37" t="n"/>
+      <c r="D164" s="37" t="n"/>
+      <c r="E164" s="37" t="n"/>
+      <c r="F164" s="37" t="n"/>
+    </row>
+    <row r="165" ht="224" customHeight="1">
+      <c r="A165" s="45" t="inlineStr">
         <is>
           <t>뽀글뽀글 풍성한 거품~
 냥이 거품 입욕제
@@ -6044,26 +6224,26 @@
 즐거움을 더해보세요.</t>
         </is>
       </c>
-      <c r="B149" s="23" t="n"/>
-      <c r="C149" s="23" t="n"/>
-      <c r="D149" s="23" t="n"/>
-      <c r="E149" s="23" t="n"/>
-      <c r="F149" s="23" t="n"/>
-    </row>
-    <row r="150" ht="14" customHeight="1">
-      <c r="A150" s="36" t="inlineStr">
+      <c r="B165" s="23" t="n"/>
+      <c r="C165" s="23" t="n"/>
+      <c r="D165" s="23" t="n"/>
+      <c r="E165" s="23" t="n"/>
+      <c r="F165" s="23" t="n"/>
+    </row>
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B150" s="37" t="n"/>
-      <c r="C150" s="37" t="n"/>
-      <c r="D150" s="37" t="n"/>
-      <c r="E150" s="37" t="n"/>
-      <c r="F150" s="37" t="n"/>
-    </row>
-    <row r="151" ht="160" customHeight="1">
-      <c r="A151" s="42" t="inlineStr">
+      <c r="B166" s="37" t="n"/>
+      <c r="C166" s="37" t="n"/>
+      <c r="D166" s="37" t="n"/>
+      <c r="E166" s="37" t="n"/>
+      <c r="F166" s="37" t="n"/>
+    </row>
+    <row r="167" ht="160" customHeight="1">
+      <c r="A167" s="45" t="inlineStr">
         <is>
           <t>버블 바스붐 만들기
 1. 베이킹소다를 비롯 베이스 원료를 계량하세요.
@@ -6077,307 +6257,327 @@
 9. 다양한 모양 입욕제를 만들어보세요.</t>
         </is>
       </c>
-      <c r="B151" s="23" t="n"/>
-      <c r="C151" s="23" t="n"/>
-      <c r="D151" s="23" t="n"/>
-      <c r="E151" s="23" t="n"/>
-      <c r="F151" s="23" t="n"/>
-    </row>
-    <row r="152" ht="125.4999999999999" customHeight="1">
-      <c r="A152" s="23" t="n"/>
-      <c r="B152" s="23" t="n"/>
-      <c r="C152" s="23" t="n"/>
-      <c r="D152" s="23" t="n"/>
-      <c r="E152" s="23" t="n"/>
-      <c r="F152" s="23" t="n"/>
-    </row>
-    <row r="153" ht="6" customHeight="1"/>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="24" t="inlineStr">
+      <c r="B167" s="23" t="n"/>
+      <c r="C167" s="23" t="n"/>
+      <c r="D167" s="23" t="n"/>
+      <c r="E167" s="23" t="n"/>
+      <c r="F167" s="23" t="n"/>
+    </row>
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B168" s="40" t="n"/>
+      <c r="C168" s="40" t="n"/>
+      <c r="D168" s="40" t="n"/>
+      <c r="E168" s="40" t="n"/>
+      <c r="F168" s="40" t="n"/>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 라임캔디블렌딩오일(2%)로 보습막·발림 설계.
+· 마무리: 점증·pH 76% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="81.49999999999997" customHeight="1">
+      <c r="A170" s="23" t="n"/>
+      <c r="B170" s="23" t="n"/>
+      <c r="C170" s="23" t="n"/>
+      <c r="D170" s="23" t="n"/>
+      <c r="E170" s="23" t="n"/>
+      <c r="F170" s="23" t="n"/>
+    </row>
+    <row r="171" ht="6" customHeight="1"/>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="24" t="inlineStr">
         <is>
           <t>흑설탕 스크럽    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B154" s="25" t="n"/>
-      <c r="C154" s="25" t="n"/>
-      <c r="D154" s="25" t="n"/>
-      <c r="E154" s="25" t="n"/>
-      <c r="F154" s="25" t="n"/>
-    </row>
-    <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="26" t="inlineStr">
+      <c r="B172" s="25" t="n"/>
+      <c r="C172" s="25" t="n"/>
+      <c r="D172" s="25" t="n"/>
+      <c r="E172" s="25" t="n"/>
+      <c r="F172" s="25" t="n"/>
+    </row>
+    <row r="173" ht="15" customHeight="1">
+      <c r="A173" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B155" s="26" t="inlineStr">
+      <c r="B173" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C155" s="26" t="inlineStr">
+      <c r="C173" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D155" s="26" t="inlineStr">
+      <c r="D173" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E155" s="26" t="inlineStr">
+      <c r="E173" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F155" s="26" t="inlineStr">
+      <c r="F173" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="27" t="inlineStr">
+    <row r="174" ht="16" customHeight="1">
+      <c r="A174" s="27" t="inlineStr">
         <is>
           <t>아보카도오일</t>
         </is>
       </c>
-      <c r="B156" s="27" t="inlineStr">
+      <c r="B174" s="27" t="inlineStr">
         <is>
           <t>63g</t>
         </is>
       </c>
-      <c r="C156" s="28" t="inlineStr">
+      <c r="C174" s="28" t="inlineStr">
         <is>
           <t>24%</t>
         </is>
       </c>
-      <c r="D156" s="43" t="inlineStr">
+      <c r="D174" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E156" s="27" t="inlineStr">
+      <c r="E174" s="27" t="inlineStr">
         <is>
           <t>풍부한 비타민, 보습오일</t>
         </is>
       </c>
-      <c r="F156" s="27" t="inlineStr">
+      <c r="F174" s="27" t="inlineStr">
         <is>
           <t>원하는 오일</t>
         </is>
       </c>
     </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="27" t="inlineStr">
+    <row r="175" ht="32" customHeight="1">
+      <c r="A175" s="27" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
-      <c r="B157" s="27" t="inlineStr">
+      <c r="B175" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C157" s="28" t="inlineStr">
+      <c r="C175" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D157" s="43" t="inlineStr">
+      <c r="D175" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E157" s="27" t="inlineStr">
+      <c r="E175" s="27" t="inlineStr">
         <is>
           <t>고보습, 카리테나무 열매에서 채취.</t>
         </is>
       </c>
-      <c r="F157" s="27" t="inlineStr">
+      <c r="F175" s="27" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="158" ht="48" customHeight="1">
-      <c r="A158" s="27" t="inlineStr">
+    <row r="176" ht="48" customHeight="1">
+      <c r="A176" s="27" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B158" s="27" t="inlineStr">
+      <c r="B176" s="27" t="inlineStr">
         <is>
           <t>12g</t>
         </is>
       </c>
-      <c r="C158" s="28" t="inlineStr">
+      <c r="C176" s="28" t="inlineStr">
         <is>
           <t>4%</t>
         </is>
       </c>
-      <c r="D158" s="45" t="inlineStr">
+      <c r="D176" s="48" t="inlineStr">
         <is>
           <t>유화</t>
         </is>
       </c>
-      <c r="E158" s="27" t="inlineStr">
+      <c r="E176" s="27" t="inlineStr">
         <is>
           <t>에코인증, 물과 오일의 분리를 저지</t>
         </is>
       </c>
-      <c r="F158" s="27" t="inlineStr">
+      <c r="F176" s="27" t="inlineStr">
         <is>
           <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="64" customHeight="1">
-      <c r="A159" s="27" t="inlineStr">
+    <row r="177" ht="64" customHeight="1">
+      <c r="A177" s="27" t="inlineStr">
         <is>
           <t>순한 (샴푸) / 베이스</t>
         </is>
       </c>
-      <c r="B159" s="27" t="inlineStr">
+      <c r="B177" s="27" t="inlineStr">
         <is>
           <t>38g</t>
         </is>
       </c>
-      <c r="C159" s="28" t="inlineStr">
+      <c r="C177" s="28" t="inlineStr">
         <is>
           <t>14%</t>
         </is>
       </c>
-      <c r="D159" s="33" t="inlineStr">
+      <c r="D177" s="33" t="inlineStr">
         <is>
           <t>계면</t>
         </is>
       </c>
-      <c r="E159" s="27" t="inlineStr">
+      <c r="E177" s="27" t="inlineStr">
         <is>
           <t>이미 만들어진 물비누. LES, 코카미도프로필베타인, 라벤더꽃수, 폴리쿼터, 글루카메이트 등등...</t>
         </is>
       </c>
-      <c r="F159" s="27" t="inlineStr"/>
-    </row>
-    <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="27" t="inlineStr">
+      <c r="F177" s="27" t="inlineStr"/>
+    </row>
+    <row r="178" ht="16" customHeight="1">
+      <c r="A178" s="27" t="inlineStr">
         <is>
           <t>식물성 글리세린</t>
         </is>
       </c>
-      <c r="B160" s="27" t="inlineStr">
+      <c r="B178" s="27" t="inlineStr">
         <is>
           <t>13g</t>
         </is>
       </c>
-      <c r="C160" s="28" t="inlineStr">
+      <c r="C178" s="28" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="D160" s="41" t="inlineStr">
+      <c r="D178" s="44" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="E160" s="27" t="inlineStr">
+      <c r="E178" s="27" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="F160" s="27" t="inlineStr">
+      <c r="F178" s="27" t="inlineStr">
         <is>
           <t>꿀 등</t>
         </is>
       </c>
     </row>
-    <row r="161" ht="48" customHeight="1">
-      <c r="A161" s="27" t="inlineStr">
+    <row r="179" ht="48" customHeight="1">
+      <c r="A179" s="27" t="inlineStr">
         <is>
           <t>(유기농) 설탕</t>
         </is>
       </c>
-      <c r="B161" s="27" t="inlineStr">
+      <c r="B179" s="27" t="inlineStr">
         <is>
           <t>125g / (~200g)</t>
         </is>
       </c>
-      <c r="C161" s="28" t="inlineStr">
+      <c r="C179" s="28" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
       </c>
-      <c r="D161" s="31" t="inlineStr">
+      <c r="D179" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E161" s="27" t="inlineStr">
+      <c r="E179" s="27" t="inlineStr">
         <is>
           <t>각질제거, 보습. · 필요에 따라 양을 더 넣어서 · 비벼도 됩니다.</t>
         </is>
       </c>
-      <c r="F161" s="27" t="inlineStr"/>
-    </row>
-    <row r="162" ht="32" customHeight="1">
-      <c r="A162" s="27" t="inlineStr">
+      <c r="F179" s="27" t="inlineStr"/>
+    </row>
+    <row r="180" ht="32" customHeight="1">
+      <c r="A180" s="27" t="inlineStr">
         <is>
           <t>오렌지 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B162" s="27" t="inlineStr">
+      <c r="B180" s="27" t="inlineStr">
         <is>
           <t>5ml / (100방울)</t>
         </is>
       </c>
-      <c r="C162" s="28" t="inlineStr">
+      <c r="C180" s="28" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="D162" s="32" t="inlineStr">
+      <c r="D180" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E162" s="27" t="inlineStr">
+      <c r="E180" s="27" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="F162" s="27" t="inlineStr">
+      <c r="F180" s="27" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="34" t="inlineStr">
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 28 · 유화 4 · 계면 14 · 보습 5 · 향 2 · 기타 47</t>
         </is>
       </c>
-      <c r="B163" s="35" t="n"/>
-      <c r="C163" s="35" t="n"/>
-      <c r="D163" s="35" t="n"/>
-      <c r="E163" s="35" t="n"/>
-      <c r="F163" s="35" t="n"/>
-    </row>
-    <row r="164" ht="14" customHeight="1">
-      <c r="A164" s="36" t="inlineStr">
+      <c r="B181" s="35" t="n"/>
+      <c r="C181" s="35" t="n"/>
+      <c r="D181" s="35" t="n"/>
+      <c r="E181" s="35" t="n"/>
+      <c r="F181" s="35" t="n"/>
+    </row>
+    <row r="182" ht="14" customHeight="1">
+      <c r="A182" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B164" s="37" t="n"/>
-      <c r="C164" s="37" t="n"/>
-      <c r="D164" s="37" t="n"/>
-      <c r="E164" s="37" t="n"/>
-      <c r="F164" s="37" t="n"/>
-    </row>
-    <row r="165" ht="336" customHeight="1">
-      <c r="A165" s="38" t="inlineStr">
+      <c r="B182" s="37" t="n"/>
+      <c r="C182" s="37" t="n"/>
+      <c r="D182" s="37" t="n"/>
+      <c r="E182" s="37" t="n"/>
+      <c r="F182" s="37" t="n"/>
+    </row>
+    <row r="183" ht="336" customHeight="1">
+      <c r="A183" s="38" t="inlineStr">
         <is>
           <t>초~정밀 만들기 과정
 1.분량의 유기농 설탕을 준비합니다.
@@ -6403,142 +6603,163 @@
         </is>
       </c>
     </row>
-    <row r="166" ht="256.5" customHeight="1"/>
-    <row r="167" ht="6" customHeight="1"/>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="24" t="inlineStr">
+    <row r="184" ht="14" customHeight="1">
+      <c r="A184" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B184" s="40" t="n"/>
+      <c r="C184" s="40" t="n"/>
+      <c r="D184" s="40" t="n"/>
+      <c r="E184" s="40" t="n"/>
+      <c r="F184" s="40" t="n"/>
+    </row>
+    <row r="185" ht="45" customHeight="1">
+      <c r="A185" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 아보카도오일(24%)로 보습막·발림 설계.
+· 마무리: 보습 5% · 향 2% 로 안정·사용감 보완.
+· 포인트: 유상 대비 유화제가 적음 → 가벼운 질감 지향(분리 주의).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="197.5" customHeight="1"/>
+    <row r="187" ht="6" customHeight="1"/>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="24" t="inlineStr">
         <is>
           <t>카카오 팩&amp;스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B168" s="25" t="n"/>
-      <c r="C168" s="25" t="n"/>
-      <c r="D168" s="25" t="n"/>
-      <c r="E168" s="25" t="n"/>
-      <c r="F168" s="25" t="n"/>
-    </row>
-    <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="26" t="inlineStr">
+      <c r="B188" s="25" t="n"/>
+      <c r="C188" s="25" t="n"/>
+      <c r="D188" s="25" t="n"/>
+      <c r="E188" s="25" t="n"/>
+      <c r="F188" s="25" t="n"/>
+    </row>
+    <row r="189" ht="15" customHeight="1">
+      <c r="A189" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B169" s="26" t="inlineStr">
+      <c r="B189" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C169" s="26" t="inlineStr">
+      <c r="C189" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D169" s="26" t="inlineStr">
+      <c r="D189" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E169" s="26" t="inlineStr">
+      <c r="E189" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F169" s="26" t="inlineStr">
+      <c r="F189" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="64" customHeight="1">
-      <c r="A170" s="39" t="inlineStr">
+    <row r="190" ht="64" customHeight="1">
+      <c r="A190" s="42" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스(멀티)</t>
         </is>
       </c>
-      <c r="B170" s="39" t="inlineStr">
+      <c r="B190" s="42" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C170" s="40" t="inlineStr">
+      <c r="C190" s="43" t="inlineStr">
         <is>
           <t>48%</t>
         </is>
       </c>
-      <c r="D170" s="43" t="inlineStr">
+      <c r="D190" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E170" s="39" t="inlineStr">
+      <c r="E190" s="42" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 · 최적의 베이스</t>
         </is>
       </c>
-      <c r="F170" s="39" t="inlineStr">
+      <c r="F190" s="42" t="inlineStr">
         <is>
           <t>코포아수버터, 망고버터, 코코아버터 등</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="48" customHeight="1">
-      <c r="A171" s="39" t="inlineStr">
+    <row r="191" ht="48" customHeight="1">
+      <c r="A191" s="42" t="inlineStr">
         <is>
           <t>카카오 스크럽 파우더</t>
         </is>
       </c>
-      <c r="B171" s="39" t="inlineStr">
+      <c r="B191" s="42" t="inlineStr">
         <is>
           <t>110g</t>
         </is>
       </c>
-      <c r="C171" s="40" t="inlineStr">
+      <c r="C191" s="43" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="D171" s="32" t="inlineStr">
+      <c r="D191" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E171" s="39" t="inlineStr">
+      <c r="E191" s="42" t="inlineStr">
         <is>
           <t>유기농 설탕+ 카카오분말 · 폴리페놀 풍부, 카카오의 달콤한 향</t>
         </is>
       </c>
-      <c r="F171" s="39" t="inlineStr">
+      <c r="F191" s="42" t="inlineStr">
         <is>
           <t>원하는 분말</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="34" t="inlineStr">
+    <row r="192" ht="14" customHeight="1">
+      <c r="A192" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 48 · 향 52</t>
         </is>
       </c>
-      <c r="B172" s="35" t="n"/>
-      <c r="C172" s="35" t="n"/>
-      <c r="D172" s="35" t="n"/>
-      <c r="E172" s="35" t="n"/>
-      <c r="F172" s="35" t="n"/>
-    </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="36" t="inlineStr">
+      <c r="B192" s="35" t="n"/>
+      <c r="C192" s="35" t="n"/>
+      <c r="D192" s="35" t="n"/>
+      <c r="E192" s="35" t="n"/>
+      <c r="F192" s="35" t="n"/>
+    </row>
+    <row r="193" ht="14" customHeight="1">
+      <c r="A193" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B173" s="37" t="n"/>
-      <c r="C173" s="37" t="n"/>
-      <c r="D173" s="37" t="n"/>
-      <c r="E173" s="37" t="n"/>
-      <c r="F173" s="37" t="n"/>
-    </row>
-    <row r="174" ht="384" customHeight="1">
-      <c r="A174" s="42" t="inlineStr">
+      <c r="B193" s="37" t="n"/>
+      <c r="C193" s="37" t="n"/>
+      <c r="D193" s="37" t="n"/>
+      <c r="E193" s="37" t="n"/>
+      <c r="F193" s="37" t="n"/>
+    </row>
+    <row r="194" ht="384" customHeight="1">
+      <c r="A194" s="45" t="inlineStr">
         <is>
           <t>2008년 흑설탕,
 2009년 카카오 스크럽제 레시피를 안내해드렸습니다.
@@ -6566,40 +6787,40 @@
 항산화작용이 우수한 폴리페놀 함량이 높은 카카오와</t>
         </is>
       </c>
-      <c r="B174" s="23" t="n"/>
-      <c r="C174" s="23" t="n"/>
-      <c r="D174" s="23" t="n"/>
-      <c r="E174" s="23" t="n"/>
-      <c r="F174" s="23" t="n"/>
-    </row>
-    <row r="175" ht="48" customHeight="1">
-      <c r="A175" s="42" t="inlineStr">
+      <c r="B194" s="23" t="n"/>
+      <c r="C194" s="23" t="n"/>
+      <c r="D194" s="23" t="n"/>
+      <c r="E194" s="23" t="n"/>
+      <c r="F194" s="23" t="n"/>
+    </row>
+    <row r="195" ht="48" customHeight="1">
+      <c r="A195" s="45" t="inlineStr">
         <is>
           <t>각종 미네랄과 무기 비타민이 풍부하게 함유된 유기농 설탕이
 결광 피부, 꿀광 피부로
 가꾸어 줍니다.</t>
         </is>
       </c>
-      <c r="B175" s="23" t="n"/>
-      <c r="C175" s="23" t="n"/>
-      <c r="D175" s="23" t="n"/>
-      <c r="E175" s="23" t="n"/>
-      <c r="F175" s="23" t="n"/>
-    </row>
-    <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="36" t="inlineStr">
+      <c r="B195" s="23" t="n"/>
+      <c r="C195" s="23" t="n"/>
+      <c r="D195" s="23" t="n"/>
+      <c r="E195" s="23" t="n"/>
+      <c r="F195" s="23" t="n"/>
+    </row>
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B176" s="37" t="n"/>
-      <c r="C176" s="37" t="n"/>
-      <c r="D176" s="37" t="n"/>
-      <c r="E176" s="37" t="n"/>
-      <c r="F176" s="37" t="n"/>
-    </row>
-    <row r="177" ht="320" customHeight="1">
-      <c r="A177" s="42" t="inlineStr">
+      <c r="B196" s="37" t="n"/>
+      <c r="C196" s="37" t="n"/>
+      <c r="D196" s="37" t="n"/>
+      <c r="E196" s="37" t="n"/>
+      <c r="F196" s="37" t="n"/>
+    </row>
+    <row r="197" ht="320" customHeight="1">
+      <c r="A197" s="45" t="inlineStr">
         <is>
           <t>초간편 만들기 과정
 사용하는 방법
@@ -6623,183 +6844,195 @@
 미온수로 씻어내면 더욱 좋다.</t>
         </is>
       </c>
-      <c r="B177" s="23" t="n"/>
-      <c r="C177" s="23" t="n"/>
-      <c r="D177" s="23" t="n"/>
-      <c r="E177" s="23" t="n"/>
-      <c r="F177" s="23" t="n"/>
-    </row>
-    <row r="178" ht="30.50000000000006" customHeight="1">
-      <c r="A178" s="23" t="n"/>
-      <c r="B178" s="23" t="n"/>
-      <c r="C178" s="23" t="n"/>
-      <c r="D178" s="23" t="n"/>
-      <c r="E178" s="23" t="n"/>
-      <c r="F178" s="23" t="n"/>
-    </row>
-    <row r="179" ht="6" customHeight="1"/>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="24" t="inlineStr">
+      <c r="B197" s="23" t="n"/>
+      <c r="C197" s="23" t="n"/>
+      <c r="D197" s="23" t="n"/>
+      <c r="E197" s="23" t="n"/>
+      <c r="F197" s="23" t="n"/>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B198" s="40" t="n"/>
+      <c r="C198" s="40" t="n"/>
+      <c r="D198" s="40" t="n"/>
+      <c r="E198" s="40" t="n"/>
+      <c r="F198" s="40" t="n"/>
+    </row>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 시어버터 / 스크럽 베이스(멀티)(48%)로 보습막·발림 설계.
+· 마무리: 향 52% 로 안정·사용감 보완.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="6" customHeight="1"/>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="24" t="inlineStr">
         <is>
           <t>일랑일랑 버블바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B180" s="25" t="n"/>
-      <c r="C180" s="25" t="n"/>
-      <c r="D180" s="25" t="n"/>
-      <c r="E180" s="25" t="n"/>
-      <c r="F180" s="25" t="n"/>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="26" t="inlineStr">
+      <c r="B201" s="25" t="n"/>
+      <c r="C201" s="25" t="n"/>
+      <c r="D201" s="25" t="n"/>
+      <c r="E201" s="25" t="n"/>
+      <c r="F201" s="25" t="n"/>
+    </row>
+    <row r="202" ht="15" customHeight="1">
+      <c r="A202" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B181" s="26" t="inlineStr">
+      <c r="B202" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C181" s="26" t="inlineStr">
+      <c r="C202" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D181" s="26" t="inlineStr">
+      <c r="D202" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E181" s="26" t="inlineStr">
+      <c r="E202" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F181" s="26" t="inlineStr">
+      <c r="F202" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="64" customHeight="1">
-      <c r="A182" s="27" t="inlineStr">
+    <row r="203" ht="64" customHeight="1">
+      <c r="A203" s="27" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B182" s="27" t="inlineStr">
+      <c r="B203" s="27" t="inlineStr">
         <is>
           <t>42.85%</t>
         </is>
       </c>
-      <c r="C182" s="28" t="inlineStr"/>
-      <c r="D182" s="29" t="inlineStr">
+      <c r="C203" s="28" t="inlineStr"/>
+      <c r="D203" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E182" s="27" t="inlineStr">
+      <c r="E203" s="27" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F182" s="27" t="inlineStr"/>
-    </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="27" t="inlineStr">
+      <c r="F203" s="27" t="inlineStr"/>
+    </row>
+    <row r="204" ht="32" customHeight="1">
+      <c r="A204" s="27" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B183" s="27" t="inlineStr">
+      <c r="B204" s="27" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C183" s="28" t="inlineStr"/>
-      <c r="D183" s="29" t="inlineStr">
+      <c r="C204" s="28" t="inlineStr"/>
+      <c r="D204" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E183" s="27" t="inlineStr">
+      <c r="E204" s="27" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F183" s="27" t="inlineStr">
+      <c r="F204" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="184" ht="32" customHeight="1">
-      <c r="A184" s="27" t="inlineStr">
+    <row r="205" ht="32" customHeight="1">
+      <c r="A205" s="27" t="inlineStr">
         <is>
           <t>사해소금</t>
         </is>
       </c>
-      <c r="B184" s="27" t="inlineStr">
+      <c r="B205" s="27" t="inlineStr">
         <is>
           <t>21.43%</t>
         </is>
       </c>
-      <c r="C184" s="28" t="inlineStr"/>
-      <c r="D184" s="30" t="inlineStr">
+      <c r="C205" s="28" t="inlineStr"/>
+      <c r="D205" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E184" s="27" t="inlineStr">
+      <c r="E205" s="27" t="inlineStr">
         <is>
           <t>스크럽, 노폐물 · 피지 삼투압으로 제거 도움</t>
         </is>
       </c>
-      <c r="F184" s="27" t="inlineStr"/>
-    </row>
-    <row r="185" ht="96" customHeight="1">
-      <c r="A185" s="27" t="inlineStr">
+      <c r="F205" s="27" t="inlineStr"/>
+    </row>
+    <row r="206" ht="96" customHeight="1">
+      <c r="A206" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B185" s="27" t="inlineStr">
+      <c r="B206" s="27" t="inlineStr">
         <is>
           <t>14.29%</t>
         </is>
       </c>
-      <c r="C185" s="28" t="inlineStr"/>
-      <c r="D185" s="29" t="inlineStr">
+      <c r="C206" s="28" t="inlineStr"/>
+      <c r="D206" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E185" s="27" t="inlineStr">
+      <c r="E206" s="27" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F185" s="27" t="inlineStr">
+      <c r="F206" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="36" t="inlineStr">
+    <row r="207" ht="14" customHeight="1">
+      <c r="A207" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B186" s="37" t="n"/>
-      <c r="C186" s="37" t="n"/>
-      <c r="D186" s="37" t="n"/>
-      <c r="E186" s="37" t="n"/>
-      <c r="F186" s="37" t="n"/>
-    </row>
-    <row r="187" ht="176" customHeight="1">
-      <c r="A187" s="38" t="inlineStr">
+      <c r="B207" s="37" t="n"/>
+      <c r="C207" s="37" t="n"/>
+      <c r="D207" s="37" t="n"/>
+      <c r="E207" s="37" t="n"/>
+      <c r="F207" s="37" t="n"/>
+    </row>
+    <row r="208" ht="176" customHeight="1">
+      <c r="A208" s="38" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 베이킹소다, 구연산, 사해소금, 옥수수전분을 양푼이에 계량하세요.
@@ -6813,121 +7046,121 @@
         </is>
       </c>
     </row>
-    <row r="188" ht="6" customHeight="1"/>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="24" t="inlineStr">
+    <row r="209" ht="6" customHeight="1"/>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="24" t="inlineStr">
         <is>
           <t>살구감초 스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B189" s="25" t="n"/>
-      <c r="C189" s="25" t="n"/>
-      <c r="D189" s="25" t="n"/>
-      <c r="E189" s="25" t="n"/>
-      <c r="F189" s="25" t="n"/>
-    </row>
-    <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="26" t="inlineStr">
+      <c r="B210" s="25" t="n"/>
+      <c r="C210" s="25" t="n"/>
+      <c r="D210" s="25" t="n"/>
+      <c r="E210" s="25" t="n"/>
+      <c r="F210" s="25" t="n"/>
+    </row>
+    <row r="211" ht="15" customHeight="1">
+      <c r="A211" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B190" s="26" t="inlineStr">
+      <c r="B211" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C190" s="26" t="inlineStr">
+      <c r="C211" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D190" s="26" t="inlineStr">
+      <c r="D211" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E190" s="26" t="inlineStr">
+      <c r="E211" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F190" s="26" t="inlineStr">
+      <c r="F211" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="32" customHeight="1">
-      <c r="A191" s="39" t="inlineStr">
+    <row r="212" ht="32" customHeight="1">
+      <c r="A212" s="42" t="inlineStr">
         <is>
           <t>살구분말</t>
         </is>
       </c>
-      <c r="B191" s="39" t="inlineStr">
+      <c r="B212" s="42" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C191" s="40" t="inlineStr"/>
-      <c r="D191" s="31" t="inlineStr">
+      <c r="C212" s="43" t="inlineStr"/>
+      <c r="D212" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E191" s="39" t="inlineStr">
+      <c r="E212" s="42" t="inlineStr">
         <is>
           <t>살구씨 분말, 각질 제거 스크럽제</t>
         </is>
       </c>
-      <c r="F191" s="39" t="inlineStr">
+      <c r="F212" s="42" t="inlineStr">
         <is>
           <t>호두분말, 살구씨오일</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="64" customHeight="1">
-      <c r="A192" s="39" t="inlineStr">
+    <row r="213" ht="64" customHeight="1">
+      <c r="A213" s="42" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B192" s="39" t="inlineStr">
+      <c r="B213" s="42" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="C192" s="40" t="inlineStr"/>
-      <c r="D192" s="46" t="inlineStr">
+      <c r="C213" s="43" t="inlineStr"/>
+      <c r="D213" s="49" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="E192" s="39" t="inlineStr">
+      <c r="E213" s="42" t="inlineStr">
         <is>
           <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
-      <c r="F192" s="39" t="inlineStr">
+      <c r="F213" s="42" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="14" customHeight="1">
-      <c r="A193" s="36" t="inlineStr">
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B193" s="37" t="n"/>
-      <c r="C193" s="37" t="n"/>
-      <c r="D193" s="37" t="n"/>
-      <c r="E193" s="37" t="n"/>
-      <c r="F193" s="37" t="n"/>
-    </row>
-    <row r="194" ht="112" customHeight="1">
-      <c r="A194" s="42" t="inlineStr">
+      <c r="B214" s="37" t="n"/>
+      <c r="C214" s="37" t="n"/>
+      <c r="D214" s="37" t="n"/>
+      <c r="E214" s="37" t="n"/>
+      <c r="F214" s="37" t="n"/>
+    </row>
+    <row r="215" ht="112" customHeight="1">
+      <c r="A215" s="45" t="inlineStr">
         <is>
           <t>각질제거와 영양공급을 한번에!
 *살구분말 - 기름성분이 많습니다. 영양공급에 효과적이고 건성피부에 팩이나 스크럽으로 좋습니다. 겨울철에 바디스크럽으로 추천
@@ -6935,26 +7168,26 @@
 *살구감초스크럽제 사용기간 - 6개월~1년, 단, 물기를 조심하세요^^</t>
         </is>
       </c>
-      <c r="B194" s="23" t="n"/>
-      <c r="C194" s="23" t="n"/>
-      <c r="D194" s="23" t="n"/>
-      <c r="E194" s="23" t="n"/>
-      <c r="F194" s="23" t="n"/>
-    </row>
-    <row r="195" ht="14" customHeight="1">
-      <c r="A195" s="36" t="inlineStr">
+      <c r="B215" s="23" t="n"/>
+      <c r="C215" s="23" t="n"/>
+      <c r="D215" s="23" t="n"/>
+      <c r="E215" s="23" t="n"/>
+      <c r="F215" s="23" t="n"/>
+    </row>
+    <row r="216" ht="14" customHeight="1">
+      <c r="A216" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B195" s="37" t="n"/>
-      <c r="C195" s="37" t="n"/>
-      <c r="D195" s="37" t="n"/>
-      <c r="E195" s="37" t="n"/>
-      <c r="F195" s="37" t="n"/>
-    </row>
-    <row r="196" ht="112" customHeight="1">
-      <c r="A196" s="42" t="inlineStr">
+      <c r="B216" s="37" t="n"/>
+      <c r="C216" s="37" t="n"/>
+      <c r="D216" s="37" t="n"/>
+      <c r="E216" s="37" t="n"/>
+      <c r="F216" s="37" t="n"/>
+    </row>
+    <row r="217" ht="112" customHeight="1">
+      <c r="A217" s="45" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 감초랑 살구를 1:1양으로 계량합니다. (90g:90g)
@@ -6964,243 +7197,243 @@
 * 요건 목욕탕 휴대버전입니다. 손에 물기가 있어도 뒤집어서 톡톡 두드리면 잘 나오죠. 보관이랑 사용면에서 추천해드리는 용기입니다.</t>
         </is>
       </c>
-      <c r="B196" s="23" t="n"/>
-      <c r="C196" s="23" t="n"/>
-      <c r="D196" s="23" t="n"/>
-      <c r="E196" s="23" t="n"/>
-      <c r="F196" s="23" t="n"/>
-    </row>
-    <row r="197" ht="22.99999999999997" customHeight="1">
-      <c r="A197" s="23" t="n"/>
-      <c r="B197" s="23" t="n"/>
-      <c r="C197" s="23" t="n"/>
-      <c r="D197" s="23" t="n"/>
-      <c r="E197" s="23" t="n"/>
-      <c r="F197" s="23" t="n"/>
-    </row>
-    <row r="198" ht="6" customHeight="1"/>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="24" t="inlineStr">
+      <c r="B217" s="23" t="n"/>
+      <c r="C217" s="23" t="n"/>
+      <c r="D217" s="23" t="n"/>
+      <c r="E217" s="23" t="n"/>
+      <c r="F217" s="23" t="n"/>
+    </row>
+    <row r="218" ht="22.99999999999997" customHeight="1">
+      <c r="A218" s="23" t="n"/>
+      <c r="B218" s="23" t="n"/>
+      <c r="C218" s="23" t="n"/>
+      <c r="D218" s="23" t="n"/>
+      <c r="E218" s="23" t="n"/>
+      <c r="F218" s="23" t="n"/>
+    </row>
+    <row r="219" ht="6" customHeight="1"/>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="24" t="inlineStr">
         <is>
           <t>바스붐    ↗ 원본</t>
         </is>
       </c>
-      <c r="B199" s="25" t="n"/>
-      <c r="C199" s="25" t="n"/>
-      <c r="D199" s="25" t="n"/>
-      <c r="E199" s="25" t="n"/>
-      <c r="F199" s="25" t="n"/>
-    </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="26" t="inlineStr">
+      <c r="B220" s="25" t="n"/>
+      <c r="C220" s="25" t="n"/>
+      <c r="D220" s="25" t="n"/>
+      <c r="E220" s="25" t="n"/>
+      <c r="F220" s="25" t="n"/>
+    </row>
+    <row r="221" ht="15" customHeight="1">
+      <c r="A221" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B200" s="26" t="inlineStr">
+      <c r="B221" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C200" s="26" t="inlineStr">
+      <c r="C221" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D200" s="26" t="inlineStr">
+      <c r="D221" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E200" s="26" t="inlineStr">
+      <c r="E221" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F200" s="26" t="inlineStr">
+      <c r="F221" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="64" customHeight="1">
-      <c r="A201" s="27" t="inlineStr">
+    <row r="222" ht="64" customHeight="1">
+      <c r="A222" s="27" t="inlineStr">
         <is>
           <t>소다</t>
         </is>
       </c>
-      <c r="B201" s="27" t="inlineStr">
+      <c r="B222" s="27" t="inlineStr">
         <is>
           <t>54.41%</t>
         </is>
       </c>
-      <c r="C201" s="28" t="inlineStr"/>
-      <c r="D201" s="29" t="inlineStr">
+      <c r="C222" s="28" t="inlineStr"/>
+      <c r="D222" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E201" s="27" t="inlineStr">
+      <c r="E222" s="27" t="inlineStr">
         <is>
           <t>베이킹소다=중조=중탄산나트륨 · 때를 부드럽게 빼내는 연마성, 중화시 발생되는 기포 묶은 때 제거,탈취효과</t>
         </is>
       </c>
-      <c r="F201" s="27" t="inlineStr"/>
-    </row>
-    <row r="202" ht="32" customHeight="1">
-      <c r="A202" s="27" t="inlineStr">
+      <c r="F222" s="27" t="inlineStr"/>
+    </row>
+    <row r="223" ht="32" customHeight="1">
+      <c r="A223" s="27" t="inlineStr">
         <is>
           <t>구연산(식품용)</t>
         </is>
       </c>
-      <c r="B202" s="27" t="inlineStr">
+      <c r="B223" s="27" t="inlineStr">
         <is>
           <t>27.21%</t>
         </is>
       </c>
-      <c r="C202" s="28" t="inlineStr"/>
-      <c r="D202" s="29" t="inlineStr">
+      <c r="C223" s="28" t="inlineStr"/>
+      <c r="D223" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E202" s="27" t="inlineStr">
+      <c r="E223" s="27" t="inlineStr">
         <is>
           <t>구연산: 정제수=1:9 pH 조절 · (주방세제는 pH 10~6 가능)</t>
         </is>
       </c>
-      <c r="F202" s="27" t="inlineStr">
+      <c r="F223" s="27" t="inlineStr">
         <is>
           <t>식초^^</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="96" customHeight="1">
-      <c r="A203" s="27" t="inlineStr">
+    <row r="224" ht="96" customHeight="1">
+      <c r="A224" s="27" t="inlineStr">
         <is>
           <t>옥수수전분</t>
         </is>
       </c>
-      <c r="B203" s="27" t="inlineStr">
+      <c r="B224" s="27" t="inlineStr">
         <is>
           <t>8.71%</t>
         </is>
       </c>
-      <c r="C203" s="28" t="inlineStr"/>
-      <c r="D203" s="29" t="inlineStr">
+      <c r="C224" s="28" t="inlineStr"/>
+      <c r="D224" s="29" t="inlineStr">
         <is>
           <t>점증/pH</t>
         </is>
       </c>
-      <c r="E203" s="27" t="inlineStr">
+      <c r="E224" s="27" t="inlineStr">
         <is>
           <t>수분, 노폐물흡착효과, 가루가 뭉쳐지지 않도록 함. 너무 많이넣으면 물 자체가 뿌옇게 될 수 있다. 모양을 뭉칠때는 베이킹소다대비 1비율로 하고 가루일때 조금 더 많이 넣는다</t>
         </is>
       </c>
-      <c r="F203" s="27" t="inlineStr">
+      <c r="F224" s="27" t="inlineStr">
         <is>
           <t>라벤더, 유칼립튜스 등 · 천연 에센셜오일 · 또는 베이비파우더, 클린코튼 등 프러그런스오일</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="48" customHeight="1">
-      <c r="A204" s="27" t="inlineStr">
+    <row r="225" ht="48" customHeight="1">
+      <c r="A225" s="27" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B204" s="27" t="inlineStr">
+      <c r="B225" s="27" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C204" s="28" t="inlineStr"/>
-      <c r="D204" s="30" t="inlineStr">
+      <c r="C225" s="28" t="inlineStr"/>
+      <c r="D225" s="30" t="inlineStr">
         <is>
           <t>수상</t>
         </is>
       </c>
-      <c r="E204" s="27" t="inlineStr">
+      <c r="E225" s="27" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="F204" s="27" t="inlineStr">
+      <c r="F225" s="27" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="80" customHeight="1">
-      <c r="A205" s="27" t="inlineStr">
+    <row r="226" ht="80" customHeight="1">
+      <c r="A226" s="27" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B205" s="27" t="inlineStr">
+      <c r="B226" s="27" t="inlineStr">
         <is>
           <t>0.97%</t>
         </is>
       </c>
-      <c r="C205" s="28" t="inlineStr"/>
-      <c r="D205" s="43" t="inlineStr">
+      <c r="C226" s="28" t="inlineStr"/>
+      <c r="D226" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E205" s="27" t="inlineStr">
+      <c r="E226" s="27" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="F205" s="27" t="inlineStr">
+      <c r="F226" s="27" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="32" customHeight="1">
-      <c r="A206" s="27" t="inlineStr">
+    <row r="227" ht="32" customHeight="1">
+      <c r="A227" s="27" t="inlineStr">
         <is>
           <t>유노하나</t>
         </is>
       </c>
-      <c r="B206" s="27" t="inlineStr">
+      <c r="B227" s="27" t="inlineStr">
         <is>
           <t>4.35%</t>
         </is>
       </c>
-      <c r="C206" s="28" t="inlineStr"/>
-      <c r="D206" s="31" t="inlineStr">
+      <c r="C227" s="28" t="inlineStr"/>
+      <c r="D227" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E206" s="27" t="inlineStr">
+      <c r="E227" s="27" t="inlineStr">
         <is>
           <t>유노하나(온천 유래 미네랄 분말), 입욕제</t>
         </is>
       </c>
-      <c r="F206" s="27" t="inlineStr">
+      <c r="F227" s="27" t="inlineStr">
         <is>
           <t>엡솜솔트</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="14" customHeight="1">
-      <c r="A207" s="36" t="inlineStr">
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B207" s="37" t="n"/>
-      <c r="C207" s="37" t="n"/>
-      <c r="D207" s="37" t="n"/>
-      <c r="E207" s="37" t="n"/>
-      <c r="F207" s="37" t="n"/>
-    </row>
-    <row r="208" ht="112" customHeight="1">
-      <c r="A208" s="38" t="inlineStr">
+      <c r="B228" s="37" t="n"/>
+      <c r="C228" s="37" t="n"/>
+      <c r="D228" s="37" t="n"/>
+      <c r="E228" s="37" t="n"/>
+      <c r="F228" s="37" t="n"/>
+    </row>
+    <row r="229" ht="112" customHeight="1">
+      <c r="A229" s="38" t="inlineStr">
         <is>
           <t>바스붐 만들기
 1~4. 재료를 준비합니다. 준비한 탄산수소나트륨, 구연산, 옥수수전분을 넣어주세요.
@@ -7210,170 +7443,170 @@
         </is>
       </c>
     </row>
-    <row r="209" ht="6" customHeight="1"/>
-    <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="24" t="inlineStr">
+    <row r="230" ht="6" customHeight="1"/>
+    <row r="231" ht="22" customHeight="1">
+      <c r="A231" s="24" t="inlineStr">
         <is>
           <t>레몬민트바쓰솔트    ↗ 원본</t>
         </is>
       </c>
-      <c r="B210" s="25" t="n"/>
-      <c r="C210" s="25" t="n"/>
-      <c r="D210" s="25" t="n"/>
-      <c r="E210" s="25" t="n"/>
-      <c r="F210" s="25" t="n"/>
-    </row>
-    <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="26" t="inlineStr">
+      <c r="B231" s="25" t="n"/>
+      <c r="C231" s="25" t="n"/>
+      <c r="D231" s="25" t="n"/>
+      <c r="E231" s="25" t="n"/>
+      <c r="F231" s="25" t="n"/>
+    </row>
+    <row r="232" ht="15" customHeight="1">
+      <c r="A232" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B211" s="26" t="inlineStr">
+      <c r="B232" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C211" s="26" t="inlineStr">
+      <c r="C232" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D211" s="26" t="inlineStr">
+      <c r="D232" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E211" s="26" t="inlineStr">
+      <c r="E232" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F211" s="26" t="inlineStr">
+      <c r="F232" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="212" ht="32" customHeight="1">
-      <c r="A212" s="39" t="inlineStr">
+    <row r="233" ht="32" customHeight="1">
+      <c r="A233" s="42" t="inlineStr">
         <is>
           <t>히말라야 핑크소금</t>
         </is>
       </c>
-      <c r="B212" s="39" t="inlineStr">
+      <c r="B233" s="42" t="inlineStr">
         <is>
           <t>98.95%</t>
         </is>
       </c>
-      <c r="C212" s="40" t="inlineStr"/>
-      <c r="D212" s="31" t="inlineStr">
+      <c r="C233" s="43" t="inlineStr"/>
+      <c r="D233" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E212" s="39" t="inlineStr">
+      <c r="E233" s="42" t="inlineStr">
         <is>
           <t>히말라야 핑크소금, 암염 · 미세입자, 미네럴 풍부</t>
         </is>
       </c>
-      <c r="F212" s="39" t="inlineStr"/>
-    </row>
-    <row r="213" ht="112" customHeight="1">
-      <c r="A213" s="39" t="inlineStr">
+      <c r="F233" s="42" t="inlineStr"/>
+    </row>
+    <row r="234" ht="112" customHeight="1">
+      <c r="A234" s="42" t="inlineStr">
         <is>
           <t>레몬 에센셜오일</t>
         </is>
       </c>
-      <c r="B213" s="39" t="inlineStr">
+      <c r="B234" s="42" t="inlineStr">
         <is>
           <t>0.5%</t>
         </is>
       </c>
-      <c r="C213" s="40" t="inlineStr"/>
-      <c r="D213" s="32" t="inlineStr">
+      <c r="C234" s="43" t="inlineStr"/>
+      <c r="D234" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E213" s="39" t="inlineStr">
+      <c r="E234" s="42" t="inlineStr">
         <is>
           <t>레몬껍질오일, 상큼한 향,피곤하면 생기는 헤르페스 도움.</t>
         </is>
       </c>
-      <c r="F213" s="39" t="inlineStr">
+      <c r="F234" s="42" t="inlineStr">
         <is>
           <t>페파민트(향이 강하기 때문에 양을 많이 줄이세요.), 라벤더, 유기농벌꿀플레이버, 유기농딸기플레이버오일 등</t>
         </is>
       </c>
     </row>
-    <row r="214" ht="32" customHeight="1">
-      <c r="A214" s="39" t="inlineStr">
+    <row r="235" ht="32" customHeight="1">
+      <c r="A235" s="42" t="inlineStr">
         <is>
           <t>스피아민트EO</t>
         </is>
       </c>
-      <c r="B214" s="39" t="inlineStr">
+      <c r="B235" s="42" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
       </c>
-      <c r="C214" s="40" t="inlineStr"/>
-      <c r="D214" s="32" t="inlineStr">
+      <c r="C235" s="43" t="inlineStr"/>
+      <c r="D235" s="32" t="inlineStr">
         <is>
           <t>향</t>
         </is>
       </c>
-      <c r="E214" s="39" t="inlineStr">
+      <c r="E235" s="42" t="inlineStr">
         <is>
           <t>시원한 박하향, 스피아민트잎에서 추출</t>
         </is>
       </c>
-      <c r="F214" s="39" t="inlineStr">
+      <c r="F235" s="42" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="14" customHeight="1">
-      <c r="A215" s="36" t="inlineStr">
+    <row r="236" ht="14" customHeight="1">
+      <c r="A236" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B215" s="37" t="n"/>
-      <c r="C215" s="37" t="n"/>
-      <c r="D215" s="37" t="n"/>
-      <c r="E215" s="37" t="n"/>
-      <c r="F215" s="37" t="n"/>
-    </row>
-    <row r="216" ht="80" customHeight="1">
-      <c r="A216" s="42" t="inlineStr">
+      <c r="B236" s="37" t="n"/>
+      <c r="C236" s="37" t="n"/>
+      <c r="D236" s="37" t="n"/>
+      <c r="E236" s="37" t="n"/>
+      <c r="F236" s="37" t="n"/>
+    </row>
+    <row r="237" ht="80" customHeight="1">
+      <c r="A237" s="45" t="inlineStr">
         <is>
           <t>여드름피부를 위한...
 * 만들기하시면서 주의할 점은.. 소금을 볶을 때 환기를 잘 시켜주시구요. 볶은 소금에 에센셜오일을 흡수시킨 후 입욕제를 넣어주셔야 소금에 색이 골고루 입혀집니다. 순서가 바뀌면 입욕제가 소금에 겉돌아서 원하는 색내기가 어렵습니다.</t>
         </is>
       </c>
-      <c r="B216" s="23" t="n"/>
-      <c r="C216" s="23" t="n"/>
-      <c r="D216" s="23" t="n"/>
-      <c r="E216" s="23" t="n"/>
-      <c r="F216" s="23" t="n"/>
-    </row>
-    <row r="217" ht="14" customHeight="1">
-      <c r="A217" s="36" t="inlineStr">
+      <c r="B237" s="23" t="n"/>
+      <c r="C237" s="23" t="n"/>
+      <c r="D237" s="23" t="n"/>
+      <c r="E237" s="23" t="n"/>
+      <c r="F237" s="23" t="n"/>
+    </row>
+    <row r="238" ht="14" customHeight="1">
+      <c r="A238" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B217" s="37" t="n"/>
-      <c r="C217" s="37" t="n"/>
-      <c r="D217" s="37" t="n"/>
-      <c r="E217" s="37" t="n"/>
-      <c r="F217" s="37" t="n"/>
-    </row>
-    <row r="218" ht="128" customHeight="1">
-      <c r="A218" s="42" t="inlineStr">
+      <c r="B238" s="37" t="n"/>
+      <c r="C238" s="37" t="n"/>
+      <c r="D238" s="37" t="n"/>
+      <c r="E238" s="37" t="n"/>
+      <c r="F238" s="37" t="n"/>
+    </row>
+    <row r="239" ht="128" customHeight="1">
+      <c r="A239" s="45" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 크리스탈소금을 약한 불에 5분 볶습니다. (수분을 날려줘서 아로마에센셜오일이 잘 흡수되도록 하고 불순물을 없애줍니다.)
@@ -7384,167 +7617,167 @@
 6. 용기에 색깔별로 반반 넣고 중간에 장미건조를 깔아줍니다. 나머지를 가득 채우면 완성!</t>
         </is>
       </c>
-      <c r="B218" s="23" t="n"/>
-      <c r="C218" s="23" t="n"/>
-      <c r="D218" s="23" t="n"/>
-      <c r="E218" s="23" t="n"/>
-      <c r="F218" s="23" t="n"/>
-    </row>
-    <row r="219" ht="6" customHeight="1"/>
-    <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="24" t="inlineStr">
+      <c r="B239" s="23" t="n"/>
+      <c r="C239" s="23" t="n"/>
+      <c r="D239" s="23" t="n"/>
+      <c r="E239" s="23" t="n"/>
+      <c r="F239" s="23" t="n"/>
+    </row>
+    <row r="240" ht="6" customHeight="1"/>
+    <row r="241" ht="22" customHeight="1">
+      <c r="A241" s="24" t="inlineStr">
         <is>
           <t>커피스크럽    ↗ 원본</t>
         </is>
       </c>
-      <c r="B220" s="25" t="n"/>
-      <c r="C220" s="25" t="n"/>
-      <c r="D220" s="25" t="n"/>
-      <c r="E220" s="25" t="n"/>
-      <c r="F220" s="25" t="n"/>
-    </row>
-    <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="26" t="inlineStr">
+      <c r="B241" s="25" t="n"/>
+      <c r="C241" s="25" t="n"/>
+      <c r="D241" s="25" t="n"/>
+      <c r="E241" s="25" t="n"/>
+      <c r="F241" s="25" t="n"/>
+    </row>
+    <row r="242" ht="15" customHeight="1">
+      <c r="A242" s="26" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B221" s="26" t="inlineStr">
+      <c r="B242" s="26" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C221" s="26" t="inlineStr">
+      <c r="C242" s="26" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D221" s="26" t="inlineStr">
+      <c r="D242" s="26" t="inlineStr">
         <is>
           <t>역할</t>
         </is>
       </c>
-      <c r="E221" s="26" t="inlineStr">
+      <c r="E242" s="26" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="F221" s="26" t="inlineStr">
+      <c r="F242" s="26" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="64" customHeight="1">
-      <c r="A222" s="27" t="inlineStr">
+    <row r="243" ht="64" customHeight="1">
+      <c r="A243" s="27" t="inlineStr">
         <is>
           <t>시어버터 / 스크럽 베이스</t>
         </is>
       </c>
-      <c r="B222" s="27" t="inlineStr">
+      <c r="B243" s="27" t="inlineStr">
         <is>
           <t>100g</t>
         </is>
       </c>
-      <c r="C222" s="28" t="inlineStr">
+      <c r="C243" s="28" t="inlineStr">
         <is>
           <t>37%</t>
         </is>
       </c>
-      <c r="D222" s="43" t="inlineStr">
+      <c r="D243" s="46" t="inlineStr">
         <is>
           <t>유상</t>
         </is>
       </c>
-      <c r="E222" s="27" t="inlineStr">
+      <c r="E243" s="27" t="inlineStr">
         <is>
           <t>6 IN ONE · 피부결 개선, 보습, 맑은 피부 · 윤기, 영양공급, 피부정화 · 스크럽제를 만들기 위한 최적의 베이스</t>
         </is>
       </c>
-      <c r="F222" s="27" t="inlineStr"/>
-    </row>
-    <row r="223" ht="32" customHeight="1">
-      <c r="A223" s="27" t="inlineStr">
+      <c r="F243" s="27" t="inlineStr"/>
+    </row>
+    <row r="244" ht="32" customHeight="1">
+      <c r="A244" s="27" t="inlineStr">
         <is>
           <t>원두 커피 / 곱게 간 것</t>
         </is>
       </c>
-      <c r="B223" s="27" t="inlineStr">
+      <c r="B244" s="27" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C223" s="28" t="inlineStr">
+      <c r="C244" s="28" t="inlineStr">
         <is>
           <t>7%</t>
         </is>
       </c>
-      <c r="D223" s="31" t="inlineStr">
+      <c r="D244" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E223" s="27" t="inlineStr">
+      <c r="E244" s="27" t="inlineStr">
         <is>
           <t>커피에 포함된 폴리페놀 · →피부 활력, 탄력 도움</t>
         </is>
       </c>
-      <c r="F223" s="27" t="inlineStr"/>
-    </row>
-    <row r="224" ht="16" customHeight="1">
-      <c r="A224" s="27" t="inlineStr">
+      <c r="F244" s="27" t="inlineStr"/>
+    </row>
+    <row r="245" ht="16" customHeight="1">
+      <c r="A245" s="27" t="inlineStr">
         <is>
           <t>설탕</t>
         </is>
       </c>
-      <c r="B224" s="27" t="inlineStr">
+      <c r="B245" s="27" t="inlineStr">
         <is>
           <t>150g</t>
         </is>
       </c>
-      <c r="C224" s="28" t="inlineStr">
+      <c r="C245" s="28" t="inlineStr">
         <is>
           <t>56%</t>
         </is>
       </c>
-      <c r="D224" s="31" t="inlineStr">
+      <c r="D245" s="31" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="E224" s="27" t="inlineStr">
+      <c r="E245" s="27" t="inlineStr">
         <is>
           <t>각질제거, 보습</t>
         </is>
       </c>
-      <c r="F224" s="27" t="inlineStr"/>
-    </row>
-    <row r="225" ht="14" customHeight="1">
-      <c r="A225" s="34" t="inlineStr">
+      <c r="F245" s="27" t="inlineStr"/>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="34" t="inlineStr">
         <is>
           <t>▶ phase 합계(%):  유상 37 · 기타 63</t>
         </is>
       </c>
-      <c r="B225" s="35" t="n"/>
-      <c r="C225" s="35" t="n"/>
-      <c r="D225" s="35" t="n"/>
-      <c r="E225" s="35" t="n"/>
-      <c r="F225" s="35" t="n"/>
-    </row>
-    <row r="226" ht="14" customHeight="1">
-      <c r="A226" s="36" t="inlineStr">
+      <c r="B246" s="35" t="n"/>
+      <c r="C246" s="35" t="n"/>
+      <c r="D246" s="35" t="n"/>
+      <c r="E246" s="35" t="n"/>
+      <c r="F246" s="35" t="n"/>
+    </row>
+    <row r="247" ht="14" customHeight="1">
+      <c r="A247" s="36" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B226" s="37" t="n"/>
-      <c r="C226" s="37" t="n"/>
-      <c r="D226" s="37" t="n"/>
-      <c r="E226" s="37" t="n"/>
-      <c r="F226" s="37" t="n"/>
-    </row>
-    <row r="227" ht="384" customHeight="1">
-      <c r="A227" s="38" t="inlineStr">
+      <c r="B247" s="37" t="n"/>
+      <c r="C247" s="37" t="n"/>
+      <c r="D247" s="37" t="n"/>
+      <c r="E247" s="37" t="n"/>
+      <c r="F247" s="37" t="n"/>
+    </row>
+    <row r="248" ht="384" customHeight="1">
+      <c r="A248" s="38" t="inlineStr">
         <is>
           <t>은은한 커피향으로 즐기는
 커피 스크럽
@@ -7573,8 +7806,8 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="112" customHeight="1">
-      <c r="A228" s="38" t="inlineStr">
+    <row r="249" ht="112" customHeight="1">
+      <c r="A249" s="38" t="inlineStr">
         <is>
           <t>1. 얼굴 사용은 신중, 사용 시 눈가, 입가는 피해 팩하듯 사용,
 얼굴에 스크럽할 경우 미세 상처 유발 가능,
@@ -7586,20 +7819,20 @@
         </is>
       </c>
     </row>
-    <row r="229" ht="14" customHeight="1">
-      <c r="A229" s="36" t="inlineStr">
+    <row r="250" ht="14" customHeight="1">
+      <c r="A250" s="36" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B229" s="37" t="n"/>
-      <c r="C229" s="37" t="n"/>
-      <c r="D229" s="37" t="n"/>
-      <c r="E229" s="37" t="n"/>
-      <c r="F229" s="37" t="n"/>
-    </row>
-    <row r="230" ht="112" customHeight="1">
-      <c r="A230" s="38" t="inlineStr">
+      <c r="B250" s="37" t="n"/>
+      <c r="C250" s="37" t="n"/>
+      <c r="D250" s="37" t="n"/>
+      <c r="E250" s="37" t="n"/>
+      <c r="F250" s="37" t="n"/>
+    </row>
+    <row r="251" ht="112" customHeight="1">
+      <c r="A251" s="38" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 비커에 곱게 간 원두 커피를 수저로 2스푼(20g) 계량해 주세요.
@@ -7611,50 +7844,85 @@
         </is>
       </c>
     </row>
-    <row r="231" ht="6" customHeight="1"/>
+    <row r="252" ht="14" customHeight="1">
+      <c r="A252" s="39" t="inlineStr">
+        <is>
+          <t>💡 설계 의도 (역설계 — 왜 이 양·비율인가)</t>
+        </is>
+      </c>
+      <c r="B252" s="40" t="n"/>
+      <c r="C252" s="40" t="n"/>
+      <c r="D252" s="40" t="n"/>
+      <c r="E252" s="40" t="n"/>
+      <c r="F252" s="40" t="n"/>
+    </row>
+    <row r="253" ht="28" customHeight="1">
+      <c r="A253" s="41" t="inlineStr">
+        <is>
+          <t>· 베이스: 유상 중심, 주 오일 시어버터 / 스크럽 베이스(37%)로 보습막·발림 설계.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="119">
-    <mergeCell ref="A174:F174"/>
+  <mergeCells count="143">
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A183:F183"/>
+    <mergeCell ref="A84:F84"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="A66:F66"/>
-    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A118:F118"/>
     <mergeCell ref="A133:F133"/>
-    <mergeCell ref="A189:F189"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A198:F198"/>
+    <mergeCell ref="A238:F238"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A239:F239"/>
     <mergeCell ref="A95:F95"/>
-    <mergeCell ref="A175:F175"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A150:F150"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A72:F72"/>
     <mergeCell ref="A134:F134"/>
+    <mergeCell ref="A81:F81"/>
     <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A152:F152"/>
     <mergeCell ref="A121:F121"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="A186:F186"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A249:F249"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A40:F40"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A73:F73"/>
     <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A226:F226"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="A82:F82"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A241:F241"/>
+    <mergeCell ref="A250:F250"/>
     <mergeCell ref="A228:F228"/>
     <mergeCell ref="A124:F124"/>
+    <mergeCell ref="A237:F237"/>
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="A172:F172"/>
+    <mergeCell ref="A252:F252"/>
     <mergeCell ref="A99:F99"/>
     <mergeCell ref="A108:F108"/>
+    <mergeCell ref="A236:F236"/>
     <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A214:F214"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A163:F163"/>
     <mergeCell ref="A195:F195"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A85:F85"/>
     <mergeCell ref="A151:F151"/>
+    <mergeCell ref="A188:F188"/>
+    <mergeCell ref="A126:F126"/>
+    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="A35:F35"/>
@@ -7664,94 +7932,102 @@
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="A199:F199"/>
     <mergeCell ref="A112:F112"/>
-    <mergeCell ref="A230:F230"/>
     <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A127:F127"/>
-    <mergeCell ref="A176:F176"/>
-    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="A167:F167"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A182:F182"/>
     <mergeCell ref="A216:F216"/>
     <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A225:F225"/>
+    <mergeCell ref="A169:F169"/>
     <mergeCell ref="A79:F79"/>
-    <mergeCell ref="A88:F88"/>
-    <mergeCell ref="A218:F218"/>
-    <mergeCell ref="A227:F227"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="A137:F137"/>
-    <mergeCell ref="A177:F177"/>
-    <mergeCell ref="A90:F90"/>
     <mergeCell ref="A208:F208"/>
     <mergeCell ref="A217:F217"/>
     <mergeCell ref="A164:F164"/>
     <mergeCell ref="A136:F136"/>
     <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A105:F105"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A139:F139"/>
-    <mergeCell ref="A154:F154"/>
     <mergeCell ref="A210:F210"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A251:F251"/>
     <mergeCell ref="A76:F76"/>
+    <mergeCell ref="A181:F181"/>
     <mergeCell ref="A100:F100"/>
+    <mergeCell ref="A253:F253"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="A109:F109"/>
     <mergeCell ref="A165:F165"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="A180:F180"/>
+    <mergeCell ref="A231:F231"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="A102:F102"/>
-    <mergeCell ref="A173:F173"/>
     <mergeCell ref="A229:F229"/>
-    <mergeCell ref="A111:F111"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A166:F166"/>
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A207:F207"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A94:F94"/>
     <mergeCell ref="A168:F168"/>
     <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="A246:F246"/>
     <mergeCell ref="A193:F193"/>
+    <mergeCell ref="A80:F80"/>
     <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A89:F89"/>
     <mergeCell ref="A120:F120"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A192:F192"/>
+    <mergeCell ref="A248:F248"/>
     <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A247:F247"/>
+    <mergeCell ref="A185:F185"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A194:F194"/>
+    <mergeCell ref="A106:F106"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A184:F184"/>
     <mergeCell ref="A147:F147"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A155:F155"/>
     <mergeCell ref="A220:F220"/>
-    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A201:F201"/>
     <mergeCell ref="A148:F148"/>
     <mergeCell ref="A123:F123"/>
+    <mergeCell ref="A138:F138"/>
     <mergeCell ref="A132:F132"/>
+    <mergeCell ref="A197:F197"/>
     <mergeCell ref="A110:F110"/>
-    <mergeCell ref="A187:F187"/>
+    <mergeCell ref="A146:F146"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="A69:F69"/>
     <mergeCell ref="A196:F196"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A154" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A168" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A180" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A155" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A172" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A201" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A210" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A220" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId18"/>
